--- a/Result/checksun_type/營養食品.xlsx
+++ b/Result/checksun_type/營養食品.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>74.24000000000001</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>74.49</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>75.24</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>74.48999999999999</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>75.23999999999999</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>308.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>551.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>551.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>863.5</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>1290.88</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>1290.88</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-131.622686315784</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>308</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>308.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>73.9</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>74.43</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>75.26</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>74.43000000000001</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>75.26000000000001</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>150.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>1114.2</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>1114.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>1031.9</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>1331.94</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>1331.94</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-101.2782191199866</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>150</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>150.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>73.94</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>74.34</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>75.31</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>74.34</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>75.31</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>697.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>1193.8</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>1193.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>1078.5</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>1371.9</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>1371.9</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-37.38332958599062</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>697</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>697.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>74.52000000000001</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>74.34</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>75.39</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>74.34</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>75.39</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>946.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>1199.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>1199.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>1252.3</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>1371.2</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>1371.2</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-3.37693990935395</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>946</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>946.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>75.02000000000001</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>74.29</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>75.42</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>74.29000000000001</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>75.42</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>658.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>1133.6</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>1133.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>1238.0</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>1373.1</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>1373.1</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>18.64565033974668</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>658</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>658.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>75.78</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>74.29</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>75.46</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>74.29000000000001</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>75.45999999999999</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>3120.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>1175.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>1175.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>1201.2</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>1414.94</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>1414.94</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>80.29772032632854</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>3120</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>3120.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>76.8</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>74.34</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>75.52</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>74.34</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>75.52</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>548.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>949.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>949.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>1005.3</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>1370.62</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>1370.62</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-98.28138399020929</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>548</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>548.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>76.96000000000001</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>74.28</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>75.52</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>74.28</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>75.52</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>724.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>963.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>963.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>1017.5</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>1387.96</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>1387.96</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-74.31291215704164</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>724</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>724.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>76.70000000000002</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>74.09</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>75.51</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>74.09</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>75.51000000000001</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>618.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>1305.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>1305.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>1003.5</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>1397.72</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>1397.72</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-56.27534838976499</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>618</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>618.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>75.84</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>73.95</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>75.46</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>73.95</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>75.45999999999999</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>866.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>1342.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>1342.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>1066.1</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>1425.92</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>1425.92</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-17.14042342259222</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>866</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>866.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>74.86</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>73.74</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>75.43</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>73.73999999999999</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>75.43000000000001</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>1992.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>1227.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>1227.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>1038.1</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>1421.24</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>1421.24</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>12.80734165274703</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>1992</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>1992.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>31.77999999999999</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>31.79</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>31.97</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>31.97</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>24752845.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>6361239.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>6361239.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>5173323.2</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>3811369.74</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>3811369.74</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>1376921.324417498</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>24752845</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>24752845.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>31.72</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>31.79</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>31.97</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>31.79</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>31.97</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>661190.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>1925877.6</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>1925877.6</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>3004447.9</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>3413913.34</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>3413913.34</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-340719.2026818991</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>661190</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>661190.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>31.69</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>31.8</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>31.98</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>31.98</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>2415396.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>2458628.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>2458628</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>3310550.9</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>3561770.12</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>3561770.12</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-201074.0912995418</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>2415396</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>2415396.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>31.66</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>31.8</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>31.99</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>31.99</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>2208385.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>2853136.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>2853136.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>3195480.8</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>3578602.06</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>3578602.06</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-182350.5003497619</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>2208385</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>2208385.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>31.65</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>31.82</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>32.0</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>31.82</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>32</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>1768383.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>3478744.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>3478744.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>3297831.0</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>3557480.34</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>3557480.34</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-126910.2454090137</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>1768383</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>1768383.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>31.69</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>31.83</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>32.01</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>31.83</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>32.01</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>2576034.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>3985406.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>3985406.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>3305598.3</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>3562799.06</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>3562799.06</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>3965.698985234834</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>2576034</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>2576034.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>31.74</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>31.85</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>32.03</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>31.85</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>32.03</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>3324942.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>4083018.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>4083018.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>3290697.3</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>3542785.62</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>3542785.62</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>104255.6660132594</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>3324942</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>3324942.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>31.78</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>31.87</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>32.04</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>31.87</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>32.04</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>4387937.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>4162473.8</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>4162473.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>3284508.8</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>3530449.16</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>3530449.16</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>163563.487981393</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>4387937</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>4387937.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>31.78</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>31.88</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>32.05</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>31.88</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>32.05</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>5336427.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>3537825.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>3537825.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>3443786.9</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>3484907.42</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>3484907.42</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>128555.0733651058</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>5336427</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>5336427.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>31.81</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>31.89</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>32.06</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>31.89</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>32.06</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>4301693.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>3116917.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>3116917.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>3381785.1</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>3490553.5</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>3490553.5</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-27672.12870691577</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>4301693</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>4301693.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>31.8</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>31.9</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>32.06</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>32.06</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>3064092.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>2625790.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>2625790</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>3337253.8</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>3465493.34</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>3465493.34</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-139001.1984988428</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>3064092</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>3064092.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>30.59</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>30.82</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>30.97</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>30.82</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>30.97</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>9252334.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>11806791.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>11806791</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>13824086.6</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>22091752.82</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>22091752.82</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-1614943.410264194</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>9252334</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>9252334.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>30.48</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>30.84</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>30.96</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>30.84</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>30.96</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>10802885.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>12529091.8</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>12529091.8</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>14102580.3</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>22250476.5</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>22250476.5</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-1430941.310826903</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>10802885</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>10802885.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>30.41</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>30.88</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>30.96</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>30.88</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>30.96</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>17732638.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>14179864.0</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>14179864</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>14548151.5</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>22337908.28</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>22337908.28</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-1283106.586244099</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>17732638</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>17732638.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>30.35</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>30.91</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>30.95</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>30.91</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>30.95</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>11848782.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>14724337.4</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>14724337.4</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>15055398.0</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>22289314.84</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>22289314.84</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-1768562.423045658</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>11848782</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>11848782.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>30.37</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>30.97</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>30.95</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>30.97</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>30.95</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>9397316.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>15029151.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>15029151</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>15624829.5</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>22274988.78</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>22274988.78</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-1768494.674796255</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>9397316</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>9397316.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>30.49</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>31.05</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>30.95</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>31.05</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>30.95</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>12863838.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>15841382.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>15841382.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>15797030.2</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>22302749.42</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>22302749.42</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-1442580.296054387</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>12863838</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>12863838.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>30.61</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>31.15</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>30.96</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>31.15</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>30.96</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>19056746.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>15676068.8</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>15676068.8</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>15559369.6</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>22247744.34</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>22247744.34</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-1296880.672992628</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>19056746</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>19056746.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>30.69</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>31.26</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>30.95</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>30.95</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>20455005.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>14916439.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>14916439</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>15405005.6</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>21988008.62</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>21988008.62</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-1705947.044583237</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>20455005</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>20455005.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>30.75</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>31.38</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>30.95</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>31.38</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>30.95</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>13372850.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>15386458.6</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>15386458.6</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>15274354.6</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>21722442.68</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>21722442.68</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-2379214.359548993</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>13372850</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>13372850.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>30.91</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>31.54</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>30.94</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>31.54</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>30.94</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>13458472.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>16220508.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>16220508</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>15742137.4</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>21724828.4</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>21724828.4</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-2497250.546659039</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>13458472</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>13458472.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>31.03</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>31.69</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>30.92</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>30.92</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>12037271.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>15752678.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>15752678.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>15856402.0</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>21843026.62</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>21843026.62</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-2585859.93729271</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>12037271</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>12037271.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>

--- a/Result/checksun_type/營養食品.xlsx
+++ b/Result/checksun_type/營養食品.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,51 +1029,51 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>98.33</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>1.91</v>
+        <v>1.51</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.15</v>
+        <v>0.42</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>75.35999999999999</t>
+          <t>75.66</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>75.23999999999999</v>
+        <v>75.34</v>
       </c>
       <c r="AN2" t="n">
         <v>74.95</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>75.33</t>
+          <t>75.35</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>437.85</t>
+          <t>241.53</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-97.85</t>
+          <t>-94.56</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>3929.535313001606</t>
+          <t>3923.423076923077</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>838.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>648.2</v>
+        <v>588</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>655.1</t>
+          <t>593.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1206.04</v>
+        <v>1176.82</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-68.62625546935479</t>
+          <t>-72.28779453591946</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-45.33519807851189</t>
+          <t>-92.42625940202515</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>838.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1295,7 +1295,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【b2】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.87</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -1441,261 +1441,261 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>0.27</v>
+        <v>1.91</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
+          <t>75.35999999999999</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>75.23999999999999</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>74.95</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>75.33</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>437.85</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-97.85</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>3923.423076923077</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>838.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>648.2</v>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>655.1</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1206.04</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-68.62625546935479</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-45.33519807851189</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>838.0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>綠茵</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>綠茵</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>食品工業</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>52.61369974141865</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>32.46296024644272</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>6.052320446915804</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>4.69</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>7.61</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>14.36</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>48.81%</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>17.38%</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>29.6</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>2074</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>保健食品配方65.97%、保健食品原料33.59%、其他0.43% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>綠茵-食品工業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>食品工業平上櫃</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
           <t>75.0</t>
         </is>
       </c>
-      <c r="AM3" t="n">
-        <v>75.06</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>74.95999999999999</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>75.31</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>1328.07</t>
-        </is>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-100.20</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>3929.535313001606</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>825.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="n">
-        <v>911.4</v>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>665.9</t>
-        </is>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1235.98</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-72.86099317678077</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>-57.9788533992604</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>825.0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>75.2</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>2025/12/04</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>綠茵</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>綠茵</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>食品工業</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>52.61369974141865</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>32.46296024644272</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>6.052320446915804</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>4.69</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>7.61</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>14.36</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>48.81%</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>17.38%</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>29.48</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>2074</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>保健食品配方65.97%、保健食品原料33.59%、其他0.43% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>綠茵-食品工業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>食品工業平上櫃</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>74.2</t>
-        </is>
-      </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1715,7 +1715,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【b2】</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>6846</t>
@@ -1723,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1738,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1748,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>36.87</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1823,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1833,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1859,61 +1863,61 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.48</v>
+        <v>0.27</v>
       </c>
       <c r="AI4" t="n">
-        <v>-0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>74.85999999999999</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>74.94</v>
+        <v>75.06</v>
       </c>
       <c r="AN4" t="n">
-        <v>75</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>75.32</t>
+          <t>75.31</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>142.67</t>
+          <t>1328.07</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.02</v>
+        <v>-0</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1922,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-100.88</t>
+          <t>-100.20</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1932,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>3929.535313001606</t>
+          <t>3923.423076923077</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>976.0</t>
+          <t>825.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>746.6</v>
+        <v>911.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>649.2</t>
+          <t>665.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1258.5</v>
+        <v>1235.98</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>245</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-75.56683677269356</t>
+          <t>-72.86099317678077</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-72.57768766464164</t>
+          <t>-57.9788533992604</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>976.0</t>
+          <t>825.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1988,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2033,17 +2037,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2073,7 +2077,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2098,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2135,7 +2139,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2145,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2160,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2170,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-29.02</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2245,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2255,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2281,58 +2285,58 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.19</v>
+        <v>-0.48</v>
       </c>
       <c r="AI5" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>-0.42</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>74.85999999999999</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>74.94</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>75.32</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>142.67</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
         <v>0.01</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>74.85999999999999</t>
-        </is>
-      </c>
-      <c r="AM5" t="n">
-        <v>74.84999999999999</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>75.06</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>75.32</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>251.70</t>
-        </is>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0.03</v>
       </c>
       <c r="AR5" t="n">
         <v>-0.02</v>
@@ -2344,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-101.19</t>
+          <t>-100.88</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2354,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>3929.535313001606</t>
+          <t>3923.423076923077</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>976.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>613</v>
+        <v>746.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>863.6</t>
+          <t>649.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1276.7</v>
+        <v>1258.5</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-250</t>
+          <t>97</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-76.110318428703</t>
+          <t>-75.56683677269356</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-107.0196763414492</t>
+          <t>-72.57768766464164</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>976.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2410,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2455,17 +2459,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2495,7 +2499,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2520,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>74.3</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>76.1</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>74.3</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>74.5</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>74.5</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>75.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2557,7 +2561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2567,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2582,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2592,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-33.24</t>
+          <t>-29.02</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2667,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2677,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2703,45 +2707,45 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.67</v>
+        <v>0.19</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.85999999999999</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>74.75</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="AN6" t="n">
-        <v>75.11</v>
+        <v>75.06</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2750,14 +2754,14 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>133.40</t>
+          <t>251.70</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2766,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-101.95</t>
+          <t>-101.19</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2776,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>3929.535313001606</t>
+          <t>3923.423076923077</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>378.0</t>
+          <t>224.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>598.2</v>
+        <v>613</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>896.0</t>
+          <t>863.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>1293.44</v>
+        <v>1276.7</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-297</t>
+          <t>-250</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-70.49043517184005</t>
+          <t>-76.110318428703</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-71.82895743897961</t>
+          <t>-107.0196763414492</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>378.0</t>
+          <t>224.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2832,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2877,17 +2881,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2917,7 +2921,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2942,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2979,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2989,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3004,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3014,17 +3018,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-28.86</t>
+          <t>-33.24</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3089,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3099,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.82</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3125,7 +3129,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3135,35 +3139,35 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>62.59</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.31</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>74.64</v>
+        <v>74.75</v>
       </c>
       <c r="AN7" t="n">
-        <v>75.15000000000001</v>
+        <v>75.11</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3172,14 +3176,14 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>133.40</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3188,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-102.60</t>
+          <t>-101.95</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3198,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>3929.535313001606</t>
+          <t>3923.423076923077</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2154.0</t>
+          <t>378.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>662</v>
+        <v>598.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>930.6</t>
+          <t>896.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1312.14</v>
+        <v>1293.44</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-268</t>
+          <t>-297</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-70.24706748690558</t>
+          <t>-70.49043517184005</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-35.49118195548817</t>
+          <t>-71.82895743897961</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2154.0</t>
+          <t>378.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3254,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3299,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3309,7 +3313,7 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3339,7 +3343,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3364,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3411,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3426,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3436,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-45.89</t>
+          <t>-28.86</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3511,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3521,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.82</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3547,58 +3551,58 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>42.18</t>
+          <t>62.59</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.19</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.25</v>
+        <v>-0.31</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>74.35999999999999</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>74.54000000000001</v>
+        <v>74.64</v>
       </c>
       <c r="AN8" t="n">
-        <v>75.19</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>75.31</t>
+          <t>75.32</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-92.58</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-0.09</v>
+        <v>-0.04</v>
       </c>
       <c r="AR8" t="n">
         <v>-0.04</v>
@@ -3610,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-102.59</t>
+          <t>-102.60</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3620,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>3929.535313001606</t>
+          <t>3923.423076923077</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2154.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>420.4</v>
+        <v>662</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>777.0</t>
+          <t>930.6</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1270.7</v>
+        <v>1312.14</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-356</t>
+          <t>-268</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-76.56631940170874</t>
+          <t>-70.24706748690558</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-172.5982461949473</t>
+          <t>-35.49118195548817</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2154.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3676,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3721,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3731,7 +3735,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3761,7 +3765,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3786,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3833,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3863,12 +3867,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-36.10</t>
+          <t>-45.89</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3943,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3969,61 +3973,61 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>42.18</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.35</v>
+        <v>0.19</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.34</v>
+        <v>-0.25</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>74.24000000000001</t>
+          <t>74.35999999999999</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>74.48999999999999</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="AN9" t="n">
-        <v>75.23999999999999</v>
+        <v>75.19</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.31</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-149.08</t>
+          <t>-92.58</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4032,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-101.99</t>
+          <t>-102.59</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4042,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>3929.535313001606</t>
+          <t>3923.423076923077</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>308.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>551.8</v>
+        <v>420.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>863.5</t>
+          <t>777.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1290.88</v>
+        <v>1270.7</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-311</t>
+          <t>-356</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-59.10596907566538</t>
+          <t>-76.56631940170874</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-131.6226863157835</t>
+          <t>-172.5982461949473</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>308.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4143,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4183,7 +4187,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4208,17 +4212,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4255,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4270,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4280,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>-36.10</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4355,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4365,12 +4369,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -4391,61 +4395,61 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>38.78</t>
+          <t>37.78</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>1.08</v>
+        <v>0.35</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.71</v>
+        <v>-0.34</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>74.24000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>74.43000000000001</v>
+        <v>74.48999999999999</v>
       </c>
       <c r="AN10" t="n">
-        <v>75.26000000000001</v>
+        <v>75.23999999999999</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>75.29</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-288.21</t>
+          <t>-149.08</t>
         </is>
       </c>
       <c r="AQ10" t="n">
         <v>-0.08</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4454,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-101.25</t>
+          <t>-101.99</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4464,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>3929.535313001606</t>
+          <t>3923.423076923077</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>308.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>1114.2</v>
+        <v>551.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>1031.9</t>
+          <t>863.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1331.94</v>
+        <v>1290.88</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>-311</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-45.92111139564389</t>
+          <t>-59.10596907566538</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-101.278219119986</t>
+          <t>-131.6226863157835</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>308.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4520,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4575,7 +4579,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4605,7 +4609,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4630,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4677,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4692,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4702,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4777,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-6.27</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4787,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4813,61 +4817,61 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>38.78</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>-0.87</v>
+        <v>1.08</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.53</v>
+        <v>-0.71</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>73.94</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>74.34</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="AN11" t="n">
-        <v>75.31</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>75.28</t>
+          <t>75.29</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-1568.99</t>
+          <t>-288.21</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="AR11" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4876,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-100.35</t>
+          <t>-101.25</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4886,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>3929.535313001606</t>
+          <t>3923.423076923077</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>697.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>1193.8</v>
+        <v>1114.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>1078.5</t>
+          <t>1031.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1371.9</v>
+        <v>1331.94</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>82</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-35.85618271849077</t>
+          <t>-45.92111139564389</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-37.38332958598994</t>
+          <t>-101.278219119986</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>697.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4942,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4987,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -4997,7 +5001,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5027,7 +5031,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5052,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5089,7 +5093,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5099,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>13.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5114,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5124,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>10.69</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5199,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-6.27</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5209,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5235,61 +5239,61 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>20.26</t>
+          <t>23.53</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>0.38</v>
+        <v>-0.87</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.25</v>
+        <v>-0.53</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-1.29</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>74.52000000000001</t>
+          <t>73.94</t>
         </is>
       </c>
       <c r="AM12" t="n">
         <v>74.34</v>
       </c>
       <c r="AN12" t="n">
-        <v>75.39</v>
+        <v>75.31</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>75.29</t>
+          <t>75.28</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>-1568.99</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5298,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-98.98</t>
+          <t>-100.35</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5308,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>3929.535313001606</t>
+          <t>3923.423076923077</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>946.0</t>
+          <t>697.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>1199.2</v>
+        <v>1193.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>1252.3</t>
+          <t>1078.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1371.2</v>
+        <v>1371.9</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-53</t>
+          <t>115</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-35.57851965167274</t>
+          <t>-35.85618271849077</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-3.376939909353268</t>
+          <t>-37.38332958598994</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>946.0</t>
+          <t>697.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5364,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5409,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5419,7 +5423,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5449,7 +5453,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.48</t>
+          <t>29.6</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5474,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5509,7 +5513,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>1737</t>
@@ -5517,42 +5525,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>38.178</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>31.6</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>62.429</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>31.65</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-55.87</t>
+          <t>-52.37</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5617,7 +5625,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5627,17 +5635,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5648,12 +5656,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5667,40 +5675,40 @@
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>-0.19</v>
+        <v>-0.32</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>31.71</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>31.73</v>
+        <v>31.72</v>
       </c>
       <c r="AN13" t="n">
-        <v>31.91</v>
+        <v>31.9</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>32.09</t>
+          <t>32.07</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AQ13" t="n">
@@ -5726,43 +5734,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>17256928.99716714</t>
+          <t>17235081.0360679</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1974440.0</t>
+          <t>1206947.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>1776964.4</v>
+        <v>1859988.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>4026265.2</t>
+          <t>3905420.3</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>3507431</v>
+        <v>3496627.64</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-2249300</t>
+          <t>-2045431</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-19655.81204074608</t>
+          <t>-88135.42649021233</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-389898.0494343466</t>
+          <t>-464773.3059622766</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>1974440.0</t>
+          <t>1206947.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5782,7 +5790,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5827,7 +5835,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5852,7 +5860,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5867,12 +5875,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5892,14 +5900,14 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>31.6</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
           <t>31.65</t>
         </is>
       </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>31.7</t>
-        </is>
-      </c>
       <c r="CF13" t="inlineStr">
         <is>
           <t>31.6</t>
@@ -5907,7 +5915,7 @@
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -5927,7 +5935,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>1737</t>
@@ -5940,7 +5952,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>47.057</t>
+          <t>62.429</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5960,17 +5972,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-59.15</t>
+          <t>-55.87</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6045,12 +6057,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -6066,12 +6078,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6081,44 +6093,44 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>-0.22</v>
+        <v>-0.19</v>
       </c>
       <c r="AI14" t="n">
         <v>-0.06</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
+          <t>-0.56</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
           <t>-0.57</t>
         </is>
       </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>-0.58</t>
-        </is>
-      </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>31.72</t>
+          <t>31.71</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>31.74</v>
+        <v>31.73</v>
       </c>
       <c r="AN14" t="n">
-        <v>31.92</v>
+        <v>31.91</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>32.11</t>
+          <t>32.09</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AQ14" t="n">
@@ -6134,7 +6146,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-117.80</t>
+          <t>-117.46</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6144,43 +6156,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>17256928.99716714</t>
+          <t>17235081.0360679</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>1489349.0</t>
+          <t>1974440.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>1654352.2</v>
+        <v>1776964.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>4049659.7</t>
+          <t>4026265.2</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>3553193.6</v>
+        <v>3507431</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-2395307</t>
+          <t>-2249300</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>47660.95839445402</t>
+          <t>-19655.81204074608</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-351239.8597717918</t>
+          <t>-389898.0494343466</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>1489349.0</t>
+          <t>1974440.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6245,7 +6257,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6270,7 +6282,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6285,12 +6297,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6310,7 +6322,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -6345,7 +6357,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>1737</t>
@@ -6353,12 +6369,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.184</t>
+          <t>47.057</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6378,17 +6394,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-56.01</t>
+          <t>-59.15</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6463,17 +6479,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6484,12 +6500,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6499,51 +6515,51 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH15" t="n">
         <v>-0.22</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
+          <t>-0.57</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
           <t>-0.58</t>
         </is>
       </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>-0.59</t>
-        </is>
-      </c>
       <c r="AL15" t="inlineStr">
         <is>
           <t>31.72</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>31.75</v>
+        <v>31.74</v>
       </c>
       <c r="AN15" t="n">
-        <v>31.93</v>
+        <v>31.92</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>32.12</t>
+          <t>32.11</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AQ15" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="AR15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
@@ -6552,7 +6568,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-118.40</t>
+          <t>-117.80</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6562,43 +6578,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>17256928.99716714</t>
+          <t>17235081.0360679</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>1372173.0</t>
+          <t>1489349.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>1793886.4</v>
+        <v>1654352.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>4077563.1</t>
+          <t>4049659.7</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>3603986.82</v>
+        <v>3553193.6</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-2283676</t>
+          <t>-2395307</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>120188.379879226</t>
+          <t>47660.95839445402</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-231495.5581191494</t>
+          <t>-351239.8597717918</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>1372173.0</t>
+          <t>1489349.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6663,7 +6679,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6688,7 +6704,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6703,12 +6719,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6728,17 +6744,17 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6765,7 +6781,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6775,12 +6791,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>102.584</t>
+          <t>43.184</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6790,7 +6806,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6800,7 +6816,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6810,7 +6826,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>54.12</t>
+          <t>-56.01</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6875,7 +6891,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -6885,17 +6901,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -6906,29 +6922,29 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>0.6</v>
+        <v>-0.22</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
@@ -6937,28 +6953,28 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>31.72</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>31.76</v>
+        <v>31.75</v>
       </c>
       <c r="AN16" t="n">
-        <v>31.94</v>
+        <v>31.93</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>32.14</t>
+          <t>32.12</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AQ16" t="n">
@@ -6974,7 +6990,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-119.41</t>
+          <t>-118.40</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -6984,43 +7000,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>17256928.99716714</t>
+          <t>17235081.0360679</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>3257034.0</t>
+          <t>1372173.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>6470020.8</v>
+        <v>1793886.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>4197949.2</t>
+          <t>4077563.1</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>3664581.38</v>
+        <v>3603986.82</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>2272071</t>
+          <t>-2283676</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>184130.9140607488</t>
+          <t>120188.379879226</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-39610.00011111982</t>
+          <t>-231495.5581191494</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>3257034.0</t>
+          <t>1372173.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7040,7 +7056,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7085,17 +7101,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7110,7 +7126,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7125,12 +7141,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7150,22 +7166,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7185,7 +7201,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>1737</t>
@@ -7193,12 +7213,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>25.016</t>
+          <t>102.584</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7208,7 +7228,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7218,17 +7238,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
+          <t>-1.11</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>41.53</t>
+          <t>54.12</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7293,7 +7313,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7303,17 +7323,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7324,67 +7344,67 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>-0.22</v>
+        <v>0.6</v>
       </c>
       <c r="AI17" t="n">
-        <v>-0.09</v>
+        <v>0.02</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>31.72</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>31.75</v>
+        <v>31.76</v>
       </c>
       <c r="AN17" t="n">
         <v>31.94</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>32.14</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="AQ17" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR17" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AR17" t="n">
-        <v>-0.08</v>
-      </c>
       <c r="AS17" t="inlineStr">
         <is>
           <t>0.36</t>
@@ -7392,7 +7412,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-121.06</t>
+          <t>-119.41</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7402,43 +7422,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>17256928.99716714</t>
+          <t>17235081.0360679</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>791826.0</t>
+          <t>3257034.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>5950852</v>
+        <v>6470020.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>4204740.0</t>
+          <t>4197949.2</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>3699795.4</v>
+        <v>3664581.38</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>1746112</t>
+          <t>2272071</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>224811.0802738158</t>
+          <t>184130.9140607488</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>33977.47561860597</t>
+          <t>-39610.00011111982</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>791826.0</t>
+          <t>3257034.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7458,7 +7478,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7503,17 +7523,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7528,7 +7548,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7543,12 +7563,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7573,7 +7593,7 @@
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
@@ -7583,7 +7603,7 @@
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7605,7 +7625,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7615,12 +7635,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>43.045</t>
+          <t>25.016</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7630,7 +7650,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7650,7 +7670,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>37.49</t>
+          <t>41.53</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7715,7 +7735,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7725,17 +7745,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7746,59 +7766,59 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH18" t="n">
         <v>-0.22</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>31.77</t>
+          <t>31.72</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>31.76</v>
+        <v>31.75</v>
       </c>
       <c r="AN18" t="n">
-        <v>31.95</v>
+        <v>31.94</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>32.17</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="AQ18" t="n">
@@ -7814,7 +7834,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-121.57</t>
+          <t>-121.06</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7824,43 +7844,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>17256928.99716714</t>
+          <t>17235081.0360679</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>1361379.0</t>
+          <t>791826.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>6275566</v>
+        <v>5950852</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>4564351.1</t>
+          <t>4204740.0</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>3728872.56</v>
+        <v>3699795.4</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>1711214</t>
+          <t>1746112</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>259508.0993020358</t>
+          <t>224811.0802738158</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>402018.3882461209</t>
+          <t>33977.47561860597</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>1361379.0</t>
+          <t>791826.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -7880,7 +7900,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -7925,12 +7945,12 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
@@ -7950,7 +7970,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -7965,12 +7985,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -7990,22 +8010,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8027,7 +8047,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8037,12 +8057,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>69.172</t>
+          <t>43.045</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8052,7 +8072,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8062,17 +8082,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
+          <t>-0.32</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>37.49</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8137,7 +8157,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8147,17 +8167,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>6.80</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8168,59 +8188,59 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>-0.41</v>
+        <v>-0.22</v>
       </c>
       <c r="AI19" t="n">
         <v>0.02</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>31.78</t>
+          <t>31.77</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="AN19" t="n">
         <v>31.95</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>32.18</t>
+          <t>32.17</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="AQ19" t="n">
@@ -8236,7 +8256,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-122.40</t>
+          <t>-121.57</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8246,43 +8266,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>17256928.99716714</t>
+          <t>17235081.0360679</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>2187020.0</t>
+          <t>1361379.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>6444967.2</v>
+        <v>6275566</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>4961855.9</t>
+          <t>4564351.1</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>3776413.54</v>
+        <v>3728872.56</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>1483111</t>
+          <t>1711214</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>233597.1376758385</t>
+          <t>259508.0993020358</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>852409.7852766393</t>
+          <t>402018.3882461209</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>2187020.0</t>
+          <t>1361379.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8302,7 +8322,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8347,7 +8367,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8372,7 +8392,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8387,12 +8407,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8412,12 +8432,12 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
@@ -8427,7 +8447,7 @@
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8447,7 +8467,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>1737</t>
@@ -8455,12 +8479,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>796.047</t>
+          <t>69.172</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8470,7 +8494,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8480,7 +8504,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8490,7 +8514,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8555,7 +8579,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8565,17 +8589,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>78.27</t>
+          <t>6.80</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8586,66 +8610,66 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>80.95</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>0.22</v>
+        <v>-0.41</v>
       </c>
       <c r="AI20" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>31.77999999999999</t>
+          <t>31.78</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>31.79</v>
+        <v>31.77</v>
       </c>
       <c r="AN20" t="n">
-        <v>31.97</v>
+        <v>31.95</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.18</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>27.11</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="AQ20" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AR20" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
@@ -8654,7 +8678,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-123.38</t>
+          <t>-122.40</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8664,43 +8688,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>17256928.99716714</t>
+          <t>17235081.0360679</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>24752845.0</t>
+          <t>2187020.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>6361239.8</v>
+        <v>6444967.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>5173323.2</t>
+          <t>4961855.9</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>3811369.74</v>
+        <v>3776413.54</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>1187916</t>
+          <t>1483111</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>121085.7472029657</t>
+          <t>233597.1376758385</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>1376921.324417498</t>
+          <t>852409.7852766393</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>24752845.0</t>
+          <t>2187020.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8720,7 +8744,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8765,17 +8789,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8790,7 +8814,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8805,12 +8829,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -8830,22 +8854,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -8865,7 +8889,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>1737</t>
@@ -8873,12 +8901,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>20.816</t>
+          <t>796.047</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -8888,7 +8916,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8898,7 +8926,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -8908,7 +8936,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-35.90</t>
+          <t>22.96</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -8973,7 +9001,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -8983,17 +9011,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>78.27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9004,43 +9032,43 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>80.95</t>
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>0.09</v>
+        <v>0.22</v>
       </c>
       <c r="AI21" t="n">
-        <v>-0.23</v>
+        <v>-0.02</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>31.72</t>
+          <t>31.77999999999999</t>
         </is>
       </c>
       <c r="AM21" t="n">
@@ -9051,16 +9079,16 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>32.22</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>17.58</t>
+          <t>27.11</t>
         </is>
       </c>
       <c r="AQ21" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="AR21" t="n">
         <v>-0.09</v>
@@ -9072,7 +9100,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-124.96</t>
+          <t>-123.38</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9082,43 +9110,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>17256928.99716714</t>
+          <t>17235081.0360679</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>661190.0</t>
+          <t>24752845.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>1925877.6</v>
+        <v>6361239.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>3004447.9</t>
+          <t>5173323.2</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>3413913.34</v>
+        <v>3811369.74</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-1078570</t>
+          <t>1187916</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-107247.9941087675</t>
+          <t>121085.7472029657</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-340719.2026818991</t>
+          <t>1376921.324417498</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>661190.0</t>
+          <t>24752845.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9138,7 +9166,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-2.60</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9183,7 +9211,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9208,7 +9236,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9223,12 +9251,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9248,22 +9276,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9283,7 +9311,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>1737</t>
@@ -9291,12 +9323,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>76.038</t>
+          <t>20.816</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9306,7 +9338,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9316,7 +9348,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9326,7 +9358,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-25.73</t>
+          <t>-35.90</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9391,7 +9423,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9401,17 +9433,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9422,63 +9454,63 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>0.66</v>
+        <v>0.09</v>
       </c>
       <c r="AI22" t="n">
-        <v>-0.35</v>
+        <v>-0.23</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>31.69</t>
+          <t>31.72</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>31.8</v>
+        <v>31.79</v>
       </c>
       <c r="AN22" t="n">
-        <v>31.98</v>
+        <v>31.97</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>32.23</t>
+          <t>32.22</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>15.63</t>
+          <t>17.58</t>
         </is>
       </c>
       <c r="AQ22" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AR22" t="n">
         <v>-0.09</v>
@@ -9490,7 +9522,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-126.06</t>
+          <t>-124.96</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9500,43 +9532,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>17256928.99716714</t>
+          <t>17235081.0360679</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>2415396.0</t>
+          <t>661190.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>2458628</v>
+        <v>1925877.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>3310550.9</t>
+          <t>3004447.9</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>3561770.12</v>
+        <v>3413913.34</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-851922</t>
+          <t>-1078570</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-64798.68345910717</t>
+          <t>-107247.9941087675</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-201074.0912995418</t>
+          <t>-340719.2026818991</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>2415396.0</t>
+          <t>661190.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9556,7 +9588,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9601,7 +9633,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9626,7 +9658,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9641,12 +9673,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9666,22 +9698,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
+          <t>31.9</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
+          <t>31.9</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
+          <t>31.7</t>
+        </is>
+      </c>
+      <c r="CG22" t="inlineStr">
+        <is>
           <t>31.75</t>
-        </is>
-      </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>31.9</t>
-        </is>
-      </c>
-      <c r="CF22" t="inlineStr">
-        <is>
-          <t>31.65</t>
-        </is>
-      </c>
-      <c r="CG22" t="inlineStr">
-        <is>
-          <t>31.9</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9703,7 +9735,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9713,12 +9745,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>69.777</t>
+          <t>76.038</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9728,7 +9760,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9738,7 +9770,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9748,7 +9780,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-10.71</t>
+          <t>-25.73</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9813,7 +9845,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -9823,12 +9855,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -9844,66 +9876,66 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
           <t>66.67</t>
         </is>
       </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>33.33</t>
-        </is>
-      </c>
       <c r="AH23" t="n">
-        <v>0.28</v>
+        <v>0.66</v>
       </c>
       <c r="AI23" t="n">
-        <v>-0.46</v>
+        <v>-0.35</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.77</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>31.66</t>
+          <t>31.69</t>
         </is>
       </c>
       <c r="AM23" t="n">
         <v>31.8</v>
       </c>
       <c r="AN23" t="n">
-        <v>31.99</v>
+        <v>31.98</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>32.24</t>
+          <t>32.23</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>15.63</t>
         </is>
       </c>
       <c r="AQ23" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="AR23" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
@@ -9912,7 +9944,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-127.08</t>
+          <t>-126.06</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -9922,43 +9954,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>17256928.99716714</t>
+          <t>17235081.0360679</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>2208385.0</t>
+          <t>2415396.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>2853136.2</v>
+        <v>2458628</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>3195480.8</t>
+          <t>3310550.9</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>3578602.06</v>
+        <v>3561770.12</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-342344</t>
+          <t>-851922</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-40021.33657902815</t>
+          <t>-64798.68345910717</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-182350.5003497619</t>
+          <t>-201074.0912995418</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>2208385.0</t>
+          <t>2415396.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -9978,7 +10010,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10023,7 +10055,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10048,7 +10080,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10063,12 +10095,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10088,22 +10120,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10125,7 +10157,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10135,12 +10167,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>289.469</t>
+          <t>271.22</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10150,7 +10182,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -10170,7 +10202,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10235,7 +10267,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -10245,17 +10277,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -10266,50 +10298,50 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>72.55</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>-0.74</v>
+        <v>-0.96</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>31.13</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="AM24" t="n">
         <v>30.72</v>
       </c>
       <c r="AN24" t="n">
-        <v>31.08</v>
+        <v>31.09</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10318,14 +10350,14 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>92.54</t>
+          <t>78.48</t>
         </is>
       </c>
       <c r="AQ24" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="AR24" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
@@ -10334,7 +10366,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-109.49</t>
+          <t>-107.93</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -10344,43 +10376,43 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>38597829.71813031</t>
+          <t>38560961.48231966</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>8958018.0</t>
+          <t>8354658.0</t>
         </is>
       </c>
       <c r="AX24" t="n">
-        <v>13694764.8</v>
+        <v>11743619</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>12617621.5</t>
+          <t>11679823.5</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>22194999.2</v>
+        <v>21908787.42</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>1077143</t>
+          <t>63795</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>-1154643.214575751</t>
+          <t>-1160606.361510194</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-1032481.359884785</t>
+          <t>-1193403.669649629</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>8958018.0</t>
+          <t>8354658.0</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -10400,7 +10432,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>-9.28</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -10445,7 +10477,7 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -10460,7 +10492,7 @@
       </c>
       <c r="BT24" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BU24" t="inlineStr">
@@ -10470,7 +10502,7 @@
       </c>
       <c r="BV24" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="BW24" t="inlineStr">
@@ -10485,12 +10517,12 @@
       </c>
       <c r="BY24" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>28276</t>
+          <t>28185</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -10510,22 +10542,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -10547,7 +10579,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -10557,12 +10589,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>267.229</t>
+          <t>289.469</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10572,7 +10604,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -10582,7 +10614,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -10592,7 +10624,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>8.90</t>
+          <t>8.54</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -10657,7 +10689,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -10667,17 +10699,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -10688,50 +10720,50 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>82.35</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>72.55</t>
         </is>
       </c>
       <c r="AH25" t="n">
-        <v>0.48</v>
+        <v>-0.74</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.98</v>
+        <v>1.32</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.13</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>30.75</v>
+        <v>30.72</v>
       </c>
       <c r="AN25" t="n">
-        <v>31.06</v>
+        <v>31.08</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -10740,14 +10772,14 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>95.13</t>
+          <t>92.54</t>
         </is>
       </c>
       <c r="AQ25" t="n">
         <v>-0.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
@@ -10756,7 +10788,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>-111.68</t>
+          <t>-109.49</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -10766,43 +10798,43 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>38597829.71813031</t>
+          <t>38560961.48231966</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>8309295.0</t>
+          <t>8958018.0</t>
         </is>
       </c>
       <c r="AX25" t="n">
-        <v>14054867.6</v>
+        <v>13694764.8</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>12906697.9</t>
+          <t>12617621.5</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>22422775.08</v>
+        <v>22194999.2</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>1148169</t>
+          <t>1077143</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>-1176854.4608832</t>
+          <t>-1154643.214575751</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-830363.725939123</t>
+          <t>-1032481.359884785</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>8309295.0</t>
+          <t>8958018.0</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -10822,7 +10854,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>-8.10</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
@@ -10867,7 +10899,7 @@
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -10877,12 +10909,12 @@
       </c>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT25" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BU25" t="inlineStr">
@@ -10892,7 +10924,7 @@
       </c>
       <c r="BV25" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="BW25" t="inlineStr">
@@ -10907,12 +10939,12 @@
       </c>
       <c r="BY25" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>28276</t>
+          <t>28185</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -10937,17 +10969,17 @@
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -10969,7 +11001,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -10979,12 +11011,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>363.041</t>
+          <t>267.229</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -10994,7 +11026,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -11004,7 +11036,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.3</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -11014,7 +11046,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>8.90</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -11079,7 +11111,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -11089,17 +11121,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -11110,50 +11142,50 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>96.08</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AH26" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.63</v>
+        <v>0.98</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>30.96</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>30.77</v>
+        <v>30.75</v>
       </c>
       <c r="AN26" t="n">
-        <v>31.05</v>
+        <v>31.06</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11162,14 +11194,14 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>95.13</t>
         </is>
       </c>
       <c r="AQ26" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="AR26" t="n">
-        <v>-0.13</v>
+        <v>-0.1</v>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
@@ -11178,7 +11210,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-114.46</t>
+          <t>-111.68</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -11188,43 +11220,43 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>38597829.71813031</t>
+          <t>38560961.48231966</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>11334528.0</t>
+          <t>8309295.0</t>
         </is>
       </c>
       <c r="AX26" t="n">
-        <v>14224209</v>
+        <v>14054867.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>13015500.0</t>
+          <t>12906697.9</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>22552981.3</v>
+        <v>22422775.08</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>1208709</t>
+          <t>1148169</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>-1239852.776327577</t>
+          <t>-1176854.4608832</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-442462.3658046369</t>
+          <t>-830363.725939123</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>11334528.0</t>
+          <t>8309295.0</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -11244,7 +11276,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -11289,7 +11321,7 @@
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -11304,7 +11336,7 @@
       </c>
       <c r="BT26" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BU26" t="inlineStr">
@@ -11314,7 +11346,7 @@
       </c>
       <c r="BV26" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="BW26" t="inlineStr">
@@ -11329,12 +11361,12 @@
       </c>
       <c r="BY26" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>28276</t>
+          <t>28185</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -11354,22 +11386,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -11391,7 +11423,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11401,12 +11433,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>699.247</t>
+          <t>363.041</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11416,7 +11448,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11436,7 +11468,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -11501,7 +11533,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -11511,17 +11543,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -11532,50 +11564,50 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>96.08</t>
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>1.59</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.31</v>
+        <v>0.63</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>30.86</t>
+          <t>30.96</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>30.76</v>
+        <v>30.77</v>
       </c>
       <c r="AN27" t="n">
-        <v>31.02</v>
+        <v>31.05</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -11584,14 +11616,14 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AQ27" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="AR27" t="n">
-        <v>-0.15</v>
+        <v>-0.13</v>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
@@ -11600,7 +11632,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-117.12</t>
+          <t>-114.46</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -11610,43 +11642,43 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>38597829.71813031</t>
+          <t>38560961.48231966</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>21761596.0</t>
+          <t>11334528.0</t>
         </is>
       </c>
       <c r="AX27" t="n">
-        <v>13807770.2</v>
+        <v>14224209</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>13168431.0</t>
+          <t>13015500.0</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>22572708.9</v>
+        <v>22552981.3</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>639339</t>
+          <t>1208709</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>-1384832.850968112</t>
+          <t>-1239852.776327577</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-196647.4454052038</t>
+          <t>-442462.3658046369</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>21761596.0</t>
+          <t>11334528.0</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -11666,7 +11698,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>-7.66</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -11711,12 +11743,12 @@
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS27" t="inlineStr">
@@ -11726,7 +11758,7 @@
       </c>
       <c r="BT27" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BU27" t="inlineStr">
@@ -11736,7 +11768,7 @@
       </c>
       <c r="BV27" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="BW27" t="inlineStr">
@@ -11751,12 +11783,12 @@
       </c>
       <c r="BY27" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>28276</t>
+          <t>28185</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -11776,22 +11808,22 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -11811,7 +11843,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>【d1】</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>1227</t>
@@ -11819,12 +11855,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>588.081</t>
+          <t>699.247</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -11834,7 +11870,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>30.95</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -11844,7 +11880,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -11854,7 +11890,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-9.94</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -11919,7 +11955,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -11929,17 +11965,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11.25</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -11950,12 +11986,12 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -11965,51 +12001,51 @@
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH28" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.59</v>
       </c>
       <c r="AI28" t="n">
-        <v>-0.17</v>
+        <v>0.31</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.86</t>
         </is>
       </c>
       <c r="AM28" t="n">
-        <v>30.75</v>
+        <v>30.76</v>
       </c>
       <c r="AN28" t="n">
-        <v>31</v>
+        <v>31.02</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>30.81</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AQ28" t="n">
-        <v>-0.14</v>
+        <v>-0.08</v>
       </c>
       <c r="AR28" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
@@ -12018,7 +12054,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-119.27</t>
+          <t>-117.12</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -12028,43 +12064,43 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>38597829.71813031</t>
+          <t>38560961.48231966</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>18110387.0</t>
+          <t>21761596.0</t>
         </is>
       </c>
       <c r="AX28" t="n">
-        <v>11616028</v>
+        <v>13807770.2</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>12897946.0</t>
+          <t>13168431.0</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>22309041.54</v>
+        <v>22572708.9</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>-1281918</t>
+          <t>639339</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>-1600866.561070459</t>
+          <t>-1384832.850968112</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-955646.007498689</t>
+          <t>-196647.4454052038</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>18110387.0</t>
+          <t>21761596.0</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
@@ -12084,7 +12120,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>-8.84</t>
+          <t>-7.66</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -12129,7 +12165,7 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -12139,12 +12175,12 @@
       </c>
       <c r="BS28" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT28" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BU28" t="inlineStr">
@@ -12154,7 +12190,7 @@
       </c>
       <c r="BV28" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="BW28" t="inlineStr">
@@ -12169,12 +12205,12 @@
       </c>
       <c r="BY28" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>28276</t>
+          <t>28185</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -12194,22 +12230,22 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>30.95</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -12229,7 +12265,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>1227</t>
@@ -12237,12 +12277,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>352.598</t>
+          <t>588.081</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12252,7 +12292,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.95</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -12262,7 +12302,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -12272,7 +12312,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-12.12</t>
+          <t>-9.94</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -12337,7 +12377,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -12347,17 +12387,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>11.25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -12368,67 +12408,67 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>80.56</t>
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>-0.55</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AI29" t="n">
-        <v>-0.28</v>
+        <v>-0.17</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>30.76</v>
+        <v>30.75</v>
       </c>
       <c r="AN29" t="n">
-        <v>30.99</v>
+        <v>31</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>30.82</t>
+          <t>30.81</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AQ29" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="AR29" t="n">
         <v>-0.17</v>
       </c>
-      <c r="AR29" t="n">
-        <v>-0.18</v>
-      </c>
       <c r="AS29" t="inlineStr">
         <is>
           <t>0.89</t>
@@ -12436,7 +12476,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>-120.23</t>
+          <t>-119.27</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -12446,43 +12486,43 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>38597829.71813031</t>
+          <t>38560961.48231966</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>10758532.0</t>
+          <t>18110387.0</t>
         </is>
       </c>
       <c r="AX29" t="n">
-        <v>11540478.2</v>
+        <v>11616028</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>13132407.8</t>
+          <t>12897946.0</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>22134858.04</v>
+        <v>22309041.54</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>-1591929</t>
+          <t>-1281918</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>-1718179.388992599</t>
+          <t>-1600866.561070459</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>-1614598.488792999</t>
+          <t>-955646.007498689</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>10758532.0</t>
+          <t>18110387.0</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
@@ -12502,7 +12542,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>-10.16</t>
+          <t>-8.84</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -12547,22 +12587,22 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS29" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT29" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BU29" t="inlineStr">
@@ -12572,7 +12612,7 @@
       </c>
       <c r="BV29" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="BW29" t="inlineStr">
@@ -12587,12 +12627,12 @@
       </c>
       <c r="BY29" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BZ29" t="inlineStr">
         <is>
-          <t>28276</t>
+          <t>28185</t>
         </is>
       </c>
       <c r="CA29" t="inlineStr">
@@ -12612,22 +12652,22 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.95</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -12647,7 +12687,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>1227</t>
@@ -12655,42 +12699,42 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>-0.82</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>352.598</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>30.5</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>298.728</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>30.75</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-12.21</t>
+          <t>-12.12</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -12755,7 +12799,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -12765,17 +12809,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -12786,38 +12830,38 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>76.67</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AH30" t="n">
-        <v>0.26</v>
+        <v>-0.55</v>
       </c>
       <c r="AI30" t="n">
-        <v>-0.43</v>
+        <v>-0.28</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
@@ -12826,19 +12870,19 @@
         </is>
       </c>
       <c r="AM30" t="n">
-        <v>30.8</v>
+        <v>30.76</v>
       </c>
       <c r="AN30" t="n">
-        <v>30.98</v>
+        <v>30.99</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>30.84</t>
+          <t>30.82</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AQ30" t="n">
@@ -12854,7 +12898,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>-120.39</t>
+          <t>-120.23</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -12864,43 +12908,43 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>38597829.71813031</t>
+          <t>38560961.48231966</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>9156002.0</t>
+          <t>10758532.0</t>
         </is>
       </c>
       <c r="AX30" t="n">
-        <v>11758528.2</v>
+        <v>11540478.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>13393839.6</t>
+          <t>13132407.8</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>22093985.98</v>
+        <v>22134858.04</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>-1635311</t>
+          <t>-1591929</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>-1737012.27993798</t>
+          <t>-1718179.388992599</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>-1710596.194613693</t>
+          <t>-1614598.488792999</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>9156002.0</t>
+          <t>10758532.0</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
@@ -12920,7 +12964,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-10.16</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -12965,7 +13009,7 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
@@ -12975,12 +13019,12 @@
       </c>
       <c r="BS30" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT30" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BU30" t="inlineStr">
@@ -12990,7 +13034,7 @@
       </c>
       <c r="BV30" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="BW30" t="inlineStr">
@@ -13005,12 +13049,12 @@
       </c>
       <c r="BY30" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BZ30" t="inlineStr">
         <is>
-          <t>28276</t>
+          <t>28185</t>
         </is>
       </c>
       <c r="CA30" t="inlineStr">
@@ -13035,17 +13079,17 @@
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -13067,7 +13111,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13077,12 +13121,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>301.716</t>
+          <t>298.728</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13102,7 +13146,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -13112,7 +13156,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-14.59</t>
+          <t>-12.21</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -13187,17 +13231,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -13208,12 +13252,12 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -13223,48 +13267,48 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>76.67</t>
         </is>
       </c>
       <c r="AH31" t="n">
-        <v>0.52</v>
+        <v>0.26</v>
       </c>
       <c r="AI31" t="n">
-        <v>-0.75</v>
+        <v>-0.43</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>30.59</t>
+          <t>30.67</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>30.82</v>
+        <v>30.8</v>
       </c>
       <c r="AN31" t="n">
-        <v>30.97</v>
+        <v>30.98</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.84</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>-5.01</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="AQ31" t="n">
-        <v>-0.19</v>
+        <v>-0.17</v>
       </c>
       <c r="AR31" t="n">
         <v>-0.18</v>
@@ -13276,7 +13320,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>-120.65</t>
+          <t>-120.39</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -13286,43 +13330,43 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>38597829.71813031</t>
+          <t>38560961.48231966</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>9252334.0</t>
+          <t>9156002.0</t>
         </is>
       </c>
       <c r="AX31" t="n">
-        <v>11806791</v>
+        <v>11758528.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>13824086.6</t>
+          <t>13393839.6</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>22091752.82</v>
+        <v>22093985.98</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>-2017295</t>
+          <t>-1635311</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>-1741815.204542396</t>
+          <t>-1737012.27993798</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>-1614943.410264194</t>
+          <t>-1710596.194613693</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>9252334.0</t>
+          <t>9156002.0</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -13402,7 +13446,7 @@
       </c>
       <c r="BT31" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BU31" t="inlineStr">
@@ -13412,7 +13456,7 @@
       </c>
       <c r="BV31" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="BW31" t="inlineStr">
@@ -13427,12 +13471,12 @@
       </c>
       <c r="BY31" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BZ31" t="inlineStr">
         <is>
-          <t>28276</t>
+          <t>28185</t>
         </is>
       </c>
       <c r="CA31" t="inlineStr">
@@ -13452,17 +13496,17 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
@@ -13499,12 +13543,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>353.844</t>
+          <t>301.716</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13514,7 +13558,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13524,7 +13568,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -13534,7 +13578,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-11.16</t>
+          <t>-14.59</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -13599,7 +13643,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -13609,17 +13653,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>5.77</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -13630,63 +13674,63 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>72.78</t>
         </is>
       </c>
       <c r="AH32" t="n">
-        <v>0.23</v>
+        <v>0.52</v>
       </c>
       <c r="AI32" t="n">
-        <v>-1.18</v>
+        <v>-0.75</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>30.59</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>30.84</v>
+        <v>30.82</v>
       </c>
       <c r="AN32" t="n">
-        <v>30.96</v>
+        <v>30.97</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>30.87</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>-19.31</t>
+          <t>-5.01</t>
         </is>
       </c>
       <c r="AQ32" t="n">
-        <v>-0.22</v>
+        <v>-0.19</v>
       </c>
       <c r="AR32" t="n">
         <v>-0.18</v>
@@ -13698,7 +13742,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>-120.39</t>
+          <t>-120.65</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -13708,43 +13752,43 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>38597829.71813031</t>
+          <t>38560961.48231966</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>10802885.0</t>
+          <t>9252334.0</t>
         </is>
       </c>
       <c r="AX32" t="n">
-        <v>12529091.8</v>
+        <v>11806791</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>14102580.3</t>
+          <t>13824086.6</t>
         </is>
       </c>
       <c r="AZ32" t="n">
-        <v>22250476.5</v>
+        <v>22091752.82</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>-1573488</t>
+          <t>-2017295</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>-1764882.803502069</t>
+          <t>-1741815.204542396</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>-1430941.310826903</t>
+          <t>-1614943.410264194</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>10802885.0</t>
+          <t>9252334.0</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -13764,7 +13808,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>-10.01</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -13809,7 +13853,7 @@
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
@@ -13819,12 +13863,12 @@
       </c>
       <c r="BS32" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT32" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BU32" t="inlineStr">
@@ -13834,7 +13878,7 @@
       </c>
       <c r="BV32" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="BW32" t="inlineStr">
@@ -13849,12 +13893,12 @@
       </c>
       <c r="BY32" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BZ32" t="inlineStr">
         <is>
-          <t>28276</t>
+          <t>28185</t>
         </is>
       </c>
       <c r="CA32" t="inlineStr">
@@ -13874,22 +13918,22 @@
       </c>
       <c r="CD32" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="CG32" t="inlineStr">
         <is>
-          <t>30.55</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CH32" t="inlineStr">
@@ -13921,12 +13965,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>577.761</t>
+          <t>353.844</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -13936,7 +13980,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -13946,7 +13990,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -13956,7 +14000,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-11.16</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -14021,7 +14065,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -14031,17 +14075,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11.05</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -14052,66 +14096,66 @@
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AH33" t="n">
-        <v>1.28</v>
+        <v>0.23</v>
       </c>
       <c r="AI33" t="n">
-        <v>-1.51</v>
+        <v>-1.18</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>30.41</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>30.88</v>
+        <v>30.84</v>
       </c>
       <c r="AN33" t="n">
         <v>30.96</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>30.89</t>
+          <t>30.87</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>-29.11</t>
+          <t>-19.31</t>
         </is>
       </c>
       <c r="AQ33" t="n">
         <v>-0.22</v>
       </c>
       <c r="AR33" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
@@ -14120,7 +14164,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>-119.40</t>
+          <t>-120.39</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -14130,43 +14174,43 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>38597829.71813031</t>
+          <t>38560961.48231966</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>17732638.0</t>
+          <t>10802885.0</t>
         </is>
       </c>
       <c r="AX33" t="n">
-        <v>14179864</v>
+        <v>12529091.8</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>14548151.5</t>
+          <t>14102580.3</t>
         </is>
       </c>
       <c r="AZ33" t="n">
-        <v>22337908.28</v>
+        <v>22250476.5</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>-368287</t>
+          <t>-1573488</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>-1825599.438533918</t>
+          <t>-1764882.803502069</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>-1283106.586244099</t>
+          <t>-1430941.310826903</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>17732638.0</t>
+          <t>10802885.0</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
@@ -14186,7 +14230,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>-9.28</t>
+          <t>-10.01</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -14231,7 +14275,7 @@
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
@@ -14241,12 +14285,12 @@
       </c>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BU33" t="inlineStr">
@@ -14256,7 +14300,7 @@
       </c>
       <c r="BV33" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="BW33" t="inlineStr">
@@ -14271,12 +14315,12 @@
       </c>
       <c r="BY33" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BZ33" t="inlineStr">
         <is>
-          <t>28276</t>
+          <t>28185</t>
         </is>
       </c>
       <c r="CA33" t="inlineStr">
@@ -14296,7 +14340,7 @@
       </c>
       <c r="CD33" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CE33" t="inlineStr">
@@ -14306,12 +14350,12 @@
       </c>
       <c r="CF33" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CG33" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>30.55</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -14343,12 +14387,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>389.506</t>
+          <t>577.761</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14358,7 +14402,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -14368,7 +14412,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -14378,7 +14422,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -14443,7 +14487,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -14453,17 +14497,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>11.05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -14474,66 +14518,66 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>271</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AH34" t="n">
-        <v>0.49</v>
+        <v>1.28</v>
       </c>
       <c r="AI34" t="n">
-        <v>-1.81</v>
+        <v>-1.51</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>30.41</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>30.91</v>
+        <v>30.88</v>
       </c>
       <c r="AN34" t="n">
-        <v>30.95</v>
+        <v>30.96</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>30.89</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>-58.32</t>
+          <t>-29.11</t>
         </is>
       </c>
       <c r="AQ34" t="n">
-        <v>-0.25</v>
+        <v>-0.22</v>
       </c>
       <c r="AR34" t="n">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
@@ -14542,7 +14586,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>-117.99</t>
+          <t>-119.40</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -14552,43 +14596,43 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>38597829.71813031</t>
+          <t>38560961.48231966</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>11848782.0</t>
+          <t>17732638.0</t>
         </is>
       </c>
       <c r="AX34" t="n">
-        <v>14724337.4</v>
+        <v>14179864</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>15055398.0</t>
+          <t>14548151.5</t>
         </is>
       </c>
       <c r="AZ34" t="n">
-        <v>22289314.84</v>
+        <v>22337908.28</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>-331060</t>
+          <t>-368287</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>-1924234.502586612</t>
+          <t>-1825599.438533918</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>-1768562.423045658</t>
+          <t>-1283106.586244099</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>11848782.0</t>
+          <t>17732638.0</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
@@ -14608,7 +14652,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>-10.16</t>
+          <t>-9.28</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
@@ -14653,7 +14697,7 @@
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
@@ -14663,12 +14707,12 @@
       </c>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT34" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="BU34" t="inlineStr">
@@ -14678,7 +14722,7 @@
       </c>
       <c r="BV34" t="inlineStr">
         <is>
-          <t>21.16</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="BW34" t="inlineStr">
@@ -14693,12 +14737,12 @@
       </c>
       <c r="BY34" t="inlineStr">
         <is>
-          <t>24.31</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="BZ34" t="inlineStr">
         <is>
-          <t>28276</t>
+          <t>28185</t>
         </is>
       </c>
       <c r="CA34" t="inlineStr">
@@ -14718,22 +14762,22 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CE34" t="inlineStr">
         <is>
+          <t>30.8</t>
+        </is>
+      </c>
+      <c r="CF34" t="inlineStr">
+        <is>
           <t>30.5</t>
         </is>
       </c>
-      <c r="CF34" t="inlineStr">
-        <is>
-          <t>30.3</t>
-        </is>
-      </c>
       <c r="CG34" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CH34" t="inlineStr">

--- a/Result/checksun_type/營養食品.xlsx
+++ b/Result/checksun_type/營養食品.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>-14.38</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
@@ -1024,53 +1024,53 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-1.62</v>
+        <v>-0.95</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>75.52000000000001</t>
+          <t>75.41999999999999</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>75.09999999999999</v>
+        <v>74.95</v>
       </c>
       <c r="AN2" t="n">
-        <v>74.84</v>
+        <v>74.79000000000001</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>75.33</t>
+          <t>75.34</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>-20.83</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="AR2" t="n">
         <v>0.12</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-92.86</t>
+          <t>-93.22</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>3916.142971246006</t>
+          <t>3910.622009569378</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>301.0</t>
+          <t>303.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>786.6</v>
+        <v>682.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>766.6</t>
+          <t>796.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>1186.8</v>
+        <v>1158.64</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-114</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-55.10042951341114</t>
+          <t>-56.45118348330261</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-32.775147706334</t>
+          <t>-63.88033031770578</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>301.0</t>
+          <t>303.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>13.96</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,17 +1330,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>20.11</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,28 +1415,28 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
@@ -1451,48 +1451,48 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-1.4</v>
+        <v>-1.62</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.37</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>75.56</t>
+          <t>75.52000000000001</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>75.28</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="AN3" t="n">
-        <v>74.90000000000001</v>
+        <v>74.84</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>75.34</t>
+          <t>75.33</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>88.21</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.23</v>
+        <v>0.13</v>
       </c>
       <c r="AR3" t="n">
         <v>0.12</v>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-93.02</t>
+          <t>-92.86</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>3916.142971246006</t>
+          <t>3910.622009569378</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1892.0</t>
+          <t>301.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>921.6</v>
+        <v>786.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>767.3</t>
+          <t>766.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>1200.84</v>
+        <v>1186.8</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>20</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-59.15957166015243</t>
+          <t>-55.10042951341114</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>13.04565415656623</t>
+          <t>-32.775147706334</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1892.0</t>
+          <t>301.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>13.96</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,17 +1752,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>20.11</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,7 +1858,7 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1868,56 +1868,56 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>98.33</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>1.51</v>
+        <v>-1.4</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.42</v>
+        <v>0.37</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>75.66</t>
+          <t>75.56</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>75.34</v>
+        <v>75.28</v>
       </c>
       <c r="AN4" t="n">
-        <v>74.95</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>75.35</t>
+          <t>75.34</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>241.53</t>
+          <t>88.21</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.32</v>
+        <v>0.23</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-94.56</t>
+          <t>-93.02</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>3916.142971246006</t>
+          <t>3910.622009569378</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>1892.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>588</v>
+        <v>921.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>593.1</t>
+          <t>767.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>1176.82</v>
+        <v>1200.84</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>154</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-72.28779453591946</t>
+          <t>-59.15957166015243</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-92.42625940202515</t>
+          <t>13.04565415656623</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>1892.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>13.96</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2174,17 +2174,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,7 +2280,7 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
@@ -2295,51 +2295,51 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>98.33</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>1.91</v>
+        <v>1.51</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.15</v>
+        <v>0.42</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>75.35999999999999</t>
+          <t>75.66</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>75.23999999999999</v>
+        <v>75.34</v>
       </c>
       <c r="AN5" t="n">
         <v>74.95</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>75.33</t>
+          <t>75.35</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>437.85</t>
+          <t>241.53</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-97.85</t>
+          <t>-94.56</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>3916.142971246006</t>
+          <t>3910.622009569378</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>838.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>648.2</v>
+        <v>588</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>655.1</t>
+          <t>593.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>1206.04</v>
+        <v>1176.82</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-68.62625546935479</t>
+          <t>-72.28779453591946</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-45.33519807851189</t>
+          <t>-92.42625940202515</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>838.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>13.96</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2561,7 +2561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【b2】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,17 +2596,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>36.87</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -2691,18 +2691,18 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
@@ -2712,256 +2712,256 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.27</v>
+        <v>1.91</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
+          <t>75.35999999999999</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>75.23999999999999</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>74.95</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>75.33</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>437.85</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-97.85</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/12/01</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>3910.622009569378</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>838.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>648.2</v>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>655.1</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1206.04</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-68.62625546935479</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-45.33519807851189</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>838.0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>綠茵</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>綠茵</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>食品工業</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>52.61369974141865</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>32.46296024644272</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>6.052320446915804</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>4.82</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>7.61</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>13.96</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>48.81%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>17.38%</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>29.22</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>保健食品配方65.97%、保健食品原料33.59%、其他0.43% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>綠茵-食品工業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>食品工業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
           <t>75.0</t>
         </is>
       </c>
-      <c r="AM6" t="n">
-        <v>75.06</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>74.95999999999999</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>75.31</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>1328.07</t>
-        </is>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-100.20</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/12/01</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>3916.142971246006</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>825.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="n">
-        <v>911.4</v>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>665.9</t>
-        </is>
-      </c>
-      <c r="AZ6" t="n">
-        <v>1235.98</v>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>245</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-72.86099317678077</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>-57.9788533992604</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>825.0</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>75.2</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/12/04</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>綠茵</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>綠茵</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>食品工業</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>52.61369974141865</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>32.46296024644272</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>6.052320446915804</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>2.19</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>4.84</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>7.61</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>13.89</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>48.81%</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>17.38%</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>29.4</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>保健食品配方65.97%、保健食品原料33.59%、其他0.43% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>綠茵-食品工業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>食品工業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>74.2</t>
-        </is>
-      </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2983,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【b2】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2993,42 +2993,42 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>-0.67</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>74.5</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-0.27</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15.00</t>
+          <t>36.87</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,7 +3124,7 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -3134,56 +3134,56 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-0.48</v>
+        <v>0.27</v>
       </c>
       <c r="AI7" t="n">
-        <v>-0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>74.85999999999999</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>74.94</v>
+        <v>75.06</v>
       </c>
       <c r="AN7" t="n">
-        <v>75</v>
+        <v>74.95999999999999</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>75.32</t>
+          <t>75.31</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>142.67</t>
+          <t>1328.07</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.02</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-100.88</t>
+          <t>-100.20</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>3916.142971246006</t>
+          <t>3910.622009569378</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>976.0</t>
+          <t>825.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>746.6</v>
+        <v>911.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>649.2</t>
+          <t>665.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>1258.5</v>
+        <v>1235.98</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>97</t>
+          <t>245</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-75.56683677269356</t>
+          <t>-72.86099317678077</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-72.57768766464164</t>
+          <t>-57.9788533992604</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>976.0</t>
+          <t>825.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,22 +3303,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>13.96</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,17 +3440,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-29.02</t>
+          <t>15.00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,7 +3546,7 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -3556,53 +3556,53 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.19</v>
+        <v>-0.48</v>
       </c>
       <c r="AI8" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>-0.42</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>74.85999999999999</t>
+        </is>
+      </c>
+      <c r="AM8" t="n">
+        <v>74.94</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>75.32</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>142.67</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
         <v>0.01</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>74.85999999999999</t>
-        </is>
-      </c>
-      <c r="AM8" t="n">
-        <v>74.84999999999999</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>75.06</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>75.32</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>251.70</t>
-        </is>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0.03</v>
       </c>
       <c r="AR8" t="n">
         <v>-0.02</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-101.19</t>
+          <t>-100.88</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>3916.142971246006</t>
+          <t>3910.622009569378</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>976.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>613</v>
+        <v>746.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>863.6</t>
+          <t>649.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>1276.7</v>
+        <v>1258.5</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-250</t>
+          <t>97</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-76.110318428703</t>
+          <t>-75.56683677269356</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-107.0196763414492</t>
+          <t>-72.57768766464164</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>976.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>13.96</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>74.3</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>76.1</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>74.3</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>74.5</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>74.5</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>75.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-33.24</t>
+          <t>-29.02</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,7 +3968,7 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
@@ -3978,40 +3978,40 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.67</v>
+        <v>0.19</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.85999999999999</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>74.75</v>
+        <v>74.84999999999999</v>
       </c>
       <c r="AN9" t="n">
-        <v>75.11</v>
+        <v>75.06</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4020,14 +4020,14 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>133.40</t>
+          <t>251.70</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-101.95</t>
+          <t>-101.19</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>3916.142971246006</t>
+          <t>3910.622009569378</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>378.0</t>
+          <t>224.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>598.2</v>
+        <v>613</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>896.0</t>
+          <t>863.6</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>1293.44</v>
+        <v>1276.7</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-297</t>
+          <t>-250</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-70.49043517184005</t>
+          <t>-76.110318428703</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-71.82895743897961</t>
+          <t>-107.0196763414492</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>378.0</t>
+          <t>224.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>13.96</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,17 +4284,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-28.86</t>
+          <t>-33.24</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.09</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.82</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,7 +4390,7 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
@@ -4405,35 +4405,35 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>62.59</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.31</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>74.64</v>
+        <v>74.75</v>
       </c>
       <c r="AN10" t="n">
-        <v>75.15000000000001</v>
+        <v>75.11</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4442,14 +4442,14 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>133.40</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-102.60</t>
+          <t>-101.95</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>3916.142971246006</t>
+          <t>3910.622009569378</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2154.0</t>
+          <t>378.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>662</v>
+        <v>598.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>930.6</t>
+          <t>896.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>1312.14</v>
+        <v>1293.44</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-268</t>
+          <t>-297</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-70.24706748690558</t>
+          <t>-70.49043517184005</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-35.49118195548817</t>
+          <t>-71.82895743897961</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>2154.0</t>
+          <t>378.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>13.96</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,17 +4706,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-45.89</t>
+          <t>-28.86</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-4.09</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.82</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,7 +4812,7 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -4822,53 +4822,53 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>42.18</t>
+          <t>62.59</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.19</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.25</v>
+        <v>-0.31</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>74.35999999999999</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>74.54000000000001</v>
+        <v>74.64</v>
       </c>
       <c r="AN11" t="n">
-        <v>75.19</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>75.31</t>
+          <t>75.32</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-92.58</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-0.09</v>
+        <v>-0.04</v>
       </c>
       <c r="AR11" t="n">
         <v>-0.04</v>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-102.59</t>
+          <t>-102.60</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>3916.142971246006</t>
+          <t>3910.622009569378</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2154.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>420.4</v>
+        <v>662</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>777.0</t>
+          <t>930.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>1270.7</v>
+        <v>1312.14</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-356</t>
+          <t>-268</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-76.56631940170874</t>
+          <t>-70.24706748690558</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-172.5982461949473</t>
+          <t>-35.49118195548817</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2154.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>13.96</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-36.10</t>
+          <t>-45.89</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>inf</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,7 +5234,7 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
@@ -5244,56 +5244,56 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>42.18</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>0.35</v>
+        <v>0.19</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.34</v>
+        <v>-0.25</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>74.24000000000001</t>
+          <t>74.35999999999999</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>74.48999999999999</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="AN12" t="n">
-        <v>75.23999999999999</v>
+        <v>75.19</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.31</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-149.08</t>
+          <t>-92.58</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="AR12" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-101.99</t>
+          <t>-102.59</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>3916.142971246006</t>
+          <t>3910.622009569378</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>308.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>551.8</v>
+        <v>420.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>863.5</t>
+          <t>777.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>1290.88</v>
+        <v>1270.7</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-311</t>
+          <t>-356</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-59.10596907566538</t>
+          <t>-76.56631940170874</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-131.6226863157835</t>
+          <t>-172.5982461949473</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>308.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>13.96</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,17 +5478,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>85.061</t>
+          <t>60.825</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>12.67</t>
+          <t>18.41</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5635,17 +5635,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>5.98</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5656,12 +5656,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5675,47 +5675,47 @@
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>-0.09</v>
+        <v>-0.19</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0.24</v>
+        <v>-0.25</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>31.63</t>
+          <t>31.61</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>31.7</v>
+        <v>31.69</v>
       </c>
       <c r="AN13" t="n">
-        <v>31.87</v>
+        <v>31.86</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>32.04</t>
+          <t>32.02</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-8.92</t>
         </is>
       </c>
       <c r="AQ13" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="AR13" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-117.57</t>
+          <t>-117.97</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5734,43 +5734,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>17201065.77715092</t>
+          <t>17180899.14507042</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>2691552.0</t>
+          <t>1921838.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>2314593</v>
+        <v>2401090.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>2054239.7</t>
+          <t>2027721.5</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>3427159.74</v>
+        <v>3393863.1</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>260353</t>
+          <t>373369</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-139293.5660992182</t>
+          <t>-163063.9462019176</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-258073.6231550472</t>
+          <t>-293801.0367667642</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>2691552.0</t>
+          <t>1921838.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5835,12 +5835,12 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5850,7 +5850,7 @@
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>6320</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5900,22 +5900,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>31.6</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
           <t>31.7</t>
         </is>
       </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>31.7</t>
-        </is>
-      </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -5937,7 +5937,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5947,12 +5947,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>132.983</t>
+          <t>85.061</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5982,7 +5982,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-51.87</t>
+          <t>12.67</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6057,17 +6057,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13.08</t>
+          <t>8.36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6078,17 +6078,17 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -6097,44 +6097,44 @@
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="AI14" t="n">
         <v>-0.24</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>31.64</t>
+          <t>31.63</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>31.72</v>
+        <v>31.7</v>
       </c>
       <c r="AN14" t="n">
-        <v>31.89</v>
+        <v>31.87</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>32.06</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AQ14" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AR14" t="n">
         <v>-0.06</v>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-117.44</t>
+          <t>-117.57</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6156,43 +6156,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>17201065.77715092</t>
+          <t>17180899.14507042</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>4210677.0</t>
+          <t>2691552.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>2050717.2</v>
+        <v>2314593</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>4260369.0</t>
+          <t>2054239.7</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>3500565.5</v>
+        <v>3427159.74</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-2209651</t>
+          <t>260353</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-117697.1920890675</t>
+          <t>-139293.5660992182</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-280286.9028827706</t>
+          <t>-258073.6231550472</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>4210677.0</t>
+          <t>2691552.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6282,7 +6282,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>6320</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6322,22 +6322,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
+          <t>31.7</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>31.7</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
           <t>31.6</t>
         </is>
       </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>31.75</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
+      <c r="CG14" t="inlineStr">
         <is>
           <t>31.6</t>
-        </is>
-      </c>
-      <c r="CG14" t="inlineStr">
-        <is>
-          <t>31.65</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6359,7 +6359,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>38.178</t>
+          <t>132.983</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6394,17 +6394,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>-0.32</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-52.37</t>
+          <t>-51.87</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>13.08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -6500,59 +6500,59 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>-0.32</v>
+        <v>0.03</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.24</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>31.64</t>
         </is>
       </c>
       <c r="AM15" t="n">
         <v>31.72</v>
       </c>
       <c r="AN15" t="n">
-        <v>31.9</v>
+        <v>31.89</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>32.07</t>
+          <t>32.06</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AQ15" t="n">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-117.46</t>
+          <t>-117.44</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6578,43 +6578,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>17201065.77715092</t>
+          <t>17180899.14507042</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>1206947.0</t>
+          <t>4210677.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>1859988.6</v>
+        <v>2050717.2</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3905420.3</t>
+          <t>4260369.0</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>3496627.64</v>
+        <v>3500565.5</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-2045431</t>
+          <t>-2209651</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-88135.42649021233</t>
+          <t>-117697.1920890675</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-464773.3059622766</t>
+          <t>-280286.9028827706</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>1206947.0</t>
+          <t>4210677.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6679,12 +6679,12 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6704,7 +6704,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>6320</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6749,17 +6749,17 @@
       </c>
       <c r="CE15" t="inlineStr">
         <is>
+          <t>31.75</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
+          <t>31.6</t>
+        </is>
+      </c>
+      <c r="CG15" t="inlineStr">
+        <is>
           <t>31.65</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>31.6</t>
-        </is>
-      </c>
-      <c r="CG15" t="inlineStr">
-        <is>
-          <t>31.6</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6781,7 +6781,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6791,127 +6791,127 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>38.178</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>31.6</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-0.16</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>62.429</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>31.65</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-52.37</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-07-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-07-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-07-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>32.95</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>32.25</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>32.9</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>32.75</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>-2.02</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
         <is>
           <t>-0.16</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-55.87</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-07-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-07-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-07-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>32.95</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>32.25</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>32.9</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>32.75</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>-1.86</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>6.14</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>0.00</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -6922,12 +6922,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -6941,40 +6941,40 @@
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>-0.19</v>
+        <v>-0.32</v>
       </c>
       <c r="AI16" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>31.71</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>31.73</v>
+        <v>31.72</v>
       </c>
       <c r="AN16" t="n">
-        <v>31.91</v>
+        <v>31.9</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>32.09</t>
+          <t>32.07</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AQ16" t="n">
@@ -7000,43 +7000,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>17201065.77715092</t>
+          <t>17180899.14507042</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>1974440.0</t>
+          <t>1206947.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>1776964.4</v>
+        <v>1859988.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>4026265.2</t>
+          <t>3905420.3</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>3507431</v>
+        <v>3496627.64</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-2249300</t>
+          <t>-2045431</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-19655.81204074608</t>
+          <t>-88135.42649021233</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-389898.0494343466</t>
+          <t>-464773.3059622766</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>1974440.0</t>
+          <t>1206947.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>6320</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7166,14 +7166,14 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
+          <t>31.6</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
           <t>31.65</t>
         </is>
       </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>31.7</t>
-        </is>
-      </c>
       <c r="CF16" t="inlineStr">
         <is>
           <t>31.6</t>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>47.057</t>
+          <t>62.429</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-59.15</t>
+          <t>-55.87</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -7344,12 +7344,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7359,44 +7359,44 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>-0.22</v>
+        <v>-0.19</v>
       </c>
       <c r="AI17" t="n">
         <v>-0.06</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
+          <t>-0.56</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
           <t>-0.57</t>
         </is>
       </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>-0.58</t>
-        </is>
-      </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>31.72</t>
+          <t>31.71</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>31.74</v>
+        <v>31.73</v>
       </c>
       <c r="AN17" t="n">
-        <v>31.92</v>
+        <v>31.91</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>32.11</t>
+          <t>32.09</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AQ17" t="n">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-117.80</t>
+          <t>-117.46</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7422,43 +7422,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>17201065.77715092</t>
+          <t>17180899.14507042</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>1489349.0</t>
+          <t>1974440.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>1654352.2</v>
+        <v>1776964.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>4049659.7</t>
+          <t>4026265.2</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>3553193.6</v>
+        <v>3507431</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-2395307</t>
+          <t>-2249300</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>47660.95839445402</t>
+          <t>-19655.81204074608</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-351239.8597717918</t>
+          <t>-389898.0494343466</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>1489349.0</t>
+          <t>1974440.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7538,7 +7538,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7548,7 +7548,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7563,12 +7563,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>6320</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7588,7 +7588,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>43.184</t>
+          <t>47.057</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-56.01</t>
+          <t>-59.15</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7745,17 +7745,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7766,12 +7766,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7781,51 +7781,51 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH18" t="n">
         <v>-0.22</v>
       </c>
       <c r="AI18" t="n">
-        <v>-0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
+          <t>-0.57</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
           <t>-0.58</t>
         </is>
       </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>-0.59</t>
-        </is>
-      </c>
       <c r="AL18" t="inlineStr">
         <is>
           <t>31.72</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>31.75</v>
+        <v>31.74</v>
       </c>
       <c r="AN18" t="n">
-        <v>31.93</v>
+        <v>31.92</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>32.12</t>
+          <t>32.11</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AQ18" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="AR18" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-118.40</t>
+          <t>-117.80</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7844,43 +7844,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>17201065.77715092</t>
+          <t>17180899.14507042</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>1372173.0</t>
+          <t>1489349.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>1793886.4</v>
+        <v>1654352.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>4077563.1</t>
+          <t>4049659.7</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>3603986.82</v>
+        <v>3553193.6</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-2283676</t>
+          <t>-2395307</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>120188.379879226</t>
+          <t>47660.95839445402</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-231495.5581191494</t>
+          <t>-351239.8597717918</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>1372173.0</t>
+          <t>1489349.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -7945,7 +7945,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>6320</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8010,17 +8010,17 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8047,7 +8047,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>102.584</t>
+          <t>43.184</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8082,102 +8082,102 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
+          <t>-0.32</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-56.01</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-07-31 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-07-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-07-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>32.95</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>32.25</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>32.9</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>32.75</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>-1.86</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
           <t>-1.11</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>54.12</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2025-07-31 00:00:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2025-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2025-07-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2025-07-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>32.95</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>32.25</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>32.9</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>32.75</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>-0.93</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10.09</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>1.11</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8188,29 +8188,29 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>0.6</v>
+        <v>-0.22</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -8219,28 +8219,28 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>31.72</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>31.76</v>
+        <v>31.75</v>
       </c>
       <c r="AN19" t="n">
-        <v>31.94</v>
+        <v>31.93</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>32.14</t>
+          <t>32.12</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>21.96</t>
         </is>
       </c>
       <c r="AQ19" t="n">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-119.41</t>
+          <t>-118.40</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8266,43 +8266,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>17201065.77715092</t>
+          <t>17180899.14507042</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>3257034.0</t>
+          <t>1372173.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>6470020.8</v>
+        <v>1793886.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>4197949.2</t>
+          <t>4077563.1</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>3664581.38</v>
+        <v>3603986.82</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>2272071</t>
+          <t>-2283676</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>184130.9140607488</t>
+          <t>120188.379879226</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-39610.00011111982</t>
+          <t>-231495.5581191494</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>3257034.0</t>
+          <t>1372173.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8367,22 +8367,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8407,12 +8407,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>6320</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8432,22 +8432,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>31.95</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8469,7 +8469,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8479,12 +8479,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>25.016</t>
+          <t>102.584</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>41.53</t>
+          <t>54.12</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8589,17 +8589,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8610,67 +8610,67 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>-0.22</v>
+        <v>0.6</v>
       </c>
       <c r="AI20" t="n">
-        <v>-0.09</v>
+        <v>0.02</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>31.72</t>
+          <t>31.76</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>31.75</v>
+        <v>31.76</v>
       </c>
       <c r="AN20" t="n">
         <v>31.94</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>32.15</t>
+          <t>32.14</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>9.72</t>
+          <t>34.08</t>
         </is>
       </c>
       <c r="AQ20" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR20" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="AR20" t="n">
-        <v>-0.08</v>
-      </c>
       <c r="AS20" t="inlineStr">
         <is>
           <t>0.36</t>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-121.06</t>
+          <t>-119.41</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8688,43 +8688,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>17201065.77715092</t>
+          <t>17180899.14507042</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>791826.0</t>
+          <t>3257034.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>5950852</v>
+        <v>6470020.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>4204740.0</t>
+          <t>4197949.2</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>3699795.4</v>
+        <v>3664581.38</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>1746112</t>
+          <t>2272071</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>224811.0802738158</t>
+          <t>184130.9140607488</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>33977.47561860597</t>
+          <t>-39610.00011111982</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>791826.0</t>
+          <t>3257034.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8789,22 +8789,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8829,12 +8829,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>6320</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
@@ -8869,7 +8869,7 @@
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.95</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -8891,7 +8891,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -8901,12 +8901,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>43.045</t>
+          <t>25.016</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>37.49</t>
+          <t>41.53</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9011,17 +9011,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9032,59 +9032,59 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH21" t="n">
         <v>-0.22</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>31.77</t>
+          <t>31.72</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>31.76</v>
+        <v>31.75</v>
       </c>
       <c r="AN21" t="n">
-        <v>31.95</v>
+        <v>31.94</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>32.17</t>
+          <t>32.15</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>15.29</t>
+          <t>9.72</t>
         </is>
       </c>
       <c r="AQ21" t="n">
@@ -9100,7 +9100,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-121.57</t>
+          <t>-121.06</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9110,43 +9110,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>17201065.77715092</t>
+          <t>17180899.14507042</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>1361379.0</t>
+          <t>791826.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>6275566</v>
+        <v>5950852</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>4564351.1</t>
+          <t>4204740.0</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>3728872.56</v>
+        <v>3699795.4</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>1711214</t>
+          <t>1746112</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>259508.0993020358</t>
+          <t>224811.0802738158</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>402018.3882461209</t>
+          <t>33977.47561860597</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>1361379.0</t>
+          <t>791826.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9226,7 +9226,7 @@
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>6320</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9276,22 +9276,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>31.75</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>69.172</t>
+          <t>43.045</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9358,7 +9358,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>37.49</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9433,17 +9433,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>6.80</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9454,59 +9454,59 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>-0.41</v>
+        <v>-0.22</v>
       </c>
       <c r="AI22" t="n">
         <v>0.02</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>31.78</t>
+          <t>31.77</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>31.77</v>
+        <v>31.76</v>
       </c>
       <c r="AN22" t="n">
         <v>31.95</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>32.18</t>
+          <t>32.17</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>17.55</t>
+          <t>15.29</t>
         </is>
       </c>
       <c r="AQ22" t="n">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-122.40</t>
+          <t>-121.57</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9532,43 +9532,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>17201065.77715092</t>
+          <t>17180899.14507042</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>2187020.0</t>
+          <t>1361379.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>6444967.2</v>
+        <v>6275566</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>4961855.9</t>
+          <t>4564351.1</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>3776413.54</v>
+        <v>3728872.56</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>1483111</t>
+          <t>1711214</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>233597.1376758385</t>
+          <t>259508.0993020358</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>852409.7852766393</t>
+          <t>402018.3882461209</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>2187020.0</t>
+          <t>1361379.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>-3.21</t>
+          <t>-3.06</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9658,7 +9658,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>6320</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9698,12 +9698,12 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>31.75</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9735,7 +9735,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>796.047</t>
+          <t>69.172</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9770,7 +9770,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>29.89</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -9855,17 +9855,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>78.27</t>
+          <t>6.80</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -9876,66 +9876,66 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>61</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>80.95</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>0.22</v>
+        <v>-0.41</v>
       </c>
       <c r="AI23" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>31.77999999999999</t>
+          <t>31.78</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>31.79</v>
+        <v>31.77</v>
       </c>
       <c r="AN23" t="n">
-        <v>31.97</v>
+        <v>31.95</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.18</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>27.11</t>
+          <t>17.55</t>
         </is>
       </c>
       <c r="AQ23" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AR23" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-123.38</t>
+          <t>-122.40</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -9954,43 +9954,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>17201065.77715092</t>
+          <t>17180899.14507042</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>24752845.0</t>
+          <t>2187020.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>6361239.8</v>
+        <v>6444967.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>5173323.2</t>
+          <t>4961855.9</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>3811369.74</v>
+        <v>3776413.54</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>1187916</t>
+          <t>1483111</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>121085.7472029657</t>
+          <t>233597.1376758385</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>1376921.324417498</t>
+          <t>852409.7852766393</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>24752845.0</t>
+          <t>2187020.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-2.60</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10055,7 +10055,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10065,12 +10065,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>6320</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10120,22 +10120,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10157,7 +10157,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10167,12 +10167,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>444.139</t>
+          <t>388.233</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10202,7 +10202,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-20.76</t>
+          <t>-16.65</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10277,12 +10277,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -10298,12 +10298,12 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>388</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -10313,51 +10313,51 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>15.69</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>-0.65</v>
+        <v>-0.26</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.29</v>
+        <v>-0.04</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
+          <t>30.68</t>
+        </is>
+      </c>
+      <c r="AM24" t="n">
+        <v>30.69</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>31.12</v>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
           <t>30.8</t>
         </is>
       </c>
-      <c r="AM24" t="n">
-        <v>30.71</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>30.8</t>
-        </is>
-      </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>-9.89</t>
         </is>
       </c>
       <c r="AQ24" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AR24" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-107.28</t>
+          <t>-107.47</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -10376,43 +10376,43 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>38496711.36600846</t>
+          <t>38467543.57816902</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>13567686.0</t>
+          <t>11858388.0</t>
         </is>
       </c>
       <c r="AX24" t="n">
-        <v>9333539.6</v>
+        <v>10043358.2</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>11778874.3</t>
+          <t>12049112.9</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>21917155.88</v>
+        <v>21792965.04</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>-2445334</t>
+          <t>-2005754</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>-1152687.124241508</t>
+          <t>-1096825.321791285</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-955677.8430660889</t>
+          <t>-789585.4083150551</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>13567686.0</t>
+          <t>11858388.0</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -10477,12 +10477,12 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS24" t="inlineStr">
@@ -10517,7 +10517,7 @@
       </c>
       <c r="BY24" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="BZ24" t="inlineStr">
@@ -10542,17 +10542,17 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
@@ -10589,12 +10589,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>244.302</t>
+          <t>444.139</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -10624,7 +10624,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-21.68</t>
+          <t>-20.76</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.70</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -10699,17 +10699,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -10720,47 +10720,47 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>388</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.76</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>27.45</t>
+          <t>15.69</t>
         </is>
       </c>
       <c r="AH25" t="n">
-        <v>-1.39</v>
+        <v>-0.65</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.68</v>
+        <v>0.29</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>30.93</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>30.72</v>
+        <v>30.71</v>
       </c>
       <c r="AN25" t="n">
         <v>31.1</v>
@@ -10772,14 +10772,14 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>30.01</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AQ25" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="AR25" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>-107.38</t>
+          <t>-107.28</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -10798,43 +10798,43 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>38496711.36600846</t>
+          <t>38467543.57816902</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>7478041.0</t>
+          <t>13567686.0</t>
         </is>
       </c>
       <c r="AX25" t="n">
-        <v>8886908</v>
+        <v>9333539.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>11347339.1</t>
+          <t>11778874.3</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>21815498.3</v>
+        <v>21917155.88</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>-2460431</t>
+          <t>-2445334</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>-1188506.99354613</t>
+          <t>-1152687.124241508</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-1341960.469743779</t>
+          <t>-955677.8430660889</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>7478041.0</t>
+          <t>13567686.0</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>-10.16</t>
+          <t>-9.87</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
@@ -10899,17 +10899,17 @@
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="BT25" t="inlineStr">
@@ -10939,7 +10939,7 @@
       </c>
       <c r="BY25" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="BZ25" t="inlineStr">
@@ -10964,22 +10964,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -11011,12 +11011,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>271.22</t>
+          <t>244.302</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -11036,7 +11036,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-21.68</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -11111,7 +11111,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -11121,17 +11121,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -11142,50 +11142,50 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>388</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>27.45</t>
         </is>
       </c>
       <c r="AH26" t="n">
-        <v>-0.96</v>
+        <v>-1.39</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.22</v>
+        <v>0.68</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>30.93</t>
         </is>
       </c>
       <c r="AM26" t="n">
         <v>30.72</v>
       </c>
       <c r="AN26" t="n">
-        <v>31.09</v>
+        <v>31.1</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11194,11 +11194,11 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>78.48</t>
+          <t>30.01</t>
         </is>
       </c>
       <c r="AQ26" t="n">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="AR26" t="n">
         <v>-0.07000000000000001</v>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-107.93</t>
+          <t>-107.38</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -11220,43 +11220,43 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>38496711.36600846</t>
+          <t>38467543.57816902</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>8354658.0</t>
+          <t>7478041.0</t>
         </is>
       </c>
       <c r="AX26" t="n">
-        <v>11743619</v>
+        <v>8886908</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>11679823.5</t>
+          <t>11347339.1</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>21908787.42</v>
+        <v>21815498.3</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>63795</t>
+          <t>-2460431</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>-1160606.361510194</t>
+          <t>-1188506.99354613</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-1193403.669649629</t>
+          <t>-1341960.469743779</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>8354658.0</t>
+          <t>7478041.0</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>-9.28</t>
+          <t>-10.16</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -11331,7 +11331,7 @@
       </c>
       <c r="BS26" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT26" t="inlineStr">
@@ -11361,7 +11361,7 @@
       </c>
       <c r="BY26" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="BZ26" t="inlineStr">
@@ -11386,22 +11386,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>289.469</t>
+          <t>271.22</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-1.75</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -11543,17 +11543,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -11564,50 +11564,50 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>388</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>72.55</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>-0.74</v>
+        <v>-0.96</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>31.13</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="AM27" t="n">
         <v>30.72</v>
       </c>
       <c r="AN27" t="n">
-        <v>31.08</v>
+        <v>31.09</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -11616,14 +11616,14 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>92.54</t>
+          <t>78.48</t>
         </is>
       </c>
       <c r="AQ27" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="AR27" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-109.49</t>
+          <t>-107.93</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -11642,43 +11642,43 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>38496711.36600846</t>
+          <t>38467543.57816902</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>8958018.0</t>
+          <t>8354658.0</t>
         </is>
       </c>
       <c r="AX27" t="n">
-        <v>13694764.8</v>
+        <v>11743619</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>12617621.5</t>
+          <t>11679823.5</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>22194999.2</v>
+        <v>21908787.42</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>1077143</t>
+          <t>63795</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>-1154643.214575751</t>
+          <t>-1160606.361510194</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-1032481.359884785</t>
+          <t>-1193403.669649629</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>8958018.0</t>
+          <t>8354658.0</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>-8.98</t>
+          <t>-9.28</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -11783,7 +11783,7 @@
       </c>
       <c r="BY27" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="BZ27" t="inlineStr">
@@ -11808,22 +11808,22 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.75</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>267.229</t>
+          <t>289.469</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -11890,7 +11890,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>8.90</t>
+          <t>8.54</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-1.75</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -11965,17 +11965,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>5.11</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -11986,50 +11986,50 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>388</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>82.35</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>72.55</t>
         </is>
       </c>
       <c r="AH28" t="n">
-        <v>0.48</v>
+        <v>-0.74</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.98</v>
+        <v>1.32</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>31.13</t>
         </is>
       </c>
       <c r="AM28" t="n">
-        <v>30.75</v>
+        <v>30.72</v>
       </c>
       <c r="AN28" t="n">
-        <v>31.06</v>
+        <v>31.08</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12038,14 +12038,14 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>95.13</t>
+          <t>92.54</t>
         </is>
       </c>
       <c r="AQ28" t="n">
         <v>-0.01</v>
       </c>
       <c r="AR28" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-111.68</t>
+          <t>-109.49</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -12064,43 +12064,43 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>38496711.36600846</t>
+          <t>38467543.57816902</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>8309295.0</t>
+          <t>8958018.0</t>
         </is>
       </c>
       <c r="AX28" t="n">
-        <v>14054867.6</v>
+        <v>13694764.8</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>12906697.9</t>
+          <t>12617621.5</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>22422775.08</v>
+        <v>22194999.2</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>1148169</t>
+          <t>1077143</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>-1176854.4608832</t>
+          <t>-1154643.214575751</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-830363.725939123</t>
+          <t>-1032481.359884785</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>8309295.0</t>
+          <t>8958018.0</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>-8.10</t>
+          <t>-8.98</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="BS28" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT28" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="BY28" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="BZ28" t="inlineStr">
@@ -12235,17 +12235,17 @@
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>363.041</t>
+          <t>267.229</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -12302,7 +12302,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -12312,7 +12312,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>8.90</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -12377,7 +12377,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -12387,17 +12387,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>6.94</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -12408,50 +12408,50 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>388</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>88.24</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>96.08</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.63</v>
+        <v>0.98</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>30.96</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>30.77</v>
+        <v>30.75</v>
       </c>
       <c r="AN29" t="n">
-        <v>31.05</v>
+        <v>31.06</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12460,14 +12460,14 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>95.13</t>
         </is>
       </c>
       <c r="AQ29" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="AR29" t="n">
-        <v>-0.13</v>
+        <v>-0.1</v>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>-114.46</t>
+          <t>-111.68</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -12486,43 +12486,43 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>38496711.36600846</t>
+          <t>38467543.57816902</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>11334528.0</t>
+          <t>8309295.0</t>
         </is>
       </c>
       <c r="AX29" t="n">
-        <v>14224209</v>
+        <v>14054867.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>13015500.0</t>
+          <t>12906697.9</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>22552981.3</v>
+        <v>22422775.08</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>1208709</t>
+          <t>1148169</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>-1239852.776327577</t>
+          <t>-1176854.4608832</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>-442462.3658046369</t>
+          <t>-830363.725939123</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>11334528.0</t>
+          <t>8309295.0</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>-7.95</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -12587,7 +12587,7 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="BY29" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="BZ29" t="inlineStr">
@@ -12652,22 +12652,22 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="CE29" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CF29" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -12699,12 +12699,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>699.247</t>
+          <t>363.041</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -12724,7 +12724,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-2.45</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -12734,7 +12734,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -12809,17 +12809,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -12830,50 +12830,50 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>388</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>88.24</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>96.08</t>
         </is>
       </c>
       <c r="AH30" t="n">
-        <v>1.59</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.31</v>
+        <v>0.63</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>30.86</t>
+          <t>30.96</t>
         </is>
       </c>
       <c r="AM30" t="n">
-        <v>30.76</v>
+        <v>30.77</v>
       </c>
       <c r="AN30" t="n">
-        <v>31.02</v>
+        <v>31.05</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -12882,14 +12882,14 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AQ30" t="n">
-        <v>-0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="AR30" t="n">
-        <v>-0.15</v>
+        <v>-0.13</v>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>-117.12</t>
+          <t>-114.46</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -12908,43 +12908,43 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>38496711.36600846</t>
+          <t>38467543.57816902</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>21761596.0</t>
+          <t>11334528.0</t>
         </is>
       </c>
       <c r="AX30" t="n">
-        <v>13807770.2</v>
+        <v>14224209</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>13168431.0</t>
+          <t>13015500.0</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>22572708.9</v>
+        <v>22552981.3</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>639339</t>
+          <t>1208709</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>-1384832.850968112</t>
+          <t>-1239852.776327577</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>-196647.4454052038</t>
+          <t>-442462.3658046369</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>21761596.0</t>
+          <t>11334528.0</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>-7.66</t>
+          <t>-7.95</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -13009,12 +13009,12 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS30" t="inlineStr">
@@ -13049,7 +13049,7 @@
       </c>
       <c r="BY30" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="BZ30" t="inlineStr">
@@ -13074,22 +13074,22 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>31.1</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>31.35</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -13111,7 +13111,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13121,12 +13121,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>588.081</t>
+          <t>699.247</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13136,7 +13136,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>30.95</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-9.94</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -13221,7 +13221,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -13231,17 +13231,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11.25</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -13252,12 +13252,12 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>388</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -13267,51 +13267,51 @@
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AH31" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.59</v>
       </c>
       <c r="AI31" t="n">
-        <v>-0.17</v>
+        <v>0.31</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.86</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>30.75</v>
+        <v>30.76</v>
       </c>
       <c r="AN31" t="n">
-        <v>31</v>
+        <v>31.02</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>30.81</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AQ31" t="n">
-        <v>-0.14</v>
+        <v>-0.08</v>
       </c>
       <c r="AR31" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>-119.27</t>
+          <t>-117.12</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -13330,43 +13330,43 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>38496711.36600846</t>
+          <t>38467543.57816902</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>18110387.0</t>
+          <t>21761596.0</t>
         </is>
       </c>
       <c r="AX31" t="n">
-        <v>11616028</v>
+        <v>13807770.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>12897946.0</t>
+          <t>13168431.0</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>22309041.54</v>
+        <v>22572708.9</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>-1281918</t>
+          <t>639339</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>-1600866.561070459</t>
+          <t>-1384832.850968112</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>-955646.007498689</t>
+          <t>-196647.4454052038</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>18110387.0</t>
+          <t>21761596.0</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>-8.84</t>
+          <t>-7.66</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
@@ -13441,7 +13441,7 @@
       </c>
       <c r="BS31" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="BT31" t="inlineStr">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="BY31" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="BZ31" t="inlineStr">
@@ -13496,22 +13496,22 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>30.35</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>30.95</t>
+          <t>31.35</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>352.598</t>
+          <t>588.081</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.95</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13568,7 +13568,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -13578,7 +13578,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-12.12</t>
+          <t>-9.94</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -13643,7 +13643,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>11.25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -13674,67 +13674,67 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>388</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>80.56</t>
         </is>
       </c>
       <c r="AH32" t="n">
-        <v>-0.55</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AI32" t="n">
-        <v>-0.28</v>
+        <v>-0.17</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>30.76</v>
+        <v>30.75</v>
       </c>
       <c r="AN32" t="n">
-        <v>30.99</v>
+        <v>31</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>30.82</t>
+          <t>30.81</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>19.75</t>
         </is>
       </c>
       <c r="AQ32" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="AR32" t="n">
         <v>-0.17</v>
       </c>
-      <c r="AR32" t="n">
-        <v>-0.18</v>
-      </c>
       <c r="AS32" t="inlineStr">
         <is>
           <t>0.89</t>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>-120.23</t>
+          <t>-119.27</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -13752,43 +13752,43 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>38496711.36600846</t>
+          <t>38467543.57816902</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>10758532.0</t>
+          <t>18110387.0</t>
         </is>
       </c>
       <c r="AX32" t="n">
-        <v>11540478.2</v>
+        <v>11616028</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>13132407.8</t>
+          <t>12897946.0</t>
         </is>
       </c>
       <c r="AZ32" t="n">
-        <v>22134858.04</v>
+        <v>22309041.54</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>-1591929</t>
+          <t>-1281918</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>-1718179.388992599</t>
+          <t>-1600866.561070459</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>-1614598.488792999</t>
+          <t>-955646.007498689</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>10758532.0</t>
+          <t>18110387.0</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -13808,7 +13808,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>-10.16</t>
+          <t>-8.84</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -13853,7 +13853,7 @@
       </c>
       <c r="BQ32" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR32" t="inlineStr">
@@ -13863,7 +13863,7 @@
       </c>
       <c r="BS32" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="BT32" t="inlineStr">
@@ -13893,7 +13893,7 @@
       </c>
       <c r="BY32" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="BZ32" t="inlineStr">
@@ -13918,22 +13918,22 @@
       </c>
       <c r="CD32" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="CE32" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="CF32" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>30.35</t>
         </is>
       </c>
       <c r="CG32" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>30.95</t>
         </is>
       </c>
       <c r="CH32" t="inlineStr">
@@ -13965,42 +13965,42 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>-0.82</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>352.598</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>30.5</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>298.728</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>30.75</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>-0.49</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-12.21</t>
+          <t>-12.12</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -14075,17 +14075,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -14096,38 +14096,38 @@
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>388</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>76.67</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AH33" t="n">
-        <v>0.26</v>
+        <v>-0.55</v>
       </c>
       <c r="AI33" t="n">
-        <v>-0.43</v>
+        <v>-0.28</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>-0.59</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
@@ -14136,19 +14136,19 @@
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>30.8</v>
+        <v>30.76</v>
       </c>
       <c r="AN33" t="n">
-        <v>30.98</v>
+        <v>30.99</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>30.84</t>
+          <t>30.82</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>5.04</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="AQ33" t="n">
@@ -14164,7 +14164,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>-120.39</t>
+          <t>-120.23</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -14174,43 +14174,43 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>38496711.36600846</t>
+          <t>38467543.57816902</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>9156002.0</t>
+          <t>10758532.0</t>
         </is>
       </c>
       <c r="AX33" t="n">
-        <v>11758528.2</v>
+        <v>11540478.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>13393839.6</t>
+          <t>13132407.8</t>
         </is>
       </c>
       <c r="AZ33" t="n">
-        <v>22093985.98</v>
+        <v>22134858.04</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>-1635311</t>
+          <t>-1591929</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>-1737012.27993798</t>
+          <t>-1718179.388992599</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>-1710596.194613693</t>
+          <t>-1614598.488792999</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>9156002.0</t>
+          <t>10758532.0</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
@@ -14230,7 +14230,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-10.16</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -14275,7 +14275,7 @@
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
@@ -14315,7 +14315,7 @@
       </c>
       <c r="BY33" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="BZ33" t="inlineStr">
@@ -14345,17 +14345,17 @@
       </c>
       <c r="CE33" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="CF33" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="CG33" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -14377,7 +14377,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -14387,12 +14387,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>301.716</t>
+          <t>298.728</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14422,7 +14422,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-14.59</t>
+          <t>-12.21</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -14497,17 +14497,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>5.77</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -14518,12 +14518,12 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>388</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -14533,48 +14533,48 @@
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>72.78</t>
+          <t>76.67</t>
         </is>
       </c>
       <c r="AH34" t="n">
-        <v>0.52</v>
+        <v>0.26</v>
       </c>
       <c r="AI34" t="n">
-        <v>-0.75</v>
+        <v>-0.43</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>-0.59</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>30.59</t>
+          <t>30.67</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>30.82</v>
+        <v>30.8</v>
       </c>
       <c r="AN34" t="n">
-        <v>30.97</v>
+        <v>30.98</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>30.84</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>-5.01</t>
+          <t>5.04</t>
         </is>
       </c>
       <c r="AQ34" t="n">
-        <v>-0.19</v>
+        <v>-0.17</v>
       </c>
       <c r="AR34" t="n">
         <v>-0.18</v>
@@ -14586,7 +14586,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>-120.65</t>
+          <t>-120.39</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -14596,43 +14596,43 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>38496711.36600846</t>
+          <t>38467543.57816902</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>9252334.0</t>
+          <t>9156002.0</t>
         </is>
       </c>
       <c r="AX34" t="n">
-        <v>11806791</v>
+        <v>11758528.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>13824086.6</t>
+          <t>13393839.6</t>
         </is>
       </c>
       <c r="AZ34" t="n">
-        <v>22091752.82</v>
+        <v>22093985.98</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>-2017295</t>
+          <t>-1635311</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>-1741815.204542396</t>
+          <t>-1737012.27993798</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>-1614943.410264194</t>
+          <t>-1710596.194613693</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>9252334.0</t>
+          <t>9156002.0</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
@@ -14737,7 +14737,7 @@
       </c>
       <c r="BY34" t="inlineStr">
         <is>
-          <t>24.03</t>
+          <t>24.05</t>
         </is>
       </c>
       <c r="BZ34" t="inlineStr">
@@ -14762,17 +14762,17 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="CE34" t="inlineStr">
         <is>
-          <t>30.75</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="CF34" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="CG34" t="inlineStr">

--- a/Result/checksun_type/營養食品.xlsx
+++ b/Result/checksun_type/營養食品.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CX23"/>
+  <dimension ref="A1:CX24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,7 +958,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-9.26</t>
+          <t>-12.03</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,22 +1123,22 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2026-01-14 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1149,7 +1149,7 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1159,65 +1159,65 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>47.62</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-0.22</v>
+        <v>-0.19</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>74.35999999999999</t>
+          <t>74.34</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>74.18000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>74.39</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>74.41</t>
+          <t>74.38</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>100.71</t>
+          <t>93.80</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-102.68</t>
+          <t>-102.27</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1227,43 +1227,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>3306.922740524781</t>
+          <t>3107.892644135189</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>1703.0</t>
+          <t>1492.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>1768.6</v>
+        <v>1709</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1949.1</t>
+          <t>1942.6</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>1235.02</v>
+        <v>1251.7</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-180</t>
+          <t>-233</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>78.86162294111104</t>
+          <t>59.63766276851573</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-26.46084201350072</t>
+          <t>-46.09411818075841</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>1703.0</t>
+          <t>1492.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1393,17 +1393,17 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1445,12 +1445,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-9.26</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2026-01-14 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>8.58</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1641,7 +1641,7 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1656,14 +1656,14 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>79.17</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-0.3</v>
+        <v>-0.22</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.36</v>
+        <v>0.24</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
@@ -1672,44 +1672,44 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>74.41999999999999</t>
+          <t>74.36</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>74.16</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="BA3" t="n">
-        <v>74.36</v>
+        <v>74.39</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>74.45</t>
+          <t>74.41</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>106.40</t>
+          <t>100.71</t>
         </is>
       </c>
       <c r="BD3" t="n">
         <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-103.36</t>
+          <t>-102.80</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1719,43 +1719,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>3306.922740524781</t>
+          <t>3107.892644135189</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>1424.0</t>
+          <t>1703.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>1652.6</v>
+        <v>1768.6</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1802.0</t>
+          <t>1949.1</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>1263.36</v>
+        <v>1235.02</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-149</t>
+          <t>-180</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>98.01116202376772</t>
+          <t>78.86162294111104</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-20.07541741693626</t>
+          <t>-26.46084201350072</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>1424.0</t>
+          <t>1703.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1885,24 +1885,24 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
+          <t>73.6</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>73.6</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
           <t>74.2</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="CS3" t="inlineStr">
-        <is>
-          <t>73.5</t>
-        </is>
-      </c>
-      <c r="CT3" t="inlineStr">
-        <is>
-          <t>74.2</t>
-        </is>
-      </c>
       <c r="CU3" t="inlineStr">
         <is>
           <t>34.3</t>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1937,192 +1937,192 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-8.29</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-03-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-02-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-02-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>85.4</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>82.4</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-13.11</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025/09/12</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026/01/06</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>74.7</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>2026-01-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>7.09</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
           <t>-0.13</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>74.5</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-13.36</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-03-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-02-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-02-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>82.3</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>85.4</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>82.4</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>79.7</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-12.76</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3.26</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025/09/12</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2026/01/06</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2025/12/15</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>74.7</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>2026-01-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>2026-01-28</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>6.72</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>-2.41</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2133,7 +2133,7 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -2143,65 +2143,65 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>88.43</t>
+          <t>79.17</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>0.19</v>
+        <v>-0.3</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>74.36</t>
+          <t>74.42</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>74.12</v>
+        <v>74.16</v>
       </c>
       <c r="BA4" t="n">
-        <v>74.38</v>
+        <v>74.36</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>74.49</t>
+          <t>74.45</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>110.87</t>
+          <t>106.40</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-104.25</t>
+          <t>-103.51</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2211,43 +2211,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>3306.922740524781</t>
+          <t>3107.892644135189</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>1358.0</t>
+          <t>1424.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>1619.8</v>
+        <v>1652.6</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1869.6</t>
+          <t>1802.0</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>1245.84</v>
+        <v>1263.36</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-249</t>
+          <t>-149</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>119.4814491948048</t>
+          <t>98.01116202376772</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>19.65645405733221</t>
+          <t>-20.07541741693626</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>1358.0</t>
+          <t>1424.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2377,22 +2377,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -2429,12 +2429,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>28.84</t>
+          <t>-13.36</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-12.65</t>
+          <t>-12.76</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2599,22 +2599,22 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2026-01-14 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2625,7 +2625,7 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2635,23 +2635,23 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>88.43</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>0.4</v>
+        <v>0.19</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
@@ -2661,230 +2661,230 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
+          <t>74.35999999999999</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>74.12</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>74.38</v>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>74.49</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>110.87</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>-104.44</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>2026/01/08</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>3107.892644135189</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>1358.0</t>
+        </is>
+      </c>
+      <c r="BK5" t="n">
+        <v>1619.8</v>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>1869.6</t>
+        </is>
+      </c>
+      <c r="BM5" t="n">
+        <v>1245.84</v>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>-249</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>119.4814491948048</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>19.65645405733221</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>1358.0</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>-0.93</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>綠茵</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>綠茵</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>食品工業</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>43.18290500198112</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>12.18914260633116</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>4.818590014463328</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>4.85</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>7.61</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>13.87</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
+          <t>48.81%</t>
+        </is>
+      </c>
+      <c r="CK5" t="inlineStr">
+        <is>
+          <t>17.38%</t>
+        </is>
+      </c>
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>27.96</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
+          <t>保健食品配方65.97%、保健食品原料33.59%、其他0.43% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO5" t="inlineStr">
+        <is>
+          <t>綠茵-食品工業-上櫃</t>
+        </is>
+      </c>
+      <c r="CP5" t="inlineStr">
+        <is>
+          <t>食品工業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CQ5" t="inlineStr">
+        <is>
           <t>74.3</t>
         </is>
       </c>
-      <c r="AZ5" t="n">
-        <v>74.09</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>74.41</v>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>74.52</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>82.76</t>
-        </is>
-      </c>
-      <c r="BD5" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-105.43</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>2026/01/08</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>3306.922740524781</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>2568.0</t>
-        </is>
-      </c>
-      <c r="BK5" t="n">
-        <v>2424.6</v>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>1881.9</t>
-        </is>
-      </c>
-      <c r="BM5" t="n">
-        <v>1233.16</v>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>542</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>137.6314483107089</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>82.78568280423974</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>2568.0</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>75.2</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>2025/12/04</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>-0.80</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>綠茵</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>綠茵</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>食品工業</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>43.18290500198112</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>12.18914260633116</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>4.818590014463328</t>
-        </is>
-      </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>4.85</t>
-        </is>
-      </c>
-      <c r="CH5" t="inlineStr">
-        <is>
-          <t>7.61</t>
-        </is>
-      </c>
-      <c r="CI5" t="inlineStr">
-        <is>
-          <t>13.87</t>
-        </is>
-      </c>
-      <c r="CJ5" t="inlineStr">
-        <is>
-          <t>48.81%</t>
-        </is>
-      </c>
-      <c r="CK5" t="inlineStr">
-        <is>
-          <t>17.38%</t>
-        </is>
-      </c>
-      <c r="CL5" t="inlineStr">
-        <is>
-          <t>27.96</t>
-        </is>
-      </c>
-      <c r="CM5" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="CN5" t="inlineStr">
-        <is>
-          <t>保健食品配方65.97%、保健食品原料33.59%、其他0.43% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO5" t="inlineStr">
-        <is>
-          <t>綠茵-食品工業-上櫃</t>
-        </is>
-      </c>
-      <c r="CP5" t="inlineStr">
-        <is>
-          <t>食品工業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CQ5" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -2921,12 +2921,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>28.84</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-13.00</t>
+          <t>-12.65</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3091,22 +3091,22 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2026-01-14 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3117,7 +3117,7 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -3127,65 +3127,65 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>69.26</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.13</v>
+        <v>0.29</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>74.14000000000001</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>74.04000000000001</v>
+        <v>74.09</v>
       </c>
       <c r="BA6" t="n">
-        <v>74.47</v>
+        <v>74.41</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>74.55</t>
+          <t>74.52</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>82.76</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-106.55</t>
+          <t>-105.67</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3195,43 +3195,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>3306.922740524781</t>
+          <t>3107.892644135189</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>1790.0</t>
+          <t>2568.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>2176.2</v>
+        <v>2424.6</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1990.3</t>
+          <t>1881.9</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>1194.16</v>
+        <v>1233.16</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>542</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>147.6034056755215</t>
+          <t>137.6314483107089</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>40.37080662824201</t>
+          <t>82.78568280423974</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>1790.0</t>
+          <t>2568.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -3413,12 +3413,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>12.70</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-12.76</t>
+          <t>-13.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3583,22 +3583,22 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2026-01-14 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3609,7 +3609,7 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3619,65 +3619,65 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>69.26</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>0.59</v>
+        <v>0.22</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>74.06</t>
+          <t>74.14</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>74</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="BA7" t="n">
-        <v>74.53</v>
+        <v>74.47</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>74.58</t>
+          <t>74.55</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-107.37</t>
+          <t>-106.84</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3687,43 +3687,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>3306.922740524781</t>
+          <t>3107.892644135189</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>1123.0</t>
+          <t>1790.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>2129.6</v>
+        <v>2176.2</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1889.7</t>
+          <t>1990.3</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>1175.68</v>
+        <v>1194.16</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>185</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>167.100241865936</t>
+          <t>147.6034056755215</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>61.69345471152246</t>
+          <t>40.37080662824201</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>1123.0</t>
+          <t>1790.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3788,12 +3788,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3853,24 +3853,24 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
+          <t>74.9</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>74.9</t>
+        </is>
+      </c>
+      <c r="CS7" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="CT7" t="inlineStr">
+        <is>
           <t>74.3</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
-        <is>
-          <t>74.5</t>
-        </is>
-      </c>
-      <c r="CS7" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="CT7" t="inlineStr">
-        <is>
-          <t>74.5</t>
-        </is>
-      </c>
       <c r="CU7" t="inlineStr">
         <is>
           <t>34.3</t>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -3905,34 +3905,34 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>0.81</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
           <t>-0.4</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>17.0</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>73.9</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>12.70</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-13.47</t>
+          <t>-12.76</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4075,22 +4075,22 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2026-01-14 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4101,7 +4101,7 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -4111,65 +4111,65 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>31.79</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-0.14</v>
+        <v>0.59</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>74.00000000000001</t>
+          <t>74.06</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>73.97</v>
+        <v>74</v>
       </c>
       <c r="BA8" t="n">
-        <v>74.59999999999999</v>
+        <v>74.53</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>74.62</t>
+          <t>74.58</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>11.57</t>
+          <t>38.85</t>
         </is>
       </c>
       <c r="BD8" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="BE8" t="n">
         <v>-0.13</v>
       </c>
-      <c r="BE8" t="n">
-        <v>-0.14</v>
-      </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-108.08</t>
+          <t>-107.70</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4179,43 +4179,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>3306.922740524781</t>
+          <t>3107.892644135189</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>1260.0</t>
+          <t>1123.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>1951.4</v>
+        <v>2129.6</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1837.0</t>
+          <t>1889.7</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>1193.06</v>
+        <v>1175.68</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>239</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>186.2651122576475</t>
+          <t>167.100241865936</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>161.4153285907973</t>
+          <t>61.69345471152246</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>1260.0</t>
+          <t>1123.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -4345,22 +4345,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4380,14 +4380,14 @@
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4422,17 +4422,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-22.77</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>-13.47</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4567,22 +4567,22 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2026-01-14 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>27.24</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4593,7 +4593,7 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4603,65 +4603,65 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>31.79</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>0.35</v>
+        <v>-0.14</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>73.94</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
         <v>73.97</v>
       </c>
       <c r="BA9" t="n">
-        <v>74.64</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>74.66</t>
+          <t>74.62</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="BD9" t="n">
         <v>-0.13</v>
       </c>
       <c r="BE9" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-108.32</t>
+          <t>-108.44</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4671,43 +4671,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>3306.922740524781</t>
+          <t>3107.892644135189</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>5382.0</t>
+          <t>1260.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>2119.4</v>
+        <v>1951.4</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>2744.4</t>
+          <t>1837.0</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>1180.18</v>
+        <v>1193.06</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-625</t>
+          <t>114</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>190.7832547425293</t>
+          <t>186.2651122576475</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>283.4317438258045</t>
+          <t>161.4153285907973</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>5382.0</t>
+          <t>1260.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4727,7 +4727,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4772,17 +4772,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4837,22 +4837,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -4889,12 +4889,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4904,139 +4904,139 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-22.77</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-03-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-02-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-02-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>85.4</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>82.4</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>-13.11</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025/09/12</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026/01/06</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
           <t>73.8</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-41.29</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-50.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-03-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-02-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-02-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>82.3</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>85.4</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>82.4</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>79.7</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>-13.58</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>3.26</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025/09/12</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2026/01/06</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
         <is>
           <t>73.8</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
           <t>2025/12/15</t>
@@ -5059,22 +5059,22 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2026-01-14 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>27.24</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5085,7 +5085,7 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -5095,65 +5095,65 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-0.08</v>
+        <v>0.35</v>
       </c>
       <c r="AV10" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>-0.89</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>73.94000000000001</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>73.97</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>74.64</v>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>74.66</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>15.76</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
         <v>-0.13</v>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>-0.93</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>73.86</t>
-        </is>
-      </c>
-      <c r="AZ10" t="n">
-        <v>73.95999999999999</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>74.65000000000001</v>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>74.69</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>2.49</t>
-        </is>
-      </c>
-      <c r="BD10" t="n">
-        <v>-0.15</v>
       </c>
       <c r="BE10" t="n">
         <v>-0.15</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-108.64</t>
+          <t>-108.69</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5163,43 +5163,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>3306.922740524781</t>
+          <t>3107.892644135189</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>1326.0</t>
+          <t>5382.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>1339.2</v>
+        <v>2119.4</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>2281.2</t>
+          <t>2744.4</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>1121.24</v>
+        <v>1180.18</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-941</t>
+          <t>-625</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>173.9380749092066</t>
+          <t>190.7832547425293</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>5.975489024892795</t>
+          <t>283.4317438258045</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>1326.0</t>
+          <t>5382.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -5329,24 +5329,24 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>74.7</t>
+        </is>
+      </c>
+      <c r="CS10" t="inlineStr">
+        <is>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="CT10" t="inlineStr">
+        <is>
           <t>74.2</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
-        <is>
-          <t>74.5</t>
-        </is>
-      </c>
-      <c r="CS10" t="inlineStr">
-        <is>
-          <t>73.4</t>
-        </is>
-      </c>
-      <c r="CT10" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
       <c r="CU10" t="inlineStr">
         <is>
           <t>34.3</t>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="CX10" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -5381,12 +5381,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-26.57</t>
+          <t>-41.29</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-13.47</t>
+          <t>-13.58</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5551,22 +5551,22 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2026-01-14 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5577,7 +5577,7 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -5587,65 +5587,65 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0.11</v>
+        <v>-0.13</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>73.98</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="BA11" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>74.73</t>
+          <t>74.69</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>-0.14</v>
+        <v>-0.15</v>
       </c>
       <c r="BE11" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-108.70</t>
+          <t>-109.03</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5655,43 +5655,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>3306.922740524781</t>
+          <t>3107.892644135189</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>1557.0</t>
+          <t>1326.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>1804.4</v>
+        <v>1339.2</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>2457.4</t>
+          <t>2281.2</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>1110.78</v>
+        <v>1121.24</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-653</t>
+          <t>-941</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>204.4767268881727</t>
+          <t>173.9380749092066</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>43.96742898698722</t>
+          <t>5.975489024892795</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>1557.0</t>
+          <t>1326.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5821,22 +5821,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5856,14 +5856,14 @@
       </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5898,17 +5898,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-30.34</t>
+          <t>-26.57</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-50.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>-13.47</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -6043,22 +6043,22 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2026-01-14 00:00:00</t>
+          <t>2026-01-12 00:00:00</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6069,7 +6069,7 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
@@ -6079,49 +6079,49 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.05</v>
+        <v>-0.11</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>74.03999999999999</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>74</v>
+        <v>73.98</v>
       </c>
       <c r="BA12" t="n">
-        <v>74.61</v>
+        <v>74.64</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>74.78</t>
+          <t>74.73</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>15.14</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="BD12" t="n">
@@ -6132,12 +6132,12 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-108.91</t>
+          <t>-109.09</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6147,43 +6147,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>3306.922740524781</t>
+          <t>3107.892644135189</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>232.0</t>
+          <t>1557.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>1649.8</v>
+        <v>1804.4</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>2368.5</t>
+          <t>2457.4</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>1085.44</v>
+        <v>1110.78</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-718</t>
+          <t>-653</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>233.6602355974792</t>
+          <t>204.4767268881727</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>71.92136361187272</t>
+          <t>43.96742898698722</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>232.0</t>
+          <t>1557.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6313,22 +6313,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6348,29 +6348,29 @@
       </c>
       <c r="CX12" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>929.211</t>
+          <t>81.467</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6380,7 +6380,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6415,32 +6415,32 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-04 00:00:00</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-20 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-28 00:00:00</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -6450,12 +6450,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -6465,22 +6465,22 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025/05/15</t>
+          <t>2025/02/21</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -6495,62 +6495,62 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2025/11/21</t>
+          <t>2025/08/28</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2025/06/10</t>
+          <t>2025/04/08</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>2025/12/26</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>2025/12/11</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-08-20 00:00:00</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6561,121 +6561,121 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-0.99</v>
+        <v>-0.44</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0.64</v>
+        <v>0.14</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>31.64</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>29.48</v>
+        <v>31.6</v>
       </c>
       <c r="BA13" t="n">
-        <v>30.18</v>
+        <v>31.72</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-0.3</v>
+        <v>-0.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>-0.31</v>
+        <v>-0.04</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-161.19</t>
+          <t>-114.07</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026/01/27</t>
+          <t>2025/12/19</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>29874713.26956522</t>
+          <t>11320400.26082474</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>26982927.0</t>
+          <t>2568418.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>25171849.8</v>
+        <v>3289054.2</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>26932073.1</t>
+          <t>3137217.9</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>17257437.18</v>
+        <v>3324051.1</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-1760223</t>
+          <t>151836</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>1270533.270786996</t>
+          <t>-3853.900231664111</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>629678.9128112085</t>
+          <t>32790.85744653689</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>26982927.0</t>
+          <t>2568418.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6685,27 +6685,27 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2025/10/15</t>
+          <t>2025/05/19</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>-14.58</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>臺鹽</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>臺鹽</t>
         </is>
       </c>
       <c r="BX13" t="inlineStr">
@@ -6720,27 +6720,27 @@
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
         <is>
-          <t>6.237608785148733</t>
+          <t>11.30964198266164</t>
         </is>
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>-17.09267911306208</t>
+          <t>7.950770160072485</t>
         </is>
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>-3.78772922691385</t>
+          <t>2.099499961706554</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6750,52 +6750,52 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
         <is>
-          <t>23.06%</t>
+          <t>39.76%</t>
         </is>
       </c>
       <c r="CK13" t="inlineStr">
         <is>
-          <t>4.46%</t>
+          <t>11.78%</t>
         </is>
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.33</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>26538</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
         <is>
-          <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
+          <t>鹽46.50%、包裝飲用水34.02%、清潔用品5.33%、保健食品5.08%、美容保養品4.12%、工程及勞務2.55%、其他2.39% (2024年)</t>
         </is>
       </c>
       <c r="CO13" t="inlineStr">
         <is>
-          <t>佳格-食品工業-上市</t>
+          <t>臺鹽-食品工業-上市</t>
         </is>
       </c>
       <c r="CP13" t="inlineStr">
@@ -6805,32 +6805,32 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>33.23</t>
         </is>
       </c>
       <c r="CV13" t="inlineStr">
         <is>
-          <t>** 食品 - 營養食品</t>
+          <t>** 食品 - 原物料、營養食品** 石化及塑橡膠 - 化妝品</t>
         </is>
       </c>
       <c r="CW13" t="inlineStr">
@@ -6840,14 +6840,14 @@
       </c>
       <c r="CX13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6857,12 +6857,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>805.179</t>
+          <t>1270.894</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-16.58</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6902,37 +6902,37 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-06-21 00:00:00</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-06-27 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-07 00:00:00</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-30 00:00:00</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-32.39</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -7007,42 +7007,42 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
+          <t>2026/02/02</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
           <t>2025/12/26</t>
         </is>
       </c>
-      <c r="AH14" t="inlineStr">
+      <c r="AJ14" t="inlineStr">
         <is>
           <t>30.45</t>
         </is>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>30.6</t>
-        </is>
-      </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-10-13 00:00:00</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>15.40</t>
+          <t>24.30</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -7053,75 +7053,75 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>64.02</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>-0.41</v>
+        <v>-1.37</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0.73</v>
+        <v>-0.74</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>29.32</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>29.54</v>
+        <v>29.42</v>
       </c>
       <c r="BA14" t="n">
-        <v>30.2</v>
+        <v>30.15</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>30.66</t>
+          <t>30.63</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>7.54</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-0.28</v>
+        <v>-0.32</v>
       </c>
       <c r="BE14" t="n">
         <v>-0.31</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-161.65</t>
+          <t>-134.70</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7131,43 +7131,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>29874713.26956522</t>
+          <t>35228493.26086956</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>23562195.0</t>
+          <t>36466880.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>22744223.8</v>
+        <v>29210335</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>27263981.0</t>
+          <t>27464981.4</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>16975055.4</v>
+        <v>17798828.46</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>-4519757</t>
+          <t>1745353</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>1387052.244964412</t>
+          <t>1287431.499790564</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>550909.8494979739</t>
+          <t>1380371.75931019</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>23562195.0</t>
+          <t>36466880.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7187,7 +7187,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>-13.99</t>
+          <t>-15.17</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -7242,12 +7242,12 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7257,7 +7257,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.73</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.33</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>26538</t>
+          <t>26355</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7297,22 +7297,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="CX14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -7349,42 +7349,42 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>-0.68</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>929.211</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>29.0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-0.69</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>750.554</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>-1.72</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-15.05</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7394,37 +7394,37 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-06-21 00:00:00</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-06-27 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-07 00:00:00</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-30 00:00:00</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -7434,12 +7434,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-31.92</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7499,42 +7499,42 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
+          <t>2026/02/02</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
           <t>2025/12/26</t>
         </is>
       </c>
-      <c r="AH15" t="inlineStr">
+      <c r="AJ15" t="inlineStr">
         <is>
           <t>30.45</t>
         </is>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>30.6</t>
-        </is>
-      </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-10-13 00:00:00</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7545,75 +7545,75 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>65.93</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>0.65</v>
+        <v>-0.99</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0.93</v>
+        <v>-0.64</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>29.58</v>
+        <v>29.48</v>
       </c>
       <c r="BA15" t="n">
-        <v>30.22</v>
+        <v>30.18</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>8.86</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="BE15" t="n">
         <v>-0.31</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-162.81</t>
+          <t>-134.41</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7623,43 +7623,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>29874713.26956522</t>
+          <t>35228493.26086956</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>22088096.0</t>
+          <t>26982927.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>22675815.4</v>
+        <v>25171849.8</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>26693420.2</t>
+          <t>26932073.1</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>16884946.42</v>
+        <v>17257437.18</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-4017604</t>
+          <t>-1760223</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>1539078.135049219</t>
+          <t>1270533.270786996</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>785214.264425572</t>
+          <t>629678.9128112085</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>22088096.0</t>
+          <t>26982927.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>-14.58</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7724,22 +7724,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7749,7 +7749,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.73</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.33</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>26538</t>
+          <t>26355</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7789,22 +7789,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="CX15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -7841,12 +7841,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1249.819</t>
+          <t>805.179</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-16.58</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7886,37 +7886,37 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-06-21 00:00:00</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-06-27 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-07 00:00:00</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-30 00:00:00</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -7926,12 +7926,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -7941,12 +7941,12 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-31.46</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7991,42 +7991,42 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
+          <t>2026/02/02</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
           <t>2025/12/26</t>
         </is>
       </c>
-      <c r="AH16" t="inlineStr">
+      <c r="AJ16" t="inlineStr">
         <is>
           <t>30.45</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>30.6</t>
-        </is>
-      </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-10-13 00:00:00</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>23.90</t>
+          <t>15.40</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -8037,75 +8037,75 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>32.59</t>
+          <t>64.02</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>0.89</v>
+        <v>-0.41</v>
       </c>
       <c r="AV16" t="n">
-        <v>-1.3</v>
+        <v>-0.73</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>29.32</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>29.62</v>
+        <v>29.54</v>
       </c>
       <c r="BA16" t="n">
-        <v>30.24</v>
+        <v>30.2</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>30.66</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="BD16" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="BE16" t="n">
         <v>-0.31</v>
       </c>
-      <c r="BE16" t="n">
-        <v>-0.32</v>
-      </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-164.20</t>
+          <t>-134.67</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8115,43 +8115,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>29874713.26956522</t>
+          <t>35228493.26086956</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>36951577.0</t>
+          <t>23562195.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>25211363.2</v>
+        <v>22744223.8</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>26502871.8</t>
+          <t>27263981.0</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>16852284.6</v>
+        <v>16975055.4</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-1291508</t>
+          <t>-4519757</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>1676144.293344427</t>
+          <t>1387052.244964412</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>1249830.669164084</t>
+          <t>550909.8494979739</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>36951577.0</t>
+          <t>23562195.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>-13.99</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.73</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.33</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>26538</t>
+          <t>26355</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8281,22 +8281,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8316,14 +8316,14 @@
       </c>
       <c r="CX16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -8333,12 +8333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>556.2</t>
+          <t>750.554</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-15.05</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8378,37 +8378,37 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-06-21 00:00:00</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-06-27 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-07 00:00:00</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-30 00:00:00</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -8418,12 +8418,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -8433,12 +8433,12 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-30.75</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8483,37 +8483,37 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
+          <t>2026/02/02</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
           <t>2025/12/26</t>
         </is>
       </c>
-      <c r="AH17" t="inlineStr">
+      <c r="AJ17" t="inlineStr">
         <is>
           <t>30.45</t>
         </is>
       </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>30.6</t>
-        </is>
-      </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-10-13 00:00:00</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
@@ -8529,75 +8529,75 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>65.93</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>0.17</v>
+        <v>0.65</v>
       </c>
       <c r="AV17" t="n">
-        <v>-1.61</v>
+        <v>-0.93</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>29.68</v>
+        <v>29.58</v>
       </c>
       <c r="BA17" t="n">
-        <v>30.27</v>
+        <v>30.22</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>30.67</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-7.01</t>
+          <t>8.86</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-0.35</v>
+        <v>-0.29</v>
       </c>
       <c r="BE17" t="n">
-        <v>-0.32</v>
+        <v>-0.31</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-164.54</t>
+          <t>-135.33</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8607,43 +8607,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>29874713.26956522</t>
+          <t>35228493.26086956</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>16274454.0</t>
+          <t>22088096.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>25719627.8</v>
+        <v>22675815.4</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>25467490.4</t>
+          <t>26693420.2</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>16380710.06</v>
+        <v>16884946.42</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>252137</t>
+          <t>-4017604</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>1753655.861377217</t>
+          <t>1539078.135049219</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>276415.7591775246</t>
+          <t>785214.264425572</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>16274454.0</t>
+          <t>22088096.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>-13.84</t>
+          <t>-13.11</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8708,22 +8708,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.73</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.33</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>26538</t>
+          <t>26355</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8773,22 +8773,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
+          <t>29.6</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>29.65</t>
+        </is>
+      </c>
+      <c r="CS17" t="inlineStr">
+        <is>
           <t>29.3</t>
         </is>
       </c>
-      <c r="CR17" t="inlineStr">
-        <is>
-          <t>29.35</t>
-        </is>
-      </c>
-      <c r="CS17" t="inlineStr">
-        <is>
-          <t>29.1</t>
-        </is>
-      </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8808,14 +8808,14 @@
       </c>
       <c r="CX17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8825,42 +8825,42 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1249.819</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-2.43</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>508.716</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>29.15</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>-0.52</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8870,37 +8870,37 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-06-21 00:00:00</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-06-27 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-07 00:00:00</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-30 00:00:00</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -8910,12 +8910,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -8925,12 +8925,12 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-30.75</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8975,42 +8975,42 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
+          <t>2026/02/02</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
           <t>2025/12/26</t>
         </is>
       </c>
-      <c r="AH18" t="inlineStr">
+      <c r="AJ18" t="inlineStr">
         <is>
           <t>30.45</t>
         </is>
       </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>30.6</t>
-        </is>
-      </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-10-13 00:00:00</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>23.90</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -9021,75 +9021,75 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>32.59</t>
         </is>
       </c>
       <c r="AU18" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>-2.05</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>-1.42</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>29.24</t>
+        </is>
+      </c>
+      <c r="AZ18" t="n">
+        <v>29.62</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>30.68</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="BD18" t="n">
         <v>-0.31</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>-1.86</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>-1.30</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>29.24</t>
-        </is>
-      </c>
-      <c r="AZ18" t="n">
-        <v>29.74</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>30.7</t>
-        </is>
-      </c>
-      <c r="BC18" t="inlineStr">
-        <is>
-          <t>-11.84</t>
-        </is>
-      </c>
-      <c r="BD18" t="n">
-        <v>-0.35</v>
       </c>
       <c r="BE18" t="n">
         <v>-0.32</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-163.41</t>
+          <t>-136.11</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9099,43 +9099,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>29874713.26956522</t>
+          <t>35228493.26086956</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>14844797.0</t>
+          <t>36951577.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>28692296.4</v>
+        <v>25211363.2</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>26444131.4</t>
+          <t>26502871.8</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>16324390.42</v>
+        <v>16852284.6</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>2248165</t>
+          <t>-1291508</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>2022244.97086807</t>
+          <t>1676144.293344427</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>1091357.074940387</t>
+          <t>1249830.669164084</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>14844797.0</t>
+          <t>36951577.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>-14.14</t>
+          <t>-13.11</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9200,22 +9200,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.73</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.33</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>26538</t>
+          <t>26355</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9265,22 +9265,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="CS18" t="inlineStr">
+        <is>
           <t>29.3</t>
         </is>
       </c>
-      <c r="CS18" t="inlineStr">
-        <is>
-          <t>29.1</t>
-        </is>
-      </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="CX18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9317,42 +9317,42 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>556.2</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>29.25</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-1.56</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>796.89</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>29.15</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>-0.52</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9362,37 +9362,37 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-06-21 00:00:00</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-06-27 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-07 00:00:00</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-30 00:00:00</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -9402,12 +9402,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -9417,12 +9417,12 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-31.34</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9467,42 +9467,42 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
+          <t>2026/02/02</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
           <t>2025/12/26</t>
         </is>
       </c>
-      <c r="AH19" t="inlineStr">
+      <c r="AJ19" t="inlineStr">
         <is>
           <t>30.45</t>
         </is>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>30.6</t>
-        </is>
-      </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-10-13 00:00:00</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9513,75 +9513,75 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>-0.55</v>
+        <v>0.17</v>
       </c>
       <c r="AV19" t="n">
-        <v>-1.66</v>
+        <v>-1.61</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>29.8</v>
+        <v>29.68</v>
       </c>
       <c r="BA19" t="n">
-        <v>30.33</v>
+        <v>30.27</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>30.72</t>
+          <t>30.69</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-14.09</t>
+          <t>-7.01</t>
         </is>
       </c>
       <c r="BD19" t="n">
         <v>-0.35</v>
       </c>
       <c r="BE19" t="n">
-        <v>-0.31</v>
+        <v>-0.32</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-161.53</t>
+          <t>-136.30</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9591,43 +9591,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>29874713.26956522</t>
+          <t>35228493.26086956</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>23220153.0</t>
+          <t>16274454.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>31783738.2</v>
+        <v>25719627.8</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>26663589.6</t>
+          <t>25467490.4</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>16268239.9</v>
+        <v>16380710.06</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>5120148</t>
+          <t>252137</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>2191497.315582194</t>
+          <t>1753655.861377217</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>2369759.451925177</t>
+          <t>276415.7591775246</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>23220153.0</t>
+          <t>16274454.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>-14.14</t>
+          <t>-13.84</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9692,22 +9692,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.73</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9732,12 +9732,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.33</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>26538</t>
+          <t>26355</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9757,24 +9757,24 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
+          <t>29.35</t>
+        </is>
+      </c>
+      <c r="CS19" t="inlineStr">
+        <is>
+          <t>29.1</t>
+        </is>
+      </c>
+      <c r="CT19" t="inlineStr">
+        <is>
           <t>29.25</t>
         </is>
       </c>
-      <c r="CS19" t="inlineStr">
-        <is>
-          <t>29.05</t>
-        </is>
-      </c>
-      <c r="CT19" t="inlineStr">
-        <is>
-          <t>29.15</t>
-        </is>
-      </c>
       <c r="CU19" t="inlineStr">
         <is>
           <t>19.66</t>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="CX19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9809,12 +9809,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1191.884</t>
+          <t>508.716</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>12.12</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9854,37 +9854,37 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-06-21 00:00:00</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-06-27 00:00:00</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-07 00:00:00</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-30 00:00:00</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -9909,12 +9909,12 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-31.57</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -9934,7 +9934,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9959,37 +9959,37 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
+          <t>2026/02/02</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
           <t>2025/12/26</t>
         </is>
       </c>
-      <c r="AH20" t="inlineStr">
+      <c r="AJ20" t="inlineStr">
         <is>
           <t>30.45</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>30.6</t>
-        </is>
-      </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-10-13 00:00:00</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>22.79</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
@@ -10005,12 +10005,12 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -10024,56 +10024,56 @@
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-0.85</v>
+        <v>-0.31</v>
       </c>
       <c r="AV20" t="n">
-        <v>-1.61</v>
+        <v>-1.67</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.24</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>29.88</v>
+        <v>29.74</v>
       </c>
       <c r="BA20" t="n">
-        <v>30.36</v>
+        <v>30.3</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>30.73</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-15.00</t>
+          <t>-11.84</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>-0.34</v>
+        <v>-0.35</v>
       </c>
       <c r="BE20" t="n">
-        <v>-0.3</v>
+        <v>-0.32</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-159.36</t>
+          <t>-135.66</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -10083,43 +10083,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>29874713.26956522</t>
+          <t>35228493.26086956</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>34765835.0</t>
+          <t>14844797.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>30711025</v>
+        <v>28692296.4</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>27390013.9</t>
+          <t>26444131.4</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>16109008.78</v>
+        <v>16324390.42</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>3321011</t>
+          <t>2248165</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>2159086.018065288</t>
+          <t>2022244.97086807</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>3214054.724334691</t>
+          <t>1091357.074940387</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>34765835.0</t>
+          <t>14844797.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10184,12 +10184,12 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.73</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.33</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>26538</t>
+          <t>26355</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10249,7 +10249,7 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="CX20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -10301,12 +10301,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1347.009</t>
+          <t>796.89</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10346,37 +10346,37 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-06-21 00:00:00</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-06-27 00:00:00</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-07 00:00:00</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-30 00:00:00</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -10386,12 +10386,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -10401,12 +10401,12 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-31.57</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10451,42 +10451,42 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
+          <t>2026/02/02</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
           <t>2025/12/26</t>
         </is>
       </c>
-      <c r="AH21" t="inlineStr">
+      <c r="AJ21" t="inlineStr">
         <is>
           <t>30.45</t>
         </is>
       </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>30.6</t>
-        </is>
-      </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-10-13 00:00:00</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10497,12 +10497,12 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -10516,56 +10516,56 @@
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-0.68</v>
+        <v>-0.55</v>
       </c>
       <c r="AV21" t="n">
-        <v>-1.54</v>
+        <v>-1.66</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>29.96</v>
+        <v>29.8</v>
       </c>
       <c r="BA21" t="n">
-        <v>30.4</v>
+        <v>30.33</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>30.72</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-13.44</t>
+          <t>-14.09</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-0.32</v>
+        <v>-0.35</v>
       </c>
       <c r="BE21" t="n">
-        <v>-0.29</v>
+        <v>-0.31</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-157.14</t>
+          <t>-134.61</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10575,43 +10575,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>29874713.26956522</t>
+          <t>35228493.26086956</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>39492900.0</t>
+          <t>23220153.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>27794380.4</v>
+        <v>31783738.2</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>26393933.9</t>
+          <t>26663589.6</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>15869794.14</v>
+        <v>16268239.9</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>1400446</t>
+          <t>5120148</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>1967273.526016306</t>
+          <t>2191497.315582194</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>3068365.801907759</t>
+          <t>2369759.451925177</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>39492900.0</t>
+          <t>23220153.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10631,7 +10631,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-14.14</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10676,22 +10676,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.73</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.33</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>26538</t>
+          <t>26355</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10741,22 +10741,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="CX21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -10793,12 +10793,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1056.469</t>
+          <t>1191.884</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>12.12</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10838,37 +10838,37 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-06-21 00:00:00</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-06-27 00:00:00</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-07 00:00:00</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-30 00:00:00</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -10878,12 +10878,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-31.57</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -10918,7 +10918,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10943,42 +10943,42 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
+          <t>2026/02/02</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
           <t>2025/12/26</t>
         </is>
       </c>
-      <c r="AH22" t="inlineStr">
+      <c r="AJ22" t="inlineStr">
         <is>
           <t>30.45</t>
         </is>
       </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>30.6</t>
-        </is>
-      </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-10-13 00:00:00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>20.20</t>
+          <t>22.79</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10989,12 +10989,12 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -11004,60 +11004,60 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU22" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>-1.59</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>-1.19</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>29.4</t>
+        </is>
+      </c>
+      <c r="AZ22" t="n">
+        <v>29.88</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>30.36</v>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>30.73</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>-15.00</t>
+        </is>
+      </c>
+      <c r="BD22" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="BE22" t="n">
         <v>-0.3</v>
       </c>
-      <c r="AV22" t="n">
-        <v>-1.66</v>
-      </c>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>-1.32</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>-1.02</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>29.54</t>
-        </is>
-      </c>
-      <c r="AZ22" t="n">
-        <v>30.04</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>30.44</v>
-      </c>
-      <c r="BB22" t="inlineStr">
-        <is>
-          <t>30.75</t>
-        </is>
-      </c>
-      <c r="BC22" t="inlineStr">
-        <is>
-          <t>-13.22</t>
-        </is>
-      </c>
-      <c r="BD22" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>-0.28</v>
-      </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-155.22</t>
+          <t>-133.39</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -11067,43 +11067,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>29874713.26956522</t>
+          <t>35228493.26086956</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>31137797.0</t>
+          <t>34765835.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>25215353</v>
+        <v>30711025</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>24579775.5</t>
+          <t>27390013.9</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>15430798.08</v>
+        <v>16109008.78</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>635577</t>
+          <t>3321011</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>1767074.930399678</t>
+          <t>2159086.018065288</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>2244183.026944011</t>
+          <t>3214054.724334691</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>31137797.0</t>
+          <t>34765835.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>-13.25</t>
+          <t>-14.14</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11168,22 +11168,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.73</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.33</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>26538</t>
+          <t>26355</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11233,22 +11233,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="CX22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -11285,12 +11285,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1028.225</t>
+          <t>1347.009</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-4.86</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11330,37 +11330,37 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-06-21 00:00:00</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-06-27 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-07 00:00:00</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-05-30 00:00:00</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -11370,12 +11370,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40.75</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -11385,12 +11385,12 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-31.22</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11435,37 +11435,37 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
+          <t>2026/02/02</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
           <t>2025/12/26</t>
         </is>
       </c>
-      <c r="AH23" t="inlineStr">
+      <c r="AJ23" t="inlineStr">
         <is>
           <t>30.45</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>30.6</t>
-        </is>
-      </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2026-01-21 00:00:00</t>
+          <t>2025-10-13 00:00:00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -11481,12 +11481,12 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -11496,271 +11496,763 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>14.36</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>-0.24</v>
+        <v>-0.68</v>
       </c>
       <c r="AV23" t="n">
-        <v>-1.73</v>
+        <v>-1.54</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>29.57</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>30.09</v>
+        <v>29.96</v>
       </c>
       <c r="BA23" t="n">
-        <v>30.48</v>
+        <v>30.4</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>30.76</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-15.62</t>
+          <t>-13.44</t>
         </is>
       </c>
       <c r="BD23" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>0.89</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>-132.14</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026/01/27</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>35228493.26086956</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>39492900.0</t>
+        </is>
+      </c>
+      <c r="BK23" t="n">
+        <v>27794380.4</v>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>26393933.9</t>
+        </is>
+      </c>
+      <c r="BM23" t="n">
+        <v>15869794.14</v>
+      </c>
+      <c r="BN23" t="inlineStr">
+        <is>
+          <t>1400446</t>
+        </is>
+      </c>
+      <c r="BO23" t="inlineStr">
+        <is>
+          <t>1967273.526016306</t>
+        </is>
+      </c>
+      <c r="BP23" t="inlineStr">
+        <is>
+          <t>3068365.801907759</t>
+        </is>
+      </c>
+      <c r="BQ23" t="inlineStr">
+        <is>
+          <t>39492900.0</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS23" t="inlineStr">
+        <is>
+          <t>33.95</t>
+        </is>
+      </c>
+      <c r="BT23" t="inlineStr">
+        <is>
+          <t>2025/10/15</t>
+        </is>
+      </c>
+      <c r="BU23" t="inlineStr">
+        <is>
+          <t>-13.70</t>
+        </is>
+      </c>
+      <c r="BV23" t="inlineStr">
+        <is>
+          <t>佳格</t>
+        </is>
+      </c>
+      <c r="BW23" t="inlineStr">
+        <is>
+          <t>佳格</t>
+        </is>
+      </c>
+      <c r="BX23" t="inlineStr">
+        <is>
+          <t>食品工業</t>
+        </is>
+      </c>
+      <c r="BY23" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ23" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="CA23" t="inlineStr">
+        <is>
+          <t>6.237608785148733</t>
+        </is>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>-17.09267911306208</t>
+        </is>
+      </c>
+      <c r="CC23" t="inlineStr">
+        <is>
+          <t>-3.78772922691385</t>
+        </is>
+      </c>
+      <c r="CD23" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="CG23" t="inlineStr">
+        <is>
+          <t>4.86</t>
+        </is>
+      </c>
+      <c r="CH23" t="inlineStr">
+        <is>
+          <t>8.02</t>
+        </is>
+      </c>
+      <c r="CI23" t="inlineStr">
+        <is>
+          <t>19.73</t>
+        </is>
+      </c>
+      <c r="CJ23" t="inlineStr">
+        <is>
+          <t>23.06%</t>
+        </is>
+      </c>
+      <c r="CK23" t="inlineStr">
+        <is>
+          <t>4.46%</t>
+        </is>
+      </c>
+      <c r="CL23" t="inlineStr">
+        <is>
+          <t>25.33</t>
+        </is>
+      </c>
+      <c r="CM23" t="inlineStr">
+        <is>
+          <t>26355</t>
+        </is>
+      </c>
+      <c r="CN23" t="inlineStr">
+        <is>
+          <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO23" t="inlineStr">
+        <is>
+          <t>佳格-食品工業-上市</t>
+        </is>
+      </c>
+      <c r="CP23" t="inlineStr">
+        <is>
+          <t>食品工業右下上市</t>
+        </is>
+      </c>
+      <c r="CQ23" t="inlineStr">
+        <is>
+          <t>29.35</t>
+        </is>
+      </c>
+      <c r="CR23" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="CS23" t="inlineStr">
+        <is>
+          <t>29.25</t>
+        </is>
+      </c>
+      <c r="CT23" t="inlineStr">
+        <is>
+          <t>29.3</t>
+        </is>
+      </c>
+      <c r="CU23" t="inlineStr">
+        <is>
+          <t>19.66</t>
+        </is>
+      </c>
+      <c r="CV23" t="inlineStr">
+        <is>
+          <t>** 食品 - 營養食品</t>
+        </is>
+      </c>
+      <c r="CW23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CX23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>-0.17</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1056.469</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-2.26</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2.59</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2024-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2024-06-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2024-05-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2024-05-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>43.0</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>42.6</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>38.75</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>40.75</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>-30.87</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>5.52</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025/05/15</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>35.5</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>30.5</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>33.25</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>2026/02/02</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>2025/12/26</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>30.45</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>20.20</t>
+        </is>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>-0.17</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>1271</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr">
+        <is>
+          <t>6.67</t>
+        </is>
+      </c>
+      <c r="AU24" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>-1.32</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>-1.02</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>29.54</t>
+        </is>
+      </c>
+      <c r="AZ24" t="n">
+        <v>30.04</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>30.44</v>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>30.75</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>-13.22</t>
+        </is>
+      </c>
+      <c r="BD24" t="n">
         <v>-0.31</v>
       </c>
-      <c r="BE23" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="BF23" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr">
-        <is>
-          <t>-153.39</t>
-        </is>
-      </c>
-      <c r="BH23" t="inlineStr">
+      <c r="BE24" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="BF24" t="inlineStr">
+        <is>
+          <t>0.89</t>
+        </is>
+      </c>
+      <c r="BG24" t="inlineStr">
+        <is>
+          <t>-131.06</t>
+        </is>
+      </c>
+      <c r="BH24" t="inlineStr">
         <is>
           <t>2026/01/27</t>
         </is>
       </c>
-      <c r="BI23" t="inlineStr">
-        <is>
-          <t>29874713.26956522</t>
-        </is>
-      </c>
-      <c r="BJ23" t="inlineStr">
-        <is>
-          <t>30302006.0</t>
-        </is>
-      </c>
-      <c r="BK23" t="n">
-        <v>24195966.4</v>
-      </c>
-      <c r="BL23" t="inlineStr">
-        <is>
-          <t>25432168.8</t>
-        </is>
-      </c>
-      <c r="BM23" t="n">
-        <v>15030428.6</v>
-      </c>
-      <c r="BN23" t="inlineStr">
-        <is>
-          <t>-1236202</t>
-        </is>
-      </c>
-      <c r="BO23" t="inlineStr">
-        <is>
-          <t>1680328.003755254</t>
-        </is>
-      </c>
-      <c r="BP23" t="inlineStr">
-        <is>
-          <t>1881819.276033513</t>
-        </is>
-      </c>
-      <c r="BQ23" t="inlineStr">
-        <is>
-          <t>30302006.0</t>
-        </is>
-      </c>
-      <c r="BR23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS23" t="inlineStr">
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>35228493.26086956</t>
+        </is>
+      </c>
+      <c r="BJ24" t="inlineStr">
+        <is>
+          <t>31137797.0</t>
+        </is>
+      </c>
+      <c r="BK24" t="n">
+        <v>25215353</v>
+      </c>
+      <c r="BL24" t="inlineStr">
+        <is>
+          <t>24579775.5</t>
+        </is>
+      </c>
+      <c r="BM24" t="n">
+        <v>15430798.08</v>
+      </c>
+      <c r="BN24" t="inlineStr">
+        <is>
+          <t>635577</t>
+        </is>
+      </c>
+      <c r="BO24" t="inlineStr">
+        <is>
+          <t>1767074.930399678</t>
+        </is>
+      </c>
+      <c r="BP24" t="inlineStr">
+        <is>
+          <t>2244183.026944011</t>
+        </is>
+      </c>
+      <c r="BQ24" t="inlineStr">
+        <is>
+          <t>31137797.0</t>
+        </is>
+      </c>
+      <c r="BR24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS24" t="inlineStr">
         <is>
           <t>33.95</t>
         </is>
       </c>
-      <c r="BT23" t="inlineStr">
+      <c r="BT24" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BU23" t="inlineStr">
-        <is>
-          <t>-13.11</t>
-        </is>
-      </c>
-      <c r="BV23" t="inlineStr">
+      <c r="BU24" t="inlineStr">
+        <is>
+          <t>-13.25</t>
+        </is>
+      </c>
+      <c r="BV24" t="inlineStr">
         <is>
           <t>佳格</t>
         </is>
       </c>
-      <c r="BW23" t="inlineStr">
+      <c r="BW24" t="inlineStr">
         <is>
           <t>佳格</t>
         </is>
       </c>
-      <c r="BX23" t="inlineStr">
+      <c r="BX24" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY23" t="inlineStr">
+      <c r="BY24" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BZ23" t="inlineStr">
+      <c r="BZ24" t="inlineStr">
         <is>
           <t>0.42</t>
         </is>
       </c>
-      <c r="CA23" t="inlineStr">
+      <c r="CA24" t="inlineStr">
         <is>
           <t>6.237608785148733</t>
         </is>
       </c>
-      <c r="CB23" t="inlineStr">
+      <c r="CB24" t="inlineStr">
         <is>
           <t>-17.09267911306208</t>
         </is>
       </c>
-      <c r="CC23" t="inlineStr">
+      <c r="CC24" t="inlineStr">
         <is>
           <t>-3.78772922691385</t>
         </is>
       </c>
-      <c r="CD23" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE23" t="inlineStr">
+      <c r="CD24" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="CE24" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CF23" t="inlineStr">
+      <c r="CF24" t="inlineStr">
         <is>
           <t>1.50</t>
         </is>
       </c>
-      <c r="CG23" t="inlineStr">
-        <is>
-          <t>4.83</t>
-        </is>
-      </c>
-      <c r="CH23" t="inlineStr">
+      <c r="CG24" t="inlineStr">
+        <is>
+          <t>4.86</t>
+        </is>
+      </c>
+      <c r="CH24" t="inlineStr">
         <is>
           <t>8.02</t>
         </is>
       </c>
-      <c r="CI23" t="inlineStr">
-        <is>
-          <t>19.86</t>
-        </is>
-      </c>
-      <c r="CJ23" t="inlineStr">
+      <c r="CI24" t="inlineStr">
+        <is>
+          <t>19.73</t>
+        </is>
+      </c>
+      <c r="CJ24" t="inlineStr">
         <is>
           <t>23.06%</t>
         </is>
       </c>
-      <c r="CK23" t="inlineStr">
+      <c r="CK24" t="inlineStr">
         <is>
           <t>4.46%</t>
         </is>
       </c>
-      <c r="CL23" t="inlineStr">
-        <is>
-          <t>25.62</t>
-        </is>
-      </c>
-      <c r="CM23" t="inlineStr">
-        <is>
-          <t>26538</t>
-        </is>
-      </c>
-      <c r="CN23" t="inlineStr">
+      <c r="CL24" t="inlineStr">
+        <is>
+          <t>25.33</t>
+        </is>
+      </c>
+      <c r="CM24" t="inlineStr">
+        <is>
+          <t>26355</t>
+        </is>
+      </c>
+      <c r="CN24" t="inlineStr">
         <is>
           <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
         </is>
       </c>
-      <c r="CO23" t="inlineStr">
+      <c r="CO24" t="inlineStr">
         <is>
           <t>佳格-食品工業-上市</t>
         </is>
       </c>
-      <c r="CP23" t="inlineStr">
+      <c r="CP24" t="inlineStr">
         <is>
           <t>食品工業右下上市</t>
         </is>
       </c>
-      <c r="CQ23" t="inlineStr">
-        <is>
-          <t>29.6</t>
-        </is>
-      </c>
-      <c r="CR23" t="inlineStr">
-        <is>
-          <t>29.7</t>
-        </is>
-      </c>
-      <c r="CS23" t="inlineStr">
-        <is>
-          <t>29.4</t>
-        </is>
-      </c>
-      <c r="CT23" t="inlineStr">
+      <c r="CQ24" t="inlineStr">
         <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="CU23" t="inlineStr">
+      <c r="CR24" t="inlineStr">
+        <is>
+          <t>29.65</t>
+        </is>
+      </c>
+      <c r="CS24" t="inlineStr">
+        <is>
+          <t>29.3</t>
+        </is>
+      </c>
+      <c r="CT24" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="CU24" t="inlineStr">
         <is>
           <t>19.66</t>
         </is>
       </c>
-      <c r="CV23" t="inlineStr">
+      <c r="CV24" t="inlineStr">
         <is>
           <t>** 食品 - 營養食品</t>
         </is>
       </c>
-      <c r="CW23" t="inlineStr">
+      <c r="CW24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX23" t="inlineStr">
-        <is>
-          <t>0.0</t>
+      <c r="CX24" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/營養食品.xlsx
+++ b/Result/checksun_type/營養食品.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CX24"/>
+  <dimension ref="A1:CX25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -943,7 +943,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>價_量;【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -953,42 +953,42 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>74.2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-12.03</t>
+          <t>-30.73</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>-12.76</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1128,17 +1128,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1149,66 +1149,66 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>47.62</t>
+          <t>59.52</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-0.19</v>
+        <v>0.24</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
+          <t>74.32000000000001</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>74.23</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>74.39</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
           <t>74.34</t>
         </is>
       </c>
-      <c r="AZ2" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>74.38</t>
-        </is>
-      </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>93.80</t>
+          <t>171.19</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0</v>
+        <v>0.02</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-102.27</t>
+          <t>-101.59</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1227,43 +1227,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>3107.892644135189</t>
+          <t>3103.053571428571</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>1492.0</t>
+          <t>446.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>1709</v>
+        <v>1284.6</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1942.6</t>
+          <t>1854.6</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>1251.7</v>
+        <v>1241.7</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-233</t>
+          <t>-570</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>59.63766276851573</t>
+          <t>29.3649364128487</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-46.09411818075841</t>
+          <t>-137.1350585433199</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>1492.0</t>
+          <t>446.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1393,22 +1393,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.0</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1470,17 +1470,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-9.26</t>
+          <t>-12.03</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1620,17 +1620,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1641,66 +1641,66 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>47.62</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-0.22</v>
+        <v>-0.19</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>74.36</t>
+          <t>74.34</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>74.18000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="BA3" t="n">
-        <v>74.39</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>74.41</t>
+          <t>74.38</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>100.71</t>
+          <t>93.80</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-102.80</t>
+          <t>-102.27</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1719,43 +1719,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>3107.892644135189</t>
+          <t>3103.053571428571</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>1703.0</t>
+          <t>1492.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>1768.6</v>
+        <v>1709</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1949.1</t>
+          <t>1942.6</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>1235.02</v>
+        <v>1251.7</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-180</t>
+          <t>-233</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>78.86162294111104</t>
+          <t>59.63766276851573</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-26.46084201350072</t>
+          <t>-46.09411818075841</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>1703.0</t>
+          <t>1492.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1860,12 +1860,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1885,17 +1885,17 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9.0</t>
         </is>
       </c>
     </row>
@@ -1937,12 +1937,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1962,17 +1962,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-9.26</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2112,17 +2112,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>8.58</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2133,12 +2133,12 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2148,14 +2148,14 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>79.17</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-0.3</v>
+        <v>-0.22</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.36</v>
+        <v>0.24</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
@@ -2164,35 +2164,35 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>74.42</t>
+          <t>74.36</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>74.16</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="BA4" t="n">
-        <v>74.36</v>
+        <v>74.39</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>74.45</t>
+          <t>74.41</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>106.40</t>
+          <t>100.71</t>
         </is>
       </c>
       <c r="BD4" t="n">
         <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-103.51</t>
+          <t>-102.80</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2211,43 +2211,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>3107.892644135189</t>
+          <t>3103.053571428571</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>1424.0</t>
+          <t>1703.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>1652.6</v>
+        <v>1768.6</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1802.0</t>
+          <t>1949.1</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>1263.36</v>
+        <v>1235.02</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-149</t>
+          <t>-180</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>98.01116202376772</t>
+          <t>78.86162294111104</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-20.07541741693626</t>
+          <t>-26.46084201350072</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>1424.0</t>
+          <t>1703.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2352,12 +2352,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
+          <t>73.6</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
+          <t>73.6</t>
+        </is>
+      </c>
+      <c r="CT4" t="inlineStr">
+        <is>
           <t>74.2</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="CS4" t="inlineStr">
-        <is>
-          <t>73.5</t>
-        </is>
-      </c>
-      <c r="CT4" t="inlineStr">
-        <is>
-          <t>74.2</t>
-        </is>
-      </c>
       <c r="CU4" t="inlineStr">
         <is>
           <t>34.3</t>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9.0</t>
         </is>
       </c>
     </row>
@@ -2429,192 +2429,192 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-8.29</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-03-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-02-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-02-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>85.4</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>82.4</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-13.11</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025/09/12</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026/01/06</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>74.7</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>2026-01-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>7.09</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
           <t>-0.13</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>74.5</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-0.4</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-13.36</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-03-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-02-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-02-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>82.3</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>85.4</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>82.4</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>79.7</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-12.76</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>3.26</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025/09/12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2026/01/06</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>2025/12/15</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>74.7</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>2026-01-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>2026-01-28</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>6.72</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>-2.41</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2625,66 +2625,66 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>88.43</t>
+          <t>79.17</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>0.19</v>
+        <v>-0.3</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>74.35999999999999</t>
+          <t>74.42</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>74.12</v>
+        <v>74.16</v>
       </c>
       <c r="BA5" t="n">
-        <v>74.38</v>
+        <v>74.36</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>74.49</t>
+          <t>74.45</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>110.87</t>
+          <t>106.40</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-104.44</t>
+          <t>-103.51</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2703,43 +2703,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>3107.892644135189</t>
+          <t>3103.053571428571</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>1358.0</t>
+          <t>1424.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>1619.8</v>
+        <v>1652.6</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1869.6</t>
+          <t>1802.0</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>1245.84</v>
+        <v>1263.36</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-249</t>
+          <t>-149</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>119.4814491948048</t>
+          <t>98.01116202376772</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>19.65645405733221</t>
+          <t>-20.07541741693626</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>1358.0</t>
+          <t>1424.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2844,12 +2844,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2869,22 +2869,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8.0</t>
         </is>
       </c>
     </row>
@@ -2921,12 +2921,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>28.84</t>
+          <t>-13.36</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-12.65</t>
+          <t>-12.76</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3096,17 +3096,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3117,33 +3117,33 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>88.43</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>0.4</v>
+        <v>0.19</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
@@ -3153,230 +3153,230 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
+          <t>74.35999999999999</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>74.12</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>74.38</v>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>74.49</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>110.87</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>-104.44</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2026/01/08</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>3103.053571428571</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>1358.0</t>
+        </is>
+      </c>
+      <c r="BK6" t="n">
+        <v>1619.8</v>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>1869.6</t>
+        </is>
+      </c>
+      <c r="BM6" t="n">
+        <v>1245.84</v>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>-249</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>119.4814491948048</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>19.65645405733221</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>1358.0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>-0.93</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>綠茵</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>綠茵</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>食品工業</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>43.18290500198112</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>12.18914260633116</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>4.818590014463328</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>4.83</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>7.61</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>13.93</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>48.81%</t>
+        </is>
+      </c>
+      <c r="CK6" t="inlineStr">
+        <is>
+          <t>17.38%</t>
+        </is>
+      </c>
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>27.84</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="CN6" t="inlineStr">
+        <is>
+          <t>保健食品配方65.97%、保健食品原料33.59%、其他0.43% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO6" t="inlineStr">
+        <is>
+          <t>綠茵-食品工業-上櫃</t>
+        </is>
+      </c>
+      <c r="CP6" t="inlineStr">
+        <is>
+          <t>食品工業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CQ6" t="inlineStr">
+        <is>
           <t>74.3</t>
         </is>
       </c>
-      <c r="AZ6" t="n">
-        <v>74.09</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>74.41</v>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>74.52</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>82.76</t>
-        </is>
-      </c>
-      <c r="BD6" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>-105.67</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>2026/01/08</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>3107.892644135189</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>2568.0</t>
-        </is>
-      </c>
-      <c r="BK6" t="n">
-        <v>2424.6</v>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>1881.9</t>
-        </is>
-      </c>
-      <c r="BM6" t="n">
-        <v>1233.16</v>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>542</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>137.6314483107089</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>82.78568280423974</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>2568.0</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>75.2</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>2025/12/04</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>-0.80</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>綠茵</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>綠茵</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>食品工業</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>43.18290500198112</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>12.18914260633116</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>4.818590014463328</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>4.85</t>
-        </is>
-      </c>
-      <c r="CH6" t="inlineStr">
-        <is>
-          <t>7.61</t>
-        </is>
-      </c>
-      <c r="CI6" t="inlineStr">
-        <is>
-          <t>13.87</t>
-        </is>
-      </c>
-      <c r="CJ6" t="inlineStr">
-        <is>
-          <t>48.81%</t>
-        </is>
-      </c>
-      <c r="CK6" t="inlineStr">
-        <is>
-          <t>17.38%</t>
-        </is>
-      </c>
-      <c r="CL6" t="inlineStr">
-        <is>
-          <t>27.96</t>
-        </is>
-      </c>
-      <c r="CM6" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="CN6" t="inlineStr">
-        <is>
-          <t>保健食品配方65.97%、保健食品原料33.59%、其他0.43% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO6" t="inlineStr">
-        <is>
-          <t>綠茵-食品工業-上櫃</t>
-        </is>
-      </c>
-      <c r="CP6" t="inlineStr">
-        <is>
-          <t>食品工業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CQ6" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9.0</t>
         </is>
       </c>
     </row>
@@ -3413,12 +3413,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>28.84</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-13.00</t>
+          <t>-12.65</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3588,17 +3588,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3609,66 +3609,66 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>69.26</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.13</v>
+        <v>0.29</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>74.14</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>74.04000000000001</v>
+        <v>74.09</v>
       </c>
       <c r="BA7" t="n">
-        <v>74.47</v>
+        <v>74.41</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>74.55</t>
+          <t>74.52</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>82.76</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-106.84</t>
+          <t>-105.67</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3687,43 +3687,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>3107.892644135189</t>
+          <t>3103.053571428571</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>1790.0</t>
+          <t>2568.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>2176.2</v>
+        <v>2424.6</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1990.3</t>
+          <t>1881.9</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>1194.16</v>
+        <v>1233.16</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>542</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>147.6034056755215</t>
+          <t>137.6314483107089</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>40.37080662824201</t>
+          <t>82.78568280423974</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>1790.0</t>
+          <t>2568.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3813,7 +3813,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3853,12 +3853,12 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3888,7 +3888,7 @@
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9.0</t>
         </is>
       </c>
     </row>
@@ -3905,12 +3905,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>12.70</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-12.76</t>
+          <t>-13.00</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4080,17 +4080,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4101,66 +4101,66 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>69.26</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>0.59</v>
+        <v>0.22</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>74.06</t>
+          <t>74.14</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>74</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="BA8" t="n">
-        <v>74.53</v>
+        <v>74.47</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>74.58</t>
+          <t>74.55</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="BE8" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-107.70</t>
+          <t>-106.84</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4179,43 +4179,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>3107.892644135189</t>
+          <t>3103.053571428571</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>1123.0</t>
+          <t>1790.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>2129.6</v>
+        <v>2176.2</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1889.7</t>
+          <t>1990.3</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>1175.68</v>
+        <v>1194.16</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>185</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>167.100241865936</t>
+          <t>147.6034056755215</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>61.69345471152246</t>
+          <t>40.37080662824201</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>1123.0</t>
+          <t>1790.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4280,12 +4280,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4345,24 +4345,24 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
+          <t>74.9</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>74.9</t>
+        </is>
+      </c>
+      <c r="CS8" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="CT8" t="inlineStr">
+        <is>
           <t>74.3</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
-        <is>
-          <t>74.5</t>
-        </is>
-      </c>
-      <c r="CS8" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="CT8" t="inlineStr">
-        <is>
-          <t>74.5</t>
-        </is>
-      </c>
       <c r="CU8" t="inlineStr">
         <is>
           <t>34.3</t>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9.0</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4422,7 +4422,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>12.70</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4497,7 +4497,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-13.47</t>
+          <t>-12.76</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4572,17 +4572,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4593,266 +4593,266 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>31.79</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-0.14</v>
+        <v>0.59</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
+          <t>74.06</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>74</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>74.53</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>74.58</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>38.85</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>-107.70</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2026/01/08</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>3103.053571428571</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>1123.0</t>
+        </is>
+      </c>
+      <c r="BK9" t="n">
+        <v>2129.6</v>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>1889.7</t>
+        </is>
+      </c>
+      <c r="BM9" t="n">
+        <v>1175.68</v>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>167.100241865936</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>61.69345471152246</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>1123.0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>-0.93</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>綠茵</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>綠茵</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>食品工業</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>43.18290500198112</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>12.18914260633116</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>4.818590014463328</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>4.83</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>7.61</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>13.93</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>48.81%</t>
+        </is>
+      </c>
+      <c r="CK9" t="inlineStr">
+        <is>
+          <t>17.38%</t>
+        </is>
+      </c>
+      <c r="CL9" t="inlineStr">
+        <is>
+          <t>27.84</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr">
+        <is>
+          <t>保健食品配方65.97%、保健食品原料33.59%、其他0.43% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO9" t="inlineStr">
+        <is>
+          <t>綠茵-食品工業-上櫃</t>
+        </is>
+      </c>
+      <c r="CP9" t="inlineStr">
+        <is>
+          <t>食品工業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>74.3</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="CS9" t="inlineStr">
+        <is>
           <t>74.0</t>
         </is>
       </c>
-      <c r="AZ9" t="n">
-        <v>73.97</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>74.62</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>11.57</t>
-        </is>
-      </c>
-      <c r="BD9" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>-108.44</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>2026/01/08</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>3107.892644135189</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>1260.0</t>
-        </is>
-      </c>
-      <c r="BK9" t="n">
-        <v>1951.4</v>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>1837.0</t>
-        </is>
-      </c>
-      <c r="BM9" t="n">
-        <v>1193.06</v>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>186.2651122576475</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>161.4153285907973</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>1260.0</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>75.2</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>2025/12/04</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>-1.73</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>綠茵</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>綠茵</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>食品工業</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>43.18290500198112</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>12.18914260633116</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>4.818590014463328</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>4.85</t>
-        </is>
-      </c>
-      <c r="CH9" t="inlineStr">
-        <is>
-          <t>7.61</t>
-        </is>
-      </c>
-      <c r="CI9" t="inlineStr">
-        <is>
-          <t>13.87</t>
-        </is>
-      </c>
-      <c r="CJ9" t="inlineStr">
-        <is>
-          <t>48.81%</t>
-        </is>
-      </c>
-      <c r="CK9" t="inlineStr">
-        <is>
-          <t>17.38%</t>
-        </is>
-      </c>
-      <c r="CL9" t="inlineStr">
-        <is>
-          <t>27.96</t>
-        </is>
-      </c>
-      <c r="CM9" t="inlineStr">
-        <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="CN9" t="inlineStr">
-        <is>
-          <t>保健食品配方65.97%、保健食品原料33.59%、其他0.43% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO9" t="inlineStr">
-        <is>
-          <t>綠茵-食品工業-上櫃</t>
-        </is>
-      </c>
-      <c r="CP9" t="inlineStr">
-        <is>
-          <t>食品工業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CQ9" t="inlineStr">
-        <is>
-          <t>74.9</t>
-        </is>
-      </c>
-      <c r="CR9" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="CS9" t="inlineStr">
-        <is>
-          <t>73.6</t>
-        </is>
-      </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4872,14 +4872,14 @@
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>9.0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4914,17 +4914,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>0.81</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-22.77</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>-13.47</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5064,17 +5064,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>27.24</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5085,66 +5085,66 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>31.79</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>0.35</v>
+        <v>-0.14</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>73.94000000000001</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
         <v>73.97</v>
       </c>
       <c r="BA10" t="n">
-        <v>74.64</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>74.66</t>
+          <t>74.62</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="BD10" t="n">
         <v>-0.13</v>
       </c>
       <c r="BE10" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-108.69</t>
+          <t>-108.44</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5163,43 +5163,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>3107.892644135189</t>
+          <t>3103.053571428571</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>5382.0</t>
+          <t>1260.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>2119.4</v>
+        <v>1951.4</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>2744.4</t>
+          <t>1837.0</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>1180.18</v>
+        <v>1193.06</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-625</t>
+          <t>114</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>190.7832547425293</t>
+          <t>186.2651122576475</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>283.4317438258045</t>
+          <t>161.4153285907973</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>5382.0</t>
+          <t>1260.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5274,12 +5274,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5329,22 +5329,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="CX10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9.0</t>
         </is>
       </c>
     </row>
@@ -5381,12 +5381,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5396,139 +5396,139 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-22.77</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-03-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-02-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-02-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>85.4</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>82.4</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>-13.11</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025/09/12</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2026/01/06</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
           <t>73.8</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-41.29</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-03-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-02-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-02-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>82.3</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>85.4</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>82.4</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>79.7</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>-13.58</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>3.26</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025/09/12</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2026/01/06</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
         <is>
           <t>73.8</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
       <c r="AG11" t="inlineStr">
         <is>
           <t>2025/12/15</t>
@@ -5556,17 +5556,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>27.24</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5577,63 +5577,63 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>29.49</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-0.08</v>
+        <v>0.35</v>
       </c>
       <c r="AV11" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>-0.89</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>73.94000000000001</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>73.97</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>74.64</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>74.66</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>15.76</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
         <v>-0.13</v>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>-0.93</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>-0.05</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>73.86</t>
-        </is>
-      </c>
-      <c r="AZ11" t="n">
-        <v>73.95999999999999</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>74.65000000000001</v>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>74.69</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>2.49</t>
-        </is>
-      </c>
-      <c r="BD11" t="n">
-        <v>-0.15</v>
       </c>
       <c r="BE11" t="n">
         <v>-0.15</v>
@@ -5645,7 +5645,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-109.03</t>
+          <t>-108.69</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5655,43 +5655,43 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>3107.892644135189</t>
+          <t>3103.053571428571</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>1326.0</t>
+          <t>5382.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>1339.2</v>
+        <v>2119.4</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>2281.2</t>
+          <t>2744.4</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>1121.24</v>
+        <v>1180.18</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-941</t>
+          <t>-625</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>173.9380749092066</t>
+          <t>190.7832547425293</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>5.975489024892795</t>
+          <t>283.4317438258045</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>1326.0</t>
+          <t>5382.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5821,24 +5821,24 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>74.7</t>
+        </is>
+      </c>
+      <c r="CS11" t="inlineStr">
+        <is>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="CT11" t="inlineStr">
+        <is>
           <t>74.2</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
-        <is>
-          <t>74.5</t>
-        </is>
-      </c>
-      <c r="CS11" t="inlineStr">
-        <is>
-          <t>73.4</t>
-        </is>
-      </c>
-      <c r="CT11" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
       <c r="CU11" t="inlineStr">
         <is>
           <t>34.3</t>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>8.0</t>
         </is>
       </c>
     </row>
@@ -5873,12 +5873,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>21.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-26.57</t>
+          <t>-41.29</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-13.47</t>
+          <t>-13.58</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -6048,17 +6048,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6069,66 +6069,66 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="AV12" t="n">
-        <v>-0.11</v>
+        <v>-0.13</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>73.98</v>
+        <v>73.95999999999999</v>
       </c>
       <c r="BA12" t="n">
-        <v>74.64</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>74.73</t>
+          <t>74.69</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.14</v>
+        <v>-0.15</v>
       </c>
       <c r="BE12" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-109.09</t>
+          <t>-109.03</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6147,43 +6147,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>3107.892644135189</t>
+          <t>3103.053571428571</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>1557.0</t>
+          <t>1326.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>1804.4</v>
+        <v>1339.2</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>2457.4</t>
+          <t>2281.2</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>1110.78</v>
+        <v>1121.24</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-653</t>
+          <t>-941</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>204.4767268881727</t>
+          <t>173.9380749092066</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>43.96742898698722</t>
+          <t>5.975489024892795</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>1557.0</t>
+          <t>1326.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6288,12 +6288,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>27.96</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6313,22 +6313,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="CX12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8.0</t>
         </is>
       </c>
     </row>
@@ -6365,192 +6365,192 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>52.658</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>4.46</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2025-08-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2025-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2025-07-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2025-07-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>32.25</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>32.9</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>32.75</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>-2.33</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025/02/21</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>32.7</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2025/08/28</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>32.2</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>2025/04/08</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>30.65</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>31.6</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>31.6</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>2025-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>5.18</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
           <t>-0.32</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>81.467</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>4.84</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2025-08-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2025-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>2025-07-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2025-07-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>32.25</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>32.9</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>32.75</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>-2.33</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2025/02/21</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>32.7</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2025/08/28</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>32.2</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>2025/04/08</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>30.65</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>31.6</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>31.6</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>2025-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>8.01</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>-0.16</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6561,12 +6561,12 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -6576,18 +6576,18 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-0.44</v>
+        <v>-0.32</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.14</v>
+        <v>0.04</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -6597,27 +6597,27 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>31.64</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>31.6</v>
+        <v>31.59</v>
       </c>
       <c r="BA13" t="n">
-        <v>31.72</v>
+        <v>31.71</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>31.87</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="BE13" t="n">
         <v>-0.04</v>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-114.07</t>
+          <t>-113.78</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6639,43 +6639,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>11320400.26082474</t>
+          <t>11302230.99382716</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>2568418.0</t>
+          <t>1660091.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>3289054.2</v>
+        <v>3220987.4</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>3137217.9</t>
+          <t>3083421.0</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>3324051.1</v>
+        <v>3297756.66</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>151836</t>
+          <t>137566</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-3853.900231664111</t>
+          <t>-16709.90572409765</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>32790.85744653689</t>
+          <t>-87417.93593248213</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>2568418.0</t>
+          <t>1660091.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>25.33</t>
+          <t>25.51</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
@@ -6805,17 +6805,17 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
           <t>31.6</t>
         </is>
       </c>
-      <c r="CR13" t="inlineStr">
-        <is>
-          <t>31.6</t>
-        </is>
-      </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
@@ -6840,29 +6840,29 @@
       </c>
       <c r="CX13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8.0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1270.894</t>
+          <t>81.467</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6902,37 +6902,37 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2024-06-21 00:00:00</t>
+          <t>2025-08-04 00:00:00</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2024-06-27 00:00:00</t>
+          <t>2025-08-20 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2024-05-07 00:00:00</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2024-05-30 00:00:00</t>
+          <t>2025-07-28 00:00:00</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -6957,22 +6957,22 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-32.39</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025/05/15</t>
+          <t>2025/02/21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -6982,52 +6982,52 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2025/11/21</t>
+          <t>2025/08/28</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2025/06/10</t>
+          <t>2025/04/08</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>2026/02/02</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>2025/12/26</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2025-10-13 00:00:00</t>
+          <t>2025-08-20 00:00:00</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
@@ -7037,12 +7037,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>24.30</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -7053,121 +7053,121 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>53</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>-1.37</v>
+        <v>-0.44</v>
       </c>
       <c r="AV14" t="n">
-        <v>-0.74</v>
+        <v>0.14</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>31.64</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>29.42</v>
+        <v>31.6</v>
       </c>
       <c r="BA14" t="n">
-        <v>30.15</v>
+        <v>31.72</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>30.63</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-0.32</v>
+        <v>-0.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0.31</v>
+        <v>-0.04</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-134.70</t>
+          <t>-114.07</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026/01/27</t>
+          <t>2025/12/19</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>35228493.26086956</t>
+          <t>11302230.99382716</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>36466880.0</t>
+          <t>2568418.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>29210335</v>
+        <v>3289054.2</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>27464981.4</t>
+          <t>3137217.9</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>17798828.46</v>
+        <v>3324051.1</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>1745353</t>
+          <t>151836</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>1287431.499790564</t>
+          <t>-3853.900231664111</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>1380371.75931019</t>
+          <t>32790.85744653689</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>36466880.0</t>
+          <t>2568418.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7177,27 +7177,27 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>2025/10/15</t>
+          <t>2025/05/19</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>-15.17</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>臺鹽</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>臺鹽</t>
         </is>
       </c>
       <c r="BX14" t="inlineStr">
@@ -7212,82 +7212,82 @@
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
         <is>
-          <t>6.237608785148733</t>
+          <t>11.30964198266164</t>
         </is>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>-17.09267911306208</t>
+          <t>7.950770160072485</t>
         </is>
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>-3.78772922691385</t>
+          <t>2.099499961706554</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>19.73</t>
+          <t>18.86</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
         <is>
-          <t>23.06%</t>
+          <t>39.76%</t>
         </is>
       </c>
       <c r="CK14" t="inlineStr">
         <is>
-          <t>4.46%</t>
+          <t>11.78%</t>
         </is>
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>25.33</t>
+          <t>25.51</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>26355</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
         <is>
-          <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
+          <t>鹽46.50%、包裝飲用水34.02%、清潔用品5.33%、保健食品5.08%、美容保養品4.12%、工程及勞務2.55%、其他2.39% (2024年)</t>
         </is>
       </c>
       <c r="CO14" t="inlineStr">
         <is>
-          <t>佳格-食品工業-上市</t>
+          <t>臺鹽-食品工業-上市</t>
         </is>
       </c>
       <c r="CP14" t="inlineStr">
@@ -7297,32 +7297,32 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>33.23</t>
         </is>
       </c>
       <c r="CV14" t="inlineStr">
         <is>
-          <t>** 食品 - 營養食品</t>
+          <t>** 食品 - 原物料、營養食品** 石化及塑橡膠 - 化妝品</t>
         </is>
       </c>
       <c r="CW14" t="inlineStr">
@@ -7332,14 +7332,14 @@
       </c>
       <c r="CX14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7349,12 +7349,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>929.211</t>
+          <t>684.565</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7449,7 +7449,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-31.92</t>
+          <t>-32.63</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7524,17 +7524,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>13.09</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7545,12 +7545,12 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>685</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -7560,48 +7560,48 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>-0.99</v>
+        <v>-1.17</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0.64</v>
+        <v>-1.08</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>29.04</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>29.48</v>
+        <v>29.36</v>
       </c>
       <c r="BA15" t="n">
-        <v>30.18</v>
+        <v>30.11</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.61</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-0.3</v>
+        <v>-0.34</v>
       </c>
       <c r="BE15" t="n">
         <v>-0.31</v>
@@ -7613,7 +7613,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-134.41</t>
+          <t>-135.41</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7623,43 +7623,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>35228493.26086956</t>
+          <t>35217063.60946746</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>26982927.0</t>
+          <t>19622440.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>25171849.8</v>
+        <v>25744507.6</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>26932073.1</t>
+          <t>25477935.4</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>17257437.18</v>
+        <v>17954301.62</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-1760223</t>
+          <t>266572</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>1270533.270786996</t>
+          <t>1182905.801034589</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>629678.9128112085</t>
+          <t>608014.4578767233</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>26982927.0</t>
+          <t>19622440.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>-14.58</t>
+          <t>-15.46</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7724,7 +7724,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7749,7 +7749,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>19.73</t>
+          <t>19.66</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>25.33</t>
+          <t>25.51</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>26355</t>
+          <t>26263</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7789,22 +7789,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.55</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7824,14 +7824,14 @@
       </c>
       <c r="CX15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>805.179</t>
+          <t>1270.894</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7866,7 +7866,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-16.58</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-31.46</t>
+          <t>-32.39</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -8016,17 +8016,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>15.40</t>
+          <t>24.30</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -8037,63 +8037,63 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>685</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>64.02</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-0.41</v>
+        <v>-1.37</v>
       </c>
       <c r="AV16" t="n">
-        <v>-0.73</v>
+        <v>-0.74</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>29.32</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>29.54</v>
+        <v>29.42</v>
       </c>
       <c r="BA16" t="n">
-        <v>30.2</v>
+        <v>30.15</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>30.66</t>
+          <t>30.63</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>7.54</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-0.28</v>
+        <v>-0.32</v>
       </c>
       <c r="BE16" t="n">
         <v>-0.31</v>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-134.67</t>
+          <t>-134.70</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8115,43 +8115,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>35228493.26086956</t>
+          <t>35217063.60946746</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>23562195.0</t>
+          <t>36466880.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>22744223.8</v>
+        <v>29210335</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>27263981.0</t>
+          <t>27464981.4</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>16975055.4</v>
+        <v>17798828.46</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-4519757</t>
+          <t>1745353</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>1387052.244964412</t>
+          <t>1287431.499790564</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>550909.8494979739</t>
+          <t>1380371.75931019</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>23562195.0</t>
+          <t>36466880.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>-13.99</t>
+          <t>-15.17</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8216,7 +8216,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>19.73</t>
+          <t>19.66</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>25.33</t>
+          <t>25.51</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>26355</t>
+          <t>26263</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8281,22 +8281,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8316,7 +8316,7 @@
       </c>
       <c r="CX16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -8333,42 +8333,42 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>-0.68</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>929.211</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>29.0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-1.05</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>750.554</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>-2.43</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-15.05</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-30.75</t>
+          <t>-31.92</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8508,17 +8508,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8529,63 +8529,63 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>685</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>65.93</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>0.65</v>
+        <v>-0.99</v>
       </c>
       <c r="AV17" t="n">
-        <v>-0.93</v>
+        <v>-0.64</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>29.58</v>
+        <v>29.48</v>
       </c>
       <c r="BA17" t="n">
-        <v>30.22</v>
+        <v>30.18</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>8.86</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="BE17" t="n">
         <v>-0.31</v>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-135.33</t>
+          <t>-134.41</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8607,43 +8607,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>35228493.26086956</t>
+          <t>35217063.60946746</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>22088096.0</t>
+          <t>26982927.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>22675815.4</v>
+        <v>25171849.8</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>26693420.2</t>
+          <t>26932073.1</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>16884946.42</v>
+        <v>17257437.18</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-4017604</t>
+          <t>-1760223</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>1539078.135049219</t>
+          <t>1270533.270786996</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>785214.264425572</t>
+          <t>629678.9128112085</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>22088096.0</t>
+          <t>26982927.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>-14.58</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8708,22 +8708,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>19.73</t>
+          <t>19.66</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>25.33</t>
+          <t>25.51</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>26355</t>
+          <t>26263</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8773,22 +8773,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8808,7 +8808,7 @@
       </c>
       <c r="CX17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -8825,12 +8825,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1249.819</t>
+          <t>805.179</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -8860,7 +8860,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-16.58</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-30.75</t>
+          <t>-31.46</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -9000,17 +9000,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>23.90</t>
+          <t>15.40</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -9021,67 +9021,67 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>685</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>32.59</t>
+          <t>64.02</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>0.89</v>
+        <v>-0.41</v>
       </c>
       <c r="AV18" t="n">
-        <v>-1.3</v>
+        <v>-0.73</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>29.32</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>29.62</v>
+        <v>29.54</v>
       </c>
       <c r="BA18" t="n">
-        <v>30.24</v>
+        <v>30.2</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>30.66</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="BD18" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="BE18" t="n">
         <v>-0.31</v>
       </c>
-      <c r="BE18" t="n">
-        <v>-0.32</v>
-      </c>
       <c r="BF18" t="inlineStr">
         <is>
           <t>0.89</t>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-136.11</t>
+          <t>-134.67</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9099,43 +9099,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>35228493.26086956</t>
+          <t>35217063.60946746</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>36951577.0</t>
+          <t>23562195.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>25211363.2</v>
+        <v>22744223.8</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>26502871.8</t>
+          <t>27263981.0</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>16852284.6</v>
+        <v>16975055.4</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-1291508</t>
+          <t>-4519757</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>1676144.293344427</t>
+          <t>1387052.244964412</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>1249830.669164084</t>
+          <t>550909.8494979739</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>36951577.0</t>
+          <t>23562195.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>-13.99</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9210,12 +9210,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>19.73</t>
+          <t>19.66</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>25.33</t>
+          <t>25.51</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>26355</t>
+          <t>26263</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9265,22 +9265,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9300,14 +9300,14 @@
       </c>
       <c r="CX18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -9317,12 +9317,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>556.2</t>
+          <t>750.554</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9332,7 +9332,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9342,7 +9342,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-15.05</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-31.34</t>
+          <t>-30.75</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
@@ -9513,66 +9513,66 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>685</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>65.93</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>0.17</v>
+        <v>0.65</v>
       </c>
       <c r="AV19" t="n">
-        <v>-1.61</v>
+        <v>-0.93</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>29.68</v>
+        <v>29.58</v>
       </c>
       <c r="BA19" t="n">
-        <v>30.27</v>
+        <v>30.22</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>30.67</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-7.01</t>
+          <t>8.86</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-0.35</v>
+        <v>-0.29</v>
       </c>
       <c r="BE19" t="n">
-        <v>-0.32</v>
+        <v>-0.31</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-136.30</t>
+          <t>-135.33</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9591,43 +9591,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>35228493.26086956</t>
+          <t>35217063.60946746</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>16274454.0</t>
+          <t>22088096.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>25719627.8</v>
+        <v>22675815.4</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>25467490.4</t>
+          <t>26693420.2</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>16380710.06</v>
+        <v>16884946.42</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>252137</t>
+          <t>-4017604</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>1753655.861377217</t>
+          <t>1539078.135049219</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>276415.7591775246</t>
+          <t>785214.264425572</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>16274454.0</t>
+          <t>22088096.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>-13.84</t>
+          <t>-13.11</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9692,22 +9692,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>19.73</t>
+          <t>19.66</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9732,12 +9732,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>25.33</t>
+          <t>25.51</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>26355</t>
+          <t>26263</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9757,22 +9757,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
+          <t>29.6</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>29.65</t>
+        </is>
+      </c>
+      <c r="CS19" t="inlineStr">
+        <is>
           <t>29.3</t>
         </is>
       </c>
-      <c r="CR19" t="inlineStr">
-        <is>
-          <t>29.35</t>
-        </is>
-      </c>
-      <c r="CS19" t="inlineStr">
-        <is>
-          <t>29.1</t>
-        </is>
-      </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9792,14 +9792,14 @@
       </c>
       <c r="CX19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9809,42 +9809,42 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1249.819</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-2.79</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>508.716</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>29.15</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>-1.22</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-31.57</t>
+          <t>-30.75</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9934,7 +9934,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9984,17 +9984,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>23.90</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -10005,63 +10005,63 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>685</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>32.59</t>
         </is>
       </c>
       <c r="AU20" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>-2.05</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>-1.42</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>29.24</t>
+        </is>
+      </c>
+      <c r="AZ20" t="n">
+        <v>29.62</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>30.68</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="BD20" t="n">
         <v>-0.31</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>-1.86</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>-1.30</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>29.24</t>
-        </is>
-      </c>
-      <c r="AZ20" t="n">
-        <v>29.74</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>30.7</t>
-        </is>
-      </c>
-      <c r="BC20" t="inlineStr">
-        <is>
-          <t>-11.84</t>
-        </is>
-      </c>
-      <c r="BD20" t="n">
-        <v>-0.35</v>
       </c>
       <c r="BE20" t="n">
         <v>-0.32</v>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-135.66</t>
+          <t>-136.11</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -10083,43 +10083,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>35228493.26086956</t>
+          <t>35217063.60946746</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>14844797.0</t>
+          <t>36951577.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>28692296.4</v>
+        <v>25211363.2</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>26444131.4</t>
+          <t>26502871.8</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>16324390.42</v>
+        <v>16852284.6</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>2248165</t>
+          <t>-1291508</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>2022244.97086807</t>
+          <t>1676144.293344427</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>1091357.074940387</t>
+          <t>1249830.669164084</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>14844797.0</t>
+          <t>36951577.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-14.14</t>
+          <t>-13.11</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10184,22 +10184,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>19.73</t>
+          <t>19.66</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>25.33</t>
+          <t>25.51</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>26355</t>
+          <t>26263</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10249,22 +10249,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="CS20" t="inlineStr">
+        <is>
           <t>29.3</t>
         </is>
       </c>
-      <c r="CS20" t="inlineStr">
-        <is>
-          <t>29.1</t>
-        </is>
-      </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="CX20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -10301,42 +10301,42 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>556.2</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>29.25</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-1.92</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>796.89</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>29.15</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>-1.22</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-31.57</t>
+          <t>-31.34</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10476,17 +10476,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10497,66 +10497,66 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>685</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-0.55</v>
+        <v>0.17</v>
       </c>
       <c r="AV21" t="n">
-        <v>-1.66</v>
+        <v>-1.61</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>29.8</v>
+        <v>29.68</v>
       </c>
       <c r="BA21" t="n">
-        <v>30.33</v>
+        <v>30.27</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>30.72</t>
+          <t>30.69</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-14.09</t>
+          <t>-7.01</t>
         </is>
       </c>
       <c r="BD21" t="n">
         <v>-0.35</v>
       </c>
       <c r="BE21" t="n">
-        <v>-0.31</v>
+        <v>-0.32</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-134.61</t>
+          <t>-136.30</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10575,43 +10575,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>35228493.26086956</t>
+          <t>35217063.60946746</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>23220153.0</t>
+          <t>16274454.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>31783738.2</v>
+        <v>25719627.8</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>26663589.6</t>
+          <t>25467490.4</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>16268239.9</v>
+        <v>16380710.06</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>5120148</t>
+          <t>252137</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>2191497.315582194</t>
+          <t>1753655.861377217</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>2369759.451925177</t>
+          <t>276415.7591775246</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>23220153.0</t>
+          <t>16274454.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10631,7 +10631,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-14.14</t>
+          <t>-13.84</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10676,22 +10676,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>19.73</t>
+          <t>19.66</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>25.33</t>
+          <t>25.51</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>26355</t>
+          <t>26263</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10741,24 +10741,24 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
+          <t>29.35</t>
+        </is>
+      </c>
+      <c r="CS21" t="inlineStr">
+        <is>
+          <t>29.1</t>
+        </is>
+      </c>
+      <c r="CT21" t="inlineStr">
+        <is>
           <t>29.25</t>
         </is>
       </c>
-      <c r="CS21" t="inlineStr">
-        <is>
-          <t>29.05</t>
-        </is>
-      </c>
-      <c r="CT21" t="inlineStr">
-        <is>
-          <t>29.15</t>
-        </is>
-      </c>
       <c r="CU21" t="inlineStr">
         <is>
           <t>19.66</t>
@@ -10776,7 +10776,7 @@
       </c>
       <c r="CX21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -10793,12 +10793,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1191.884</t>
+          <t>508.716</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10818,7 +10818,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>12.12</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10918,7 +10918,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10968,12 +10968,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>22.79</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
@@ -10989,12 +10989,12 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>685</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -11008,47 +11008,47 @@
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>-0.85</v>
+        <v>-0.31</v>
       </c>
       <c r="AV22" t="n">
-        <v>-1.61</v>
+        <v>-1.67</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.24</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>29.88</v>
+        <v>29.74</v>
       </c>
       <c r="BA22" t="n">
-        <v>30.36</v>
+        <v>30.3</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>30.73</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-15.00</t>
+          <t>-11.84</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>-0.34</v>
+        <v>-0.35</v>
       </c>
       <c r="BE22" t="n">
-        <v>-0.3</v>
+        <v>-0.32</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-133.39</t>
+          <t>-135.66</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -11067,43 +11067,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>35228493.26086956</t>
+          <t>35217063.60946746</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>34765835.0</t>
+          <t>14844797.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>30711025</v>
+        <v>28692296.4</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>27390013.9</t>
+          <t>26444131.4</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>16109008.78</v>
+        <v>16324390.42</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>3321011</t>
+          <t>2248165</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>2159086.018065288</t>
+          <t>2022244.97086807</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>3214054.724334691</t>
+          <t>1091357.074940387</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>34765835.0</t>
+          <t>14844797.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
@@ -11183,7 +11183,7 @@
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>19.73</t>
+          <t>19.66</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>25.33</t>
+          <t>25.51</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>26355</t>
+          <t>26263</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
@@ -11268,7 +11268,7 @@
       </c>
       <c r="CX22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -11285,12 +11285,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1347.009</t>
+          <t>796.89</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>19.20</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11385,7 +11385,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-31.22</t>
+          <t>-31.57</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11460,17 +11460,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>15.24</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11481,12 +11481,12 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>685</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -11500,47 +11500,47 @@
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>-0.68</v>
+        <v>-0.55</v>
       </c>
       <c r="AV23" t="n">
-        <v>-1.54</v>
+        <v>-1.66</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>29.96</v>
+        <v>29.8</v>
       </c>
       <c r="BA23" t="n">
-        <v>30.4</v>
+        <v>30.33</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>30.72</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-13.44</t>
+          <t>-14.09</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>-0.32</v>
+        <v>-0.35</v>
       </c>
       <c r="BE23" t="n">
-        <v>-0.29</v>
+        <v>-0.31</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-132.14</t>
+          <t>-134.61</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11559,43 +11559,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>35228493.26086956</t>
+          <t>35217063.60946746</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>39492900.0</t>
+          <t>23220153.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>27794380.4</v>
+        <v>31783738.2</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>26393933.9</t>
+          <t>26663589.6</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>15869794.14</v>
+        <v>16268239.9</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>1400446</t>
+          <t>5120148</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>1967273.526016306</t>
+          <t>2191497.315582194</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>3068365.801907759</t>
+          <t>2369759.451925177</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>39492900.0</t>
+          <t>23220153.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11615,7 +11615,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>-14.14</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11660,22 +11660,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11685,7 +11685,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>19.73</t>
+          <t>19.66</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>25.33</t>
+          <t>25.51</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>26355</t>
+          <t>26263</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11725,22 +11725,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>29.35</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.25</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.05</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11760,7 +11760,7 @@
       </c>
       <c r="CX23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -11777,12 +11777,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1056.469</t>
+          <t>1191.884</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11802,7 +11802,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-2.26</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>12.12</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-30.87</t>
+          <t>-31.57</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -11902,7 +11902,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11952,17 +11952,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>20.20</t>
+          <t>22.79</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11973,12 +11973,12 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>685</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -11988,52 +11988,52 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU24" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>-1.59</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>-1.19</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>29.4</t>
+        </is>
+      </c>
+      <c r="AZ24" t="n">
+        <v>29.88</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>30.36</v>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>30.73</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>-15.00</t>
+        </is>
+      </c>
+      <c r="BD24" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="BE24" t="n">
         <v>-0.3</v>
       </c>
-      <c r="AV24" t="n">
-        <v>-1.66</v>
-      </c>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>-1.32</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>-1.02</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>29.54</t>
-        </is>
-      </c>
-      <c r="AZ24" t="n">
-        <v>30.04</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>30.44</v>
-      </c>
-      <c r="BB24" t="inlineStr">
-        <is>
-          <t>30.75</t>
-        </is>
-      </c>
-      <c r="BC24" t="inlineStr">
-        <is>
-          <t>-13.22</t>
-        </is>
-      </c>
-      <c r="BD24" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>-0.28</v>
-      </c>
       <c r="BF24" t="inlineStr">
         <is>
           <t>0.89</t>
@@ -12041,7 +12041,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-131.06</t>
+          <t>-133.39</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -12051,43 +12051,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>35228493.26086956</t>
+          <t>35217063.60946746</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>31137797.0</t>
+          <t>34765835.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>25215353</v>
+        <v>30711025</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>24579775.5</t>
+          <t>27390013.9</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>15430798.08</v>
+        <v>16109008.78</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>635577</t>
+          <t>3321011</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>1767074.930399678</t>
+          <t>2159086.018065288</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>2244183.026944011</t>
+          <t>3214054.724334691</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>31137797.0</t>
+          <t>34765835.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -12107,7 +12107,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>-13.25</t>
+          <t>-14.14</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.88</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12177,7 +12177,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>19.73</t>
+          <t>19.66</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12192,12 +12192,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>25.33</t>
+          <t>25.51</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>26355</t>
+          <t>26263</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12217,42 +12217,534 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
+          <t>29.2</t>
+        </is>
+      </c>
+      <c r="CR24" t="inlineStr">
+        <is>
+          <t>29.3</t>
+        </is>
+      </c>
+      <c r="CS24" t="inlineStr">
+        <is>
+          <t>29.1</t>
+        </is>
+      </c>
+      <c r="CT24" t="inlineStr">
+        <is>
+          <t>29.15</t>
+        </is>
+      </c>
+      <c r="CU24" t="inlineStr">
+        <is>
+          <t>19.66</t>
+        </is>
+      </c>
+      <c r="CV24" t="inlineStr">
+        <is>
+          <t>** 食品 - 營養食品</t>
+        </is>
+      </c>
+      <c r="CW24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CX24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>-0.51</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1347.009</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>29.3</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-2.09</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>5.31</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2024-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2024-06-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2024-05-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2024-05-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>43.0</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>42.6</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>38.75</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>40.75</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>-31.22</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>5.52</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025/05/15</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>35.5</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>30.5</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>33.25</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>2026/02/02</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>2025/12/26</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>30.45</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>25.76</t>
+        </is>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>-0.34</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU25" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>-1.43</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>-1.12</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="CR24" t="inlineStr">
-        <is>
-          <t>29.65</t>
-        </is>
-      </c>
-      <c r="CS24" t="inlineStr">
+      <c r="AZ25" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>30.74</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>-13.44</t>
+        </is>
+      </c>
+      <c r="BD25" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="BF25" t="inlineStr">
+        <is>
+          <t>0.89</t>
+        </is>
+      </c>
+      <c r="BG25" t="inlineStr">
+        <is>
+          <t>-132.14</t>
+        </is>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026/01/27</t>
+        </is>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>35217063.60946746</t>
+        </is>
+      </c>
+      <c r="BJ25" t="inlineStr">
+        <is>
+          <t>39492900.0</t>
+        </is>
+      </c>
+      <c r="BK25" t="n">
+        <v>27794380.4</v>
+      </c>
+      <c r="BL25" t="inlineStr">
+        <is>
+          <t>26393933.9</t>
+        </is>
+      </c>
+      <c r="BM25" t="n">
+        <v>15869794.14</v>
+      </c>
+      <c r="BN25" t="inlineStr">
+        <is>
+          <t>1400446</t>
+        </is>
+      </c>
+      <c r="BO25" t="inlineStr">
+        <is>
+          <t>1967273.526016306</t>
+        </is>
+      </c>
+      <c r="BP25" t="inlineStr">
+        <is>
+          <t>3068365.801907759</t>
+        </is>
+      </c>
+      <c r="BQ25" t="inlineStr">
+        <is>
+          <t>39492900.0</t>
+        </is>
+      </c>
+      <c r="BR25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS25" t="inlineStr">
+        <is>
+          <t>33.95</t>
+        </is>
+      </c>
+      <c r="BT25" t="inlineStr">
+        <is>
+          <t>2025/10/15</t>
+        </is>
+      </c>
+      <c r="BU25" t="inlineStr">
+        <is>
+          <t>-13.70</t>
+        </is>
+      </c>
+      <c r="BV25" t="inlineStr">
+        <is>
+          <t>佳格</t>
+        </is>
+      </c>
+      <c r="BW25" t="inlineStr">
+        <is>
+          <t>佳格</t>
+        </is>
+      </c>
+      <c r="BX25" t="inlineStr">
+        <is>
+          <t>食品工業</t>
+        </is>
+      </c>
+      <c r="BY25" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ25" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
+      <c r="CA25" t="inlineStr">
+        <is>
+          <t>6.237608785148733</t>
+        </is>
+      </c>
+      <c r="CB25" t="inlineStr">
+        <is>
+          <t>-17.09267911306208</t>
+        </is>
+      </c>
+      <c r="CC25" t="inlineStr">
+        <is>
+          <t>-3.78772922691385</t>
+        </is>
+      </c>
+      <c r="CD25" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="CE25" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF25" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="CG25" t="inlineStr">
+        <is>
+          <t>4.88</t>
+        </is>
+      </c>
+      <c r="CH25" t="inlineStr">
+        <is>
+          <t>8.02</t>
+        </is>
+      </c>
+      <c r="CI25" t="inlineStr">
+        <is>
+          <t>19.66</t>
+        </is>
+      </c>
+      <c r="CJ25" t="inlineStr">
+        <is>
+          <t>23.06%</t>
+        </is>
+      </c>
+      <c r="CK25" t="inlineStr">
+        <is>
+          <t>4.46%</t>
+        </is>
+      </c>
+      <c r="CL25" t="inlineStr">
+        <is>
+          <t>25.51</t>
+        </is>
+      </c>
+      <c r="CM25" t="inlineStr">
+        <is>
+          <t>26263</t>
+        </is>
+      </c>
+      <c r="CN25" t="inlineStr">
+        <is>
+          <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO25" t="inlineStr">
+        <is>
+          <t>佳格-食品工業-上市</t>
+        </is>
+      </c>
+      <c r="CP25" t="inlineStr">
+        <is>
+          <t>食品工業右下上市</t>
+        </is>
+      </c>
+      <c r="CQ25" t="inlineStr">
+        <is>
+          <t>29.35</t>
+        </is>
+      </c>
+      <c r="CR25" t="inlineStr">
+        <is>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="CS25" t="inlineStr">
+        <is>
+          <t>29.25</t>
+        </is>
+      </c>
+      <c r="CT25" t="inlineStr">
         <is>
           <t>29.3</t>
         </is>
       </c>
-      <c r="CT24" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="CU24" t="inlineStr">
+      <c r="CU25" t="inlineStr">
         <is>
           <t>19.66</t>
         </is>
       </c>
-      <c r="CV24" t="inlineStr">
+      <c r="CV25" t="inlineStr">
         <is>
           <t>** 食品 - 營養食品</t>
         </is>
       </c>
-      <c r="CW24" t="inlineStr">
+      <c r="CW25" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX24" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="CX25" t="inlineStr">
+        <is>
+          <t>0.0</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/營養食品.xlsx
+++ b/Result/checksun_type/營養食品.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CX25"/>
+  <dimension ref="A1:CY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -939,11 +939,16 @@
           <t>盤整震盪_前15日次數</t>
         </is>
       </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>多頭排列_前5日次數</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【d1】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -978,14 +983,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>-30.73</t>
@@ -998,37 +1003,37 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2025-03-06 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-03-25 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2025-02-10 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2025-02-17 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -1038,12 +1043,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -1053,12 +1058,12 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-12.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -1123,7 +1128,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2026-01-12 00:00:00</t>
+          <t>2025-06-13 00:00:00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1149,12 +1154,12 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1227,7 +1232,7 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>3103.053571428571</t>
+          <t>3560.736</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1253,12 +1258,12 @@
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>29.3649364128487</t>
+          <t>29.36493641285267</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-137.1350585433199</t>
+          <t>-137.135058543319</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1343,7 +1348,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1353,7 +1358,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1368,12 +1373,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>28.01</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,7 +1393,7 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>食品工業右下上櫃</t>
+          <t>食品工業平上櫃</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
@@ -1428,7 +1433,12 @@
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1480,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1490,37 +1500,37 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2025-03-06 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-03-25 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2025-02-10 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2025-02-17 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1530,12 +1540,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -1545,12 +1555,12 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1615,7 +1625,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2026-01-12 00:00:00</t>
+          <t>2025-06-13 00:00:00</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1641,12 +1651,12 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1719,7 +1729,7 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>3103.053571428571</t>
+          <t>3560.736</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1745,12 +1755,12 @@
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>59.63766276851573</t>
+          <t>59.63766276852026</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-46.09411818075841</t>
+          <t>-46.0941181807575</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1835,7 +1845,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1845,7 +1855,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1860,12 +1870,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>28.01</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1880,7 +1890,7 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>食品工業右下上櫃</t>
+          <t>食品工業平上櫃</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
@@ -1920,7 +1930,12 @@
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1977,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1982,37 +1997,37 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2025-03-06 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-03-25 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2025-02-10 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2025-02-17 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -2022,12 +2037,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -2037,12 +2052,12 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -2107,7 +2122,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2026-01-12 00:00:00</t>
+          <t>2025-06-13 00:00:00</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -2133,12 +2148,12 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2169,7 +2184,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>74.36</t>
+          <t>74.35999999999999</t>
         </is>
       </c>
       <c r="AZ4" t="n">
@@ -2211,7 +2226,7 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>3103.053571428571</t>
+          <t>3560.736</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -2237,12 +2252,12 @@
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>78.86162294111104</t>
+          <t>78.86162294111622</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-26.46084201350072</t>
+          <t>-26.46084201349981</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2327,7 +2342,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2337,7 +2352,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2352,12 +2367,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>28.01</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2372,7 +2387,7 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>食品工業右下上櫃</t>
+          <t>食品工業平上櫃</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
@@ -2412,7 +2427,12 @@
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2474,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2474,37 +2494,37 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2025-03-06 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-03-25 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2025-02-10 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2025-02-17 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -2514,12 +2534,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -2529,12 +2549,12 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -2599,7 +2619,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2026-01-12 00:00:00</t>
+          <t>2025-06-13 00:00:00</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -2625,12 +2645,12 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2661,7 +2681,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>74.42</t>
+          <t>74.41999999999999</t>
         </is>
       </c>
       <c r="AZ5" t="n">
@@ -2703,7 +2723,7 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>3103.053571428571</t>
+          <t>3560.736</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2729,12 +2749,12 @@
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>98.01116202376772</t>
+          <t>98.0111620237737</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-20.07541741693626</t>
+          <t>-20.07541741693512</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2819,7 +2839,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2829,7 +2849,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2844,12 +2864,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>28.01</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2864,7 +2884,7 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>食品工業右下上櫃</t>
+          <t>食品工業平上櫃</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
@@ -2904,7 +2924,12 @@
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="CY5" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2946,109 +2971,109 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-13.36</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025/09/12</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-13.36</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-03-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-02-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-02-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>82.3</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>85.4</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>82.4</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>79.7</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>-12.76</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>3.26</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025/09/12</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>2026/01/06</t>
@@ -3091,7 +3116,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2026-01-12 00:00:00</t>
+          <t>2025-06-13 00:00:00</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -3117,12 +3142,12 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -3153,7 +3178,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>74.35999999999999</t>
+          <t>74.36</t>
         </is>
       </c>
       <c r="AZ6" t="n">
@@ -3195,7 +3220,7 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>3103.053571428571</t>
+          <t>3560.736</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
@@ -3221,12 +3246,12 @@
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>119.4814491948048</t>
+          <t>119.4814491948117</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>19.65645405733221</t>
+          <t>19.65645405733358</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3311,7 +3336,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3321,7 +3346,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3336,12 +3361,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>28.01</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3356,7 +3381,7 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>食品工業右下上櫃</t>
+          <t>食品工業平上櫃</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
@@ -3396,7 +3421,12 @@
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="CY6" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3438,7 +3468,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3458,37 +3488,37 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2025-03-06 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-03-25 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2025-02-10 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2025-02-17 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -3498,12 +3528,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -3513,12 +3543,12 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-12.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -3583,7 +3613,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2026-01-12 00:00:00</t>
+          <t>2025-06-13 00:00:00</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3609,12 +3639,12 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3649,7 +3679,7 @@
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>74.09</v>
+        <v>74.08</v>
       </c>
       <c r="BA7" t="n">
         <v>74.41</v>
@@ -3687,7 +3717,7 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>3103.053571428571</t>
+          <t>3560.736</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
@@ -3713,12 +3743,12 @@
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>137.6314483107089</t>
+          <t>137.6314483107168</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>82.78568280423974</t>
+          <t>82.78568280424133</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3803,7 +3833,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3813,7 +3843,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3828,12 +3858,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>28.01</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3848,7 +3878,7 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>食品工業右下上櫃</t>
+          <t>食品工業平上櫃</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
@@ -3888,7 +3918,12 @@
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="CY7" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3930,7 +3965,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3950,37 +3985,37 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2025-03-06 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-03-25 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2025-02-10 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2025-02-17 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -3990,12 +4025,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -4005,12 +4040,12 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-13.00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -4075,7 +4110,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2026-01-12 00:00:00</t>
+          <t>2025-06-13 00:00:00</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -4101,12 +4136,12 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -4137,7 +4172,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>74.14</t>
+          <t>74.14000000000001</t>
         </is>
       </c>
       <c r="AZ8" t="n">
@@ -4179,7 +4214,7 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>3103.053571428571</t>
+          <t>3560.736</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
@@ -4205,12 +4240,12 @@
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>147.6034056755215</t>
+          <t>147.6034056755305</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>40.37080662824201</t>
+          <t>40.37080662824383</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4295,7 +4330,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4305,7 +4340,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4320,12 +4355,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>28.01</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4340,7 +4375,7 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>食品工業右下上櫃</t>
+          <t>食品工業平上櫃</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
@@ -4380,7 +4415,12 @@
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="CY8" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4422,14 +4462,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>12.70</t>
@@ -4442,37 +4482,37 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2025-03-06 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-03-25 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2025-02-10 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2025-02-17 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -4482,12 +4522,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -4497,12 +4537,12 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-12.76</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -4567,7 +4607,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2026-01-12 00:00:00</t>
+          <t>2025-06-13 00:00:00</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -4593,12 +4633,12 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4633,7 +4673,7 @@
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>74</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="BA9" t="n">
         <v>74.53</v>
@@ -4671,7 +4711,7 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>3103.053571428571</t>
+          <t>3560.736</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
@@ -4697,12 +4737,12 @@
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>167.100241865936</t>
+          <t>167.1002418659462</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>61.69345471152246</t>
+          <t>61.69345471152451</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4777,7 +4817,7 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4787,7 +4827,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4797,7 +4837,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4812,12 +4852,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>28.01</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4832,7 +4872,7 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>食品工業右下上櫃</t>
+          <t>食品工業平上櫃</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
@@ -4872,7 +4912,12 @@
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="CY9" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4959,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4934,37 +4979,37 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2025-03-06 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-03-25 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2025-02-10 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2025-02-17 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -4974,12 +5019,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -4989,12 +5034,12 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-13.47</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -5059,7 +5104,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2026-01-12 00:00:00</t>
+          <t>2025-06-13 00:00:00</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -5085,12 +5130,12 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -5121,7 +5166,7 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.00000000000001</t>
         </is>
       </c>
       <c r="AZ10" t="n">
@@ -5153,7 +5198,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-108.44</t>
+          <t>-108.45</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5163,7 +5208,7 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>3103.053571428571</t>
+          <t>3560.736</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
@@ -5189,12 +5234,12 @@
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>186.2651122576475</t>
+          <t>186.2651122576593</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>161.4153285907973</t>
+          <t>161.4153285907996</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -5269,7 +5314,7 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -5279,7 +5324,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5289,7 +5334,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5304,12 +5349,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>28.01</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5324,7 +5369,7 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>食品工業右下上櫃</t>
+          <t>食品工業平上櫃</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
@@ -5364,7 +5409,12 @@
       </c>
       <c r="CX10" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="CY10" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5456,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5426,37 +5476,37 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2025-03-06 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-03-25 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2025-02-10 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2025-02-17 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -5466,12 +5516,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -5481,12 +5531,12 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -5551,7 +5601,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2026-01-12 00:00:00</t>
+          <t>2025-06-13 00:00:00</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -5577,12 +5627,12 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5613,7 +5663,7 @@
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>73.94000000000001</t>
+          <t>73.94</t>
         </is>
       </c>
       <c r="AZ11" t="n">
@@ -5655,7 +5705,7 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>3103.053571428571</t>
+          <t>3560.736</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
@@ -5681,12 +5731,12 @@
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>190.7832547425293</t>
+          <t>190.7832547425429</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>283.4317438258045</t>
+          <t>283.4317438258072</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5771,7 +5821,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5781,7 +5831,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5796,12 +5846,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>28.01</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5816,7 +5866,7 @@
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>食品工業右下上櫃</t>
+          <t>食品工業平上櫃</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
@@ -5856,29 +5906,34 @@
       </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="CY11" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6846</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>52.658</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5888,7 +5943,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5898,7 +5953,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5908,7 +5963,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-41.29</t>
+          <t>4.46</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5918,37 +5973,37 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-65.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2025-03-06 00:00:00</t>
+          <t>2025-08-04 00:00:00</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-03-25 00:00:00</t>
+          <t>2025-08-20 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2025-02-10 00:00:00</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2025-02-17 00:00:00</t>
+          <t>2025-07-28 00:00:00</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -5958,12 +6013,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -5973,22 +6028,22 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-13.58</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025/09/12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -6003,62 +6058,62 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026/01/06</t>
+          <t>2025/08/28</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2025/10/22</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025/12/15</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2025/12/11</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2026-01-12 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>6.72</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6069,121 +6124,121 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>-0.08</v>
+        <v>-0.32</v>
       </c>
       <c r="AV12" t="n">
-        <v>-0.13</v>
+        <v>0.04</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>73.95999999999999</v>
+        <v>31.59</v>
       </c>
       <c r="BA12" t="n">
-        <v>74.65000000000001</v>
+        <v>31.71</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>74.69</t>
+          <t>31.87</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.15</v>
+        <v>-0.04</v>
       </c>
       <c r="BE12" t="n">
-        <v>-0.15</v>
+        <v>-0.04</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-109.03</t>
+          <t>-118.35</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026/01/08</t>
+          <t>2025/12/19</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>3103.053571428571</t>
+          <t>5770029.975982533</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>1326.0</t>
+          <t>1660091.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>1339.2</v>
+        <v>3220987.4</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>2281.2</t>
+          <t>3083421.0</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>1121.24</v>
+        <v>3297756.66</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-941</t>
+          <t>137566</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>173.9380749092066</t>
+          <t>-16709.90572457966</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>5.975489024892795</t>
+          <t>-87417.93593258597</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>1326.0</t>
+          <t>1660091.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6193,27 +6248,27 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2025/12/04</t>
+          <t>2025/05/19</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>綠茵</t>
+          <t>臺鹽</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>綠茵</t>
+          <t>臺鹽</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
@@ -6223,32 +6278,32 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>43.18290500198112</t>
+          <t>11.30964198266164</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>12.18914260633116</t>
+          <t>7.950770160072485</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>4.818590014463328</t>
+          <t>2.099499961706554</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6258,87 +6313,87 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>7.61</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>48.81%</t>
+          <t>39.76%</t>
         </is>
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>17.38%</t>
+          <t>11.78%</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>25.62</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>保健食品配方65.97%、保健食品原料33.59%、其他0.43% (2024年)</t>
+          <t>鹽46.50%、包裝飲用水34.02%、清潔用品5.33%、保健食品5.08%、美容保養品4.12%、工程及勞務2.55%、其他2.39% (2024年)</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>綠茵-食品工業-上櫃</t>
+          <t>臺鹽-食品工業-上市</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>食品工業右下上櫃</t>
+          <t>食品工業右下上市</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
         <is>
-          <t>34.3</t>
+          <t>33.23</t>
         </is>
       </c>
       <c r="CV12" t="inlineStr">
         <is>
-          <t>** 食品 - 原物料、加工食品、營養食品** 食品生技 - 原料、加工製成品</t>
+          <t>** 食品 - 原物料、營養食品** 石化及塑橡膠 - 化妝品</t>
         </is>
       </c>
       <c r="CW12" t="inlineStr">
@@ -6348,7 +6403,12 @@
       </c>
       <c r="CX12" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="CY12" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -6365,42 +6425,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>-0.32</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>81.467</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>52.658</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6475,12 +6535,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025/02/21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -6505,12 +6565,12 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2025/04/08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
@@ -6535,22 +6595,22 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6561,12 +6621,12 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>102</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -6576,18 +6636,18 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-0.32</v>
+        <v>-0.44</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.04</v>
+        <v>0.14</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -6597,39 +6657,39 @@
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>31.64</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>31.59</v>
+        <v>31.6</v>
       </c>
       <c r="BA13" t="n">
-        <v>31.71</v>
+        <v>31.72</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="BE13" t="n">
         <v>-0.04</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-113.78</t>
+          <t>-118.73</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6639,43 +6699,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>11302230.99382716</t>
+          <t>5770029.975982533</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>1660091.0</t>
+          <t>2568418.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>3220987.4</v>
+        <v>3289054.2</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>3083421.0</t>
+          <t>3137217.9</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>3297756.66</v>
+        <v>3324051.1</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>137566</t>
+          <t>151836</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-16709.90572409765</t>
+          <t>-3853.900232214874</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-87417.93593248213</t>
+          <t>32790.85744641861</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>1660091.0</t>
+          <t>2568418.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6740,7 +6800,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6755,7 +6815,7 @@
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6765,7 +6825,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6780,12 +6840,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>25.51</t>
+          <t>25.62</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6805,24 +6865,24 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
+          <t>31.6</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>31.6</t>
+        </is>
+      </c>
+      <c r="CS13" t="inlineStr">
+        <is>
+          <t>31.45</t>
+        </is>
+      </c>
+      <c r="CT13" t="inlineStr">
+        <is>
           <t>31.5</t>
         </is>
       </c>
-      <c r="CR13" t="inlineStr">
-        <is>
-          <t>31.6</t>
-        </is>
-      </c>
-      <c r="CS13" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
-      </c>
-      <c r="CT13" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
-      </c>
       <c r="CU13" t="inlineStr">
         <is>
           <t>33.23</t>
@@ -6840,29 +6900,34 @@
       </c>
       <c r="CX13" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="CY13" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1737</t>
+          <t>1227</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>81.467</t>
+          <t>686.442</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6872,7 +6937,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6892,7 +6957,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>5.41</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6907,32 +6972,32 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2025-08-04 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2025-07-25 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2025-07-28 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>33.05</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -6942,12 +7007,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>32.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -6957,22 +7022,22 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025/02/21</t>
+          <t>2025/05/15</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>35.5</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -6982,67 +7047,67 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2025/08/28</t>
+          <t>2025/11/21</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2025/04/08</t>
+          <t>2025/06/10</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>33.25</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>2025/12/10</t>
+          <t>2026/02/02</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>2025/12/08</t>
+          <t>2025/12/26</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>30.45</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2026-01-22 00:00:00</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -7053,121 +7118,121 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>686</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>-0.44</v>
+        <v>-0.48</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.14</v>
+        <v>-1.42</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>31.64</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>31.6</v>
+        <v>29.3</v>
       </c>
       <c r="BA14" t="n">
-        <v>31.72</v>
+        <v>30.07</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-0.03</v>
+        <v>-0.35</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0.04</v>
+        <v>-0.32</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-114.07</t>
+          <t>-163.53</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2025/12/19</t>
+          <t>2026/01/27</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>11302230.99382716</t>
+          <t>30792858.1314741</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>2568418.0</t>
+          <t>19713512.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>3289054.2</v>
+        <v>25269590.8</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>3137217.9</t>
+          <t>23972703.1</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>3324051.1</v>
+        <v>17993919.1</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>151836</t>
+          <t>1296887</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-3853.900231664111</t>
+          <t>1009996.352479468</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>32790.85744653689</t>
+          <t>58994.38542637974</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>2568418.0</t>
+          <t>19713512.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7177,27 +7242,27 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>2025/05/19</t>
+          <t>2025/10/15</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>臺鹽</t>
+          <t>佳格</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
         <is>
-          <t>臺鹽</t>
+          <t>佳格</t>
         </is>
       </c>
       <c r="BX14" t="inlineStr">
@@ -7212,27 +7277,27 @@
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
         <is>
-          <t>11.30964198266164</t>
+          <t>6.237608785148733</t>
         </is>
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>7.950770160072485</t>
+          <t>-17.09267911306208</t>
         </is>
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>2.099499961706554</t>
+          <t>-3.78772922691385</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
@@ -7242,52 +7307,52 @@
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>18.86</t>
+          <t>19.69</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
         <is>
-          <t>39.76%</t>
+          <t>23.06%</t>
         </is>
       </c>
       <c r="CK14" t="inlineStr">
         <is>
-          <t>11.78%</t>
+          <t>4.46%</t>
         </is>
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>25.51</t>
+          <t>25.62</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>26309</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
         <is>
-          <t>鹽46.50%、包裝飲用水34.02%、清潔用品5.33%、保健食品5.08%、美容保養品4.12%、工程及勞務2.55%、其他2.39% (2024年)</t>
+          <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
         </is>
       </c>
       <c r="CO14" t="inlineStr">
         <is>
-          <t>臺鹽-食品工業-上市</t>
+          <t>佳格-食品工業-上市</t>
         </is>
       </c>
       <c r="CP14" t="inlineStr">
@@ -7297,32 +7362,32 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>28.55</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
         <is>
-          <t>33.23</t>
+          <t>19.66</t>
         </is>
       </c>
       <c r="CV14" t="inlineStr">
         <is>
-          <t>** 食品 - 原物料、營養食品** 石化及塑橡膠 - 化妝品</t>
+          <t>** 食品 - 營養食品</t>
         </is>
       </c>
       <c r="CW14" t="inlineStr">
@@ -7332,7 +7397,12 @@
       </c>
       <c r="CX14" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY14" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -7374,14 +7444,14 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>0.17</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>1.05</t>
@@ -7394,37 +7464,37 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2024-06-21 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2024-06-27 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2024-05-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2024-05-30 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -7434,12 +7504,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -7449,12 +7519,12 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-32.63</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -7519,7 +7589,7 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2025-10-13 00:00:00</t>
+          <t>2026-01-22 00:00:00</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
@@ -7545,12 +7615,12 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>686</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -7608,12 +7678,12 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-135.41</t>
+          <t>-162.18</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7623,7 +7693,7 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>35217063.60946746</t>
+          <t>30792858.1314741</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -7649,12 +7719,12 @@
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>1182905.801034589</t>
+          <t>1182905.801034575</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>608014.4578767233</t>
+          <t>608014.4578767195</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -7739,7 +7809,7 @@
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7749,69 +7819,69 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
+          <t>19.69</t>
+        </is>
+      </c>
+      <c r="CJ15" t="inlineStr">
+        <is>
+          <t>23.06%</t>
+        </is>
+      </c>
+      <c r="CK15" t="inlineStr">
+        <is>
+          <t>4.46%</t>
+        </is>
+      </c>
+      <c r="CL15" t="inlineStr">
+        <is>
+          <t>25.62</t>
+        </is>
+      </c>
+      <c r="CM15" t="inlineStr">
+        <is>
+          <t>26309</t>
+        </is>
+      </c>
+      <c r="CN15" t="inlineStr">
+        <is>
+          <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO15" t="inlineStr">
+        <is>
+          <t>佳格-食品工業-上市</t>
+        </is>
+      </c>
+      <c r="CP15" t="inlineStr">
+        <is>
+          <t>食品工業右下上市</t>
+        </is>
+      </c>
+      <c r="CQ15" t="inlineStr">
+        <is>
+          <t>28.85</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t>28.85</t>
+        </is>
+      </c>
+      <c r="CS15" t="inlineStr">
+        <is>
+          <t>28.55</t>
+        </is>
+      </c>
+      <c r="CT15" t="inlineStr">
+        <is>
+          <t>28.7</t>
+        </is>
+      </c>
+      <c r="CU15" t="inlineStr">
+        <is>
           <t>19.66</t>
         </is>
       </c>
-      <c r="CJ15" t="inlineStr">
-        <is>
-          <t>23.06%</t>
-        </is>
-      </c>
-      <c r="CK15" t="inlineStr">
-        <is>
-          <t>4.46%</t>
-        </is>
-      </c>
-      <c r="CL15" t="inlineStr">
-        <is>
-          <t>25.51</t>
-        </is>
-      </c>
-      <c r="CM15" t="inlineStr">
-        <is>
-          <t>26263</t>
-        </is>
-      </c>
-      <c r="CN15" t="inlineStr">
-        <is>
-          <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO15" t="inlineStr">
-        <is>
-          <t>佳格-食品工業-上市</t>
-        </is>
-      </c>
-      <c r="CP15" t="inlineStr">
-        <is>
-          <t>食品工業右下上市</t>
-        </is>
-      </c>
-      <c r="CQ15" t="inlineStr">
-        <is>
-          <t>28.85</t>
-        </is>
-      </c>
-      <c r="CR15" t="inlineStr">
-        <is>
-          <t>28.85</t>
-        </is>
-      </c>
-      <c r="CS15" t="inlineStr">
-        <is>
-          <t>28.55</t>
-        </is>
-      </c>
-      <c r="CT15" t="inlineStr">
-        <is>
-          <t>28.7</t>
-        </is>
-      </c>
-      <c r="CU15" t="inlineStr">
-        <is>
-          <t>19.66</t>
-        </is>
-      </c>
       <c r="CV15" t="inlineStr">
         <is>
           <t>** 食品 - 營養食品</t>
@@ -7824,7 +7894,12 @@
       </c>
       <c r="CX15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY15" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -7866,7 +7941,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -7886,37 +7961,37 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2024-06-21 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2024-06-27 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2024-05-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2024-05-30 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -7926,12 +8001,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -7941,12 +8016,12 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-32.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -8011,7 +8086,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2025-10-13 00:00:00</t>
+          <t>2026-01-22 00:00:00</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -8037,12 +8112,12 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>686</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -8100,12 +8175,12 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-134.70</t>
+          <t>-160.94</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8115,7 +8190,7 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>35217063.60946746</t>
+          <t>30792858.1314741</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -8141,12 +8216,12 @@
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>1287431.499790564</t>
+          <t>1287431.499790549</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>1380371.75931019</t>
+          <t>1380371.759310186</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -8231,7 +8306,7 @@
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8241,69 +8316,69 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
+          <t>19.69</t>
+        </is>
+      </c>
+      <c r="CJ16" t="inlineStr">
+        <is>
+          <t>23.06%</t>
+        </is>
+      </c>
+      <c r="CK16" t="inlineStr">
+        <is>
+          <t>4.46%</t>
+        </is>
+      </c>
+      <c r="CL16" t="inlineStr">
+        <is>
+          <t>25.62</t>
+        </is>
+      </c>
+      <c r="CM16" t="inlineStr">
+        <is>
+          <t>26309</t>
+        </is>
+      </c>
+      <c r="CN16" t="inlineStr">
+        <is>
+          <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO16" t="inlineStr">
+        <is>
+          <t>佳格-食品工業-上市</t>
+        </is>
+      </c>
+      <c r="CP16" t="inlineStr">
+        <is>
+          <t>食品工業右下上市</t>
+        </is>
+      </c>
+      <c r="CQ16" t="inlineStr">
+        <is>
+          <t>29.1</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>29.1</t>
+        </is>
+      </c>
+      <c r="CS16" t="inlineStr">
+        <is>
+          <t>28.5</t>
+        </is>
+      </c>
+      <c r="CT16" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="CU16" t="inlineStr">
+        <is>
           <t>19.66</t>
         </is>
       </c>
-      <c r="CJ16" t="inlineStr">
-        <is>
-          <t>23.06%</t>
-        </is>
-      </c>
-      <c r="CK16" t="inlineStr">
-        <is>
-          <t>4.46%</t>
-        </is>
-      </c>
-      <c r="CL16" t="inlineStr">
-        <is>
-          <t>25.51</t>
-        </is>
-      </c>
-      <c r="CM16" t="inlineStr">
-        <is>
-          <t>26263</t>
-        </is>
-      </c>
-      <c r="CN16" t="inlineStr">
-        <is>
-          <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO16" t="inlineStr">
-        <is>
-          <t>佳格-食品工業-上市</t>
-        </is>
-      </c>
-      <c r="CP16" t="inlineStr">
-        <is>
-          <t>食品工業右下上市</t>
-        </is>
-      </c>
-      <c r="CQ16" t="inlineStr">
-        <is>
-          <t>29.1</t>
-        </is>
-      </c>
-      <c r="CR16" t="inlineStr">
-        <is>
-          <t>29.1</t>
-        </is>
-      </c>
-      <c r="CS16" t="inlineStr">
-        <is>
-          <t>28.5</t>
-        </is>
-      </c>
-      <c r="CT16" t="inlineStr">
-        <is>
-          <t>28.8</t>
-        </is>
-      </c>
-      <c r="CU16" t="inlineStr">
-        <is>
-          <t>19.66</t>
-        </is>
-      </c>
       <c r="CV16" t="inlineStr">
         <is>
           <t>** 食品 - 營養食品</t>
@@ -8316,7 +8391,12 @@
       </c>
       <c r="CX16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY16" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8438,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-0.87</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -8378,37 +8458,37 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2024-06-21 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2024-06-27 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2024-05-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2024-05-30 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -8418,12 +8498,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -8433,12 +8513,12 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-31.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -8503,7 +8583,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2025-10-13 00:00:00</t>
+          <t>2026-01-22 00:00:00</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -8529,12 +8609,12 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>686</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -8592,12 +8672,12 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-134.41</t>
+          <t>-160.44</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8607,7 +8687,7 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>35217063.60946746</t>
+          <t>30792858.1314741</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -8633,12 +8713,12 @@
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>1270533.270786996</t>
+          <t>1270533.270786978</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>629678.9128112085</t>
+          <t>629678.9128112048</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -8723,7 +8803,7 @@
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8733,69 +8813,69 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
+          <t>19.69</t>
+        </is>
+      </c>
+      <c r="CJ17" t="inlineStr">
+        <is>
+          <t>23.06%</t>
+        </is>
+      </c>
+      <c r="CK17" t="inlineStr">
+        <is>
+          <t>4.46%</t>
+        </is>
+      </c>
+      <c r="CL17" t="inlineStr">
+        <is>
+          <t>25.62</t>
+        </is>
+      </c>
+      <c r="CM17" t="inlineStr">
+        <is>
+          <t>26309</t>
+        </is>
+      </c>
+      <c r="CN17" t="inlineStr">
+        <is>
+          <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO17" t="inlineStr">
+        <is>
+          <t>佳格-食品工業-上市</t>
+        </is>
+      </c>
+      <c r="CP17" t="inlineStr">
+        <is>
+          <t>食品工業右下上市</t>
+        </is>
+      </c>
+      <c r="CQ17" t="inlineStr">
+        <is>
+          <t>29.2</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>29.2</t>
+        </is>
+      </c>
+      <c r="CS17" t="inlineStr">
+        <is>
+          <t>29.0</t>
+        </is>
+      </c>
+      <c r="CT17" t="inlineStr">
+        <is>
+          <t>29.0</t>
+        </is>
+      </c>
+      <c r="CU17" t="inlineStr">
+        <is>
           <t>19.66</t>
         </is>
       </c>
-      <c r="CJ17" t="inlineStr">
-        <is>
-          <t>23.06%</t>
-        </is>
-      </c>
-      <c r="CK17" t="inlineStr">
-        <is>
-          <t>4.46%</t>
-        </is>
-      </c>
-      <c r="CL17" t="inlineStr">
-        <is>
-          <t>25.51</t>
-        </is>
-      </c>
-      <c r="CM17" t="inlineStr">
-        <is>
-          <t>26263</t>
-        </is>
-      </c>
-      <c r="CN17" t="inlineStr">
-        <is>
-          <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO17" t="inlineStr">
-        <is>
-          <t>佳格-食品工業-上市</t>
-        </is>
-      </c>
-      <c r="CP17" t="inlineStr">
-        <is>
-          <t>食品工業右下上市</t>
-        </is>
-      </c>
-      <c r="CQ17" t="inlineStr">
-        <is>
-          <t>29.2</t>
-        </is>
-      </c>
-      <c r="CR17" t="inlineStr">
-        <is>
-          <t>29.2</t>
-        </is>
-      </c>
-      <c r="CS17" t="inlineStr">
-        <is>
-          <t>29.0</t>
-        </is>
-      </c>
-      <c r="CT17" t="inlineStr">
-        <is>
-          <t>29.0</t>
-        </is>
-      </c>
-      <c r="CU17" t="inlineStr">
-        <is>
-          <t>19.66</t>
-        </is>
-      </c>
       <c r="CV17" t="inlineStr">
         <is>
           <t>** 食品 - 營養食品</t>
@@ -8808,7 +8888,12 @@
       </c>
       <c r="CX17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY17" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -8850,7 +8935,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -8870,37 +8955,37 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2024-06-21 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2024-06-27 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2024-05-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2024-05-30 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -8910,12 +8995,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -8925,12 +9010,12 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-31.46</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -8995,7 +9080,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2025-10-13 00:00:00</t>
+          <t>2026-01-22 00:00:00</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -9021,12 +9106,12 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>686</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -9084,12 +9169,12 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-134.67</t>
+          <t>-160.89</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9099,7 +9184,7 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>35217063.60946746</t>
+          <t>30792858.1314741</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
@@ -9125,12 +9210,12 @@
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>1387052.244964412</t>
+          <t>1387052.244964392</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>550909.8494979739</t>
+          <t>550909.8494979702</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -9215,7 +9300,7 @@
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9225,69 +9310,69 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
+          <t>19.69</t>
+        </is>
+      </c>
+      <c r="CJ18" t="inlineStr">
+        <is>
+          <t>23.06%</t>
+        </is>
+      </c>
+      <c r="CK18" t="inlineStr">
+        <is>
+          <t>4.46%</t>
+        </is>
+      </c>
+      <c r="CL18" t="inlineStr">
+        <is>
+          <t>25.62</t>
+        </is>
+      </c>
+      <c r="CM18" t="inlineStr">
+        <is>
+          <t>26309</t>
+        </is>
+      </c>
+      <c r="CN18" t="inlineStr">
+        <is>
+          <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO18" t="inlineStr">
+        <is>
+          <t>佳格-食品工業-上市</t>
+        </is>
+      </c>
+      <c r="CP18" t="inlineStr">
+        <is>
+          <t>食品工業右下上市</t>
+        </is>
+      </c>
+      <c r="CQ18" t="inlineStr">
+        <is>
+          <t>29.4</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="CS18" t="inlineStr">
+        <is>
+          <t>29.2</t>
+        </is>
+      </c>
+      <c r="CT18" t="inlineStr">
+        <is>
+          <t>29.2</t>
+        </is>
+      </c>
+      <c r="CU18" t="inlineStr">
+        <is>
           <t>19.66</t>
         </is>
       </c>
-      <c r="CJ18" t="inlineStr">
-        <is>
-          <t>23.06%</t>
-        </is>
-      </c>
-      <c r="CK18" t="inlineStr">
-        <is>
-          <t>4.46%</t>
-        </is>
-      </c>
-      <c r="CL18" t="inlineStr">
-        <is>
-          <t>25.51</t>
-        </is>
-      </c>
-      <c r="CM18" t="inlineStr">
-        <is>
-          <t>26263</t>
-        </is>
-      </c>
-      <c r="CN18" t="inlineStr">
-        <is>
-          <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO18" t="inlineStr">
-        <is>
-          <t>佳格-食品工業-上市</t>
-        </is>
-      </c>
-      <c r="CP18" t="inlineStr">
-        <is>
-          <t>食品工業右下上市</t>
-        </is>
-      </c>
-      <c r="CQ18" t="inlineStr">
-        <is>
-          <t>29.4</t>
-        </is>
-      </c>
-      <c r="CR18" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
-      <c r="CS18" t="inlineStr">
-        <is>
-          <t>29.2</t>
-        </is>
-      </c>
-      <c r="CT18" t="inlineStr">
-        <is>
-          <t>29.2</t>
-        </is>
-      </c>
-      <c r="CU18" t="inlineStr">
-        <is>
-          <t>19.66</t>
-        </is>
-      </c>
       <c r="CV18" t="inlineStr">
         <is>
           <t>** 食品 - 營養食品</t>
@@ -9300,7 +9385,12 @@
       </c>
       <c r="CX18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY18" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9342,7 +9432,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -9362,37 +9452,37 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2024-06-21 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2024-06-27 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2024-05-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2024-05-30 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -9402,12 +9492,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -9417,12 +9507,12 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-30.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -9487,7 +9577,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2025-10-13 00:00:00</t>
+          <t>2026-01-22 00:00:00</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -9513,12 +9603,12 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>686</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -9576,12 +9666,12 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-135.33</t>
+          <t>-162.04</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9591,7 +9681,7 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>35217063.60946746</t>
+          <t>30792858.1314741</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
@@ -9617,12 +9707,12 @@
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>1539078.135049219</t>
+          <t>1539078.135049196</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>785214.264425572</t>
+          <t>785214.2644255646</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -9707,7 +9797,7 @@
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9717,69 +9807,69 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
+          <t>19.69</t>
+        </is>
+      </c>
+      <c r="CJ19" t="inlineStr">
+        <is>
+          <t>23.06%</t>
+        </is>
+      </c>
+      <c r="CK19" t="inlineStr">
+        <is>
+          <t>4.46%</t>
+        </is>
+      </c>
+      <c r="CL19" t="inlineStr">
+        <is>
+          <t>25.62</t>
+        </is>
+      </c>
+      <c r="CM19" t="inlineStr">
+        <is>
+          <t>26309</t>
+        </is>
+      </c>
+      <c r="CN19" t="inlineStr">
+        <is>
+          <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO19" t="inlineStr">
+        <is>
+          <t>佳格-食品工業-上市</t>
+        </is>
+      </c>
+      <c r="CP19" t="inlineStr">
+        <is>
+          <t>食品工業右下上市</t>
+        </is>
+      </c>
+      <c r="CQ19" t="inlineStr">
+        <is>
+          <t>29.6</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>29.65</t>
+        </is>
+      </c>
+      <c r="CS19" t="inlineStr">
+        <is>
+          <t>29.3</t>
+        </is>
+      </c>
+      <c r="CT19" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="CU19" t="inlineStr">
+        <is>
           <t>19.66</t>
         </is>
       </c>
-      <c r="CJ19" t="inlineStr">
-        <is>
-          <t>23.06%</t>
-        </is>
-      </c>
-      <c r="CK19" t="inlineStr">
-        <is>
-          <t>4.46%</t>
-        </is>
-      </c>
-      <c r="CL19" t="inlineStr">
-        <is>
-          <t>25.51</t>
-        </is>
-      </c>
-      <c r="CM19" t="inlineStr">
-        <is>
-          <t>26263</t>
-        </is>
-      </c>
-      <c r="CN19" t="inlineStr">
-        <is>
-          <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO19" t="inlineStr">
-        <is>
-          <t>佳格-食品工業-上市</t>
-        </is>
-      </c>
-      <c r="CP19" t="inlineStr">
-        <is>
-          <t>食品工業右下上市</t>
-        </is>
-      </c>
-      <c r="CQ19" t="inlineStr">
-        <is>
-          <t>29.6</t>
-        </is>
-      </c>
-      <c r="CR19" t="inlineStr">
-        <is>
-          <t>29.65</t>
-        </is>
-      </c>
-      <c r="CS19" t="inlineStr">
-        <is>
-          <t>29.3</t>
-        </is>
-      </c>
-      <c r="CT19" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
-      <c r="CU19" t="inlineStr">
-        <is>
-          <t>19.66</t>
-        </is>
-      </c>
       <c r="CV19" t="inlineStr">
         <is>
           <t>** 食品 - 營養食品</t>
@@ -9792,7 +9882,12 @@
       </c>
       <c r="CX19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9929,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -9854,37 +9949,37 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2024-06-21 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2024-06-27 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2024-05-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2024-05-30 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -9894,12 +9989,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -9909,12 +10004,12 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-30.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -9979,7 +10074,7 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2025-10-13 00:00:00</t>
+          <t>2026-01-22 00:00:00</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
@@ -10005,12 +10100,12 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>686</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -10068,12 +10163,12 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-136.11</t>
+          <t>-163.41</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -10083,7 +10178,7 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>35217063.60946746</t>
+          <t>30792858.1314741</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
@@ -10109,12 +10204,12 @@
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>1676144.293344427</t>
+          <t>1676144.293344401</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>1249830.669164084</t>
+          <t>1249830.669164076</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -10199,7 +10294,7 @@
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10209,69 +10304,69 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
+          <t>19.69</t>
+        </is>
+      </c>
+      <c r="CJ20" t="inlineStr">
+        <is>
+          <t>23.06%</t>
+        </is>
+      </c>
+      <c r="CK20" t="inlineStr">
+        <is>
+          <t>4.46%</t>
+        </is>
+      </c>
+      <c r="CL20" t="inlineStr">
+        <is>
+          <t>25.62</t>
+        </is>
+      </c>
+      <c r="CM20" t="inlineStr">
+        <is>
+          <t>26309</t>
+        </is>
+      </c>
+      <c r="CN20" t="inlineStr">
+        <is>
+          <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO20" t="inlineStr">
+        <is>
+          <t>佳格-食品工業-上市</t>
+        </is>
+      </c>
+      <c r="CP20" t="inlineStr">
+        <is>
+          <t>食品工業右下上市</t>
+        </is>
+      </c>
+      <c r="CQ20" t="inlineStr">
+        <is>
+          <t>29.3</t>
+        </is>
+      </c>
+      <c r="CR20" t="inlineStr">
+        <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="CS20" t="inlineStr">
+        <is>
+          <t>29.3</t>
+        </is>
+      </c>
+      <c r="CT20" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="CU20" t="inlineStr">
+        <is>
           <t>19.66</t>
         </is>
       </c>
-      <c r="CJ20" t="inlineStr">
-        <is>
-          <t>23.06%</t>
-        </is>
-      </c>
-      <c r="CK20" t="inlineStr">
-        <is>
-          <t>4.46%</t>
-        </is>
-      </c>
-      <c r="CL20" t="inlineStr">
-        <is>
-          <t>25.51</t>
-        </is>
-      </c>
-      <c r="CM20" t="inlineStr">
-        <is>
-          <t>26263</t>
-        </is>
-      </c>
-      <c r="CN20" t="inlineStr">
-        <is>
-          <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO20" t="inlineStr">
-        <is>
-          <t>佳格-食品工業-上市</t>
-        </is>
-      </c>
-      <c r="CP20" t="inlineStr">
-        <is>
-          <t>食品工業右下上市</t>
-        </is>
-      </c>
-      <c r="CQ20" t="inlineStr">
-        <is>
-          <t>29.3</t>
-        </is>
-      </c>
-      <c r="CR20" t="inlineStr">
-        <is>
-          <t>29.75</t>
-        </is>
-      </c>
-      <c r="CS20" t="inlineStr">
-        <is>
-          <t>29.3</t>
-        </is>
-      </c>
-      <c r="CT20" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
-      <c r="CU20" t="inlineStr">
-        <is>
-          <t>19.66</t>
-        </is>
-      </c>
       <c r="CV20" t="inlineStr">
         <is>
           <t>** 食品 - 營養食品</t>
@@ -10284,7 +10379,12 @@
       </c>
       <c r="CX20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY20" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -10326,7 +10426,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -10346,37 +10446,37 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2024-06-21 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2024-06-27 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2024-05-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2024-05-30 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -10386,12 +10486,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -10401,12 +10501,12 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-31.34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -10471,7 +10571,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2025-10-13 00:00:00</t>
+          <t>2026-01-22 00:00:00</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
@@ -10497,12 +10597,12 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>686</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -10560,12 +10660,12 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-136.30</t>
+          <t>-163.75</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10575,7 +10675,7 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>35217063.60946746</t>
+          <t>30792858.1314741</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
@@ -10601,12 +10701,12 @@
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>1753655.861377217</t>
+          <t>1753655.861377188</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>276415.7591775246</t>
+          <t>276415.7591775171</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -10691,7 +10791,7 @@
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10701,69 +10801,69 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
+          <t>19.69</t>
+        </is>
+      </c>
+      <c r="CJ21" t="inlineStr">
+        <is>
+          <t>23.06%</t>
+        </is>
+      </c>
+      <c r="CK21" t="inlineStr">
+        <is>
+          <t>4.46%</t>
+        </is>
+      </c>
+      <c r="CL21" t="inlineStr">
+        <is>
+          <t>25.62</t>
+        </is>
+      </c>
+      <c r="CM21" t="inlineStr">
+        <is>
+          <t>26309</t>
+        </is>
+      </c>
+      <c r="CN21" t="inlineStr">
+        <is>
+          <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO21" t="inlineStr">
+        <is>
+          <t>佳格-食品工業-上市</t>
+        </is>
+      </c>
+      <c r="CP21" t="inlineStr">
+        <is>
+          <t>食品工業右下上市</t>
+        </is>
+      </c>
+      <c r="CQ21" t="inlineStr">
+        <is>
+          <t>29.3</t>
+        </is>
+      </c>
+      <c r="CR21" t="inlineStr">
+        <is>
+          <t>29.35</t>
+        </is>
+      </c>
+      <c r="CS21" t="inlineStr">
+        <is>
+          <t>29.1</t>
+        </is>
+      </c>
+      <c r="CT21" t="inlineStr">
+        <is>
+          <t>29.25</t>
+        </is>
+      </c>
+      <c r="CU21" t="inlineStr">
+        <is>
           <t>19.66</t>
         </is>
       </c>
-      <c r="CJ21" t="inlineStr">
-        <is>
-          <t>23.06%</t>
-        </is>
-      </c>
-      <c r="CK21" t="inlineStr">
-        <is>
-          <t>4.46%</t>
-        </is>
-      </c>
-      <c r="CL21" t="inlineStr">
-        <is>
-          <t>25.51</t>
-        </is>
-      </c>
-      <c r="CM21" t="inlineStr">
-        <is>
-          <t>26263</t>
-        </is>
-      </c>
-      <c r="CN21" t="inlineStr">
-        <is>
-          <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO21" t="inlineStr">
-        <is>
-          <t>佳格-食品工業-上市</t>
-        </is>
-      </c>
-      <c r="CP21" t="inlineStr">
-        <is>
-          <t>食品工業右下上市</t>
-        </is>
-      </c>
-      <c r="CQ21" t="inlineStr">
-        <is>
-          <t>29.3</t>
-        </is>
-      </c>
-      <c r="CR21" t="inlineStr">
-        <is>
-          <t>29.35</t>
-        </is>
-      </c>
-      <c r="CS21" t="inlineStr">
-        <is>
-          <t>29.1</t>
-        </is>
-      </c>
-      <c r="CT21" t="inlineStr">
-        <is>
-          <t>29.25</t>
-        </is>
-      </c>
-      <c r="CU21" t="inlineStr">
-        <is>
-          <t>19.66</t>
-        </is>
-      </c>
       <c r="CV21" t="inlineStr">
         <is>
           <t>** 食品 - 營養食品</t>
@@ -10776,7 +10876,12 @@
       </c>
       <c r="CX21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY21" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -10818,7 +10923,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -10838,37 +10943,37 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2024-06-21 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2024-06-27 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2024-05-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2024-05-30 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -10878,12 +10983,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -10893,12 +10998,12 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-31.57</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -10963,7 +11068,7 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2025-10-13 00:00:00</t>
+          <t>2026-01-22 00:00:00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
@@ -10989,12 +11094,12 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>686</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -11052,12 +11157,12 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-135.66</t>
+          <t>-162.63</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -11067,7 +11172,7 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>35217063.60946746</t>
+          <t>30792858.1314741</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
@@ -11093,12 +11198,12 @@
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>2022244.97086807</t>
+          <t>2022244.970868037</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>1091357.074940387</t>
+          <t>1091357.074940376</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -11173,7 +11278,7 @@
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
@@ -11183,7 +11288,7 @@
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11193,69 +11298,69 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
+          <t>19.69</t>
+        </is>
+      </c>
+      <c r="CJ22" t="inlineStr">
+        <is>
+          <t>23.06%</t>
+        </is>
+      </c>
+      <c r="CK22" t="inlineStr">
+        <is>
+          <t>4.46%</t>
+        </is>
+      </c>
+      <c r="CL22" t="inlineStr">
+        <is>
+          <t>25.62</t>
+        </is>
+      </c>
+      <c r="CM22" t="inlineStr">
+        <is>
+          <t>26309</t>
+        </is>
+      </c>
+      <c r="CN22" t="inlineStr">
+        <is>
+          <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO22" t="inlineStr">
+        <is>
+          <t>佳格-食品工業-上市</t>
+        </is>
+      </c>
+      <c r="CP22" t="inlineStr">
+        <is>
+          <t>食品工業右下上市</t>
+        </is>
+      </c>
+      <c r="CQ22" t="inlineStr">
+        <is>
+          <t>29.15</t>
+        </is>
+      </c>
+      <c r="CR22" t="inlineStr">
+        <is>
+          <t>29.3</t>
+        </is>
+      </c>
+      <c r="CS22" t="inlineStr">
+        <is>
+          <t>29.1</t>
+        </is>
+      </c>
+      <c r="CT22" t="inlineStr">
+        <is>
+          <t>29.15</t>
+        </is>
+      </c>
+      <c r="CU22" t="inlineStr">
+        <is>
           <t>19.66</t>
         </is>
       </c>
-      <c r="CJ22" t="inlineStr">
-        <is>
-          <t>23.06%</t>
-        </is>
-      </c>
-      <c r="CK22" t="inlineStr">
-        <is>
-          <t>4.46%</t>
-        </is>
-      </c>
-      <c r="CL22" t="inlineStr">
-        <is>
-          <t>25.51</t>
-        </is>
-      </c>
-      <c r="CM22" t="inlineStr">
-        <is>
-          <t>26263</t>
-        </is>
-      </c>
-      <c r="CN22" t="inlineStr">
-        <is>
-          <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO22" t="inlineStr">
-        <is>
-          <t>佳格-食品工業-上市</t>
-        </is>
-      </c>
-      <c r="CP22" t="inlineStr">
-        <is>
-          <t>食品工業右下上市</t>
-        </is>
-      </c>
-      <c r="CQ22" t="inlineStr">
-        <is>
-          <t>29.15</t>
-        </is>
-      </c>
-      <c r="CR22" t="inlineStr">
-        <is>
-          <t>29.3</t>
-        </is>
-      </c>
-      <c r="CS22" t="inlineStr">
-        <is>
-          <t>29.1</t>
-        </is>
-      </c>
-      <c r="CT22" t="inlineStr">
-        <is>
-          <t>29.15</t>
-        </is>
-      </c>
-      <c r="CU22" t="inlineStr">
-        <is>
-          <t>19.66</t>
-        </is>
-      </c>
       <c r="CV22" t="inlineStr">
         <is>
           <t>** 食品 - 營養食品</t>
@@ -11268,7 +11373,12 @@
       </c>
       <c r="CX22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY22" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -11310,7 +11420,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -11330,37 +11440,37 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2024-06-21 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2024-06-27 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2024-05-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2024-05-30 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -11370,12 +11480,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -11385,12 +11495,12 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-31.57</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -11455,7 +11565,7 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2025-10-13 00:00:00</t>
+          <t>2026-01-22 00:00:00</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
@@ -11481,12 +11591,12 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>686</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -11544,12 +11654,12 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-134.61</t>
+          <t>-160.78</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11559,7 +11669,7 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>35217063.60946746</t>
+          <t>30792858.1314741</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
@@ -11585,12 +11695,12 @@
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>2191497.315582194</t>
+          <t>2191497.315582157</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>2369759.451925177</t>
+          <t>2369759.451925166</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -11665,7 +11775,7 @@
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
@@ -11675,7 +11785,7 @@
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11685,69 +11795,69 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
+          <t>19.69</t>
+        </is>
+      </c>
+      <c r="CJ23" t="inlineStr">
+        <is>
+          <t>23.06%</t>
+        </is>
+      </c>
+      <c r="CK23" t="inlineStr">
+        <is>
+          <t>4.46%</t>
+        </is>
+      </c>
+      <c r="CL23" t="inlineStr">
+        <is>
+          <t>25.62</t>
+        </is>
+      </c>
+      <c r="CM23" t="inlineStr">
+        <is>
+          <t>26309</t>
+        </is>
+      </c>
+      <c r="CN23" t="inlineStr">
+        <is>
+          <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO23" t="inlineStr">
+        <is>
+          <t>佳格-食品工業-上市</t>
+        </is>
+      </c>
+      <c r="CP23" t="inlineStr">
+        <is>
+          <t>食品工業右下上市</t>
+        </is>
+      </c>
+      <c r="CQ23" t="inlineStr">
+        <is>
+          <t>29.15</t>
+        </is>
+      </c>
+      <c r="CR23" t="inlineStr">
+        <is>
+          <t>29.25</t>
+        </is>
+      </c>
+      <c r="CS23" t="inlineStr">
+        <is>
+          <t>29.05</t>
+        </is>
+      </c>
+      <c r="CT23" t="inlineStr">
+        <is>
+          <t>29.15</t>
+        </is>
+      </c>
+      <c r="CU23" t="inlineStr">
+        <is>
           <t>19.66</t>
         </is>
       </c>
-      <c r="CJ23" t="inlineStr">
-        <is>
-          <t>23.06%</t>
-        </is>
-      </c>
-      <c r="CK23" t="inlineStr">
-        <is>
-          <t>4.46%</t>
-        </is>
-      </c>
-      <c r="CL23" t="inlineStr">
-        <is>
-          <t>25.51</t>
-        </is>
-      </c>
-      <c r="CM23" t="inlineStr">
-        <is>
-          <t>26263</t>
-        </is>
-      </c>
-      <c r="CN23" t="inlineStr">
-        <is>
-          <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO23" t="inlineStr">
-        <is>
-          <t>佳格-食品工業-上市</t>
-        </is>
-      </c>
-      <c r="CP23" t="inlineStr">
-        <is>
-          <t>食品工業右下上市</t>
-        </is>
-      </c>
-      <c r="CQ23" t="inlineStr">
-        <is>
-          <t>29.15</t>
-        </is>
-      </c>
-      <c r="CR23" t="inlineStr">
-        <is>
-          <t>29.25</t>
-        </is>
-      </c>
-      <c r="CS23" t="inlineStr">
-        <is>
-          <t>29.05</t>
-        </is>
-      </c>
-      <c r="CT23" t="inlineStr">
-        <is>
-          <t>29.15</t>
-        </is>
-      </c>
-      <c r="CU23" t="inlineStr">
-        <is>
-          <t>19.66</t>
-        </is>
-      </c>
       <c r="CV23" t="inlineStr">
         <is>
           <t>** 食品 - 營養食品</t>
@@ -11760,7 +11870,12 @@
       </c>
       <c r="CX23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY23" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -11802,7 +11917,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -11822,37 +11937,37 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2024-06-21 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2024-06-27 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2024-05-07 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2024-05-30 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -11862,12 +11977,12 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -11877,12 +11992,12 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-31.57</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -11947,7 +12062,7 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2025-10-13 00:00:00</t>
+          <t>2026-01-22 00:00:00</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
@@ -11973,12 +12088,12 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>686</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -12036,12 +12151,12 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-133.39</t>
+          <t>-158.64</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -12051,7 +12166,7 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>35217063.60946746</t>
+          <t>30792858.1314741</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
@@ -12077,12 +12192,12 @@
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>2159086.018065288</t>
+          <t>2159086.018065246</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>3214054.724334691</t>
+          <t>3214054.72433468</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
@@ -12167,7 +12282,7 @@
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>4.88</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12177,69 +12292,69 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
+          <t>19.69</t>
+        </is>
+      </c>
+      <c r="CJ24" t="inlineStr">
+        <is>
+          <t>23.06%</t>
+        </is>
+      </c>
+      <c r="CK24" t="inlineStr">
+        <is>
+          <t>4.46%</t>
+        </is>
+      </c>
+      <c r="CL24" t="inlineStr">
+        <is>
+          <t>25.62</t>
+        </is>
+      </c>
+      <c r="CM24" t="inlineStr">
+        <is>
+          <t>26309</t>
+        </is>
+      </c>
+      <c r="CN24" t="inlineStr">
+        <is>
+          <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO24" t="inlineStr">
+        <is>
+          <t>佳格-食品工業-上市</t>
+        </is>
+      </c>
+      <c r="CP24" t="inlineStr">
+        <is>
+          <t>食品工業右下上市</t>
+        </is>
+      </c>
+      <c r="CQ24" t="inlineStr">
+        <is>
+          <t>29.2</t>
+        </is>
+      </c>
+      <c r="CR24" t="inlineStr">
+        <is>
+          <t>29.3</t>
+        </is>
+      </c>
+      <c r="CS24" t="inlineStr">
+        <is>
+          <t>29.1</t>
+        </is>
+      </c>
+      <c r="CT24" t="inlineStr">
+        <is>
+          <t>29.15</t>
+        </is>
+      </c>
+      <c r="CU24" t="inlineStr">
+        <is>
           <t>19.66</t>
         </is>
       </c>
-      <c r="CJ24" t="inlineStr">
-        <is>
-          <t>23.06%</t>
-        </is>
-      </c>
-      <c r="CK24" t="inlineStr">
-        <is>
-          <t>4.46%</t>
-        </is>
-      </c>
-      <c r="CL24" t="inlineStr">
-        <is>
-          <t>25.51</t>
-        </is>
-      </c>
-      <c r="CM24" t="inlineStr">
-        <is>
-          <t>26263</t>
-        </is>
-      </c>
-      <c r="CN24" t="inlineStr">
-        <is>
-          <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO24" t="inlineStr">
-        <is>
-          <t>佳格-食品工業-上市</t>
-        </is>
-      </c>
-      <c r="CP24" t="inlineStr">
-        <is>
-          <t>食品工業右下上市</t>
-        </is>
-      </c>
-      <c r="CQ24" t="inlineStr">
-        <is>
-          <t>29.2</t>
-        </is>
-      </c>
-      <c r="CR24" t="inlineStr">
-        <is>
-          <t>29.3</t>
-        </is>
-      </c>
-      <c r="CS24" t="inlineStr">
-        <is>
-          <t>29.1</t>
-        </is>
-      </c>
-      <c r="CT24" t="inlineStr">
-        <is>
-          <t>29.15</t>
-        </is>
-      </c>
-      <c r="CU24" t="inlineStr">
-        <is>
-          <t>19.66</t>
-        </is>
-      </c>
       <c r="CV24" t="inlineStr">
         <is>
           <t>** 食品 - 營養食品</t>
@@ -12252,499 +12367,12 @@
       </c>
       <c r="CX24" t="inlineStr">
         <is>
-          <t>0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1227</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>-0.51</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>1347.009</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>29.3</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>-2.09</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>5.31</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>2024-06-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>2024-06-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>2024-05-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>2024-05-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>43.0</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>42.6</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>38.75</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>40.75</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>-31.22</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>5.52</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2025/05/15</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>35.5</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>-0.0</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>2025/11/21</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>30.5</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>33.25</t>
-        </is>
-      </c>
-      <c r="AG25" t="inlineStr">
-        <is>
-          <t>2026/02/02</t>
-        </is>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>28.8</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>2025/12/26</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>30.45</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>25.76</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AP25" t="inlineStr"/>
-      <c r="AQ25" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>685</t>
-        </is>
-      </c>
-      <c r="AS25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AT25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AU25" t="n">
-        <v>-0.68</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>-1.43</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>-1.12</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
-      <c r="AZ25" t="n">
-        <v>29.96</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="BB25" t="inlineStr">
-        <is>
-          <t>30.74</t>
-        </is>
-      </c>
-      <c r="BC25" t="inlineStr">
-        <is>
-          <t>-13.44</t>
-        </is>
-      </c>
-      <c r="BD25" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="BF25" t="inlineStr">
-        <is>
-          <t>0.89</t>
-        </is>
-      </c>
-      <c r="BG25" t="inlineStr">
-        <is>
-          <t>-132.14</t>
-        </is>
-      </c>
-      <c r="BH25" t="inlineStr">
-        <is>
-          <t>2026/01/27</t>
-        </is>
-      </c>
-      <c r="BI25" t="inlineStr">
-        <is>
-          <t>35217063.60946746</t>
-        </is>
-      </c>
-      <c r="BJ25" t="inlineStr">
-        <is>
-          <t>39492900.0</t>
-        </is>
-      </c>
-      <c r="BK25" t="n">
-        <v>27794380.4</v>
-      </c>
-      <c r="BL25" t="inlineStr">
-        <is>
-          <t>26393933.9</t>
-        </is>
-      </c>
-      <c r="BM25" t="n">
-        <v>15869794.14</v>
-      </c>
-      <c r="BN25" t="inlineStr">
-        <is>
-          <t>1400446</t>
-        </is>
-      </c>
-      <c r="BO25" t="inlineStr">
-        <is>
-          <t>1967273.526016306</t>
-        </is>
-      </c>
-      <c r="BP25" t="inlineStr">
-        <is>
-          <t>3068365.801907759</t>
-        </is>
-      </c>
-      <c r="BQ25" t="inlineStr">
-        <is>
-          <t>39492900.0</t>
-        </is>
-      </c>
-      <c r="BR25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS25" t="inlineStr">
-        <is>
-          <t>33.95</t>
-        </is>
-      </c>
-      <c r="BT25" t="inlineStr">
-        <is>
-          <t>2025/10/15</t>
-        </is>
-      </c>
-      <c r="BU25" t="inlineStr">
-        <is>
-          <t>-13.70</t>
-        </is>
-      </c>
-      <c r="BV25" t="inlineStr">
-        <is>
-          <t>佳格</t>
-        </is>
-      </c>
-      <c r="BW25" t="inlineStr">
-        <is>
-          <t>佳格</t>
-        </is>
-      </c>
-      <c r="BX25" t="inlineStr">
-        <is>
-          <t>食品工業</t>
-        </is>
-      </c>
-      <c r="BY25" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BZ25" t="inlineStr">
-        <is>
-          <t>0.42</t>
-        </is>
-      </c>
-      <c r="CA25" t="inlineStr">
-        <is>
-          <t>6.237608785148733</t>
-        </is>
-      </c>
-      <c r="CB25" t="inlineStr">
-        <is>
-          <t>-17.09267911306208</t>
-        </is>
-      </c>
-      <c r="CC25" t="inlineStr">
-        <is>
-          <t>-3.78772922691385</t>
-        </is>
-      </c>
-      <c r="CD25" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="CE25" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF25" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="CG25" t="inlineStr">
-        <is>
-          <t>4.88</t>
-        </is>
-      </c>
-      <c r="CH25" t="inlineStr">
-        <is>
-          <t>8.02</t>
-        </is>
-      </c>
-      <c r="CI25" t="inlineStr">
-        <is>
-          <t>19.66</t>
-        </is>
-      </c>
-      <c r="CJ25" t="inlineStr">
-        <is>
-          <t>23.06%</t>
-        </is>
-      </c>
-      <c r="CK25" t="inlineStr">
-        <is>
-          <t>4.46%</t>
-        </is>
-      </c>
-      <c r="CL25" t="inlineStr">
-        <is>
-          <t>25.51</t>
-        </is>
-      </c>
-      <c r="CM25" t="inlineStr">
-        <is>
-          <t>26263</t>
-        </is>
-      </c>
-      <c r="CN25" t="inlineStr">
-        <is>
-          <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO25" t="inlineStr">
-        <is>
-          <t>佳格-食品工業-上市</t>
-        </is>
-      </c>
-      <c r="CP25" t="inlineStr">
-        <is>
-          <t>食品工業右下上市</t>
-        </is>
-      </c>
-      <c r="CQ25" t="inlineStr">
-        <is>
-          <t>29.35</t>
-        </is>
-      </c>
-      <c r="CR25" t="inlineStr">
-        <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="CS25" t="inlineStr">
-        <is>
-          <t>29.25</t>
-        </is>
-      </c>
-      <c r="CT25" t="inlineStr">
-        <is>
-          <t>29.3</t>
-        </is>
-      </c>
-      <c r="CU25" t="inlineStr">
-        <is>
-          <t>19.66</t>
-        </is>
-      </c>
-      <c r="CV25" t="inlineStr">
-        <is>
-          <t>** 食品 - 營養食品</t>
-        </is>
-      </c>
-      <c r="CW25" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="CX25" t="inlineStr">
-        <is>
-          <t>0.0</t>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY24" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/營養食品.xlsx
+++ b/Result/checksun_type/營養食品.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CY26"/>
+  <dimension ref="A1:CY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -948,7 +948,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【d1】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -983,17 +983,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-20.19</t>
+          <t>-17.41</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-12.88</t>
+          <t>-13.35</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1133,17 +1133,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1164,23 +1164,23 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>59.52</t>
+          <t>45.24</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>0.13</v>
+        <v>-0.35</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1190,30 +1190,30 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
+          <t>74.25999999999999</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>74.20999999999999</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
           <t>74.3</t>
         </is>
       </c>
-      <c r="AZ2" t="n">
-        <v>74.26000000000001</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>74.41</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>74.32</t>
-        </is>
-      </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>275.25</t>
+          <t>124.41</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-100.94</t>
+          <t>-100.72</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1232,43 +1232,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>3097.838613861386</t>
+          <t>3097.227272727273</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>313.0</t>
+          <t>1859.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>1075.6</v>
+        <v>1162.6</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1347.7</t>
+          <t>1407.6</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>1234.02</v>
+        <v>1268.2</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-272</t>
+          <t>-245</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-7.062029240440335</t>
+          <t>-26.81675998473243</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-207.41034033353</t>
+          <t>-135.4677790783389</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>313.0</t>
+          <t>1859.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-1.60</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1403,17 +1403,17 @@
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1455,12 +1455,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-30.73</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-12.76</t>
+          <t>-12.88</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1630,17 +1630,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
@@ -1670,47 +1670,47 @@
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>0.24</v>
+        <v>0.13</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>74.32000000000001</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>74.23</v>
+        <v>74.26000000000001</v>
       </c>
       <c r="BA3" t="n">
-        <v>74.39</v>
+        <v>74.41</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>74.34</t>
+          <t>74.32</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>171.19</t>
+          <t>275.25</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-101.59</t>
+          <t>-100.94</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1729,43 +1729,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>3097.838613861386</t>
+          <t>3097.227272727273</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>446.0</t>
+          <t>313.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>1284.6</v>
+        <v>1075.6</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1854.6</t>
+          <t>1347.7</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>1241.7</v>
+        <v>1234.02</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-570</t>
+          <t>-272</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>29.3649364128487</t>
+          <t>-7.062029240440335</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-137.1350585433199</t>
+          <t>-207.41034033353</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>446.0</t>
+          <t>313.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1895,22 +1895,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="CY3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1952,42 +1952,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>20.0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>74.2</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.27</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-12.03</t>
+          <t>-30.73</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>-12.76</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2127,17 +2127,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2158,56 +2158,56 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>47.62</t>
+          <t>59.52</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-0.19</v>
+        <v>0.24</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
+          <t>74.32000000000001</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>74.23</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>74.39</v>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
           <t>74.34</t>
         </is>
       </c>
-      <c r="AZ4" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>74.40000000000001</v>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>74.38</t>
-        </is>
-      </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>93.80</t>
+          <t>171.19</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0</v>
+        <v>0.02</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-102.27</t>
+          <t>-101.59</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2226,43 +2226,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>3097.838613861386</t>
+          <t>3097.227272727273</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>1492.0</t>
+          <t>446.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>1709</v>
+        <v>1284.6</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1942.6</t>
+          <t>1854.6</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>1251.7</v>
+        <v>1241.7</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-233</t>
+          <t>-570</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>59.63766276851573</t>
+          <t>29.3649364128487</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-46.09411818075841</t>
+          <t>-137.1350585433199</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>1492.0</t>
+          <t>446.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2392,22 +2392,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2427,12 +2427,12 @@
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-9.26</t>
+          <t>-12.03</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2624,17 +2624,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2655,56 +2655,56 @@
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>47.62</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-0.22</v>
+        <v>-0.19</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>74.36</t>
+          <t>74.34</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>74.18000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>74.39</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>74.41</t>
+          <t>74.38</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>100.71</t>
+          <t>93.80</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-102.80</t>
+          <t>-102.27</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2723,43 +2723,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>3097.838613861386</t>
+          <t>3097.227272727273</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>1703.0</t>
+          <t>1492.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>1768.6</v>
+        <v>1709</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1949.1</t>
+          <t>1942.6</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>1235.02</v>
+        <v>1251.7</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-180</t>
+          <t>-233</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>78.86162294111104</t>
+          <t>59.63766276851573</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-26.46084201350072</t>
+          <t>-46.09411818075841</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>1703.0</t>
+          <t>1492.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2889,17 +2889,17 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="CX5" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="CY5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -2946,12 +2946,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-9.26</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -3121,17 +3121,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>7.09</t>
+          <t>8.58</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3157,14 +3157,14 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>79.17</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-0.3</v>
+        <v>-0.22</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.36</v>
+        <v>0.24</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
@@ -3173,35 +3173,35 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>74.42</t>
+          <t>74.36</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>74.16</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="BA6" t="n">
-        <v>74.36</v>
+        <v>74.39</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>74.45</t>
+          <t>74.41</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>106.40</t>
+          <t>100.71</t>
         </is>
       </c>
       <c r="BD6" t="n">
         <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-103.51</t>
+          <t>-102.80</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3220,43 +3220,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>3097.838613861386</t>
+          <t>3097.227272727273</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>1424.0</t>
+          <t>1703.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>1652.6</v>
+        <v>1768.6</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1802.0</t>
+          <t>1949.1</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>1263.36</v>
+        <v>1235.02</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-149</t>
+          <t>-180</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>98.01116202376772</t>
+          <t>78.86162294111104</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-20.07541741693626</t>
+          <t>-26.46084201350072</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>1424.0</t>
+          <t>1703.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3386,24 +3386,24 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
+          <t>73.6</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="CS6" t="inlineStr">
+        <is>
+          <t>73.6</t>
+        </is>
+      </c>
+      <c r="CT6" t="inlineStr">
+        <is>
           <t>74.2</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="CS6" t="inlineStr">
-        <is>
-          <t>73.5</t>
-        </is>
-      </c>
-      <c r="CT6" t="inlineStr">
-        <is>
-          <t>74.2</t>
-        </is>
-      </c>
       <c r="CU6" t="inlineStr">
         <is>
           <t>34.3</t>
@@ -3421,12 +3421,12 @@
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3443,192 +3443,192 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>19.0</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>74.2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.27</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-8.29</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-03-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-02-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-02-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>85.4</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>82.4</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>-13.11</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025/09/12</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026/01/06</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>2025/10/22</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>73.8</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2025/12/15</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/12/11</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>74.7</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>2026-01-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>7.09</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
           <t>-0.13</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>18.0</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>74.5</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-13.36</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-03-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-03-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-02-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-02-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>82.3</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>85.4</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>82.4</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>79.7</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>-12.76</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>3.26</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025/09/12</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026/01/06</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>73.8</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>2025/12/15</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>2025/12/11</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>74.7</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>2026-01-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>2026-01-28</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>6.72</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>-2.41</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3649,56 +3649,56 @@
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>88.43</t>
+          <t>79.17</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>0.19</v>
+        <v>-0.3</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.32</v>
+        <v>0.36</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>74.35999999999999</t>
+          <t>74.42</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>74.12</v>
+        <v>74.16</v>
       </c>
       <c r="BA7" t="n">
-        <v>74.38</v>
+        <v>74.36</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>74.49</t>
+          <t>74.45</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>110.87</t>
+          <t>106.40</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-104.44</t>
+          <t>-103.51</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3717,43 +3717,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>3097.838613861386</t>
+          <t>3097.227272727273</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>1358.0</t>
+          <t>1424.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>1619.8</v>
+        <v>1652.6</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1869.6</t>
+          <t>1802.0</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>1245.84</v>
+        <v>1263.36</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-249</t>
+          <t>-149</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>119.4814491948048</t>
+          <t>98.01116202376772</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>19.65645405733221</t>
+          <t>-20.07541741693626</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>1358.0</t>
+          <t>1424.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3883,22 +3883,22 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3918,12 +3918,12 @@
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3940,12 +3940,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>28.84</t>
+          <t>-13.36</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-12.65</t>
+          <t>-12.76</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4115,17 +4115,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>6.72</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4146,23 +4146,23 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>92.59</t>
+          <t>88.43</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>0.4</v>
+        <v>0.19</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -4172,230 +4172,230 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
+          <t>74.35999999999999</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>74.12</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>74.38</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>74.49</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>110.87</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>-104.44</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2026/01/08</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>3097.227272727273</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>1358.0</t>
+        </is>
+      </c>
+      <c r="BK8" t="n">
+        <v>1619.8</v>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>1869.6</t>
+        </is>
+      </c>
+      <c r="BM8" t="n">
+        <v>1245.84</v>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>-249</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>119.4814491948048</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>19.65645405733221</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>1358.0</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>-0.93</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>綠茵</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>綠茵</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>食品工業</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>43.18290500198112</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>12.18914260633116</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>4.818590014463328</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>4.86</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>7.61</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>13.91</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
+          <t>48.81%</t>
+        </is>
+      </c>
+      <c r="CK8" t="inlineStr">
+        <is>
+          <t>17.38%</t>
+        </is>
+      </c>
+      <c r="CL8" t="inlineStr">
+        <is>
+          <t>28.01</t>
+        </is>
+      </c>
+      <c r="CM8" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="CN8" t="inlineStr">
+        <is>
+          <t>保健食品配方65.97%、保健食品原料33.59%、其他0.43% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO8" t="inlineStr">
+        <is>
+          <t>綠茵-食品工業-上櫃</t>
+        </is>
+      </c>
+      <c r="CP8" t="inlineStr">
+        <is>
+          <t>食品工業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CQ8" t="inlineStr">
+        <is>
           <t>74.3</t>
         </is>
       </c>
-      <c r="AZ8" t="n">
-        <v>74.09</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>74.41</v>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>74.52</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>82.76</t>
-        </is>
-      </c>
-      <c r="BD8" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>-105.67</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>2026/01/08</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>3097.838613861386</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>2568.0</t>
-        </is>
-      </c>
-      <c r="BK8" t="n">
-        <v>2424.6</v>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>1881.9</t>
-        </is>
-      </c>
-      <c r="BM8" t="n">
-        <v>1233.16</v>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>542</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>137.6314483107089</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>82.78568280423974</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>2568.0</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>75.2</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>2025/12/04</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>-0.80</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>綠茵</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>綠茵</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>食品工業</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>43.18290500198112</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>12.18914260633116</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>4.818590014463328</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>4.84</t>
-        </is>
-      </c>
-      <c r="CH8" t="inlineStr">
-        <is>
-          <t>7.61</t>
-        </is>
-      </c>
-      <c r="CI8" t="inlineStr">
-        <is>
-          <t>13.91</t>
-        </is>
-      </c>
-      <c r="CJ8" t="inlineStr">
-        <is>
-          <t>48.81%</t>
-        </is>
-      </c>
-      <c r="CK8" t="inlineStr">
-        <is>
-          <t>17.38%</t>
-        </is>
-      </c>
-      <c r="CL8" t="inlineStr">
-        <is>
-          <t>28.01</t>
-        </is>
-      </c>
-      <c r="CM8" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="CN8" t="inlineStr">
-        <is>
-          <t>保健食品配方65.97%、保健食品原料33.59%、其他0.43% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO8" t="inlineStr">
-        <is>
-          <t>綠茵-食品工業-上櫃</t>
-        </is>
-      </c>
-      <c r="CP8" t="inlineStr">
-        <is>
-          <t>食品工業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CQ8" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4415,12 +4415,12 @@
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="CY8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4437,34 +4437,34 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>0.41</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>34.0</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>74.6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
           <t>-0.27</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>24.0</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>74.3</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>28.84</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-13.00</t>
+          <t>-12.65</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4612,17 +4612,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>8.96</t>
+          <t>12.69</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4643,56 +4643,56 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>69.26</t>
+          <t>92.59</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.13</v>
+        <v>0.29</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>74.14</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>74.04000000000001</v>
+        <v>74.09</v>
       </c>
       <c r="BA9" t="n">
-        <v>74.47</v>
+        <v>74.41</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>74.55</t>
+          <t>74.52</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>82.76</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="BE9" t="n">
-        <v>-0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-106.84</t>
+          <t>-105.67</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4711,43 +4711,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>3097.838613861386</t>
+          <t>3097.227272727273</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>1790.0</t>
+          <t>2568.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>2176.2</v>
+        <v>2424.6</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1990.3</t>
+          <t>1881.9</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>1194.16</v>
+        <v>1233.16</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>542</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>147.6034056755215</t>
+          <t>137.6314483107089</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>40.37080662824201</t>
+          <t>82.78568280423974</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>1790.0</t>
+          <t>2568.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-0.80</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
@@ -4892,7 +4892,7 @@
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="CY9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -4934,12 +4934,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>24.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>12.70</t>
+          <t>9.34</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-12.76</t>
+          <t>-13.00</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5109,17 +5109,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>5.60</t>
+          <t>8.96</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5140,56 +5140,56 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>69.26</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>0.59</v>
+        <v>0.22</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>74.06</t>
+          <t>74.14</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>74</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="BA10" t="n">
-        <v>74.53</v>
+        <v>74.47</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>74.58</t>
+          <t>74.55</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>38.85</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="BE10" t="n">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-107.70</t>
+          <t>-106.84</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5208,43 +5208,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>3097.838613861386</t>
+          <t>3097.227272727273</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>1123.0</t>
+          <t>1790.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>2129.6</v>
+        <v>2176.2</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1889.7</t>
+          <t>1990.3</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>1175.68</v>
+        <v>1194.16</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>185</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>167.100241865936</t>
+          <t>147.6034056755215</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>61.69345471152246</t>
+          <t>40.37080662824201</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>1123.0</t>
+          <t>1790.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5374,24 +5374,24 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
+          <t>74.9</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>74.9</t>
+        </is>
+      </c>
+      <c r="CS10" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="CT10" t="inlineStr">
+        <is>
           <t>74.3</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
-        <is>
-          <t>74.5</t>
-        </is>
-      </c>
-      <c r="CS10" t="inlineStr">
-        <is>
-          <t>74.0</t>
-        </is>
-      </c>
-      <c r="CT10" t="inlineStr">
-        <is>
-          <t>74.5</t>
-        </is>
-      </c>
       <c r="CU10" t="inlineStr">
         <is>
           <t>34.3</t>
@@ -5409,12 +5409,12 @@
       </c>
       <c r="CX10" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="CY10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -5431,12 +5431,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>12.70</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-13.47</t>
+          <t>-12.76</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5606,17 +5606,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>5.60</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5637,256 +5637,256 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>31.79</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-0.14</v>
+        <v>0.59</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
+          <t>74.06</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>74</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>74.53</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>74.58</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>38.85</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>-107.70</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2026/01/08</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>3097.227272727273</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>1123.0</t>
+        </is>
+      </c>
+      <c r="BK11" t="n">
+        <v>2129.6</v>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>1889.7</t>
+        </is>
+      </c>
+      <c r="BM11" t="n">
+        <v>1175.68</v>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>167.100241865936</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>61.69345471152246</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>1123.0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>2025/12/04</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>-0.93</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>綠茵</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>綠茵</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>食品工業</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>43.18290500198112</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>12.18914260633116</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>4.818590014463328</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>4.86</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>7.61</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>13.91</t>
+        </is>
+      </c>
+      <c r="CJ11" t="inlineStr">
+        <is>
+          <t>48.81%</t>
+        </is>
+      </c>
+      <c r="CK11" t="inlineStr">
+        <is>
+          <t>17.38%</t>
+        </is>
+      </c>
+      <c r="CL11" t="inlineStr">
+        <is>
+          <t>28.01</t>
+        </is>
+      </c>
+      <c r="CM11" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="CN11" t="inlineStr">
+        <is>
+          <t>保健食品配方65.97%、保健食品原料33.59%、其他0.43% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO11" t="inlineStr">
+        <is>
+          <t>綠茵-食品工業-上櫃</t>
+        </is>
+      </c>
+      <c r="CP11" t="inlineStr">
+        <is>
+          <t>食品工業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>74.3</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="CS11" t="inlineStr">
+        <is>
           <t>74.0</t>
         </is>
       </c>
-      <c r="AZ11" t="n">
-        <v>73.97</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>74.59999999999999</v>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>74.62</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>11.57</t>
-        </is>
-      </c>
-      <c r="BD11" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>-0.14</v>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>-108.44</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>2026/01/08</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>3097.838613861386</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>1260.0</t>
-        </is>
-      </c>
-      <c r="BK11" t="n">
-        <v>1951.4</v>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>1837.0</t>
-        </is>
-      </c>
-      <c r="BM11" t="n">
-        <v>1193.06</v>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>186.2651122576475</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>161.4153285907973</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>1260.0</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>75.2</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>2025/12/04</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>-1.73</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>綠茵</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>綠茵</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>食品工業</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>43.18290500198112</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>12.18914260633116</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>4.818590014463328</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>4.84</t>
-        </is>
-      </c>
-      <c r="CH11" t="inlineStr">
-        <is>
-          <t>7.61</t>
-        </is>
-      </c>
-      <c r="CI11" t="inlineStr">
-        <is>
-          <t>13.91</t>
-        </is>
-      </c>
-      <c r="CJ11" t="inlineStr">
-        <is>
-          <t>48.81%</t>
-        </is>
-      </c>
-      <c r="CK11" t="inlineStr">
-        <is>
-          <t>17.38%</t>
-        </is>
-      </c>
-      <c r="CL11" t="inlineStr">
-        <is>
-          <t>28.01</t>
-        </is>
-      </c>
-      <c r="CM11" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="CN11" t="inlineStr">
-        <is>
-          <t>保健食品配方65.97%、保健食品原料33.59%、其他0.43% (2024年)</t>
-        </is>
-      </c>
-      <c r="CO11" t="inlineStr">
-        <is>
-          <t>綠茵-食品工業-上櫃</t>
-        </is>
-      </c>
-      <c r="CP11" t="inlineStr">
-        <is>
-          <t>食品工業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CQ11" t="inlineStr">
-        <is>
-          <t>74.9</t>
-        </is>
-      </c>
-      <c r="CR11" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="CS11" t="inlineStr">
-        <is>
-          <t>73.6</t>
-        </is>
-      </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5906,19 +5906,19 @@
       </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="CY11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-22.77</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>-13.47</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -6103,17 +6103,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>27.24</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6134,56 +6134,56 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>29.49</t>
+          <t>31.79</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>0.35</v>
+        <v>-0.14</v>
       </c>
       <c r="AV12" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>73.94000000000001</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
         <v>73.97</v>
       </c>
       <c r="BA12" t="n">
-        <v>74.64</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>74.66</t>
+          <t>74.62</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>15.76</t>
+          <t>11.57</t>
         </is>
       </c>
       <c r="BD12" t="n">
         <v>-0.13</v>
       </c>
       <c r="BE12" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-108.69</t>
+          <t>-108.44</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6202,43 +6202,43 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>3097.838613861386</t>
+          <t>3097.227272727273</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>5382.0</t>
+          <t>1260.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>2119.4</v>
+        <v>1951.4</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>2744.4</t>
+          <t>1837.0</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>1180.18</v>
+        <v>1193.06</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-625</t>
+          <t>114</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>190.7832547425293</t>
+          <t>186.2651122576475</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>283.4317438258045</t>
+          <t>161.4153285907973</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>5382.0</t>
+          <t>1260.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6368,22 +6368,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6403,12 +6403,12 @@
       </c>
       <c r="CX12" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="CY12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -6430,7 +6430,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>101.762</t>
+          <t>68.288</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6460,7 +6460,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-14.66</t>
+          <t>-16.55</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6595,22 +6595,22 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2025-08-19 00:00:00</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6621,33 +6621,33 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>-0.06</v>
+        <v>0.1</v>
       </c>
       <c r="AV13" t="n">
         <v>-0.04</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
@@ -6668,16 +6668,16 @@
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>31.86</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>12.12</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="BE13" t="n">
         <v>-0.04</v>
@@ -6689,7 +6689,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-113.60</t>
+          <t>-113.20</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6699,43 +6699,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>11288918.23613963</t>
+          <t>11272415.87397541</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>3212612.0</t>
+          <t>2157177.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>2760471</v>
+        <v>2705911.6</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>3234603.8</t>
+          <t>3242660.5</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>3330946.94</v>
+        <v>3299515.58</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>-474132</t>
+          <t>-536748</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-22283.69990492628</t>
+          <t>-35261.4147009219</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-52939.56789948372</t>
+          <t>-106638.8460788978</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>3212612.0</t>
+          <t>2157177.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
@@ -6815,7 +6815,7 @@
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
+          <t>31.55</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
           <t>31.6</t>
         </is>
       </c>
-      <c r="CR13" t="inlineStr">
-        <is>
-          <t>31.65</t>
-        </is>
-      </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6900,19 +6900,19 @@
       </c>
       <c r="CX13" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="CY13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【d1】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6922,42 +6922,42 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>101.762</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>31.55</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>52.658</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4.46</t>
+          <t>-14.66</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.17</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -7092,22 +7092,22 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2025-08-19 00:00:00</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -7118,59 +7118,59 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>22.86</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>-0.32</v>
+        <v>-0.06</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>31.57</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>31.59</v>
+        <v>31.58</v>
       </c>
       <c r="BA14" t="n">
-        <v>31.71</v>
+        <v>31.7</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>31.87</t>
+          <t>31.86</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>8.23</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="BD14" t="n">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-113.78</t>
+          <t>-113.60</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7196,43 +7196,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>11288918.23613963</t>
+          <t>11272415.87397541</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>1660091.0</t>
+          <t>3212612.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>3220987.4</v>
+        <v>2760471</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>3083421.0</t>
+          <t>3234603.8</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>3297756.66</v>
+        <v>3330946.94</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>137566</t>
+          <t>-474132</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-16709.90572409765</t>
+          <t>-22283.69990492628</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-87417.93593248213</t>
+          <t>-52939.56789948372</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>1660091.0</t>
+          <t>3212612.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-3.52</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7297,12 +7297,12 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
@@ -7312,7 +7312,7 @@
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7337,12 +7337,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7362,22 +7362,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
+          <t>31.6</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
+          <t>31.65</t>
+        </is>
+      </c>
+      <c r="CS14" t="inlineStr">
+        <is>
           <t>31.5</t>
         </is>
       </c>
-      <c r="CR14" t="inlineStr">
-        <is>
-          <t>31.6</t>
-        </is>
-      </c>
-      <c r="CS14" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
-      </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7397,12 +7397,12 @@
       </c>
       <c r="CX14" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="CY14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -7419,192 +7419,192 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>52.658</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>4.46</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-08-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-07-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-07-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>33.05</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>32.25</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>32.9</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>32.75</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>-2.33</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025/02/21</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>32.7</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2025/08/28</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>32.2</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>2025/04/08</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>30.65</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>2025/12/10</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>31.6</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>2025/12/08</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>31.6</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>2025-08-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>5.18</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
           <t>-0.32</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>81.467</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>31.5</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>4.84</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2025-08-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-07-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-07-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>33.05</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>32.25</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>32.9</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>32.75</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>-2.33</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025/02/21</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>32.7</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2025/08/28</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>32.2</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>2025/04/08</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>30.65</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>2025/12/10</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>31.6</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>2025/12/08</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>31.6</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>2025-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>8.01</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>-0.16</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7615,12 +7615,12 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -7630,18 +7630,18 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>-0.44</v>
+        <v>-0.32</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.14</v>
+        <v>0.04</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.39</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
@@ -7651,27 +7651,27 @@
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>31.64</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>31.6</v>
+        <v>31.59</v>
       </c>
       <c r="BA15" t="n">
-        <v>31.72</v>
+        <v>31.71</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>31.88</t>
+          <t>31.87</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>25.55</t>
+          <t>8.23</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="BE15" t="n">
         <v>-0.04</v>
@@ -7683,7 +7683,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-114.07</t>
+          <t>-113.78</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7693,43 +7693,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>11288918.23613963</t>
+          <t>11272415.87397541</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>2568418.0</t>
+          <t>1660091.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>3289054.2</v>
+        <v>3220987.4</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>3137217.9</t>
+          <t>3083421.0</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>3324051.1</v>
+        <v>3297756.66</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>151836</t>
+          <t>137566</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-3853.900231664111</t>
+          <t>-16709.90572409765</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>32790.85744653689</t>
+          <t>-87417.93593248213</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>2568418.0</t>
+          <t>1660091.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
+          <t>31.5</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
           <t>31.6</t>
         </is>
       </c>
-      <c r="CR15" t="inlineStr">
-        <is>
-          <t>31.6</t>
-        </is>
-      </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>31.45</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
@@ -7894,34 +7894,34 @@
       </c>
       <c r="CX15" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="CY15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1227</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>686.442</t>
+          <t>81.467</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>0.32</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>5.41</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7961,37 +7961,37 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2024-06-21 00:00:00</t>
+          <t>2025-08-04 00:00:00</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2024-06-27 00:00:00</t>
+          <t>2025-08-20 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2024-05-07 00:00:00</t>
+          <t>2025-07-25 00:00:00</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2024-05-30 00:00:00</t>
+          <t>2025-07-28 00:00:00</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>33.05</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -8001,12 +8001,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>40.75</t>
+          <t>32.75</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -8016,22 +8016,22 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-32.51</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025/05/15</t>
+          <t>2025/02/21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -8041,67 +8041,67 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>2025/11/21</t>
+          <t>2025/08/28</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2025/06/10</t>
+          <t>2025/04/08</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>2026/02/02</t>
+          <t>2025/12/10</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>2025/12/26</t>
+          <t>2025/12/08</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>30.45</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2025-10-13 00:00:00</t>
+          <t>2025-08-19 00:00:00</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -8112,121 +8112,121 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>68</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-0.48</v>
+        <v>-0.44</v>
       </c>
       <c r="AV16" t="n">
-        <v>-1.42</v>
+        <v>0.14</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>28.89</t>
+          <t>31.64</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>29.3</v>
+        <v>31.6</v>
       </c>
       <c r="BA16" t="n">
-        <v>30.07</v>
+        <v>31.72</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>30.56</t>
+          <t>31.88</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-8.49</t>
+          <t>25.55</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-0.35</v>
+        <v>-0.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>-0.32</v>
+        <v>-0.04</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-136.17</t>
+          <t>-114.07</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026/01/27</t>
+          <t>2025/12/19</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>35205947.87007874</t>
+          <t>11272415.87397541</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>19713512.0</t>
+          <t>2568418.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>25269590.8</v>
+        <v>3289054.2</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>23972703.1</t>
+          <t>3137217.9</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>17993919.1</v>
+        <v>3324051.1</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>1296887</t>
+          <t>151836</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>1009996.35247948</t>
+          <t>-3853.900231664111</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>58994.38542637974</t>
+          <t>32790.85744653689</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>19713512.0</t>
+          <t>2568418.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8236,27 +8236,27 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>2025/10/15</t>
+          <t>2025/05/19</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>-15.32</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>臺鹽</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
         <is>
-          <t>佳格</t>
+          <t>臺鹽</t>
         </is>
       </c>
       <c r="BX16" t="inlineStr">
@@ -8271,27 +8271,27 @@
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
         <is>
-          <t>6.237608785148733</t>
+          <t>11.30964198266164</t>
         </is>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>-17.09267911306208</t>
+          <t>7.950770160072485</t>
         </is>
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>-3.78772922691385</t>
+          <t>2.099499961706554</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8301,52 +8301,52 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>19.69</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
         <is>
-          <t>23.06%</t>
+          <t>39.76%</t>
         </is>
       </c>
       <c r="CK16" t="inlineStr">
         <is>
-          <t>4.46%</t>
+          <t>11.78%</t>
         </is>
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>26309</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
         <is>
-          <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
+          <t>鹽46.50%、包裝飲用水34.02%、清潔用品5.33%、保健食品5.08%、美容保養品4.12%、工程及勞務2.55%、其他2.39% (2024年)</t>
         </is>
       </c>
       <c r="CO16" t="inlineStr">
         <is>
-          <t>佳格-食品工業-上市</t>
+          <t>臺鹽-食品工業-上市</t>
         </is>
       </c>
       <c r="CP16" t="inlineStr">
@@ -8356,32 +8356,32 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>28.9</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>28.55</t>
+          <t>31.45</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
         <is>
-          <t>19.66</t>
+          <t>33.23</t>
         </is>
       </c>
       <c r="CV16" t="inlineStr">
         <is>
-          <t>** 食品 - 營養食品</t>
+          <t>** 食品 - 原物料、營養食品** 石化及塑橡膠 - 化妝品</t>
         </is>
       </c>
       <c r="CW16" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="CX16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="CY16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -8413,12 +8413,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>684.565</t>
+          <t>641.618</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8513,7 +8513,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-32.63</t>
+          <t>-31.92</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8588,17 +8588,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>13.09</t>
+          <t>12.27</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8609,66 +8609,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>642</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.58</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-1.17</v>
+        <v>0.52</v>
       </c>
       <c r="AV17" t="n">
-        <v>-1.08</v>
+        <v>-1.44</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>29.04</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>29.36</v>
+        <v>29.27</v>
       </c>
       <c r="BA17" t="n">
-        <v>30.11</v>
+        <v>30.04</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>30.61</t>
+          <t>30.53</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-8.01</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-0.34</v>
+        <v>-0.33</v>
       </c>
       <c r="BE17" t="n">
-        <v>-0.31</v>
+        <v>-0.32</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-135.41</t>
+          <t>-136.41</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8687,43 +8687,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>35205947.87007874</t>
+          <t>35191611.34774067</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>19622440.0</t>
+          <t>18605772.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>25744507.6</v>
+        <v>24278306.2</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>25477935.4</t>
+          <t>23511265.0</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>17954301.62</v>
+        <v>18149976.84</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>266572</t>
+          <t>767041</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>1182905.801034589</t>
+          <t>791554.6021096328</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>608014.4578767233</t>
+          <t>-409875.0249245241</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>19622440.0</t>
+          <t>18605772.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>-15.46</t>
+          <t>-14.58</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -8788,22 +8788,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>19.69</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8828,12 +8828,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>26309</t>
+          <t>26538</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8853,22 +8853,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>28.85</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>28.55</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="CX17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CY17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -8910,12 +8910,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1270.894</t>
+          <t>686.442</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8925,149 +8925,149 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>28.75</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>5.41</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2024-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2024-06-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2024-05-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2024-05-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>43.0</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>42.6</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>38.75</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>40.75</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>-32.51</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>5.52</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025/05/15</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>35.5</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>-0.0</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>30.5</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>33.25</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>2026/02/02</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
           <t>28.8</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>-0.17</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>6.35</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2024-06-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2024-06-27 00:00:00</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2024-05-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2024-05-30 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>43.0</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>42.6</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>38.75</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>40.75</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>-32.39</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>5.52</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2025/05/15</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>35.5</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>2025/11/21</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>30.5</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>2025/06/10</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>33.25</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>2026/02/02</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>28.8</t>
-        </is>
-      </c>
       <c r="AI18" t="inlineStr">
         <is>
           <t>2025/12/26</t>
@@ -9085,17 +9085,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>24.30</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -9106,67 +9106,67 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>642</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>-1.37</v>
+        <v>-0.48</v>
       </c>
       <c r="AV18" t="n">
-        <v>-0.74</v>
+        <v>-1.42</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>-2.43</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.89</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>29.42</v>
+        <v>29.3</v>
       </c>
       <c r="BA18" t="n">
-        <v>30.15</v>
+        <v>30.07</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>30.63</t>
+          <t>30.56</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-8.49</t>
         </is>
       </c>
       <c r="BD18" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="BE18" t="n">
         <v>-0.32</v>
       </c>
-      <c r="BE18" t="n">
-        <v>-0.31</v>
-      </c>
       <c r="BF18" t="inlineStr">
         <is>
           <t>0.89</t>
@@ -9174,7 +9174,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-134.70</t>
+          <t>-136.17</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9184,43 +9184,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>35205947.87007874</t>
+          <t>35191611.34774067</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>36466880.0</t>
+          <t>19713512.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>29210335</v>
+        <v>25269590.8</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>27464981.4</t>
+          <t>23972703.1</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>17798828.46</v>
+        <v>17993919.1</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>1745353</t>
+          <t>1296887</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>1287431.499790564</t>
+          <t>1009996.35247948</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>1380371.75931019</t>
+          <t>58994.38542637974</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>36466880.0</t>
+          <t>19713512.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>-15.17</t>
+          <t>-15.32</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9265,7 +9265,7 @@
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -9285,12 +9285,12 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9310,7 +9310,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>19.69</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9325,12 +9325,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>26309</t>
+          <t>26538</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9350,22 +9350,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>28.9</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>28.5</t>
+          <t>28.55</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9385,19 +9385,19 @@
       </c>
       <c r="CX18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CY18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>929.211</t>
+          <t>684.565</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9432,7 +9432,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.87</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -9442,7 +9442,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-31.92</t>
+          <t>-32.63</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9582,17 +9582,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>17.77</t>
+          <t>13.09</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9603,12 +9603,12 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>642</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -9618,48 +9618,48 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>-0.99</v>
+        <v>-1.17</v>
       </c>
       <c r="AV19" t="n">
-        <v>-0.64</v>
+        <v>-1.08</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>29.04</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>29.48</v>
+        <v>29.36</v>
       </c>
       <c r="BA19" t="n">
-        <v>30.18</v>
+        <v>30.11</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>30.65</t>
+          <t>30.61</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>-8.01</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-0.3</v>
+        <v>-0.34</v>
       </c>
       <c r="BE19" t="n">
         <v>-0.31</v>
@@ -9671,7 +9671,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-134.41</t>
+          <t>-135.41</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9681,43 +9681,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>35205947.87007874</t>
+          <t>35191611.34774067</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>26982927.0</t>
+          <t>19622440.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>25171849.8</v>
+        <v>25744507.6</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>26932073.1</t>
+          <t>25477935.4</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>17257437.18</v>
+        <v>17954301.62</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-1760223</t>
+          <t>266572</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>1270533.270786996</t>
+          <t>1182905.801034589</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>629678.9128112085</t>
+          <t>608014.4578767233</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>26982927.0</t>
+          <t>19622440.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9737,7 +9737,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>-14.58</t>
+          <t>-15.46</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -9782,7 +9782,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9792,12 +9792,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9807,7 +9807,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>19.69</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9822,12 +9822,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>26309</t>
+          <t>26538</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9847,22 +9847,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.85</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.55</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9882,19 +9882,19 @@
       </c>
       <c r="CX19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CY19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>805.179</t>
+          <t>1270.894</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9919,7 +9919,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9929,7 +9929,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-16.58</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-31.46</t>
+          <t>-32.39</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -10079,17 +10079,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>15.40</t>
+          <t>24.30</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -10100,63 +10100,63 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>642</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>64.02</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-0.41</v>
+        <v>-1.37</v>
       </c>
       <c r="AV20" t="n">
-        <v>-0.73</v>
+        <v>-0.74</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.43</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>29.32</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>29.54</v>
+        <v>29.42</v>
       </c>
       <c r="BA20" t="n">
-        <v>30.2</v>
+        <v>30.15</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>30.66</t>
+          <t>30.63</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>7.54</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>-0.28</v>
+        <v>-0.32</v>
       </c>
       <c r="BE20" t="n">
         <v>-0.31</v>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-134.67</t>
+          <t>-134.70</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -10178,43 +10178,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>35205947.87007874</t>
+          <t>35191611.34774067</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>23562195.0</t>
+          <t>36466880.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>22744223.8</v>
+        <v>29210335</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>27263981.0</t>
+          <t>27464981.4</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>16975055.4</v>
+        <v>17798828.46</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-4519757</t>
+          <t>1745353</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>1387052.244964412</t>
+          <t>1287431.499790564</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>550909.8494979739</t>
+          <t>1380371.75931019</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>23562195.0</t>
+          <t>36466880.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-13.99</t>
+          <t>-15.17</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10259,7 +10259,7 @@
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -10289,12 +10289,12 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>19.69</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>26309</t>
+          <t>26538</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10344,22 +10344,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10379,12 +10379,12 @@
       </c>
       <c r="CX20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CY20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -10401,34 +10401,34 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>-0.68</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>929.211</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>29.0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>750.554</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>29.5</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>-2.61</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -10436,7 +10436,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-15.05</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10501,7 +10501,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-30.75</t>
+          <t>-31.92</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10526,7 +10526,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10576,17 +10576,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>17.77</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10597,63 +10597,63 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>642</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>65.93</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>0.65</v>
+        <v>-0.99</v>
       </c>
       <c r="AV21" t="n">
-        <v>-0.93</v>
+        <v>-0.64</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-2.12</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>29.58</v>
+        <v>29.48</v>
       </c>
       <c r="BA21" t="n">
-        <v>30.22</v>
+        <v>30.18</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>30.67</t>
+          <t>30.65</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>8.86</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="BE21" t="n">
         <v>-0.31</v>
@@ -10665,7 +10665,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-135.33</t>
+          <t>-134.41</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10675,43 +10675,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>35205947.87007874</t>
+          <t>35191611.34774067</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>22088096.0</t>
+          <t>26982927.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>22675815.4</v>
+        <v>25171849.8</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>26693420.2</t>
+          <t>26932073.1</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>16884946.42</v>
+        <v>17257437.18</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-4017604</t>
+          <t>-1760223</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>1539078.135049219</t>
+          <t>1270533.270786996</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>785214.264425572</t>
+          <t>629678.9128112085</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>22088096.0</t>
+          <t>26982927.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>-14.58</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -10776,22 +10776,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>19.69</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>26309</t>
+          <t>26538</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10841,22 +10841,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>29.6</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="CX21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CY21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -10898,12 +10898,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1249.819</t>
+          <t>805.179</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10913,7 +10913,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -10933,7 +10933,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-4.87</t>
+          <t>-16.58</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10998,7 +10998,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-30.75</t>
+          <t>-31.46</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -11073,17 +11073,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>23.90</t>
+          <t>15.40</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -11094,67 +11094,67 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>642</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>77.78</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>32.59</t>
+          <t>64.02</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>0.89</v>
+        <v>-0.41</v>
       </c>
       <c r="AV22" t="n">
-        <v>-1.3</v>
+        <v>-0.73</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>29.32</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>29.62</v>
+        <v>29.54</v>
       </c>
       <c r="BA22" t="n">
-        <v>30.24</v>
+        <v>30.2</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>30.66</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>7.54</t>
         </is>
       </c>
       <c r="BD22" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="BE22" t="n">
         <v>-0.31</v>
       </c>
-      <c r="BE22" t="n">
-        <v>-0.32</v>
-      </c>
       <c r="BF22" t="inlineStr">
         <is>
           <t>0.89</t>
@@ -11162,7 +11162,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-136.11</t>
+          <t>-134.67</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -11172,43 +11172,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>35205947.87007874</t>
+          <t>35191611.34774067</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>36951577.0</t>
+          <t>23562195.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>25211363.2</v>
+        <v>22744223.8</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>26502871.8</t>
+          <t>27263981.0</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>16852284.6</v>
+        <v>16975055.4</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-1291508</t>
+          <t>-4519757</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>1676144.293344427</t>
+          <t>1387052.244964412</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>1249830.669164084</t>
+          <t>550909.8494979739</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>36951577.0</t>
+          <t>23562195.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>-13.11</t>
+          <t>-13.99</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11253,7 +11253,7 @@
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -11273,7 +11273,7 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11298,7 +11298,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>19.69</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11313,12 +11313,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>26309</t>
+          <t>26538</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11338,22 +11338,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>29.75</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>29.3</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11373,19 +11373,19 @@
       </c>
       <c r="CX22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CY22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>556.2</t>
+          <t>750.554</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11420,7 +11420,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -11430,7 +11430,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-15.05</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11495,7 +11495,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-31.34</t>
+          <t>-30.75</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>14.35</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -11591,66 +11591,66 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>642</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>65.93</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>0.17</v>
+        <v>0.65</v>
       </c>
       <c r="AV23" t="n">
-        <v>-1.61</v>
+        <v>-0.93</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.12</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.31</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>29.68</v>
+        <v>29.58</v>
       </c>
       <c r="BA23" t="n">
-        <v>30.27</v>
+        <v>30.22</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>30.69</t>
+          <t>30.67</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-7.01</t>
+          <t>8.86</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>-0.35</v>
+        <v>-0.29</v>
       </c>
       <c r="BE23" t="n">
-        <v>-0.32</v>
+        <v>-0.31</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-136.30</t>
+          <t>-135.33</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11669,43 +11669,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>35205947.87007874</t>
+          <t>35191611.34774067</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>16274454.0</t>
+          <t>22088096.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>25719627.8</v>
+        <v>22675815.4</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>25467490.4</t>
+          <t>26693420.2</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>16380710.06</v>
+        <v>16884946.42</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>252137</t>
+          <t>-4017604</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>1753655.861377217</t>
+          <t>1539078.135049219</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>276415.7591775246</t>
+          <t>785214.264425572</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>16274454.0</t>
+          <t>22088096.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-13.84</t>
+          <t>-13.11</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11750,7 +11750,7 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -11770,22 +11770,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>19.69</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11810,12 +11810,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>26309</t>
+          <t>26538</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11835,22 +11835,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
+          <t>29.6</t>
+        </is>
+      </c>
+      <c r="CR23" t="inlineStr">
+        <is>
+          <t>29.65</t>
+        </is>
+      </c>
+      <c r="CS23" t="inlineStr">
+        <is>
           <t>29.3</t>
         </is>
       </c>
-      <c r="CR23" t="inlineStr">
-        <is>
-          <t>29.35</t>
-        </is>
-      </c>
-      <c r="CS23" t="inlineStr">
-        <is>
-          <t>29.1</t>
-        </is>
-      </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11870,19 +11870,19 @@
       </c>
       <c r="CX23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CY23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -11892,42 +11892,42 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1249.819</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>29.5</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-1.72</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>508.716</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>29.15</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>-1.39</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>-4.87</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-31.57</t>
+          <t>-30.75</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -12067,17 +12067,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>23.90</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -12088,63 +12088,63 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>642</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>77.78</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>32.59</t>
         </is>
       </c>
       <c r="AU24" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>-2.05</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>-1.42</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>29.24</t>
+        </is>
+      </c>
+      <c r="AZ24" t="n">
+        <v>29.62</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>30.24</v>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>30.68</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="BD24" t="n">
         <v>-0.31</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>-1.86</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>-1.30</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>29.24</t>
-        </is>
-      </c>
-      <c r="AZ24" t="n">
-        <v>29.74</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="BB24" t="inlineStr">
-        <is>
-          <t>30.7</t>
-        </is>
-      </c>
-      <c r="BC24" t="inlineStr">
-        <is>
-          <t>-11.84</t>
-        </is>
-      </c>
-      <c r="BD24" t="n">
-        <v>-0.35</v>
       </c>
       <c r="BE24" t="n">
         <v>-0.32</v>
@@ -12156,7 +12156,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-135.66</t>
+          <t>-136.11</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -12166,43 +12166,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>35205947.87007874</t>
+          <t>35191611.34774067</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>14844797.0</t>
+          <t>36951577.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>28692296.4</v>
+        <v>25211363.2</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>26444131.4</t>
+          <t>26502871.8</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>16324390.42</v>
+        <v>16852284.6</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>2248165</t>
+          <t>-1291508</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>2022244.97086807</t>
+          <t>1676144.293344427</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>1091357.074940387</t>
+          <t>1249830.669164084</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>14844797.0</t>
+          <t>36951577.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>-14.14</t>
+          <t>-13.11</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12247,7 +12247,7 @@
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -12267,7 +12267,7 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>19.69</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12307,12 +12307,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>26309</t>
+          <t>26538</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12332,22 +12332,22 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
+          <t>29.75</t>
+        </is>
+      </c>
+      <c r="CS24" t="inlineStr">
+        <is>
           <t>29.3</t>
         </is>
       </c>
-      <c r="CS24" t="inlineStr">
-        <is>
-          <t>29.1</t>
-        </is>
-      </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.5</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="CX24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CY24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -12389,42 +12389,42 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>0.34</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>556.2</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>29.25</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>796.89</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>29.15</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>-1.39</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>19.20</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-31.57</t>
+          <t>-31.34</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12564,17 +12564,17 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12585,66 +12585,66 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>642</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>-0.55</v>
+        <v>0.17</v>
       </c>
       <c r="AV25" t="n">
-        <v>-1.66</v>
+        <v>-1.61</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>29.31</t>
+          <t>29.2</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>29.8</v>
+        <v>29.68</v>
       </c>
       <c r="BA25" t="n">
-        <v>30.33</v>
+        <v>30.27</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>30.72</t>
+          <t>30.69</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-14.09</t>
+          <t>-7.01</t>
         </is>
       </c>
       <c r="BD25" t="n">
         <v>-0.35</v>
       </c>
       <c r="BE25" t="n">
-        <v>-0.31</v>
+        <v>-0.32</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-134.61</t>
+          <t>-136.30</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12663,43 +12663,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>35205947.87007874</t>
+          <t>35191611.34774067</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>23220153.0</t>
+          <t>16274454.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>31783738.2</v>
+        <v>25719627.8</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>26663589.6</t>
+          <t>25467490.4</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>16268239.9</v>
+        <v>16380710.06</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>5120148</t>
+          <t>252137</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>2191497.315582194</t>
+          <t>1753655.861377217</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>2369759.451925177</t>
+          <t>276415.7591775246</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>23220153.0</t>
+          <t>16274454.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12719,7 +12719,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>-14.14</t>
+          <t>-13.84</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -12764,22 +12764,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>19.69</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12804,12 +12804,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>26309</t>
+          <t>26538</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12829,24 +12829,24 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>29.15</t>
+          <t>29.3</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
+          <t>29.35</t>
+        </is>
+      </c>
+      <c r="CS25" t="inlineStr">
+        <is>
+          <t>29.1</t>
+        </is>
+      </c>
+      <c r="CT25" t="inlineStr">
+        <is>
           <t>29.25</t>
         </is>
       </c>
-      <c r="CS25" t="inlineStr">
-        <is>
-          <t>29.05</t>
-        </is>
-      </c>
-      <c r="CT25" t="inlineStr">
-        <is>
-          <t>29.15</t>
-        </is>
-      </c>
       <c r="CU25" t="inlineStr">
         <is>
           <t>19.66</t>
@@ -12864,12 +12864,12 @@
       </c>
       <c r="CX25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CY25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -12886,12 +12886,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1191.884</t>
+          <t>508.716</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12911,7 +12911,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>12.12</t>
+          <t>8.50</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -13061,12 +13061,12 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>22.79</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
@@ -13082,12 +13082,12 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>642</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -13101,47 +13101,47 @@
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>-0.85</v>
+        <v>-0.31</v>
       </c>
       <c r="AV26" t="n">
-        <v>-1.61</v>
+        <v>-1.67</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.30</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>29.24</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>29.88</v>
+        <v>29.74</v>
       </c>
       <c r="BA26" t="n">
-        <v>30.36</v>
+        <v>30.3</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>30.73</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-15.00</t>
+          <t>-11.84</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>-0.34</v>
+        <v>-0.35</v>
       </c>
       <c r="BE26" t="n">
-        <v>-0.3</v>
+        <v>-0.32</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-133.39</t>
+          <t>-135.66</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -13160,43 +13160,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>35205947.87007874</t>
+          <t>35191611.34774067</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>34765835.0</t>
+          <t>14844797.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>30711025</v>
+        <v>28692296.4</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>27390013.9</t>
+          <t>26444131.4</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>16109008.78</v>
+        <v>16324390.42</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>3321011</t>
+          <t>2248165</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>2159086.018065288</t>
+          <t>2022244.97086807</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>3214054.724334691</t>
+          <t>1091357.074940387</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>34765835.0</t>
+          <t>14844797.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -13261,7 +13261,7 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13276,7 +13276,7 @@
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>19.69</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>25.82</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>26309</t>
+          <t>26538</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13326,7 +13326,7 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>29.2</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
@@ -13361,12 +13361,509 @@
       </c>
       <c r="CX26" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1227</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CY26" t="inlineStr">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>796.89</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>29.15</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-0.52</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>0.0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>19.20</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2024-06-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2024-06-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2024-05-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2024-05-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>43.0</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>42.6</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>38.75</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>40.75</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>-31.57</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>5.52</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025/05/15</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>35.5</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>30.5</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>2025/06/10</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>33.25</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>2026/02/02</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>28.8</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>2025/12/26</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>30.45</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>15.24</t>
+        </is>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU27" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>-1.66</v>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>-1.74</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>-1.24</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>29.31</t>
+        </is>
+      </c>
+      <c r="AZ27" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>30.33</v>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>30.72</t>
+        </is>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>-14.09</t>
+        </is>
+      </c>
+      <c r="BD27" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="BF27" t="inlineStr">
+        <is>
+          <t>0.89</t>
+        </is>
+      </c>
+      <c r="BG27" t="inlineStr">
+        <is>
+          <t>-134.61</t>
+        </is>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026/01/27</t>
+        </is>
+      </c>
+      <c r="BI27" t="inlineStr">
+        <is>
+          <t>35191611.34774067</t>
+        </is>
+      </c>
+      <c r="BJ27" t="inlineStr">
+        <is>
+          <t>23220153.0</t>
+        </is>
+      </c>
+      <c r="BK27" t="n">
+        <v>31783738.2</v>
+      </c>
+      <c r="BL27" t="inlineStr">
+        <is>
+          <t>26663589.6</t>
+        </is>
+      </c>
+      <c r="BM27" t="n">
+        <v>16268239.9</v>
+      </c>
+      <c r="BN27" t="inlineStr">
+        <is>
+          <t>5120148</t>
+        </is>
+      </c>
+      <c r="BO27" t="inlineStr">
+        <is>
+          <t>2191497.315582194</t>
+        </is>
+      </c>
+      <c r="BP27" t="inlineStr">
+        <is>
+          <t>2369759.451925177</t>
+        </is>
+      </c>
+      <c r="BQ27" t="inlineStr">
+        <is>
+          <t>23220153.0</t>
+        </is>
+      </c>
+      <c r="BR27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BS27" t="inlineStr">
+        <is>
+          <t>33.95</t>
+        </is>
+      </c>
+      <c r="BT27" t="inlineStr">
+        <is>
+          <t>2025/10/15</t>
+        </is>
+      </c>
+      <c r="BU27" t="inlineStr">
+        <is>
+          <t>-14.14</t>
+        </is>
+      </c>
+      <c r="BV27" t="inlineStr">
+        <is>
+          <t>佳格</t>
+        </is>
+      </c>
+      <c r="BW27" t="inlineStr">
+        <is>
+          <t>佳格</t>
+        </is>
+      </c>
+      <c r="BX27" t="inlineStr">
+        <is>
+          <t>食品工業</t>
+        </is>
+      </c>
+      <c r="BY27" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BZ27" t="inlineStr">
+        <is>
+          <t>0.41</t>
+        </is>
+      </c>
+      <c r="CA27" t="inlineStr">
+        <is>
+          <t>6.237608785148733</t>
+        </is>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>-17.09267911306208</t>
+        </is>
+      </c>
+      <c r="CC27" t="inlineStr">
+        <is>
+          <t>-3.78772922691385</t>
+        </is>
+      </c>
+      <c r="CD27" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="CE27" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="CF27" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="CG27" t="inlineStr">
+        <is>
+          <t>4.83</t>
+        </is>
+      </c>
+      <c r="CH27" t="inlineStr">
+        <is>
+          <t>8.02</t>
+        </is>
+      </c>
+      <c r="CI27" t="inlineStr">
+        <is>
+          <t>19.86</t>
+        </is>
+      </c>
+      <c r="CJ27" t="inlineStr">
+        <is>
+          <t>23.06%</t>
+        </is>
+      </c>
+      <c r="CK27" t="inlineStr">
+        <is>
+          <t>4.46%</t>
+        </is>
+      </c>
+      <c r="CL27" t="inlineStr">
+        <is>
+          <t>25.82</t>
+        </is>
+      </c>
+      <c r="CM27" t="inlineStr">
+        <is>
+          <t>26538</t>
+        </is>
+      </c>
+      <c r="CN27" t="inlineStr">
+        <is>
+          <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
+        </is>
+      </c>
+      <c r="CO27" t="inlineStr">
+        <is>
+          <t>佳格-食品工業-上市</t>
+        </is>
+      </c>
+      <c r="CP27" t="inlineStr">
+        <is>
+          <t>食品工業右下上市</t>
+        </is>
+      </c>
+      <c r="CQ27" t="inlineStr">
+        <is>
+          <t>29.15</t>
+        </is>
+      </c>
+      <c r="CR27" t="inlineStr">
+        <is>
+          <t>29.25</t>
+        </is>
+      </c>
+      <c r="CS27" t="inlineStr">
+        <is>
+          <t>29.05</t>
+        </is>
+      </c>
+      <c r="CT27" t="inlineStr">
+        <is>
+          <t>29.15</t>
+        </is>
+      </c>
+      <c r="CU27" t="inlineStr">
+        <is>
+          <t>19.66</t>
+        </is>
+      </c>
+      <c r="CV27" t="inlineStr">
+        <is>
+          <t>** 食品 - 營養食品</t>
+        </is>
+      </c>
+      <c r="CW27" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CX27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="CY27" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/Result/checksun_type/營養食品.xlsx
+++ b/Result/checksun_type/營養食品.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CY29"/>
+  <dimension ref="A1:CZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -686,260 +686,265 @@
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
+          <t>MA_10</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>盤整震盪_前15日次數</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>多頭排列_前5日次數</t>
         </is>
@@ -1193,250 +1198,255 @@
           <t>74.17999999999999</t>
         </is>
       </c>
-      <c r="AZ2" t="n">
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>74.26</t>
+        </is>
+      </c>
+      <c r="BA2" t="n">
         <v>74.14</v>
       </c>
-      <c r="BA2" t="n">
+      <c r="BB2" t="n">
         <v>74.38</v>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>74.31</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>-69.44</t>
         </is>
       </c>
-      <c r="BD2" t="n">
+      <c r="BE2" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BE2" t="n">
+      <c r="BF2" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>1.71</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>-101.04</t>
         </is>
       </c>
-      <c r="BH2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>2026/01/08</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>3089.660433070866</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>370.0</t>
         </is>
       </c>
-      <c r="BK2" t="n">
+      <c r="BL2" t="n">
         <v>837</v>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>1273.0</t>
         </is>
       </c>
-      <c r="BM2" t="n">
+      <c r="BN2" t="n">
         <v>1293.36</v>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-436</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>-65.10859497841946</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
         <is>
           <t>-187.2444682807632</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BR2" t="inlineStr">
         <is>
           <t>370.0</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BS2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
           <t>75.2</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>2025/12/04</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>-1.46</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>綠茵</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>綠茵</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>43.18290500198112</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>12.18914260633116</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>4.818590014463328</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>2.16</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>4.86</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>7.61</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>13.85</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>48.81%</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>17.38%</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>27.8</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>保健食品配方65.97%、保健食品原料33.59%、其他0.43% (2024年)</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>綠茵-食品工業-上櫃</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>食品工業右下上櫃</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>73.8</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>74.1</t>
         </is>
       </c>
-      <c r="CS2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>73.8</t>
         </is>
       </c>
-      <c r="CT2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>74.1</t>
         </is>
       </c>
-      <c r="CU2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>34.3</t>
         </is>
       </c>
-      <c r="CV2" t="inlineStr">
+      <c r="CW2" t="inlineStr">
         <is>
           <t>** 食品 - 原物料、加工食品、營養食品** 食品生技 - 原料、加工製成品</t>
         </is>
       </c>
-      <c r="CW2" t="inlineStr">
+      <c r="CX2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
+      <c r="CY2" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="CY2" t="inlineStr">
+      <c r="CZ2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -1690,250 +1700,255 @@
           <t>74.2</t>
         </is>
       </c>
-      <c r="AZ3" t="n">
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>74.28</t>
+        </is>
+      </c>
+      <c r="BA3" t="n">
         <v>74.17</v>
       </c>
-      <c r="BA3" t="n">
+      <c r="BB3" t="n">
         <v>74.39</v>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>74.3</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>-67.54</t>
         </is>
       </c>
-      <c r="BD3" t="n">
+      <c r="BE3" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BE3" t="n">
+      <c r="BF3" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BF3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>1.71</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>-100.86</t>
         </is>
       </c>
-      <c r="BH3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>2026/01/08</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>3089.660433070866</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>1197.0</t>
         </is>
       </c>
-      <c r="BK3" t="n">
+      <c r="BL3" t="n">
         <v>1061.4</v>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>1415.0</t>
         </is>
       </c>
-      <c r="BM3" t="n">
+      <c r="BN3" t="n">
         <v>1285.98</v>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-353</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>-42.90207255981151</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
         <is>
           <t>-131.3712917227465</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BR3" t="inlineStr">
         <is>
           <t>1197.0</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BS3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
           <t>75.2</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>2025/12/04</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>-1.73</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>綠茵</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>綠茵</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>43.18290500198112</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>12.18914260633116</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>4.818590014463328</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>2.15</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>4.86</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>7.61</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>13.85</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>48.81%</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>17.38%</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>27.8</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>保健食品配方65.97%、保健食品原料33.59%、其他0.43% (2024年)</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>綠茵-食品工業-上櫃</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>食品工業右下上櫃</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>74.2</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>74.2</t>
         </is>
       </c>
-      <c r="CS3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>73.2</t>
         </is>
       </c>
-      <c r="CT3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>73.9</t>
         </is>
       </c>
-      <c r="CU3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>34.3</t>
         </is>
       </c>
-      <c r="CV3" t="inlineStr">
+      <c r="CW3" t="inlineStr">
         <is>
           <t>** 食品 - 原物料、加工食品、營養食品** 食品生技 - 原料、加工製成品</t>
         </is>
       </c>
-      <c r="CW3" t="inlineStr">
+      <c r="CX3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX3" t="inlineStr">
+      <c r="CY3" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="CY3" t="inlineStr">
+      <c r="CZ3" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -2187,250 +2202,255 @@
           <t>74.25999999999999</t>
         </is>
       </c>
-      <c r="AZ4" t="n">
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>74.34</t>
+        </is>
+      </c>
+      <c r="BA4" t="n">
         <v>74.20999999999999</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="BB4" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>74.3</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BD4" t="inlineStr">
         <is>
           <t>124.41</t>
         </is>
       </c>
-      <c r="BD4" t="n">
+      <c r="BE4" t="n">
         <v>0</v>
       </c>
-      <c r="BE4" t="n">
+      <c r="BF4" t="n">
         <v>-0.01</v>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>1.71</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>-100.72</t>
         </is>
       </c>
-      <c r="BH4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>2026/01/08</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>3089.660433070866</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>1859.0</t>
         </is>
       </c>
-      <c r="BK4" t="n">
+      <c r="BL4" t="n">
         <v>1162.6</v>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>1407.6</t>
         </is>
       </c>
-      <c r="BM4" t="n">
+      <c r="BN4" t="n">
         <v>1268.2</v>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-245</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>-26.81675998473243</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
         <is>
           <t>-135.4677790783389</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BR4" t="inlineStr">
         <is>
           <t>1859.0</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BS4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
           <t>75.2</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>2025/12/04</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>-1.60</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>綠茵</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>綠茵</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>43.18290500198112</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>12.18914260633116</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>4.818590014463328</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>2.16</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>4.86</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>7.61</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>13.85</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>48.81%</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>17.38%</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>27.8</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>保健食品配方65.97%、保健食品原料33.59%、其他0.43% (2024年)</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>綠茵-食品工業-上櫃</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>食品工業右下上櫃</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>74.4</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>74.6</t>
         </is>
       </c>
-      <c r="CS4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>74.0</t>
         </is>
       </c>
-      <c r="CT4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>74.0</t>
         </is>
       </c>
-      <c r="CU4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>34.3</t>
         </is>
       </c>
-      <c r="CV4" t="inlineStr">
+      <c r="CW4" t="inlineStr">
         <is>
           <t>** 食品 - 原物料、加工食品、營養食品** 食品生技 - 原料、加工製成品</t>
         </is>
       </c>
-      <c r="CW4" t="inlineStr">
+      <c r="CX4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX4" t="inlineStr">
+      <c r="CY4" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="CY4" t="inlineStr">
+      <c r="CZ4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -2684,250 +2704,255 @@
           <t>74.3</t>
         </is>
       </c>
-      <c r="AZ5" t="n">
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>74.33</t>
+        </is>
+      </c>
+      <c r="BA5" t="n">
         <v>74.26000000000001</v>
       </c>
-      <c r="BA5" t="n">
+      <c r="BB5" t="n">
         <v>74.41</v>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>74.32</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BD5" t="inlineStr">
         <is>
           <t>275.25</t>
         </is>
       </c>
-      <c r="BD5" t="n">
+      <c r="BE5" t="n">
         <v>0.03</v>
       </c>
-      <c r="BE5" t="n">
+      <c r="BF5" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>1.71</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>-100.94</t>
         </is>
       </c>
-      <c r="BH5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>2026/01/08</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>3089.660433070866</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>313.0</t>
         </is>
       </c>
-      <c r="BK5" t="n">
+      <c r="BL5" t="n">
         <v>1075.6</v>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>1347.7</t>
         </is>
       </c>
-      <c r="BM5" t="n">
+      <c r="BN5" t="n">
         <v>1234.02</v>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-272</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>-7.062029240440335</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
         <is>
           <t>-207.41034033353</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BR5" t="inlineStr">
         <is>
           <t>313.0</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BS5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
           <t>75.2</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>2025/12/04</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>-1.06</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>綠茵</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>綠茵</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>43.18290500198112</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>12.18914260633116</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>4.818590014463328</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>2.17</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>4.86</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>7.61</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>13.85</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>48.81%</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>17.38%</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>27.8</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>保健食品配方65.97%、保健食品原料33.59%、其他0.43% (2024年)</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>綠茵-食品工業-上櫃</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>食品工業右下上櫃</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>74.4</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>74.4</t>
         </is>
       </c>
-      <c r="CS5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>74.4</t>
         </is>
       </c>
-      <c r="CT5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>74.4</t>
         </is>
       </c>
-      <c r="CU5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>34.3</t>
         </is>
       </c>
-      <c r="CV5" t="inlineStr">
+      <c r="CW5" t="inlineStr">
         <is>
           <t>** 食品 - 原物料、加工食品、營養食品** 食品生技 - 原料、加工製成品</t>
         </is>
       </c>
-      <c r="CW5" t="inlineStr">
+      <c r="CX5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX5" t="inlineStr">
+      <c r="CY5" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="CY5" t="inlineStr">
+      <c r="CZ5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -3181,250 +3206,255 @@
           <t>74.32000000000001</t>
         </is>
       </c>
-      <c r="AZ6" t="n">
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>74.31</t>
+        </is>
+      </c>
+      <c r="BA6" t="n">
         <v>74.23</v>
       </c>
-      <c r="BA6" t="n">
+      <c r="BB6" t="n">
         <v>74.39</v>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>74.34</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BD6" t="inlineStr">
         <is>
           <t>171.19</t>
         </is>
       </c>
-      <c r="BD6" t="n">
+      <c r="BE6" t="n">
         <v>0.02</v>
       </c>
-      <c r="BE6" t="n">
+      <c r="BF6" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BF6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>1.71</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>-101.59</t>
         </is>
       </c>
-      <c r="BH6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>2026/01/08</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BJ6" t="inlineStr">
         <is>
           <t>3089.660433070866</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>446.0</t>
         </is>
       </c>
-      <c r="BK6" t="n">
+      <c r="BL6" t="n">
         <v>1284.6</v>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>1854.6</t>
         </is>
       </c>
-      <c r="BM6" t="n">
+      <c r="BN6" t="n">
         <v>1241.7</v>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-570</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>29.3649364128487</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
         <is>
           <t>-137.1350585433199</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BR6" t="inlineStr">
         <is>
           <t>446.0</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BS6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
           <t>75.2</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>2025/12/04</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>-0.93</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>綠茵</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>綠茵</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="BZ6" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CA6" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>43.18290500198112</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>12.18914260633116</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>4.818590014463328</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
         <is>
           <t>2.17</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
         <is>
           <t>4.86</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>7.61</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>13.85</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>48.81%</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>17.38%</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>27.8</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>保健食品配方65.97%、保健食品原料33.59%、其他0.43% (2024年)</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>綠茵-食品工業-上櫃</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>食品工業右下上櫃</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>74.2</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>74.5</t>
         </is>
       </c>
-      <c r="CS6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>74.2</t>
         </is>
       </c>
-      <c r="CT6" t="inlineStr">
+      <c r="CU6" t="inlineStr">
         <is>
           <t>74.5</t>
         </is>
       </c>
-      <c r="CU6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>34.3</t>
         </is>
       </c>
-      <c r="CV6" t="inlineStr">
+      <c r="CW6" t="inlineStr">
         <is>
           <t>** 食品 - 原物料、加工食品、營養食品** 食品生技 - 原料、加工製成品</t>
         </is>
       </c>
-      <c r="CW6" t="inlineStr">
+      <c r="CX6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX6" t="inlineStr">
+      <c r="CY6" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="CY6" t="inlineStr">
+      <c r="CZ6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -3678,250 +3708,255 @@
           <t>74.34</t>
         </is>
       </c>
-      <c r="AZ7" t="n">
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>74.24</t>
+        </is>
+      </c>
+      <c r="BA7" t="n">
         <v>74.2</v>
       </c>
-      <c r="BA7" t="n">
+      <c r="BB7" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>74.38</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BD7" t="inlineStr">
         <is>
           <t>93.80</t>
         </is>
       </c>
-      <c r="BD7" t="n">
+      <c r="BE7" t="n">
         <v>-0</v>
       </c>
-      <c r="BE7" t="n">
+      <c r="BF7" t="n">
         <v>-0.04</v>
       </c>
-      <c r="BF7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>1.71</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>-102.27</t>
         </is>
       </c>
-      <c r="BH7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>2026/01/08</t>
         </is>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>3089.660433070866</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>1492.0</t>
         </is>
       </c>
-      <c r="BK7" t="n">
+      <c r="BL7" t="n">
         <v>1709</v>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>1942.6</t>
         </is>
       </c>
-      <c r="BM7" t="n">
+      <c r="BN7" t="n">
         <v>1251.7</v>
       </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-233</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>59.63766276851573</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
         <is>
           <t>-46.09411818075841</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BR7" t="inlineStr">
         <is>
           <t>1492.0</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BS7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
           <t>75.2</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>2025/12/04</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>-1.33</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>綠茵</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>綠茵</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>43.18290500198112</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>12.18914260633116</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>4.818590014463328</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
         <is>
           <t>2.16</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>4.86</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>7.61</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>13.85</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>48.81%</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>17.38%</t>
         </is>
       </c>
-      <c r="CL7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>27.8</t>
         </is>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>保健食品配方65.97%、保健食品原料33.59%、其他0.43% (2024年)</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>綠茵-食品工業-上櫃</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>食品工業右下上櫃</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>74.6</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>74.6</t>
         </is>
       </c>
-      <c r="CS7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>73.9</t>
         </is>
       </c>
-      <c r="CT7" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>74.2</t>
         </is>
       </c>
-      <c r="CU7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>34.3</t>
         </is>
       </c>
-      <c r="CV7" t="inlineStr">
+      <c r="CW7" t="inlineStr">
         <is>
           <t>** 食品 - 原物料、加工食品、營養食品** 食品生技 - 原料、加工製成品</t>
         </is>
       </c>
-      <c r="CW7" t="inlineStr">
+      <c r="CX7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX7" t="inlineStr">
+      <c r="CY7" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="CY7" t="inlineStr">
+      <c r="CZ7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -4175,250 +4210,255 @@
           <t>74.36</t>
         </is>
       </c>
-      <c r="AZ8" t="n">
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>74.21000000000001</t>
+        </is>
+      </c>
+      <c r="BA8" t="n">
         <v>74.18000000000001</v>
       </c>
-      <c r="BA8" t="n">
+      <c r="BB8" t="n">
         <v>74.39</v>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BC8" t="inlineStr">
         <is>
           <t>74.41</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BD8" t="inlineStr">
         <is>
           <t>100.71</t>
         </is>
       </c>
-      <c r="BD8" t="n">
+      <c r="BE8" t="n">
         <v>0</v>
       </c>
-      <c r="BE8" t="n">
+      <c r="BF8" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>1.71</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>-102.80</t>
         </is>
       </c>
-      <c r="BH8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>2026/01/08</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>3089.660433070866</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>1703.0</t>
         </is>
       </c>
-      <c r="BK8" t="n">
+      <c r="BL8" t="n">
         <v>1768.6</v>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>1949.1</t>
         </is>
       </c>
-      <c r="BM8" t="n">
+      <c r="BN8" t="n">
         <v>1235.02</v>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-180</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>78.86162294111104</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
         <is>
           <t>-26.46084201350072</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BR8" t="inlineStr">
         <is>
           <t>1703.0</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BS8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
           <t>75.2</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>2025/12/04</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>-1.33</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>綠茵</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>綠茵</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>43.18290500198112</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>12.18914260633116</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>4.818590014463328</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
         <is>
           <t>2.16</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>4.86</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>7.61</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>13.85</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>48.81%</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>17.38%</t>
         </is>
       </c>
-      <c r="CL8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
         <is>
           <t>27.8</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>保健食品配方65.97%、保健食品原料33.59%、其他0.43% (2024年)</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>綠茵-食品工業-上櫃</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>食品工業右下上櫃</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>73.6</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>74.5</t>
         </is>
       </c>
-      <c r="CS8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>73.6</t>
         </is>
       </c>
-      <c r="CT8" t="inlineStr">
+      <c r="CU8" t="inlineStr">
         <is>
           <t>74.2</t>
         </is>
       </c>
-      <c r="CU8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>34.3</t>
         </is>
       </c>
-      <c r="CV8" t="inlineStr">
+      <c r="CW8" t="inlineStr">
         <is>
           <t>** 食品 - 原物料、加工食品、營養食品** 食品生技 - 原料、加工製成品</t>
         </is>
       </c>
-      <c r="CW8" t="inlineStr">
+      <c r="CX8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX8" t="inlineStr">
+      <c r="CY8" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="CY8" t="inlineStr">
+      <c r="CZ8" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -4672,250 +4712,255 @@
           <t>74.42</t>
         </is>
       </c>
-      <c r="AZ9" t="n">
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>74.21000000000001</t>
+        </is>
+      </c>
+      <c r="BA9" t="n">
         <v>74.16</v>
       </c>
-      <c r="BA9" t="n">
+      <c r="BB9" t="n">
         <v>74.36</v>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BC9" t="inlineStr">
         <is>
           <t>74.45</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BD9" t="inlineStr">
         <is>
           <t>106.40</t>
         </is>
       </c>
-      <c r="BD9" t="n">
+      <c r="BE9" t="n">
         <v>0</v>
       </c>
-      <c r="BE9" t="n">
+      <c r="BF9" t="n">
         <v>-0.06</v>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>1.71</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>-103.51</t>
         </is>
       </c>
-      <c r="BH9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>2026/01/08</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>3089.660433070866</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>1424.0</t>
         </is>
       </c>
-      <c r="BK9" t="n">
+      <c r="BL9" t="n">
         <v>1652.6</v>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>1802.0</t>
         </is>
       </c>
-      <c r="BM9" t="n">
+      <c r="BN9" t="n">
         <v>1263.36</v>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-149</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>98.01116202376772</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
         <is>
           <t>-20.07541741693626</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BR9" t="inlineStr">
         <is>
           <t>1424.0</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BS9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
           <t>75.2</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>2025/12/04</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>-1.33</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>綠茵</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>綠茵</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>43.18290500198112</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>12.18914260633116</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>4.818590014463328</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
+      <c r="CG9" t="inlineStr">
         <is>
           <t>2.16</t>
         </is>
       </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
         <is>
           <t>4.86</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>7.61</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>13.85</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>48.81%</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>17.38%</t>
         </is>
       </c>
-      <c r="CL9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>27.8</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>保健食品配方65.97%、保健食品原料33.59%、其他0.43% (2024年)</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>綠茵-食品工業-上櫃</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>食品工業右下上櫃</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>74.2</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>75.0</t>
         </is>
       </c>
-      <c r="CS9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>73.5</t>
         </is>
       </c>
-      <c r="CT9" t="inlineStr">
+      <c r="CU9" t="inlineStr">
         <is>
           <t>74.2</t>
         </is>
       </c>
-      <c r="CU9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>34.3</t>
         </is>
       </c>
-      <c r="CV9" t="inlineStr">
+      <c r="CW9" t="inlineStr">
         <is>
           <t>** 食品 - 原物料、加工食品、營養食品** 食品生技 - 原料、加工製成品</t>
         </is>
       </c>
-      <c r="CW9" t="inlineStr">
+      <c r="CX9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX9" t="inlineStr">
+      <c r="CY9" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="CY9" t="inlineStr">
+      <c r="CZ9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -5169,250 +5214,255 @@
           <t>74.35999999999999</t>
         </is>
       </c>
-      <c r="AZ10" t="n">
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>74.15</t>
+        </is>
+      </c>
+      <c r="BA10" t="n">
         <v>74.12</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="BB10" t="n">
         <v>74.38</v>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BC10" t="inlineStr">
         <is>
           <t>74.49</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BD10" t="inlineStr">
         <is>
           <t>110.87</t>
         </is>
       </c>
-      <c r="BD10" t="n">
+      <c r="BE10" t="n">
         <v>0.01</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="BF10" t="n">
         <v>-0.08</v>
       </c>
-      <c r="BF10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>1.71</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>-104.44</t>
         </is>
       </c>
-      <c r="BH10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>2026/01/08</t>
         </is>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BJ10" t="inlineStr">
         <is>
           <t>3089.660433070866</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>1358.0</t>
         </is>
       </c>
-      <c r="BK10" t="n">
+      <c r="BL10" t="n">
         <v>1619.8</v>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>1869.6</t>
         </is>
       </c>
-      <c r="BM10" t="n">
+      <c r="BN10" t="n">
         <v>1245.84</v>
       </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-249</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>119.4814491948048</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BQ10" t="inlineStr">
         <is>
           <t>19.65645405733221</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BR10" t="inlineStr">
         <is>
           <t>1358.0</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BS10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
           <t>75.2</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>2025/12/04</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>-0.93</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>綠茵</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>綠茵</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>43.18290500198112</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>12.18914260633116</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>4.818590014463328</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
+      <c r="CG10" t="inlineStr">
         <is>
           <t>2.17</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>4.86</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>7.61</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>13.85</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>48.81%</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>17.38%</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>27.8</t>
         </is>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>保健食品配方65.97%、保健食品原料33.59%、其他0.43% (2024年)</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>綠茵-食品工業-上櫃</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>食品工業右下上櫃</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>74.3</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>76.7</t>
         </is>
       </c>
-      <c r="CS10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>74.1</t>
         </is>
       </c>
-      <c r="CT10" t="inlineStr">
+      <c r="CU10" t="inlineStr">
         <is>
           <t>74.5</t>
         </is>
       </c>
-      <c r="CU10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>34.3</t>
         </is>
       </c>
-      <c r="CV10" t="inlineStr">
+      <c r="CW10" t="inlineStr">
         <is>
           <t>** 食品 - 原物料、加工食品、營養食品** 食品生技 - 原料、加工製成品</t>
         </is>
       </c>
-      <c r="CW10" t="inlineStr">
+      <c r="CX10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX10" t="inlineStr">
+      <c r="CY10" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="CY10" t="inlineStr">
+      <c r="CZ10" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -5666,250 +5716,255 @@
           <t>74.3</t>
         </is>
       </c>
-      <c r="AZ11" t="n">
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>74.08</t>
+        </is>
+      </c>
+      <c r="BA11" t="n">
         <v>74.09</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BB11" t="n">
         <v>74.41</v>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BC11" t="inlineStr">
         <is>
           <t>74.52</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BD11" t="inlineStr">
         <is>
           <t>82.76</t>
         </is>
       </c>
-      <c r="BD11" t="n">
+      <c r="BE11" t="n">
         <v>-0.02</v>
       </c>
-      <c r="BE11" t="n">
+      <c r="BF11" t="n">
         <v>-0.1</v>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>1.71</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>-105.67</t>
         </is>
       </c>
-      <c r="BH11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>2026/01/08</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>3089.660433070866</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>2568.0</t>
         </is>
       </c>
-      <c r="BK11" t="n">
+      <c r="BL11" t="n">
         <v>2424.6</v>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>1881.9</t>
         </is>
       </c>
-      <c r="BM11" t="n">
+      <c r="BN11" t="n">
         <v>1233.16</v>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>542</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>137.6314483107089</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
         <is>
           <t>82.78568280423974</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BR11" t="inlineStr">
         <is>
           <t>2568.0</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
           <t>75.2</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>2025/12/04</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>-0.80</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>綠茵</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>綠茵</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>43.18290500198112</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>12.18914260633116</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>4.818590014463328</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CG11" t="inlineStr">
         <is>
           <t>2.17</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>4.86</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>7.61</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>13.85</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>48.81%</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>17.38%</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>27.8</t>
         </is>
       </c>
-      <c r="CM11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>保健食品配方65.97%、保健食品原料33.59%、其他0.43% (2024年)</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>綠茵-食品工業-上櫃</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>食品工業右下上櫃</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>74.0</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>75.0</t>
         </is>
       </c>
-      <c r="CS11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>74.0</t>
         </is>
       </c>
-      <c r="CT11" t="inlineStr">
+      <c r="CU11" t="inlineStr">
         <is>
           <t>74.6</t>
         </is>
       </c>
-      <c r="CU11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>34.3</t>
         </is>
       </c>
-      <c r="CV11" t="inlineStr">
+      <c r="CW11" t="inlineStr">
         <is>
           <t>** 食品 - 原物料、加工食品、營養食品** 食品生技 - 原料、加工製成品</t>
         </is>
       </c>
-      <c r="CW11" t="inlineStr">
+      <c r="CX11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX11" t="inlineStr">
+      <c r="CY11" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="CY11" t="inlineStr">
+      <c r="CZ11" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -6163,250 +6218,255 @@
           <t>74.14</t>
         </is>
       </c>
-      <c r="AZ12" t="n">
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>74.02</t>
+        </is>
+      </c>
+      <c r="BA12" t="n">
         <v>74.04000000000001</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BB12" t="n">
         <v>74.47</v>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BC12" t="inlineStr">
         <is>
           <t>74.55</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BD12" t="inlineStr">
         <is>
           <t>50.01</t>
         </is>
       </c>
-      <c r="BD12" t="n">
+      <c r="BE12" t="n">
         <v>-0.06</v>
       </c>
-      <c r="BE12" t="n">
+      <c r="BF12" t="n">
         <v>-0.12</v>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>1.71</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>-106.84</t>
         </is>
       </c>
-      <c r="BH12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>2026/01/08</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>3089.660433070866</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>1790.0</t>
         </is>
       </c>
-      <c r="BK12" t="n">
+      <c r="BL12" t="n">
         <v>2176.2</v>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>1990.3</t>
         </is>
       </c>
-      <c r="BM12" t="n">
+      <c r="BN12" t="n">
         <v>1194.16</v>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>147.6034056755215</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
         <is>
           <t>40.37080662824201</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BR12" t="inlineStr">
         <is>
           <t>1790.0</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BS12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
           <t>75.2</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>2025/12/04</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>-1.20</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>綠茵</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>綠茵</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>上櫃</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
         <is>
           <t>0.54</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>43.18290500198112</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>12.18914260633116</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>4.818590014463328</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
+      <c r="CE12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
         <is>
           <t>2.17</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
         <is>
           <t>4.86</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>7.61</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>13.85</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>48.81%</t>
         </is>
       </c>
-      <c r="CK12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
         <is>
           <t>17.38%</t>
         </is>
       </c>
-      <c r="CL12" t="inlineStr">
+      <c r="CM12" t="inlineStr">
         <is>
           <t>27.8</t>
         </is>
       </c>
-      <c r="CM12" t="inlineStr">
+      <c r="CN12" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="CN12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>保健食品配方65.97%、保健食品原料33.59%、其他0.43% (2024年)</t>
         </is>
       </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>綠茵-食品工業-上櫃</t>
         </is>
       </c>
-      <c r="CP12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>食品工業右下上櫃</t>
         </is>
       </c>
-      <c r="CQ12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>74.9</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
+      <c r="CS12" t="inlineStr">
         <is>
           <t>74.9</t>
         </is>
       </c>
-      <c r="CS12" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>74.0</t>
         </is>
       </c>
-      <c r="CT12" t="inlineStr">
+      <c r="CU12" t="inlineStr">
         <is>
           <t>74.3</t>
         </is>
       </c>
-      <c r="CU12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>34.3</t>
         </is>
       </c>
-      <c r="CV12" t="inlineStr">
+      <c r="CW12" t="inlineStr">
         <is>
           <t>** 食品 - 原物料、加工食品、營養食品** 食品生技 - 原料、加工製成品</t>
         </is>
       </c>
-      <c r="CW12" t="inlineStr">
+      <c r="CX12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX12" t="inlineStr">
+      <c r="CY12" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="CY12" t="inlineStr">
+      <c r="CZ12" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -6660,250 +6720,255 @@
           <t>31.52</t>
         </is>
       </c>
-      <c r="AZ13" t="n">
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>31.58</t>
+        </is>
+      </c>
+      <c r="BA13" t="n">
         <v>31.57</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="BB13" t="n">
         <v>31.68</v>
       </c>
-      <c r="BB13" t="inlineStr">
+      <c r="BC13" t="inlineStr">
         <is>
           <t>31.83</t>
         </is>
       </c>
-      <c r="BC13" t="inlineStr">
+      <c r="BD13" t="inlineStr">
         <is>
           <t>-13.38</t>
         </is>
       </c>
-      <c r="BD13" t="n">
+      <c r="BE13" t="n">
         <v>-0.05</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="BF13" t="n">
         <v>-0.04</v>
       </c>
-      <c r="BF13" t="inlineStr">
+      <c r="BG13" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr">
+      <c r="BH13" t="inlineStr">
         <is>
           <t>-113.64</t>
         </is>
       </c>
-      <c r="BH13" t="inlineStr">
+      <c r="BI13" t="inlineStr">
         <is>
           <t>2025/12/19</t>
         </is>
       </c>
-      <c r="BI13" t="inlineStr">
+      <c r="BJ13" t="inlineStr">
         <is>
           <t>11240202.0244898</t>
         </is>
       </c>
-      <c r="BJ13" t="inlineStr">
+      <c r="BK13" t="inlineStr">
         <is>
           <t>2557691.0</t>
         </is>
       </c>
-      <c r="BK13" t="n">
+      <c r="BL13" t="n">
         <v>2307315.4</v>
       </c>
-      <c r="BL13" t="inlineStr">
+      <c r="BM13" t="inlineStr">
         <is>
           <t>2798184.8</t>
         </is>
       </c>
-      <c r="BM13" t="n">
+      <c r="BN13" t="n">
         <v>3266759.3</v>
       </c>
-      <c r="BN13" t="inlineStr">
+      <c r="BO13" t="inlineStr">
         <is>
           <t>-490869</t>
         </is>
       </c>
-      <c r="BO13" t="inlineStr">
+      <c r="BP13" t="inlineStr">
         <is>
           <t>-67702.38129969216</t>
         </is>
       </c>
-      <c r="BP13" t="inlineStr">
+      <c r="BQ13" t="inlineStr">
         <is>
           <t>-142969.8837877344</t>
         </is>
       </c>
-      <c r="BQ13" t="inlineStr">
+      <c r="BR13" t="inlineStr">
         <is>
           <t>2557691.0</t>
         </is>
       </c>
-      <c r="BR13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BS13" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
           <t>32.7</t>
         </is>
       </c>
-      <c r="BT13" t="inlineStr">
+      <c r="BU13" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
       </c>
-      <c r="BU13" t="inlineStr">
+      <c r="BV13" t="inlineStr">
         <is>
           <t>-3.82</t>
         </is>
       </c>
-      <c r="BV13" t="inlineStr">
+      <c r="BW13" t="inlineStr">
         <is>
           <t>臺鹽</t>
         </is>
       </c>
-      <c r="BW13" t="inlineStr">
+      <c r="BX13" t="inlineStr">
         <is>
           <t>臺鹽</t>
         </is>
       </c>
-      <c r="BX13" t="inlineStr">
+      <c r="BY13" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY13" t="inlineStr">
+      <c r="BZ13" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BZ13" t="inlineStr">
+      <c r="CA13" t="inlineStr">
         <is>
           <t>0.28</t>
         </is>
       </c>
-      <c r="CA13" t="inlineStr">
+      <c r="CB13" t="inlineStr">
         <is>
           <t>11.30964198266164</t>
         </is>
       </c>
-      <c r="CB13" t="inlineStr">
+      <c r="CC13" t="inlineStr">
         <is>
           <t>7.950770160072485</t>
         </is>
       </c>
-      <c r="CC13" t="inlineStr">
+      <c r="CD13" t="inlineStr">
         <is>
           <t>2.099499961706554</t>
         </is>
       </c>
-      <c r="CD13" t="inlineStr">
+      <c r="CE13" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CE13" t="inlineStr">
+      <c r="CF13" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CF13" t="inlineStr">
+      <c r="CG13" t="inlineStr">
         <is>
           <t>0.95</t>
         </is>
       </c>
-      <c r="CG13" t="inlineStr">
+      <c r="CH13" t="inlineStr">
         <is>
           <t>4.13</t>
         </is>
       </c>
-      <c r="CH13" t="inlineStr">
+      <c r="CI13" t="inlineStr">
         <is>
           <t>4.07</t>
         </is>
       </c>
-      <c r="CI13" t="inlineStr">
+      <c r="CJ13" t="inlineStr">
         <is>
           <t>18.83</t>
         </is>
       </c>
-      <c r="CJ13" t="inlineStr">
+      <c r="CK13" t="inlineStr">
         <is>
           <t>39.76%</t>
         </is>
       </c>
-      <c r="CK13" t="inlineStr">
+      <c r="CL13" t="inlineStr">
         <is>
           <t>11.78%</t>
         </is>
       </c>
-      <c r="CL13" t="inlineStr">
+      <c r="CM13" t="inlineStr">
         <is>
           <t>25.48</t>
         </is>
       </c>
-      <c r="CM13" t="inlineStr">
+      <c r="CN13" t="inlineStr">
         <is>
           <t>6290</t>
         </is>
       </c>
-      <c r="CN13" t="inlineStr">
+      <c r="CO13" t="inlineStr">
         <is>
           <t>鹽46.50%、包裝飲用水34.02%、清潔用品5.33%、保健食品5.08%、美容保養品4.12%、工程及勞務2.55%、其他2.39% (2024年)</t>
         </is>
       </c>
-      <c r="CO13" t="inlineStr">
+      <c r="CP13" t="inlineStr">
         <is>
           <t>臺鹽-食品工業-上市</t>
         </is>
       </c>
-      <c r="CP13" t="inlineStr">
+      <c r="CQ13" t="inlineStr">
         <is>
           <t>食品工業右下上市</t>
         </is>
       </c>
-      <c r="CQ13" t="inlineStr">
+      <c r="CR13" t="inlineStr">
         <is>
           <t>31.5</t>
         </is>
       </c>
-      <c r="CR13" t="inlineStr">
+      <c r="CS13" t="inlineStr">
         <is>
           <t>31.6</t>
         </is>
       </c>
-      <c r="CS13" t="inlineStr">
+      <c r="CT13" t="inlineStr">
         <is>
           <t>31.45</t>
         </is>
       </c>
-      <c r="CT13" t="inlineStr">
+      <c r="CU13" t="inlineStr">
         <is>
           <t>31.45</t>
         </is>
       </c>
-      <c r="CU13" t="inlineStr">
+      <c r="CV13" t="inlineStr">
         <is>
           <t>33.23</t>
         </is>
       </c>
-      <c r="CV13" t="inlineStr">
+      <c r="CW13" t="inlineStr">
         <is>
           <t>** 食品 - 原物料、營養食品** 石化及塑橡膠 - 化妝品</t>
         </is>
       </c>
-      <c r="CW13" t="inlineStr">
+      <c r="CX13" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX13" t="inlineStr">
+      <c r="CY13" t="inlineStr">
         <is>
           <t>11.0</t>
         </is>
       </c>
-      <c r="CY13" t="inlineStr">
+      <c r="CZ13" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -7157,250 +7222,255 @@
           <t>31.53</t>
         </is>
       </c>
-      <c r="AZ14" t="n">
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>31.58</t>
+        </is>
+      </c>
+      <c r="BA14" t="n">
         <v>31.58</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BB14" t="n">
         <v>31.69</v>
       </c>
-      <c r="BB14" t="inlineStr">
+      <c r="BC14" t="inlineStr">
         <is>
           <t>31.84</t>
         </is>
       </c>
-      <c r="BC14" t="inlineStr">
+      <c r="BD14" t="inlineStr">
         <is>
           <t>0.56</t>
         </is>
-      </c>
-      <c r="BD14" t="n">
-        <v>-0.04</v>
       </c>
       <c r="BE14" t="n">
         <v>-0.04</v>
       </c>
-      <c r="BF14" t="inlineStr">
+      <c r="BF14" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="BG14" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr">
+      <c r="BH14" t="inlineStr">
         <is>
           <t>-113.18</t>
         </is>
       </c>
-      <c r="BH14" t="inlineStr">
+      <c r="BI14" t="inlineStr">
         <is>
           <t>2025/12/19</t>
         </is>
       </c>
-      <c r="BI14" t="inlineStr">
+      <c r="BJ14" t="inlineStr">
         <is>
           <t>11240202.0244898</t>
         </is>
       </c>
-      <c r="BJ14" t="inlineStr">
+      <c r="BK14" t="inlineStr">
         <is>
           <t>1949006.0</t>
         </is>
       </c>
-      <c r="BK14" t="n">
+      <c r="BL14" t="n">
         <v>2309460.8</v>
       </c>
-      <c r="BL14" t="inlineStr">
+      <c r="BM14" t="inlineStr">
         <is>
           <t>2807125.6</t>
         </is>
       </c>
-      <c r="BM14" t="n">
+      <c r="BN14" t="n">
         <v>3265178.2</v>
       </c>
-      <c r="BN14" t="inlineStr">
+      <c r="BO14" t="inlineStr">
         <is>
           <t>-497664</t>
         </is>
       </c>
-      <c r="BO14" t="inlineStr">
+      <c r="BP14" t="inlineStr">
         <is>
           <t>-54017.38084732084</t>
         </is>
       </c>
-      <c r="BP14" t="inlineStr">
+      <c r="BQ14" t="inlineStr">
         <is>
           <t>-157175.194652515</t>
         </is>
       </c>
-      <c r="BQ14" t="inlineStr">
+      <c r="BR14" t="inlineStr">
         <is>
           <t>1949006.0</t>
         </is>
       </c>
-      <c r="BR14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BS14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
           <t>32.7</t>
         </is>
       </c>
-      <c r="BT14" t="inlineStr">
+      <c r="BU14" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
       </c>
-      <c r="BU14" t="inlineStr">
+      <c r="BV14" t="inlineStr">
         <is>
           <t>-3.67</t>
         </is>
       </c>
-      <c r="BV14" t="inlineStr">
+      <c r="BW14" t="inlineStr">
         <is>
           <t>臺鹽</t>
         </is>
       </c>
-      <c r="BW14" t="inlineStr">
+      <c r="BX14" t="inlineStr">
         <is>
           <t>臺鹽</t>
         </is>
       </c>
-      <c r="BX14" t="inlineStr">
+      <c r="BY14" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY14" t="inlineStr">
+      <c r="BZ14" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BZ14" t="inlineStr">
+      <c r="CA14" t="inlineStr">
         <is>
           <t>0.28</t>
         </is>
       </c>
-      <c r="CA14" t="inlineStr">
+      <c r="CB14" t="inlineStr">
         <is>
           <t>11.30964198266164</t>
         </is>
       </c>
-      <c r="CB14" t="inlineStr">
+      <c r="CC14" t="inlineStr">
         <is>
           <t>7.950770160072485</t>
         </is>
       </c>
-      <c r="CC14" t="inlineStr">
+      <c r="CD14" t="inlineStr">
         <is>
           <t>2.099499961706554</t>
         </is>
       </c>
-      <c r="CD14" t="inlineStr">
+      <c r="CE14" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CE14" t="inlineStr">
+      <c r="CF14" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CF14" t="inlineStr">
+      <c r="CG14" t="inlineStr">
         <is>
           <t>0.95</t>
         </is>
       </c>
-      <c r="CG14" t="inlineStr">
+      <c r="CH14" t="inlineStr">
         <is>
           <t>4.13</t>
         </is>
       </c>
-      <c r="CH14" t="inlineStr">
+      <c r="CI14" t="inlineStr">
         <is>
           <t>4.07</t>
         </is>
       </c>
-      <c r="CI14" t="inlineStr">
+      <c r="CJ14" t="inlineStr">
         <is>
           <t>18.83</t>
         </is>
       </c>
-      <c r="CJ14" t="inlineStr">
+      <c r="CK14" t="inlineStr">
         <is>
           <t>39.76%</t>
         </is>
       </c>
-      <c r="CK14" t="inlineStr">
+      <c r="CL14" t="inlineStr">
         <is>
           <t>11.78%</t>
         </is>
       </c>
-      <c r="CL14" t="inlineStr">
+      <c r="CM14" t="inlineStr">
         <is>
           <t>25.48</t>
         </is>
       </c>
-      <c r="CM14" t="inlineStr">
+      <c r="CN14" t="inlineStr">
         <is>
           <t>6290</t>
         </is>
       </c>
-      <c r="CN14" t="inlineStr">
+      <c r="CO14" t="inlineStr">
         <is>
           <t>鹽46.50%、包裝飲用水34.02%、清潔用品5.33%、保健食品5.08%、美容保養品4.12%、工程及勞務2.55%、其他2.39% (2024年)</t>
         </is>
       </c>
-      <c r="CO14" t="inlineStr">
+      <c r="CP14" t="inlineStr">
         <is>
           <t>臺鹽-食品工業-上市</t>
         </is>
       </c>
-      <c r="CP14" t="inlineStr">
+      <c r="CQ14" t="inlineStr">
         <is>
           <t>食品工業右下上市</t>
         </is>
       </c>
-      <c r="CQ14" t="inlineStr">
+      <c r="CR14" t="inlineStr">
         <is>
           <t>31.6</t>
         </is>
       </c>
-      <c r="CR14" t="inlineStr">
+      <c r="CS14" t="inlineStr">
         <is>
           <t>31.6</t>
         </is>
       </c>
-      <c r="CS14" t="inlineStr">
+      <c r="CT14" t="inlineStr">
         <is>
           <t>31.5</t>
         </is>
       </c>
-      <c r="CT14" t="inlineStr">
+      <c r="CU14" t="inlineStr">
         <is>
           <t>31.5</t>
         </is>
       </c>
-      <c r="CU14" t="inlineStr">
+      <c r="CV14" t="inlineStr">
         <is>
           <t>33.23</t>
         </is>
       </c>
-      <c r="CV14" t="inlineStr">
+      <c r="CW14" t="inlineStr">
         <is>
           <t>** 食品 - 原物料、營養食品** 石化及塑橡膠 - 化妝品</t>
         </is>
       </c>
-      <c r="CW14" t="inlineStr">
+      <c r="CX14" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX14" t="inlineStr">
+      <c r="CY14" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="CY14" t="inlineStr">
+      <c r="CZ14" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -7654,250 +7724,255 @@
           <t>31.57</t>
         </is>
       </c>
-      <c r="AZ15" t="n">
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>31.595</t>
+        </is>
+      </c>
+      <c r="BA15" t="n">
         <v>31.58</v>
       </c>
-      <c r="BA15" t="n">
+      <c r="BB15" t="n">
         <v>31.7</v>
       </c>
-      <c r="BB15" t="inlineStr">
+      <c r="BC15" t="inlineStr">
         <is>
           <t>31.85</t>
         </is>
       </c>
-      <c r="BC15" t="inlineStr">
+      <c r="BD15" t="inlineStr">
         <is>
           <t>12.12</t>
         </is>
       </c>
-      <c r="BD15" t="n">
+      <c r="BE15" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BE15" t="n">
+      <c r="BF15" t="n">
         <v>-0.04</v>
       </c>
-      <c r="BF15" t="inlineStr">
+      <c r="BG15" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr">
+      <c r="BH15" t="inlineStr">
         <is>
           <t>-113.20</t>
         </is>
       </c>
-      <c r="BH15" t="inlineStr">
+      <c r="BI15" t="inlineStr">
         <is>
           <t>2025/12/19</t>
         </is>
       </c>
-      <c r="BI15" t="inlineStr">
+      <c r="BJ15" t="inlineStr">
         <is>
           <t>11240202.0244898</t>
         </is>
       </c>
-      <c r="BJ15" t="inlineStr">
+      <c r="BK15" t="inlineStr">
         <is>
           <t>2157177.0</t>
         </is>
       </c>
-      <c r="BK15" t="n">
+      <c r="BL15" t="n">
         <v>2705911.6</v>
       </c>
-      <c r="BL15" t="inlineStr">
+      <c r="BM15" t="inlineStr">
         <is>
           <t>3242660.5</t>
         </is>
       </c>
-      <c r="BM15" t="n">
+      <c r="BN15" t="n">
         <v>3299515.58</v>
       </c>
-      <c r="BN15" t="inlineStr">
+      <c r="BO15" t="inlineStr">
         <is>
           <t>-536748</t>
         </is>
       </c>
-      <c r="BO15" t="inlineStr">
+      <c r="BP15" t="inlineStr">
         <is>
           <t>-35261.4147009219</t>
         </is>
       </c>
-      <c r="BP15" t="inlineStr">
+      <c r="BQ15" t="inlineStr">
         <is>
           <t>-106638.8460788978</t>
         </is>
       </c>
-      <c r="BQ15" t="inlineStr">
+      <c r="BR15" t="inlineStr">
         <is>
           <t>2157177.0</t>
         </is>
       </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BS15" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
           <t>32.7</t>
         </is>
       </c>
-      <c r="BT15" t="inlineStr">
+      <c r="BU15" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
       </c>
-      <c r="BU15" t="inlineStr">
+      <c r="BV15" t="inlineStr">
         <is>
           <t>-3.36</t>
         </is>
       </c>
-      <c r="BV15" t="inlineStr">
+      <c r="BW15" t="inlineStr">
         <is>
           <t>臺鹽</t>
         </is>
       </c>
-      <c r="BW15" t="inlineStr">
+      <c r="BX15" t="inlineStr">
         <is>
           <t>臺鹽</t>
         </is>
       </c>
-      <c r="BX15" t="inlineStr">
+      <c r="BY15" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY15" t="inlineStr">
+      <c r="BZ15" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BZ15" t="inlineStr">
+      <c r="CA15" t="inlineStr">
         <is>
           <t>0.28</t>
         </is>
       </c>
-      <c r="CA15" t="inlineStr">
+      <c r="CB15" t="inlineStr">
         <is>
           <t>11.30964198266164</t>
         </is>
       </c>
-      <c r="CB15" t="inlineStr">
+      <c r="CC15" t="inlineStr">
         <is>
           <t>7.950770160072485</t>
         </is>
       </c>
-      <c r="CC15" t="inlineStr">
+      <c r="CD15" t="inlineStr">
         <is>
           <t>2.099499961706554</t>
         </is>
       </c>
-      <c r="CD15" t="inlineStr">
+      <c r="CE15" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CE15" t="inlineStr">
+      <c r="CF15" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CF15" t="inlineStr">
+      <c r="CG15" t="inlineStr">
         <is>
           <t>0.95</t>
         </is>
       </c>
-      <c r="CG15" t="inlineStr">
+      <c r="CH15" t="inlineStr">
         <is>
           <t>4.13</t>
         </is>
       </c>
-      <c r="CH15" t="inlineStr">
+      <c r="CI15" t="inlineStr">
         <is>
           <t>4.07</t>
         </is>
       </c>
-      <c r="CI15" t="inlineStr">
+      <c r="CJ15" t="inlineStr">
         <is>
           <t>18.83</t>
         </is>
       </c>
-      <c r="CJ15" t="inlineStr">
+      <c r="CK15" t="inlineStr">
         <is>
           <t>39.76%</t>
         </is>
       </c>
-      <c r="CK15" t="inlineStr">
+      <c r="CL15" t="inlineStr">
         <is>
           <t>11.78%</t>
         </is>
       </c>
-      <c r="CL15" t="inlineStr">
+      <c r="CM15" t="inlineStr">
         <is>
           <t>25.48</t>
         </is>
       </c>
-      <c r="CM15" t="inlineStr">
+      <c r="CN15" t="inlineStr">
         <is>
           <t>6290</t>
         </is>
       </c>
-      <c r="CN15" t="inlineStr">
+      <c r="CO15" t="inlineStr">
         <is>
           <t>鹽46.50%、包裝飲用水34.02%、清潔用品5.33%、保健食品5.08%、美容保養品4.12%、工程及勞務2.55%、其他2.39% (2024年)</t>
         </is>
       </c>
-      <c r="CO15" t="inlineStr">
+      <c r="CP15" t="inlineStr">
         <is>
           <t>臺鹽-食品工業-上市</t>
         </is>
       </c>
-      <c r="CP15" t="inlineStr">
+      <c r="CQ15" t="inlineStr">
         <is>
           <t>食品工業右下上市</t>
         </is>
       </c>
-      <c r="CQ15" t="inlineStr">
+      <c r="CR15" t="inlineStr">
         <is>
           <t>31.55</t>
         </is>
       </c>
-      <c r="CR15" t="inlineStr">
+      <c r="CS15" t="inlineStr">
         <is>
           <t>31.6</t>
         </is>
       </c>
-      <c r="CS15" t="inlineStr">
+      <c r="CT15" t="inlineStr">
         <is>
           <t>31.55</t>
         </is>
       </c>
-      <c r="CT15" t="inlineStr">
+      <c r="CU15" t="inlineStr">
         <is>
           <t>31.6</t>
         </is>
       </c>
-      <c r="CU15" t="inlineStr">
+      <c r="CV15" t="inlineStr">
         <is>
           <t>33.23</t>
         </is>
       </c>
-      <c r="CV15" t="inlineStr">
+      <c r="CW15" t="inlineStr">
         <is>
           <t>** 食品 - 原物料、營養食品** 石化及塑橡膠 - 化妝品</t>
         </is>
       </c>
-      <c r="CW15" t="inlineStr">
+      <c r="CX15" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX15" t="inlineStr">
+      <c r="CY15" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="CY15" t="inlineStr">
+      <c r="CZ15" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -8151,250 +8226,255 @@
           <t>31.57</t>
         </is>
       </c>
-      <c r="AZ16" t="n">
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>31.615</t>
+        </is>
+      </c>
+      <c r="BA16" t="n">
         <v>31.58</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BB16" t="n">
         <v>31.7</v>
       </c>
-      <c r="BB16" t="inlineStr">
+      <c r="BC16" t="inlineStr">
         <is>
           <t>31.86</t>
         </is>
       </c>
-      <c r="BC16" t="inlineStr">
+      <c r="BD16" t="inlineStr">
         <is>
           <t>5.27</t>
         </is>
-      </c>
-      <c r="BD16" t="n">
-        <v>-0.04</v>
       </c>
       <c r="BE16" t="n">
         <v>-0.04</v>
       </c>
-      <c r="BF16" t="inlineStr">
+      <c r="BF16" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="BG16" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr">
+      <c r="BH16" t="inlineStr">
         <is>
           <t>-113.60</t>
         </is>
       </c>
-      <c r="BH16" t="inlineStr">
+      <c r="BI16" t="inlineStr">
         <is>
           <t>2025/12/19</t>
         </is>
       </c>
-      <c r="BI16" t="inlineStr">
+      <c r="BJ16" t="inlineStr">
         <is>
           <t>11240202.0244898</t>
         </is>
       </c>
-      <c r="BJ16" t="inlineStr">
+      <c r="BK16" t="inlineStr">
         <is>
           <t>3212612.0</t>
         </is>
       </c>
-      <c r="BK16" t="n">
+      <c r="BL16" t="n">
         <v>2760471</v>
       </c>
-      <c r="BL16" t="inlineStr">
+      <c r="BM16" t="inlineStr">
         <is>
           <t>3234603.8</t>
         </is>
       </c>
-      <c r="BM16" t="n">
+      <c r="BN16" t="n">
         <v>3330946.94</v>
       </c>
-      <c r="BN16" t="inlineStr">
+      <c r="BO16" t="inlineStr">
         <is>
           <t>-474132</t>
         </is>
       </c>
-      <c r="BO16" t="inlineStr">
+      <c r="BP16" t="inlineStr">
         <is>
           <t>-22283.69990492628</t>
         </is>
       </c>
-      <c r="BP16" t="inlineStr">
+      <c r="BQ16" t="inlineStr">
         <is>
           <t>-52939.56789948372</t>
         </is>
       </c>
-      <c r="BQ16" t="inlineStr">
+      <c r="BR16" t="inlineStr">
         <is>
           <t>3212612.0</t>
         </is>
       </c>
-      <c r="BR16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BS16" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT16" t="inlineStr">
+        <is>
           <t>32.7</t>
         </is>
       </c>
-      <c r="BT16" t="inlineStr">
+      <c r="BU16" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
       </c>
-      <c r="BU16" t="inlineStr">
+      <c r="BV16" t="inlineStr">
         <is>
           <t>-3.52</t>
         </is>
       </c>
-      <c r="BV16" t="inlineStr">
+      <c r="BW16" t="inlineStr">
         <is>
           <t>臺鹽</t>
         </is>
       </c>
-      <c r="BW16" t="inlineStr">
+      <c r="BX16" t="inlineStr">
         <is>
           <t>臺鹽</t>
         </is>
       </c>
-      <c r="BX16" t="inlineStr">
+      <c r="BY16" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY16" t="inlineStr">
+      <c r="BZ16" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BZ16" t="inlineStr">
+      <c r="CA16" t="inlineStr">
         <is>
           <t>0.28</t>
         </is>
       </c>
-      <c r="CA16" t="inlineStr">
+      <c r="CB16" t="inlineStr">
         <is>
           <t>11.30964198266164</t>
         </is>
       </c>
-      <c r="CB16" t="inlineStr">
+      <c r="CC16" t="inlineStr">
         <is>
           <t>7.950770160072485</t>
         </is>
       </c>
-      <c r="CC16" t="inlineStr">
+      <c r="CD16" t="inlineStr">
         <is>
           <t>2.099499961706554</t>
         </is>
       </c>
-      <c r="CD16" t="inlineStr">
+      <c r="CE16" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CE16" t="inlineStr">
+      <c r="CF16" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CF16" t="inlineStr">
+      <c r="CG16" t="inlineStr">
         <is>
           <t>0.95</t>
         </is>
       </c>
-      <c r="CG16" t="inlineStr">
+      <c r="CH16" t="inlineStr">
         <is>
           <t>4.13</t>
         </is>
       </c>
-      <c r="CH16" t="inlineStr">
+      <c r="CI16" t="inlineStr">
         <is>
           <t>4.07</t>
         </is>
       </c>
-      <c r="CI16" t="inlineStr">
+      <c r="CJ16" t="inlineStr">
         <is>
           <t>18.83</t>
         </is>
       </c>
-      <c r="CJ16" t="inlineStr">
+      <c r="CK16" t="inlineStr">
         <is>
           <t>39.76%</t>
         </is>
       </c>
-      <c r="CK16" t="inlineStr">
+      <c r="CL16" t="inlineStr">
         <is>
           <t>11.78%</t>
         </is>
       </c>
-      <c r="CL16" t="inlineStr">
+      <c r="CM16" t="inlineStr">
         <is>
           <t>25.48</t>
         </is>
       </c>
-      <c r="CM16" t="inlineStr">
+      <c r="CN16" t="inlineStr">
         <is>
           <t>6290</t>
         </is>
       </c>
-      <c r="CN16" t="inlineStr">
+      <c r="CO16" t="inlineStr">
         <is>
           <t>鹽46.50%、包裝飲用水34.02%、清潔用品5.33%、保健食品5.08%、美容保養品4.12%、工程及勞務2.55%、其他2.39% (2024年)</t>
         </is>
       </c>
-      <c r="CO16" t="inlineStr">
+      <c r="CP16" t="inlineStr">
         <is>
           <t>臺鹽-食品工業-上市</t>
         </is>
       </c>
-      <c r="CP16" t="inlineStr">
+      <c r="CQ16" t="inlineStr">
         <is>
           <t>食品工業右下上市</t>
         </is>
       </c>
-      <c r="CQ16" t="inlineStr">
+      <c r="CR16" t="inlineStr">
         <is>
           <t>31.6</t>
         </is>
       </c>
-      <c r="CR16" t="inlineStr">
+      <c r="CS16" t="inlineStr">
         <is>
           <t>31.65</t>
         </is>
       </c>
-      <c r="CS16" t="inlineStr">
+      <c r="CT16" t="inlineStr">
         <is>
           <t>31.5</t>
         </is>
       </c>
-      <c r="CT16" t="inlineStr">
+      <c r="CU16" t="inlineStr">
         <is>
           <t>31.55</t>
         </is>
       </c>
-      <c r="CU16" t="inlineStr">
+      <c r="CV16" t="inlineStr">
         <is>
           <t>33.23</t>
         </is>
       </c>
-      <c r="CV16" t="inlineStr">
+      <c r="CW16" t="inlineStr">
         <is>
           <t>** 食品 - 原物料、營養食品** 石化及塑橡膠 - 化妝品</t>
         </is>
       </c>
-      <c r="CW16" t="inlineStr">
+      <c r="CX16" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX16" t="inlineStr">
+      <c r="CY16" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="CY16" t="inlineStr">
+      <c r="CZ16" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -8648,250 +8728,255 @@
           <t>31.6</t>
         </is>
       </c>
-      <c r="AZ17" t="n">
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>31.63</t>
+        </is>
+      </c>
+      <c r="BA17" t="n">
         <v>31.59</v>
       </c>
-      <c r="BA17" t="n">
+      <c r="BB17" t="n">
         <v>31.71</v>
       </c>
-      <c r="BB17" t="inlineStr">
+      <c r="BC17" t="inlineStr">
         <is>
           <t>31.87</t>
         </is>
       </c>
-      <c r="BC17" t="inlineStr">
+      <c r="BD17" t="inlineStr">
         <is>
           <t>8.23</t>
         </is>
-      </c>
-      <c r="BD17" t="n">
-        <v>-0.04</v>
       </c>
       <c r="BE17" t="n">
         <v>-0.04</v>
       </c>
-      <c r="BF17" t="inlineStr">
+      <c r="BF17" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="BG17" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr">
+      <c r="BH17" t="inlineStr">
         <is>
           <t>-113.78</t>
         </is>
       </c>
-      <c r="BH17" t="inlineStr">
+      <c r="BI17" t="inlineStr">
         <is>
           <t>2025/12/19</t>
         </is>
       </c>
-      <c r="BI17" t="inlineStr">
+      <c r="BJ17" t="inlineStr">
         <is>
           <t>11240202.0244898</t>
         </is>
       </c>
-      <c r="BJ17" t="inlineStr">
+      <c r="BK17" t="inlineStr">
         <is>
           <t>1660091.0</t>
         </is>
       </c>
-      <c r="BK17" t="n">
+      <c r="BL17" t="n">
         <v>3220987.4</v>
       </c>
-      <c r="BL17" t="inlineStr">
+      <c r="BM17" t="inlineStr">
         <is>
           <t>3083421.0</t>
         </is>
       </c>
-      <c r="BM17" t="n">
+      <c r="BN17" t="n">
         <v>3297756.66</v>
       </c>
-      <c r="BN17" t="inlineStr">
+      <c r="BO17" t="inlineStr">
         <is>
           <t>137566</t>
         </is>
       </c>
-      <c r="BO17" t="inlineStr">
+      <c r="BP17" t="inlineStr">
         <is>
           <t>-16709.90572409765</t>
         </is>
       </c>
-      <c r="BP17" t="inlineStr">
+      <c r="BQ17" t="inlineStr">
         <is>
           <t>-87417.93593248213</t>
         </is>
       </c>
-      <c r="BQ17" t="inlineStr">
+      <c r="BR17" t="inlineStr">
         <is>
           <t>1660091.0</t>
         </is>
       </c>
-      <c r="BR17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BS17" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT17" t="inlineStr">
+        <is>
           <t>32.7</t>
         </is>
       </c>
-      <c r="BT17" t="inlineStr">
+      <c r="BU17" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
       </c>
-      <c r="BU17" t="inlineStr">
+      <c r="BV17" t="inlineStr">
         <is>
           <t>-3.67</t>
         </is>
       </c>
-      <c r="BV17" t="inlineStr">
+      <c r="BW17" t="inlineStr">
         <is>
           <t>臺鹽</t>
         </is>
       </c>
-      <c r="BW17" t="inlineStr">
+      <c r="BX17" t="inlineStr">
         <is>
           <t>臺鹽</t>
         </is>
       </c>
-      <c r="BX17" t="inlineStr">
+      <c r="BY17" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY17" t="inlineStr">
+      <c r="BZ17" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BZ17" t="inlineStr">
+      <c r="CA17" t="inlineStr">
         <is>
           <t>0.28</t>
         </is>
       </c>
-      <c r="CA17" t="inlineStr">
+      <c r="CB17" t="inlineStr">
         <is>
           <t>11.30964198266164</t>
         </is>
       </c>
-      <c r="CB17" t="inlineStr">
+      <c r="CC17" t="inlineStr">
         <is>
           <t>7.950770160072485</t>
         </is>
       </c>
-      <c r="CC17" t="inlineStr">
+      <c r="CD17" t="inlineStr">
         <is>
           <t>2.099499961706554</t>
         </is>
       </c>
-      <c r="CD17" t="inlineStr">
+      <c r="CE17" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CE17" t="inlineStr">
+      <c r="CF17" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CF17" t="inlineStr">
+      <c r="CG17" t="inlineStr">
         <is>
           <t>0.95</t>
         </is>
       </c>
-      <c r="CG17" t="inlineStr">
+      <c r="CH17" t="inlineStr">
         <is>
           <t>4.13</t>
         </is>
       </c>
-      <c r="CH17" t="inlineStr">
+      <c r="CI17" t="inlineStr">
         <is>
           <t>4.07</t>
         </is>
       </c>
-      <c r="CI17" t="inlineStr">
+      <c r="CJ17" t="inlineStr">
         <is>
           <t>18.83</t>
         </is>
       </c>
-      <c r="CJ17" t="inlineStr">
+      <c r="CK17" t="inlineStr">
         <is>
           <t>39.76%</t>
         </is>
       </c>
-      <c r="CK17" t="inlineStr">
+      <c r="CL17" t="inlineStr">
         <is>
           <t>11.78%</t>
         </is>
       </c>
-      <c r="CL17" t="inlineStr">
+      <c r="CM17" t="inlineStr">
         <is>
           <t>25.48</t>
         </is>
       </c>
-      <c r="CM17" t="inlineStr">
+      <c r="CN17" t="inlineStr">
         <is>
           <t>6290</t>
         </is>
       </c>
-      <c r="CN17" t="inlineStr">
+      <c r="CO17" t="inlineStr">
         <is>
           <t>鹽46.50%、包裝飲用水34.02%、清潔用品5.33%、保健食品5.08%、美容保養品4.12%、工程及勞務2.55%、其他2.39% (2024年)</t>
         </is>
       </c>
-      <c r="CO17" t="inlineStr">
+      <c r="CP17" t="inlineStr">
         <is>
           <t>臺鹽-食品工業-上市</t>
         </is>
       </c>
-      <c r="CP17" t="inlineStr">
+      <c r="CQ17" t="inlineStr">
         <is>
           <t>食品工業右下上市</t>
         </is>
       </c>
-      <c r="CQ17" t="inlineStr">
+      <c r="CR17" t="inlineStr">
         <is>
           <t>31.5</t>
         </is>
       </c>
-      <c r="CR17" t="inlineStr">
+      <c r="CS17" t="inlineStr">
         <is>
           <t>31.6</t>
         </is>
       </c>
-      <c r="CS17" t="inlineStr">
+      <c r="CT17" t="inlineStr">
         <is>
           <t>31.5</t>
         </is>
       </c>
-      <c r="CT17" t="inlineStr">
+      <c r="CU17" t="inlineStr">
         <is>
           <t>31.5</t>
         </is>
       </c>
-      <c r="CU17" t="inlineStr">
+      <c r="CV17" t="inlineStr">
         <is>
           <t>33.23</t>
         </is>
       </c>
-      <c r="CV17" t="inlineStr">
+      <c r="CW17" t="inlineStr">
         <is>
           <t>** 食品 - 原物料、營養食品** 石化及塑橡膠 - 化妝品</t>
         </is>
       </c>
-      <c r="CW17" t="inlineStr">
+      <c r="CX17" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX17" t="inlineStr">
+      <c r="CY17" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="CY17" t="inlineStr">
+      <c r="CZ17" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -9145,250 +9230,255 @@
           <t>31.64</t>
         </is>
       </c>
-      <c r="AZ18" t="n">
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>31.63</t>
+        </is>
+      </c>
+      <c r="BA18" t="n">
         <v>31.6</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BB18" t="n">
         <v>31.72</v>
       </c>
-      <c r="BB18" t="inlineStr">
+      <c r="BC18" t="inlineStr">
         <is>
           <t>31.88</t>
         </is>
       </c>
-      <c r="BC18" t="inlineStr">
+      <c r="BD18" t="inlineStr">
         <is>
           <t>25.55</t>
         </is>
       </c>
-      <c r="BD18" t="n">
+      <c r="BE18" t="n">
         <v>-0.03</v>
       </c>
-      <c r="BE18" t="n">
+      <c r="BF18" t="n">
         <v>-0.04</v>
       </c>
-      <c r="BF18" t="inlineStr">
+      <c r="BG18" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr">
+      <c r="BH18" t="inlineStr">
         <is>
           <t>-114.07</t>
         </is>
       </c>
-      <c r="BH18" t="inlineStr">
+      <c r="BI18" t="inlineStr">
         <is>
           <t>2025/12/19</t>
         </is>
       </c>
-      <c r="BI18" t="inlineStr">
+      <c r="BJ18" t="inlineStr">
         <is>
           <t>11240202.0244898</t>
         </is>
       </c>
-      <c r="BJ18" t="inlineStr">
+      <c r="BK18" t="inlineStr">
         <is>
           <t>2568418.0</t>
         </is>
       </c>
-      <c r="BK18" t="n">
+      <c r="BL18" t="n">
         <v>3289054.2</v>
       </c>
-      <c r="BL18" t="inlineStr">
+      <c r="BM18" t="inlineStr">
         <is>
           <t>3137217.9</t>
         </is>
       </c>
-      <c r="BM18" t="n">
+      <c r="BN18" t="n">
         <v>3324051.1</v>
       </c>
-      <c r="BN18" t="inlineStr">
+      <c r="BO18" t="inlineStr">
         <is>
           <t>151836</t>
         </is>
       </c>
-      <c r="BO18" t="inlineStr">
+      <c r="BP18" t="inlineStr">
         <is>
           <t>-3853.900231664111</t>
         </is>
       </c>
-      <c r="BP18" t="inlineStr">
+      <c r="BQ18" t="inlineStr">
         <is>
           <t>32790.85744653689</t>
         </is>
       </c>
-      <c r="BQ18" t="inlineStr">
+      <c r="BR18" t="inlineStr">
         <is>
           <t>2568418.0</t>
         </is>
       </c>
-      <c r="BR18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BS18" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT18" t="inlineStr">
+        <is>
           <t>32.7</t>
         </is>
       </c>
-      <c r="BT18" t="inlineStr">
+      <c r="BU18" t="inlineStr">
         <is>
           <t>2025/05/19</t>
         </is>
       </c>
-      <c r="BU18" t="inlineStr">
+      <c r="BV18" t="inlineStr">
         <is>
           <t>-3.67</t>
         </is>
       </c>
-      <c r="BV18" t="inlineStr">
+      <c r="BW18" t="inlineStr">
         <is>
           <t>臺鹽</t>
         </is>
       </c>
-      <c r="BW18" t="inlineStr">
+      <c r="BX18" t="inlineStr">
         <is>
           <t>臺鹽</t>
         </is>
       </c>
-      <c r="BX18" t="inlineStr">
+      <c r="BY18" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY18" t="inlineStr">
+      <c r="BZ18" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BZ18" t="inlineStr">
+      <c r="CA18" t="inlineStr">
         <is>
           <t>0.28</t>
         </is>
       </c>
-      <c r="CA18" t="inlineStr">
+      <c r="CB18" t="inlineStr">
         <is>
           <t>11.30964198266164</t>
         </is>
       </c>
-      <c r="CB18" t="inlineStr">
+      <c r="CC18" t="inlineStr">
         <is>
           <t>7.950770160072485</t>
         </is>
       </c>
-      <c r="CC18" t="inlineStr">
+      <c r="CD18" t="inlineStr">
         <is>
           <t>2.099499961706554</t>
         </is>
       </c>
-      <c r="CD18" t="inlineStr">
+      <c r="CE18" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CE18" t="inlineStr">
+      <c r="CF18" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CF18" t="inlineStr">
+      <c r="CG18" t="inlineStr">
         <is>
           <t>0.95</t>
         </is>
       </c>
-      <c r="CG18" t="inlineStr">
+      <c r="CH18" t="inlineStr">
         <is>
           <t>4.13</t>
         </is>
       </c>
-      <c r="CH18" t="inlineStr">
+      <c r="CI18" t="inlineStr">
         <is>
           <t>4.07</t>
         </is>
       </c>
-      <c r="CI18" t="inlineStr">
+      <c r="CJ18" t="inlineStr">
         <is>
           <t>18.83</t>
         </is>
       </c>
-      <c r="CJ18" t="inlineStr">
+      <c r="CK18" t="inlineStr">
         <is>
           <t>39.76%</t>
         </is>
       </c>
-      <c r="CK18" t="inlineStr">
+      <c r="CL18" t="inlineStr">
         <is>
           <t>11.78%</t>
         </is>
       </c>
-      <c r="CL18" t="inlineStr">
+      <c r="CM18" t="inlineStr">
         <is>
           <t>25.48</t>
         </is>
       </c>
-      <c r="CM18" t="inlineStr">
+      <c r="CN18" t="inlineStr">
         <is>
           <t>6290</t>
         </is>
       </c>
-      <c r="CN18" t="inlineStr">
+      <c r="CO18" t="inlineStr">
         <is>
           <t>鹽46.50%、包裝飲用水34.02%、清潔用品5.33%、保健食品5.08%、美容保養品4.12%、工程及勞務2.55%、其他2.39% (2024年)</t>
         </is>
       </c>
-      <c r="CO18" t="inlineStr">
+      <c r="CP18" t="inlineStr">
         <is>
           <t>臺鹽-食品工業-上市</t>
         </is>
       </c>
-      <c r="CP18" t="inlineStr">
+      <c r="CQ18" t="inlineStr">
         <is>
           <t>食品工業右下上市</t>
         </is>
       </c>
-      <c r="CQ18" t="inlineStr">
+      <c r="CR18" t="inlineStr">
         <is>
           <t>31.6</t>
         </is>
       </c>
-      <c r="CR18" t="inlineStr">
+      <c r="CS18" t="inlineStr">
         <is>
           <t>31.6</t>
         </is>
       </c>
-      <c r="CS18" t="inlineStr">
+      <c r="CT18" t="inlineStr">
         <is>
           <t>31.45</t>
         </is>
       </c>
-      <c r="CT18" t="inlineStr">
+      <c r="CU18" t="inlineStr">
         <is>
           <t>31.5</t>
         </is>
       </c>
-      <c r="CU18" t="inlineStr">
+      <c r="CV18" t="inlineStr">
         <is>
           <t>33.23</t>
         </is>
       </c>
-      <c r="CV18" t="inlineStr">
+      <c r="CW18" t="inlineStr">
         <is>
           <t>** 食品 - 原物料、營養食品** 石化及塑橡膠 - 化妝品</t>
         </is>
       </c>
-      <c r="CW18" t="inlineStr">
+      <c r="CX18" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX18" t="inlineStr">
+      <c r="CY18" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="CY18" t="inlineStr">
+      <c r="CZ18" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -9642,250 +9732,255 @@
           <t>28.83</t>
         </is>
       </c>
-      <c r="AZ19" t="n">
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>29.015</t>
+        </is>
+      </c>
+      <c r="BA19" t="n">
         <v>29.19</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BB19" t="n">
         <v>29.97</v>
       </c>
-      <c r="BB19" t="inlineStr">
+      <c r="BC19" t="inlineStr">
         <is>
           <t>30.43</t>
         </is>
       </c>
-      <c r="BC19" t="inlineStr">
+      <c r="BD19" t="inlineStr">
         <is>
           <t>1.69</t>
         </is>
-      </c>
-      <c r="BD19" t="n">
-        <v>-0.32</v>
       </c>
       <c r="BE19" t="n">
         <v>-0.32</v>
       </c>
-      <c r="BF19" t="inlineStr">
+      <c r="BF19" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="BG19" t="inlineStr">
         <is>
           <t>0.89</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr">
+      <c r="BH19" t="inlineStr">
         <is>
           <t>-136.42</t>
         </is>
       </c>
-      <c r="BH19" t="inlineStr">
+      <c r="BI19" t="inlineStr">
         <is>
           <t>2026/02/09</t>
         </is>
       </c>
-      <c r="BI19" t="inlineStr">
+      <c r="BJ19" t="inlineStr">
         <is>
           <t>35140491.56066536</t>
         </is>
       </c>
-      <c r="BJ19" t="inlineStr">
+      <c r="BK19" t="inlineStr">
         <is>
           <t>17061536.0</t>
         </is>
       </c>
-      <c r="BK19" t="n">
+      <c r="BL19" t="n">
         <v>17489813</v>
       </c>
-      <c r="BL19" t="inlineStr">
+      <c r="BM19" t="inlineStr">
         <is>
           <t>23350074.0</t>
         </is>
       </c>
-      <c r="BM19" t="n">
+      <c r="BN19" t="n">
         <v>18371956.94</v>
       </c>
-      <c r="BN19" t="inlineStr">
+      <c r="BO19" t="inlineStr">
         <is>
           <t>-5860261</t>
         </is>
       </c>
-      <c r="BO19" t="inlineStr">
+      <c r="BP19" t="inlineStr">
         <is>
           <t>202632.3781922093</t>
         </is>
       </c>
-      <c r="BP19" t="inlineStr">
+      <c r="BQ19" t="inlineStr">
         <is>
           <t>-1359880.045644127</t>
         </is>
       </c>
-      <c r="BQ19" t="inlineStr">
+      <c r="BR19" t="inlineStr">
         <is>
           <t>17061536.0</t>
         </is>
       </c>
-      <c r="BR19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BS19" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT19" t="inlineStr">
+        <is>
           <t>33.95</t>
         </is>
       </c>
-      <c r="BT19" t="inlineStr">
+      <c r="BU19" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BU19" t="inlineStr">
+      <c r="BV19" t="inlineStr">
         <is>
           <t>-14.87</t>
         </is>
       </c>
-      <c r="BV19" t="inlineStr">
+      <c r="BW19" t="inlineStr">
         <is>
           <t>佳格</t>
         </is>
       </c>
-      <c r="BW19" t="inlineStr">
+      <c r="BX19" t="inlineStr">
         <is>
           <t>佳格</t>
         </is>
       </c>
-      <c r="BX19" t="inlineStr">
+      <c r="BY19" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY19" t="inlineStr">
+      <c r="BZ19" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BZ19" t="inlineStr">
+      <c r="CA19" t="inlineStr">
         <is>
           <t>0.41</t>
         </is>
       </c>
-      <c r="CA19" t="inlineStr">
+      <c r="CB19" t="inlineStr">
         <is>
           <t>6.237608785148733</t>
         </is>
       </c>
-      <c r="CB19" t="inlineStr">
+      <c r="CC19" t="inlineStr">
         <is>
           <t>-17.09267911306208</t>
         </is>
       </c>
-      <c r="CC19" t="inlineStr">
+      <c r="CD19" t="inlineStr">
         <is>
           <t>-3.78772922691385</t>
         </is>
       </c>
-      <c r="CD19" t="inlineStr">
+      <c r="CE19" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CE19" t="inlineStr">
+      <c r="CF19" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CF19" t="inlineStr">
+      <c r="CG19" t="inlineStr">
         <is>
           <t>1.47</t>
         </is>
       </c>
-      <c r="CG19" t="inlineStr">
+      <c r="CH19" t="inlineStr">
         <is>
           <t>4.84</t>
         </is>
       </c>
-      <c r="CH19" t="inlineStr">
+      <c r="CI19" t="inlineStr">
         <is>
           <t>8.02</t>
         </is>
       </c>
-      <c r="CI19" t="inlineStr">
+      <c r="CJ19" t="inlineStr">
         <is>
           <t>19.79</t>
         </is>
       </c>
-      <c r="CJ19" t="inlineStr">
+      <c r="CK19" t="inlineStr">
         <is>
           <t>23.06%</t>
         </is>
       </c>
-      <c r="CK19" t="inlineStr">
+      <c r="CL19" t="inlineStr">
         <is>
           <t>4.46%</t>
         </is>
       </c>
-      <c r="CL19" t="inlineStr">
+      <c r="CM19" t="inlineStr">
         <is>
           <t>25.48</t>
         </is>
       </c>
-      <c r="CM19" t="inlineStr">
+      <c r="CN19" t="inlineStr">
         <is>
           <t>26446</t>
         </is>
       </c>
-      <c r="CN19" t="inlineStr">
+      <c r="CO19" t="inlineStr">
         <is>
           <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
         </is>
       </c>
-      <c r="CO19" t="inlineStr">
+      <c r="CP19" t="inlineStr">
         <is>
           <t>佳格-食品工業-上市</t>
         </is>
       </c>
-      <c r="CP19" t="inlineStr">
+      <c r="CQ19" t="inlineStr">
         <is>
           <t>食品工業右下上市</t>
         </is>
       </c>
-      <c r="CQ19" t="inlineStr">
+      <c r="CR19" t="inlineStr">
         <is>
           <t>29.25</t>
         </is>
       </c>
-      <c r="CR19" t="inlineStr">
+      <c r="CS19" t="inlineStr">
         <is>
           <t>29.25</t>
         </is>
       </c>
-      <c r="CS19" t="inlineStr">
+      <c r="CT19" t="inlineStr">
         <is>
           <t>28.8</t>
         </is>
       </c>
-      <c r="CT19" t="inlineStr">
+      <c r="CU19" t="inlineStr">
         <is>
           <t>28.9</t>
         </is>
       </c>
-      <c r="CU19" t="inlineStr">
+      <c r="CV19" t="inlineStr">
         <is>
           <t>19.66</t>
         </is>
       </c>
-      <c r="CV19" t="inlineStr">
+      <c r="CW19" t="inlineStr">
         <is>
           <t>** 食品 - 營養食品</t>
         </is>
       </c>
-      <c r="CW19" t="inlineStr">
+      <c r="CX19" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX19" t="inlineStr">
+      <c r="CY19" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CY19" t="inlineStr">
+      <c r="CZ19" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -10139,250 +10234,255 @@
           <t>28.81</t>
         </is>
       </c>
-      <c r="AZ20" t="n">
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>29.05</t>
+        </is>
+      </c>
+      <c r="BA20" t="n">
         <v>29.23</v>
       </c>
-      <c r="BA20" t="n">
+      <c r="BB20" t="n">
         <v>30</v>
       </c>
-      <c r="BB20" t="inlineStr">
+      <c r="BC20" t="inlineStr">
         <is>
           <t>30.49</t>
         </is>
       </c>
-      <c r="BC20" t="inlineStr">
+      <c r="BD20" t="inlineStr">
         <is>
           <t>-1.77</t>
         </is>
       </c>
-      <c r="BD20" t="n">
+      <c r="BE20" t="n">
         <v>-0.33</v>
       </c>
-      <c r="BE20" t="n">
+      <c r="BF20" t="n">
         <v>-0.32</v>
       </c>
-      <c r="BF20" t="inlineStr">
+      <c r="BG20" t="inlineStr">
         <is>
           <t>0.89</t>
         </is>
       </c>
-      <c r="BG20" t="inlineStr">
+      <c r="BH20" t="inlineStr">
         <is>
           <t>-136.57</t>
         </is>
       </c>
-      <c r="BH20" t="inlineStr">
+      <c r="BI20" t="inlineStr">
         <is>
           <t>2026/02/09</t>
         </is>
       </c>
-      <c r="BI20" t="inlineStr">
+      <c r="BJ20" t="inlineStr">
         <is>
           <t>35140491.56066536</t>
         </is>
       </c>
-      <c r="BJ20" t="inlineStr">
+      <c r="BK20" t="inlineStr">
         <is>
           <t>12445805.0</t>
         </is>
       </c>
-      <c r="BK20" t="n">
+      <c r="BL20" t="n">
         <v>21370881.8</v>
       </c>
-      <c r="BL20" t="inlineStr">
+      <c r="BM20" t="inlineStr">
         <is>
           <t>23271365.8</t>
         </is>
       </c>
-      <c r="BM20" t="n">
+      <c r="BN20" t="n">
         <v>18213846.26</v>
       </c>
-      <c r="BN20" t="inlineStr">
+      <c r="BO20" t="inlineStr">
         <is>
           <t>-1900484</t>
         </is>
       </c>
-      <c r="BO20" t="inlineStr">
+      <c r="BP20" t="inlineStr">
         <is>
           <t>486725.5461624523</t>
         </is>
       </c>
-      <c r="BP20" t="inlineStr">
+      <c r="BQ20" t="inlineStr">
         <is>
           <t>-1189834.26154704</t>
         </is>
       </c>
-      <c r="BQ20" t="inlineStr">
+      <c r="BR20" t="inlineStr">
         <is>
           <t>12445805.0</t>
         </is>
       </c>
-      <c r="BR20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BS20" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT20" t="inlineStr">
+        <is>
           <t>33.95</t>
         </is>
       </c>
-      <c r="BT20" t="inlineStr">
+      <c r="BU20" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BU20" t="inlineStr">
+      <c r="BV20" t="inlineStr">
         <is>
           <t>-15.17</t>
         </is>
       </c>
-      <c r="BV20" t="inlineStr">
+      <c r="BW20" t="inlineStr">
         <is>
           <t>佳格</t>
         </is>
       </c>
-      <c r="BW20" t="inlineStr">
+      <c r="BX20" t="inlineStr">
         <is>
           <t>佳格</t>
         </is>
       </c>
-      <c r="BX20" t="inlineStr">
+      <c r="BY20" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY20" t="inlineStr">
+      <c r="BZ20" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BZ20" t="inlineStr">
+      <c r="CA20" t="inlineStr">
         <is>
           <t>0.41</t>
         </is>
       </c>
-      <c r="CA20" t="inlineStr">
+      <c r="CB20" t="inlineStr">
         <is>
           <t>6.237608785148733</t>
         </is>
       </c>
-      <c r="CB20" t="inlineStr">
+      <c r="CC20" t="inlineStr">
         <is>
           <t>-17.09267911306208</t>
         </is>
       </c>
-      <c r="CC20" t="inlineStr">
+      <c r="CD20" t="inlineStr">
         <is>
           <t>-3.78772922691385</t>
         </is>
       </c>
-      <c r="CD20" t="inlineStr">
+      <c r="CE20" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CE20" t="inlineStr">
+      <c r="CF20" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CF20" t="inlineStr">
+      <c r="CG20" t="inlineStr">
         <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="CG20" t="inlineStr">
+      <c r="CH20" t="inlineStr">
         <is>
           <t>4.84</t>
         </is>
       </c>
-      <c r="CH20" t="inlineStr">
+      <c r="CI20" t="inlineStr">
         <is>
           <t>8.02</t>
         </is>
       </c>
-      <c r="CI20" t="inlineStr">
+      <c r="CJ20" t="inlineStr">
         <is>
           <t>19.79</t>
         </is>
       </c>
-      <c r="CJ20" t="inlineStr">
+      <c r="CK20" t="inlineStr">
         <is>
           <t>23.06%</t>
         </is>
       </c>
-      <c r="CK20" t="inlineStr">
+      <c r="CL20" t="inlineStr">
         <is>
           <t>4.46%</t>
         </is>
       </c>
-      <c r="CL20" t="inlineStr">
+      <c r="CM20" t="inlineStr">
         <is>
           <t>25.48</t>
         </is>
       </c>
-      <c r="CM20" t="inlineStr">
+      <c r="CN20" t="inlineStr">
         <is>
           <t>26446</t>
         </is>
       </c>
-      <c r="CN20" t="inlineStr">
+      <c r="CO20" t="inlineStr">
         <is>
           <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
         </is>
       </c>
-      <c r="CO20" t="inlineStr">
+      <c r="CP20" t="inlineStr">
         <is>
           <t>佳格-食品工業-上市</t>
         </is>
       </c>
-      <c r="CP20" t="inlineStr">
+      <c r="CQ20" t="inlineStr">
         <is>
           <t>食品工業右下上市</t>
         </is>
       </c>
-      <c r="CQ20" t="inlineStr">
+      <c r="CR20" t="inlineStr">
         <is>
           <t>29.1</t>
         </is>
       </c>
-      <c r="CR20" t="inlineStr">
+      <c r="CS20" t="inlineStr">
         <is>
           <t>29.1</t>
         </is>
       </c>
-      <c r="CS20" t="inlineStr">
+      <c r="CT20" t="inlineStr">
         <is>
           <t>28.75</t>
         </is>
       </c>
-      <c r="CT20" t="inlineStr">
+      <c r="CU20" t="inlineStr">
         <is>
           <t>28.8</t>
         </is>
       </c>
-      <c r="CU20" t="inlineStr">
+      <c r="CV20" t="inlineStr">
         <is>
           <t>19.66</t>
         </is>
       </c>
-      <c r="CV20" t="inlineStr">
+      <c r="CW20" t="inlineStr">
         <is>
           <t>** 食品 - 營養食品</t>
         </is>
       </c>
-      <c r="CW20" t="inlineStr">
+      <c r="CX20" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX20" t="inlineStr">
+      <c r="CY20" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CY20" t="inlineStr">
+      <c r="CZ20" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -10636,250 +10736,255 @@
           <t>28.85</t>
         </is>
       </c>
-      <c r="AZ21" t="n">
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>29.085</t>
+        </is>
+      </c>
+      <c r="BA21" t="n">
         <v>29.27</v>
       </c>
-      <c r="BA21" t="n">
+      <c r="BB21" t="n">
         <v>30.04</v>
       </c>
-      <c r="BB21" t="inlineStr">
+      <c r="BC21" t="inlineStr">
         <is>
           <t>30.53</t>
         </is>
       </c>
-      <c r="BC21" t="inlineStr">
+      <c r="BD21" t="inlineStr">
         <is>
           <t>-2.56</t>
         </is>
       </c>
-      <c r="BD21" t="n">
+      <c r="BE21" t="n">
         <v>-0.33</v>
       </c>
-      <c r="BE21" t="n">
+      <c r="BF21" t="n">
         <v>-0.32</v>
       </c>
-      <c r="BF21" t="inlineStr">
+      <c r="BG21" t="inlineStr">
         <is>
           <t>0.89</t>
         </is>
       </c>
-      <c r="BG21" t="inlineStr">
+      <c r="BH21" t="inlineStr">
         <is>
           <t>-136.41</t>
         </is>
       </c>
-      <c r="BH21" t="inlineStr">
+      <c r="BI21" t="inlineStr">
         <is>
           <t>2026/02/09</t>
         </is>
       </c>
-      <c r="BI21" t="inlineStr">
+      <c r="BJ21" t="inlineStr">
         <is>
           <t>35140491.56066536</t>
         </is>
       </c>
-      <c r="BJ21" t="inlineStr">
+      <c r="BK21" t="inlineStr">
         <is>
           <t>18605772.0</t>
         </is>
       </c>
-      <c r="BK21" t="n">
+      <c r="BL21" t="n">
         <v>24278306.2</v>
       </c>
-      <c r="BL21" t="inlineStr">
+      <c r="BM21" t="inlineStr">
         <is>
           <t>23511265.0</t>
         </is>
       </c>
-      <c r="BM21" t="n">
+      <c r="BN21" t="n">
         <v>18149976.84</v>
       </c>
-      <c r="BN21" t="inlineStr">
+      <c r="BO21" t="inlineStr">
         <is>
           <t>767041</t>
         </is>
       </c>
-      <c r="BO21" t="inlineStr">
+      <c r="BP21" t="inlineStr">
         <is>
           <t>791554.6021096328</t>
         </is>
       </c>
-      <c r="BP21" t="inlineStr">
+      <c r="BQ21" t="inlineStr">
         <is>
           <t>-409875.0249245241</t>
         </is>
       </c>
-      <c r="BQ21" t="inlineStr">
+      <c r="BR21" t="inlineStr">
         <is>
           <t>18605772.0</t>
         </is>
       </c>
-      <c r="BR21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BS21" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT21" t="inlineStr">
+        <is>
           <t>33.95</t>
         </is>
       </c>
-      <c r="BT21" t="inlineStr">
+      <c r="BU21" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BU21" t="inlineStr">
+      <c r="BV21" t="inlineStr">
         <is>
           <t>-14.58</t>
         </is>
       </c>
-      <c r="BV21" t="inlineStr">
+      <c r="BW21" t="inlineStr">
         <is>
           <t>佳格</t>
         </is>
       </c>
-      <c r="BW21" t="inlineStr">
+      <c r="BX21" t="inlineStr">
         <is>
           <t>佳格</t>
         </is>
       </c>
-      <c r="BX21" t="inlineStr">
+      <c r="BY21" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY21" t="inlineStr">
+      <c r="BZ21" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BZ21" t="inlineStr">
+      <c r="CA21" t="inlineStr">
         <is>
           <t>0.41</t>
         </is>
       </c>
-      <c r="CA21" t="inlineStr">
+      <c r="CB21" t="inlineStr">
         <is>
           <t>6.237608785148733</t>
         </is>
       </c>
-      <c r="CB21" t="inlineStr">
+      <c r="CC21" t="inlineStr">
         <is>
           <t>-17.09267911306208</t>
         </is>
       </c>
-      <c r="CC21" t="inlineStr">
+      <c r="CD21" t="inlineStr">
         <is>
           <t>-3.78772922691385</t>
         </is>
       </c>
-      <c r="CD21" t="inlineStr">
+      <c r="CE21" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CE21" t="inlineStr">
+      <c r="CF21" t="inlineStr">
         <is>
           <t>價-量縮</t>
         </is>
       </c>
-      <c r="CF21" t="inlineStr">
+      <c r="CG21" t="inlineStr">
         <is>
           <t>1.48</t>
         </is>
       </c>
-      <c r="CG21" t="inlineStr">
+      <c r="CH21" t="inlineStr">
         <is>
           <t>4.84</t>
         </is>
       </c>
-      <c r="CH21" t="inlineStr">
+      <c r="CI21" t="inlineStr">
         <is>
           <t>8.02</t>
         </is>
       </c>
-      <c r="CI21" t="inlineStr">
+      <c r="CJ21" t="inlineStr">
         <is>
           <t>19.79</t>
         </is>
       </c>
-      <c r="CJ21" t="inlineStr">
+      <c r="CK21" t="inlineStr">
         <is>
           <t>23.06%</t>
         </is>
       </c>
-      <c r="CK21" t="inlineStr">
+      <c r="CL21" t="inlineStr">
         <is>
           <t>4.46%</t>
         </is>
       </c>
-      <c r="CL21" t="inlineStr">
+      <c r="CM21" t="inlineStr">
         <is>
           <t>25.48</t>
         </is>
       </c>
-      <c r="CM21" t="inlineStr">
+      <c r="CN21" t="inlineStr">
         <is>
           <t>26446</t>
         </is>
       </c>
-      <c r="CN21" t="inlineStr">
+      <c r="CO21" t="inlineStr">
         <is>
           <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
         </is>
       </c>
-      <c r="CO21" t="inlineStr">
+      <c r="CP21" t="inlineStr">
         <is>
           <t>佳格-食品工業-上市</t>
         </is>
       </c>
-      <c r="CP21" t="inlineStr">
+      <c r="CQ21" t="inlineStr">
         <is>
           <t>食品工業右下上市</t>
         </is>
       </c>
-      <c r="CQ21" t="inlineStr">
+      <c r="CR21" t="inlineStr">
         <is>
           <t>28.7</t>
         </is>
       </c>
-      <c r="CR21" t="inlineStr">
+      <c r="CS21" t="inlineStr">
         <is>
           <t>29.15</t>
         </is>
       </c>
-      <c r="CS21" t="inlineStr">
+      <c r="CT21" t="inlineStr">
         <is>
           <t>28.7</t>
         </is>
       </c>
-      <c r="CT21" t="inlineStr">
+      <c r="CU21" t="inlineStr">
         <is>
           <t>29.0</t>
         </is>
       </c>
-      <c r="CU21" t="inlineStr">
+      <c r="CV21" t="inlineStr">
         <is>
           <t>19.66</t>
         </is>
       </c>
-      <c r="CV21" t="inlineStr">
+      <c r="CW21" t="inlineStr">
         <is>
           <t>** 食品 - 營養食品</t>
         </is>
       </c>
-      <c r="CW21" t="inlineStr">
+      <c r="CX21" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX21" t="inlineStr">
+      <c r="CY21" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CY21" t="inlineStr">
+      <c r="CZ21" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -11133,250 +11238,255 @@
           <t>28.89</t>
         </is>
       </c>
-      <c r="AZ22" t="n">
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>29.1</t>
+        </is>
+      </c>
+      <c r="BA22" t="n">
         <v>29.3</v>
       </c>
-      <c r="BA22" t="n">
+      <c r="BB22" t="n">
         <v>30.07</v>
       </c>
-      <c r="BB22" t="inlineStr">
+      <c r="BC22" t="inlineStr">
         <is>
           <t>30.56</t>
         </is>
       </c>
-      <c r="BC22" t="inlineStr">
+      <c r="BD22" t="inlineStr">
         <is>
           <t>-8.49</t>
         </is>
       </c>
-      <c r="BD22" t="n">
+      <c r="BE22" t="n">
         <v>-0.35</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BF22" t="n">
         <v>-0.32</v>
       </c>
-      <c r="BF22" t="inlineStr">
+      <c r="BG22" t="inlineStr">
         <is>
           <t>0.89</t>
         </is>
       </c>
-      <c r="BG22" t="inlineStr">
+      <c r="BH22" t="inlineStr">
         <is>
           <t>-136.17</t>
         </is>
       </c>
-      <c r="BH22" t="inlineStr">
+      <c r="BI22" t="inlineStr">
         <is>
           <t>2026/02/09</t>
         </is>
       </c>
-      <c r="BI22" t="inlineStr">
+      <c r="BJ22" t="inlineStr">
         <is>
           <t>35140491.56066536</t>
         </is>
       </c>
-      <c r="BJ22" t="inlineStr">
+      <c r="BK22" t="inlineStr">
         <is>
           <t>19713512.0</t>
         </is>
       </c>
-      <c r="BK22" t="n">
+      <c r="BL22" t="n">
         <v>25269590.8</v>
       </c>
-      <c r="BL22" t="inlineStr">
+      <c r="BM22" t="inlineStr">
         <is>
           <t>23972703.1</t>
         </is>
       </c>
-      <c r="BM22" t="n">
+      <c r="BN22" t="n">
         <v>17993919.1</v>
       </c>
-      <c r="BN22" t="inlineStr">
+      <c r="BO22" t="inlineStr">
         <is>
           <t>1296887</t>
         </is>
       </c>
-      <c r="BO22" t="inlineStr">
+      <c r="BP22" t="inlineStr">
         <is>
           <t>1009996.35247948</t>
         </is>
       </c>
-      <c r="BP22" t="inlineStr">
+      <c r="BQ22" t="inlineStr">
         <is>
           <t>58994.38542637974</t>
         </is>
       </c>
-      <c r="BQ22" t="inlineStr">
+      <c r="BR22" t="inlineStr">
         <is>
           <t>19713512.0</t>
         </is>
       </c>
-      <c r="BR22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BS22" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT22" t="inlineStr">
+        <is>
           <t>33.95</t>
         </is>
       </c>
-      <c r="BT22" t="inlineStr">
+      <c r="BU22" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BU22" t="inlineStr">
+      <c r="BV22" t="inlineStr">
         <is>
           <t>-15.32</t>
         </is>
       </c>
-      <c r="BV22" t="inlineStr">
+      <c r="BW22" t="inlineStr">
         <is>
           <t>佳格</t>
         </is>
       </c>
-      <c r="BW22" t="inlineStr">
+      <c r="BX22" t="inlineStr">
         <is>
           <t>佳格</t>
         </is>
       </c>
-      <c r="BX22" t="inlineStr">
+      <c r="BY22" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY22" t="inlineStr">
+      <c r="BZ22" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BZ22" t="inlineStr">
+      <c r="CA22" t="inlineStr">
         <is>
           <t>0.41</t>
         </is>
       </c>
-      <c r="CA22" t="inlineStr">
+      <c r="CB22" t="inlineStr">
         <is>
           <t>6.237608785148733</t>
         </is>
       </c>
-      <c r="CB22" t="inlineStr">
+      <c r="CC22" t="inlineStr">
         <is>
           <t>-17.09267911306208</t>
         </is>
       </c>
-      <c r="CC22" t="inlineStr">
+      <c r="CD22" t="inlineStr">
         <is>
           <t>-3.78772922691385</t>
         </is>
       </c>
-      <c r="CD22" t="inlineStr">
+      <c r="CE22" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CE22" t="inlineStr">
+      <c r="CF22" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CF22" t="inlineStr">
+      <c r="CG22" t="inlineStr">
         <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="CG22" t="inlineStr">
+      <c r="CH22" t="inlineStr">
         <is>
           <t>4.84</t>
         </is>
       </c>
-      <c r="CH22" t="inlineStr">
+      <c r="CI22" t="inlineStr">
         <is>
           <t>8.02</t>
         </is>
       </c>
-      <c r="CI22" t="inlineStr">
+      <c r="CJ22" t="inlineStr">
         <is>
           <t>19.79</t>
         </is>
       </c>
-      <c r="CJ22" t="inlineStr">
+      <c r="CK22" t="inlineStr">
         <is>
           <t>23.06%</t>
         </is>
       </c>
-      <c r="CK22" t="inlineStr">
+      <c r="CL22" t="inlineStr">
         <is>
           <t>4.46%</t>
         </is>
       </c>
-      <c r="CL22" t="inlineStr">
+      <c r="CM22" t="inlineStr">
         <is>
           <t>25.48</t>
         </is>
       </c>
-      <c r="CM22" t="inlineStr">
+      <c r="CN22" t="inlineStr">
         <is>
           <t>26446</t>
         </is>
       </c>
-      <c r="CN22" t="inlineStr">
+      <c r="CO22" t="inlineStr">
         <is>
           <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
         </is>
       </c>
-      <c r="CO22" t="inlineStr">
+      <c r="CP22" t="inlineStr">
         <is>
           <t>佳格-食品工業-上市</t>
         </is>
       </c>
-      <c r="CP22" t="inlineStr">
+      <c r="CQ22" t="inlineStr">
         <is>
           <t>食品工業右下上市</t>
         </is>
       </c>
-      <c r="CQ22" t="inlineStr">
+      <c r="CR22" t="inlineStr">
         <is>
           <t>28.6</t>
         </is>
       </c>
-      <c r="CR22" t="inlineStr">
+      <c r="CS22" t="inlineStr">
         <is>
           <t>28.9</t>
         </is>
       </c>
-      <c r="CS22" t="inlineStr">
+      <c r="CT22" t="inlineStr">
         <is>
           <t>28.55</t>
         </is>
       </c>
-      <c r="CT22" t="inlineStr">
+      <c r="CU22" t="inlineStr">
         <is>
           <t>28.75</t>
         </is>
       </c>
-      <c r="CU22" t="inlineStr">
+      <c r="CV22" t="inlineStr">
         <is>
           <t>19.66</t>
         </is>
       </c>
-      <c r="CV22" t="inlineStr">
+      <c r="CW22" t="inlineStr">
         <is>
           <t>** 食品 - 營養食品</t>
         </is>
       </c>
-      <c r="CW22" t="inlineStr">
+      <c r="CX22" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX22" t="inlineStr">
+      <c r="CY22" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CY22" t="inlineStr">
+      <c r="CZ22" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -11630,250 +11740,255 @@
           <t>29.04</t>
         </is>
       </c>
-      <c r="AZ23" t="n">
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>29.14</t>
+        </is>
+      </c>
+      <c r="BA23" t="n">
         <v>29.36</v>
       </c>
-      <c r="BA23" t="n">
+      <c r="BB23" t="n">
         <v>30.11</v>
       </c>
-      <c r="BB23" t="inlineStr">
+      <c r="BC23" t="inlineStr">
         <is>
           <t>30.61</t>
         </is>
       </c>
-      <c r="BC23" t="inlineStr">
+      <c r="BD23" t="inlineStr">
         <is>
           <t>-8.01</t>
         </is>
       </c>
-      <c r="BD23" t="n">
+      <c r="BE23" t="n">
         <v>-0.34</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BF23" t="n">
         <v>-0.31</v>
       </c>
-      <c r="BF23" t="inlineStr">
+      <c r="BG23" t="inlineStr">
         <is>
           <t>0.89</t>
         </is>
       </c>
-      <c r="BG23" t="inlineStr">
+      <c r="BH23" t="inlineStr">
         <is>
           <t>-135.41</t>
         </is>
       </c>
-      <c r="BH23" t="inlineStr">
+      <c r="BI23" t="inlineStr">
         <is>
           <t>2026/02/09</t>
         </is>
       </c>
-      <c r="BI23" t="inlineStr">
+      <c r="BJ23" t="inlineStr">
         <is>
           <t>35140491.56066536</t>
         </is>
       </c>
-      <c r="BJ23" t="inlineStr">
+      <c r="BK23" t="inlineStr">
         <is>
           <t>19622440.0</t>
         </is>
       </c>
-      <c r="BK23" t="n">
+      <c r="BL23" t="n">
         <v>25744507.6</v>
       </c>
-      <c r="BL23" t="inlineStr">
+      <c r="BM23" t="inlineStr">
         <is>
           <t>25477935.4</t>
         </is>
       </c>
-      <c r="BM23" t="n">
+      <c r="BN23" t="n">
         <v>17954301.62</v>
       </c>
-      <c r="BN23" t="inlineStr">
+      <c r="BO23" t="inlineStr">
         <is>
           <t>266572</t>
         </is>
       </c>
-      <c r="BO23" t="inlineStr">
+      <c r="BP23" t="inlineStr">
         <is>
           <t>1182905.801034589</t>
         </is>
       </c>
-      <c r="BP23" t="inlineStr">
+      <c r="BQ23" t="inlineStr">
         <is>
           <t>608014.4578767233</t>
         </is>
       </c>
-      <c r="BQ23" t="inlineStr">
+      <c r="BR23" t="inlineStr">
         <is>
           <t>19622440.0</t>
         </is>
       </c>
-      <c r="BR23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BS23" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT23" t="inlineStr">
+        <is>
           <t>33.95</t>
         </is>
       </c>
-      <c r="BT23" t="inlineStr">
+      <c r="BU23" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BU23" t="inlineStr">
+      <c r="BV23" t="inlineStr">
         <is>
           <t>-15.46</t>
         </is>
       </c>
-      <c r="BV23" t="inlineStr">
+      <c r="BW23" t="inlineStr">
         <is>
           <t>佳格</t>
         </is>
       </c>
-      <c r="BW23" t="inlineStr">
+      <c r="BX23" t="inlineStr">
         <is>
           <t>佳格</t>
         </is>
       </c>
-      <c r="BX23" t="inlineStr">
+      <c r="BY23" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY23" t="inlineStr">
+      <c r="BZ23" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BZ23" t="inlineStr">
+      <c r="CA23" t="inlineStr">
         <is>
           <t>0.41</t>
         </is>
       </c>
-      <c r="CA23" t="inlineStr">
+      <c r="CB23" t="inlineStr">
         <is>
           <t>6.237608785148733</t>
         </is>
       </c>
-      <c r="CB23" t="inlineStr">
+      <c r="CC23" t="inlineStr">
         <is>
           <t>-17.09267911306208</t>
         </is>
       </c>
-      <c r="CC23" t="inlineStr">
+      <c r="CD23" t="inlineStr">
         <is>
           <t>-3.78772922691385</t>
         </is>
       </c>
-      <c r="CD23" t="inlineStr">
+      <c r="CE23" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="CE23" t="inlineStr">
+      <c r="CF23" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CF23" t="inlineStr">
+      <c r="CG23" t="inlineStr">
         <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="CG23" t="inlineStr">
+      <c r="CH23" t="inlineStr">
         <is>
           <t>4.84</t>
         </is>
       </c>
-      <c r="CH23" t="inlineStr">
+      <c r="CI23" t="inlineStr">
         <is>
           <t>8.02</t>
         </is>
       </c>
-      <c r="CI23" t="inlineStr">
+      <c r="CJ23" t="inlineStr">
         <is>
           <t>19.79</t>
         </is>
       </c>
-      <c r="CJ23" t="inlineStr">
+      <c r="CK23" t="inlineStr">
         <is>
           <t>23.06%</t>
         </is>
       </c>
-      <c r="CK23" t="inlineStr">
+      <c r="CL23" t="inlineStr">
         <is>
           <t>4.46%</t>
         </is>
       </c>
-      <c r="CL23" t="inlineStr">
+      <c r="CM23" t="inlineStr">
         <is>
           <t>25.48</t>
         </is>
       </c>
-      <c r="CM23" t="inlineStr">
+      <c r="CN23" t="inlineStr">
         <is>
           <t>26446</t>
         </is>
       </c>
-      <c r="CN23" t="inlineStr">
+      <c r="CO23" t="inlineStr">
         <is>
           <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
         </is>
       </c>
-      <c r="CO23" t="inlineStr">
+      <c r="CP23" t="inlineStr">
         <is>
           <t>佳格-食品工業-上市</t>
         </is>
       </c>
-      <c r="CP23" t="inlineStr">
+      <c r="CQ23" t="inlineStr">
         <is>
           <t>食品工業右下上市</t>
         </is>
       </c>
-      <c r="CQ23" t="inlineStr">
+      <c r="CR23" t="inlineStr">
         <is>
           <t>28.85</t>
         </is>
       </c>
-      <c r="CR23" t="inlineStr">
+      <c r="CS23" t="inlineStr">
         <is>
           <t>28.85</t>
         </is>
       </c>
-      <c r="CS23" t="inlineStr">
+      <c r="CT23" t="inlineStr">
         <is>
           <t>28.55</t>
         </is>
       </c>
-      <c r="CT23" t="inlineStr">
+      <c r="CU23" t="inlineStr">
         <is>
           <t>28.7</t>
         </is>
       </c>
-      <c r="CU23" t="inlineStr">
+      <c r="CV23" t="inlineStr">
         <is>
           <t>19.66</t>
         </is>
       </c>
-      <c r="CV23" t="inlineStr">
+      <c r="CW23" t="inlineStr">
         <is>
           <t>** 食品 - 營養食品</t>
         </is>
       </c>
-      <c r="CW23" t="inlineStr">
+      <c r="CX23" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX23" t="inlineStr">
+      <c r="CY23" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CY23" t="inlineStr">
+      <c r="CZ23" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -12127,250 +12242,255 @@
           <t>29.2</t>
         </is>
       </c>
-      <c r="AZ24" t="n">
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>29.2</t>
+        </is>
+      </c>
+      <c r="BA24" t="n">
         <v>29.42</v>
       </c>
-      <c r="BA24" t="n">
+      <c r="BB24" t="n">
         <v>30.15</v>
       </c>
-      <c r="BB24" t="inlineStr">
+      <c r="BC24" t="inlineStr">
         <is>
           <t>30.63</t>
         </is>
       </c>
-      <c r="BC24" t="inlineStr">
+      <c r="BD24" t="inlineStr">
         <is>
           <t>-3.27</t>
         </is>
       </c>
-      <c r="BD24" t="n">
+      <c r="BE24" t="n">
         <v>-0.32</v>
       </c>
-      <c r="BE24" t="n">
+      <c r="BF24" t="n">
         <v>-0.31</v>
       </c>
-      <c r="BF24" t="inlineStr">
+      <c r="BG24" t="inlineStr">
         <is>
           <t>0.89</t>
         </is>
       </c>
-      <c r="BG24" t="inlineStr">
+      <c r="BH24" t="inlineStr">
         <is>
           <t>-134.70</t>
         </is>
       </c>
-      <c r="BH24" t="inlineStr">
+      <c r="BI24" t="inlineStr">
         <is>
           <t>2026/02/09</t>
         </is>
       </c>
-      <c r="BI24" t="inlineStr">
+      <c r="BJ24" t="inlineStr">
         <is>
           <t>35140491.56066536</t>
         </is>
       </c>
-      <c r="BJ24" t="inlineStr">
+      <c r="BK24" t="inlineStr">
         <is>
           <t>36466880.0</t>
         </is>
       </c>
-      <c r="BK24" t="n">
+      <c r="BL24" t="n">
         <v>29210335</v>
       </c>
-      <c r="BL24" t="inlineStr">
+      <c r="BM24" t="inlineStr">
         <is>
           <t>27464981.4</t>
         </is>
       </c>
-      <c r="BM24" t="n">
+      <c r="BN24" t="n">
         <v>17798828.46</v>
       </c>
-      <c r="BN24" t="inlineStr">
+      <c r="BO24" t="inlineStr">
         <is>
           <t>1745353</t>
         </is>
       </c>
-      <c r="BO24" t="inlineStr">
+      <c r="BP24" t="inlineStr">
         <is>
           <t>1287431.499790564</t>
         </is>
       </c>
-      <c r="BP24" t="inlineStr">
+      <c r="BQ24" t="inlineStr">
         <is>
           <t>1380371.75931019</t>
         </is>
       </c>
-      <c r="BQ24" t="inlineStr">
+      <c r="BR24" t="inlineStr">
         <is>
           <t>36466880.0</t>
         </is>
       </c>
-      <c r="BR24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BS24" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT24" t="inlineStr">
+        <is>
           <t>33.95</t>
         </is>
       </c>
-      <c r="BT24" t="inlineStr">
+      <c r="BU24" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BU24" t="inlineStr">
+      <c r="BV24" t="inlineStr">
         <is>
           <t>-15.17</t>
         </is>
       </c>
-      <c r="BV24" t="inlineStr">
+      <c r="BW24" t="inlineStr">
         <is>
           <t>佳格</t>
         </is>
       </c>
-      <c r="BW24" t="inlineStr">
+      <c r="BX24" t="inlineStr">
         <is>
           <t>佳格</t>
         </is>
       </c>
-      <c r="BX24" t="inlineStr">
+      <c r="BY24" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY24" t="inlineStr">
+      <c r="BZ24" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BZ24" t="inlineStr">
+      <c r="CA24" t="inlineStr">
         <is>
           <t>0.41</t>
         </is>
       </c>
-      <c r="CA24" t="inlineStr">
+      <c r="CB24" t="inlineStr">
         <is>
           <t>6.237608785148733</t>
         </is>
       </c>
-      <c r="CB24" t="inlineStr">
+      <c r="CC24" t="inlineStr">
         <is>
           <t>-17.09267911306208</t>
         </is>
       </c>
-      <c r="CC24" t="inlineStr">
+      <c r="CD24" t="inlineStr">
         <is>
           <t>-3.78772922691385</t>
         </is>
       </c>
-      <c r="CD24" t="inlineStr">
+      <c r="CE24" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="CE24" t="inlineStr">
+      <c r="CF24" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CF24" t="inlineStr">
+      <c r="CG24" t="inlineStr">
         <is>
           <t>1.46</t>
         </is>
       </c>
-      <c r="CG24" t="inlineStr">
+      <c r="CH24" t="inlineStr">
         <is>
           <t>4.84</t>
         </is>
       </c>
-      <c r="CH24" t="inlineStr">
+      <c r="CI24" t="inlineStr">
         <is>
           <t>8.02</t>
         </is>
       </c>
-      <c r="CI24" t="inlineStr">
+      <c r="CJ24" t="inlineStr">
         <is>
           <t>19.79</t>
         </is>
       </c>
-      <c r="CJ24" t="inlineStr">
+      <c r="CK24" t="inlineStr">
         <is>
           <t>23.06%</t>
         </is>
       </c>
-      <c r="CK24" t="inlineStr">
+      <c r="CL24" t="inlineStr">
         <is>
           <t>4.46%</t>
         </is>
       </c>
-      <c r="CL24" t="inlineStr">
+      <c r="CM24" t="inlineStr">
         <is>
           <t>25.48</t>
         </is>
       </c>
-      <c r="CM24" t="inlineStr">
+      <c r="CN24" t="inlineStr">
         <is>
           <t>26446</t>
         </is>
       </c>
-      <c r="CN24" t="inlineStr">
+      <c r="CO24" t="inlineStr">
         <is>
           <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
         </is>
       </c>
-      <c r="CO24" t="inlineStr">
+      <c r="CP24" t="inlineStr">
         <is>
           <t>佳格-食品工業-上市</t>
         </is>
       </c>
-      <c r="CP24" t="inlineStr">
+      <c r="CQ24" t="inlineStr">
         <is>
           <t>食品工業右下上市</t>
         </is>
       </c>
-      <c r="CQ24" t="inlineStr">
+      <c r="CR24" t="inlineStr">
         <is>
           <t>29.1</t>
         </is>
       </c>
-      <c r="CR24" t="inlineStr">
+      <c r="CS24" t="inlineStr">
         <is>
           <t>29.1</t>
         </is>
       </c>
-      <c r="CS24" t="inlineStr">
+      <c r="CT24" t="inlineStr">
         <is>
           <t>28.5</t>
         </is>
       </c>
-      <c r="CT24" t="inlineStr">
+      <c r="CU24" t="inlineStr">
         <is>
           <t>28.8</t>
         </is>
       </c>
-      <c r="CU24" t="inlineStr">
+      <c r="CV24" t="inlineStr">
         <is>
           <t>19.66</t>
         </is>
       </c>
-      <c r="CV24" t="inlineStr">
+      <c r="CW24" t="inlineStr">
         <is>
           <t>** 食品 - 營養食品</t>
         </is>
       </c>
-      <c r="CW24" t="inlineStr">
+      <c r="CX24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX24" t="inlineStr">
+      <c r="CY24" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CY24" t="inlineStr">
+      <c r="CZ24" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -12624,250 +12744,255 @@
           <t>29.29</t>
         </is>
       </c>
-      <c r="AZ25" t="n">
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>29.265</t>
+        </is>
+      </c>
+      <c r="BA25" t="n">
         <v>29.48</v>
       </c>
-      <c r="BA25" t="n">
+      <c r="BB25" t="n">
         <v>30.18</v>
       </c>
-      <c r="BB25" t="inlineStr">
+      <c r="BC25" t="inlineStr">
         <is>
           <t>30.65</t>
         </is>
       </c>
-      <c r="BC25" t="inlineStr">
+      <c r="BD25" t="inlineStr">
         <is>
           <t>3.00</t>
         </is>
       </c>
-      <c r="BD25" t="n">
+      <c r="BE25" t="n">
         <v>-0.3</v>
       </c>
-      <c r="BE25" t="n">
+      <c r="BF25" t="n">
         <v>-0.31</v>
       </c>
-      <c r="BF25" t="inlineStr">
+      <c r="BG25" t="inlineStr">
         <is>
           <t>0.89</t>
         </is>
       </c>
-      <c r="BG25" t="inlineStr">
+      <c r="BH25" t="inlineStr">
         <is>
           <t>-134.41</t>
         </is>
       </c>
-      <c r="BH25" t="inlineStr">
+      <c r="BI25" t="inlineStr">
         <is>
           <t>2026/02/09</t>
         </is>
       </c>
-      <c r="BI25" t="inlineStr">
+      <c r="BJ25" t="inlineStr">
         <is>
           <t>35140491.56066536</t>
         </is>
       </c>
-      <c r="BJ25" t="inlineStr">
+      <c r="BK25" t="inlineStr">
         <is>
           <t>26982927.0</t>
         </is>
       </c>
-      <c r="BK25" t="n">
+      <c r="BL25" t="n">
         <v>25171849.8</v>
       </c>
-      <c r="BL25" t="inlineStr">
+      <c r="BM25" t="inlineStr">
         <is>
           <t>26932073.1</t>
         </is>
       </c>
-      <c r="BM25" t="n">
+      <c r="BN25" t="n">
         <v>17257437.18</v>
       </c>
-      <c r="BN25" t="inlineStr">
+      <c r="BO25" t="inlineStr">
         <is>
           <t>-1760223</t>
         </is>
       </c>
-      <c r="BO25" t="inlineStr">
+      <c r="BP25" t="inlineStr">
         <is>
           <t>1270533.270786996</t>
         </is>
       </c>
-      <c r="BP25" t="inlineStr">
+      <c r="BQ25" t="inlineStr">
         <is>
           <t>629678.9128112085</t>
         </is>
       </c>
-      <c r="BQ25" t="inlineStr">
+      <c r="BR25" t="inlineStr">
         <is>
           <t>26982927.0</t>
         </is>
       </c>
-      <c r="BR25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BS25" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT25" t="inlineStr">
+        <is>
           <t>33.95</t>
         </is>
       </c>
-      <c r="BT25" t="inlineStr">
+      <c r="BU25" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BU25" t="inlineStr">
+      <c r="BV25" t="inlineStr">
         <is>
           <t>-14.58</t>
         </is>
       </c>
-      <c r="BV25" t="inlineStr">
+      <c r="BW25" t="inlineStr">
         <is>
           <t>佳格</t>
         </is>
       </c>
-      <c r="BW25" t="inlineStr">
+      <c r="BX25" t="inlineStr">
         <is>
           <t>佳格</t>
         </is>
       </c>
-      <c r="BX25" t="inlineStr">
+      <c r="BY25" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY25" t="inlineStr">
+      <c r="BZ25" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BZ25" t="inlineStr">
+      <c r="CA25" t="inlineStr">
         <is>
           <t>0.41</t>
         </is>
       </c>
-      <c r="CA25" t="inlineStr">
+      <c r="CB25" t="inlineStr">
         <is>
           <t>6.237608785148733</t>
         </is>
       </c>
-      <c r="CB25" t="inlineStr">
+      <c r="CC25" t="inlineStr">
         <is>
           <t>-17.09267911306208</t>
         </is>
       </c>
-      <c r="CC25" t="inlineStr">
+      <c r="CD25" t="inlineStr">
         <is>
           <t>-3.78772922691385</t>
         </is>
       </c>
-      <c r="CD25" t="inlineStr">
+      <c r="CE25" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
-      <c r="CE25" t="inlineStr">
+      <c r="CF25" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CF25" t="inlineStr">
+      <c r="CG25" t="inlineStr">
         <is>
           <t>1.48</t>
         </is>
       </c>
-      <c r="CG25" t="inlineStr">
+      <c r="CH25" t="inlineStr">
         <is>
           <t>4.84</t>
         </is>
       </c>
-      <c r="CH25" t="inlineStr">
+      <c r="CI25" t="inlineStr">
         <is>
           <t>8.02</t>
         </is>
       </c>
-      <c r="CI25" t="inlineStr">
+      <c r="CJ25" t="inlineStr">
         <is>
           <t>19.79</t>
         </is>
       </c>
-      <c r="CJ25" t="inlineStr">
+      <c r="CK25" t="inlineStr">
         <is>
           <t>23.06%</t>
         </is>
       </c>
-      <c r="CK25" t="inlineStr">
+      <c r="CL25" t="inlineStr">
         <is>
           <t>4.46%</t>
         </is>
       </c>
-      <c r="CL25" t="inlineStr">
+      <c r="CM25" t="inlineStr">
         <is>
           <t>25.48</t>
         </is>
       </c>
-      <c r="CM25" t="inlineStr">
+      <c r="CN25" t="inlineStr">
         <is>
           <t>26446</t>
         </is>
       </c>
-      <c r="CN25" t="inlineStr">
+      <c r="CO25" t="inlineStr">
         <is>
           <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
         </is>
       </c>
-      <c r="CO25" t="inlineStr">
+      <c r="CP25" t="inlineStr">
         <is>
           <t>佳格-食品工業-上市</t>
         </is>
       </c>
-      <c r="CP25" t="inlineStr">
+      <c r="CQ25" t="inlineStr">
         <is>
           <t>食品工業右下上市</t>
         </is>
       </c>
-      <c r="CQ25" t="inlineStr">
+      <c r="CR25" t="inlineStr">
         <is>
           <t>29.2</t>
         </is>
       </c>
-      <c r="CR25" t="inlineStr">
+      <c r="CS25" t="inlineStr">
         <is>
           <t>29.2</t>
         </is>
       </c>
-      <c r="CS25" t="inlineStr">
+      <c r="CT25" t="inlineStr">
         <is>
           <t>29.0</t>
         </is>
       </c>
-      <c r="CT25" t="inlineStr">
+      <c r="CU25" t="inlineStr">
         <is>
           <t>29.0</t>
         </is>
       </c>
-      <c r="CU25" t="inlineStr">
+      <c r="CV25" t="inlineStr">
         <is>
           <t>19.66</t>
         </is>
       </c>
-      <c r="CV25" t="inlineStr">
+      <c r="CW25" t="inlineStr">
         <is>
           <t>** 食品 - 營養食品</t>
         </is>
       </c>
-      <c r="CW25" t="inlineStr">
+      <c r="CX25" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX25" t="inlineStr">
+      <c r="CY25" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CY25" t="inlineStr">
+      <c r="CZ25" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -13121,250 +13246,255 @@
           <t>29.32</t>
         </is>
       </c>
-      <c r="AZ26" t="n">
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>29.315</t>
+        </is>
+      </c>
+      <c r="BA26" t="n">
         <v>29.54</v>
       </c>
-      <c r="BA26" t="n">
+      <c r="BB26" t="n">
         <v>30.2</v>
       </c>
-      <c r="BB26" t="inlineStr">
+      <c r="BC26" t="inlineStr">
         <is>
           <t>30.66</t>
         </is>
       </c>
-      <c r="BC26" t="inlineStr">
+      <c r="BD26" t="inlineStr">
         <is>
           <t>7.54</t>
         </is>
       </c>
-      <c r="BD26" t="n">
+      <c r="BE26" t="n">
         <v>-0.28</v>
       </c>
-      <c r="BE26" t="n">
+      <c r="BF26" t="n">
         <v>-0.31</v>
       </c>
-      <c r="BF26" t="inlineStr">
+      <c r="BG26" t="inlineStr">
         <is>
           <t>0.89</t>
         </is>
       </c>
-      <c r="BG26" t="inlineStr">
+      <c r="BH26" t="inlineStr">
         <is>
           <t>-134.67</t>
         </is>
       </c>
-      <c r="BH26" t="inlineStr">
+      <c r="BI26" t="inlineStr">
         <is>
           <t>2026/02/09</t>
         </is>
       </c>
-      <c r="BI26" t="inlineStr">
+      <c r="BJ26" t="inlineStr">
         <is>
           <t>35140491.56066536</t>
         </is>
       </c>
-      <c r="BJ26" t="inlineStr">
+      <c r="BK26" t="inlineStr">
         <is>
           <t>23562195.0</t>
         </is>
       </c>
-      <c r="BK26" t="n">
+      <c r="BL26" t="n">
         <v>22744223.8</v>
       </c>
-      <c r="BL26" t="inlineStr">
+      <c r="BM26" t="inlineStr">
         <is>
           <t>27263981.0</t>
         </is>
       </c>
-      <c r="BM26" t="n">
+      <c r="BN26" t="n">
         <v>16975055.4</v>
       </c>
-      <c r="BN26" t="inlineStr">
+      <c r="BO26" t="inlineStr">
         <is>
           <t>-4519757</t>
         </is>
       </c>
-      <c r="BO26" t="inlineStr">
+      <c r="BP26" t="inlineStr">
         <is>
           <t>1387052.244964412</t>
         </is>
       </c>
-      <c r="BP26" t="inlineStr">
+      <c r="BQ26" t="inlineStr">
         <is>
           <t>550909.8494979739</t>
         </is>
       </c>
-      <c r="BQ26" t="inlineStr">
+      <c r="BR26" t="inlineStr">
         <is>
           <t>23562195.0</t>
         </is>
       </c>
-      <c r="BR26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BS26" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT26" t="inlineStr">
+        <is>
           <t>33.95</t>
         </is>
       </c>
-      <c r="BT26" t="inlineStr">
+      <c r="BU26" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BU26" t="inlineStr">
+      <c r="BV26" t="inlineStr">
         <is>
           <t>-13.99</t>
         </is>
       </c>
-      <c r="BV26" t="inlineStr">
+      <c r="BW26" t="inlineStr">
         <is>
           <t>佳格</t>
         </is>
       </c>
-      <c r="BW26" t="inlineStr">
+      <c r="BX26" t="inlineStr">
         <is>
           <t>佳格</t>
         </is>
       </c>
-      <c r="BX26" t="inlineStr">
+      <c r="BY26" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY26" t="inlineStr">
+      <c r="BZ26" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BZ26" t="inlineStr">
+      <c r="CA26" t="inlineStr">
         <is>
           <t>0.41</t>
         </is>
       </c>
-      <c r="CA26" t="inlineStr">
+      <c r="CB26" t="inlineStr">
         <is>
           <t>6.237608785148733</t>
         </is>
       </c>
-      <c r="CB26" t="inlineStr">
+      <c r="CC26" t="inlineStr">
         <is>
           <t>-17.09267911306208</t>
         </is>
       </c>
-      <c r="CC26" t="inlineStr">
+      <c r="CD26" t="inlineStr">
         <is>
           <t>-3.78772922691385</t>
         </is>
       </c>
-      <c r="CD26" t="inlineStr">
+      <c r="CE26" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CE26" t="inlineStr">
+      <c r="CF26" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CF26" t="inlineStr">
+      <c r="CG26" t="inlineStr">
         <is>
           <t>1.49</t>
         </is>
       </c>
-      <c r="CG26" t="inlineStr">
+      <c r="CH26" t="inlineStr">
         <is>
           <t>4.84</t>
         </is>
       </c>
-      <c r="CH26" t="inlineStr">
+      <c r="CI26" t="inlineStr">
         <is>
           <t>8.02</t>
         </is>
       </c>
-      <c r="CI26" t="inlineStr">
+      <c r="CJ26" t="inlineStr">
         <is>
           <t>19.79</t>
         </is>
       </c>
-      <c r="CJ26" t="inlineStr">
+      <c r="CK26" t="inlineStr">
         <is>
           <t>23.06%</t>
         </is>
       </c>
-      <c r="CK26" t="inlineStr">
+      <c r="CL26" t="inlineStr">
         <is>
           <t>4.46%</t>
         </is>
       </c>
-      <c r="CL26" t="inlineStr">
+      <c r="CM26" t="inlineStr">
         <is>
           <t>25.48</t>
         </is>
       </c>
-      <c r="CM26" t="inlineStr">
+      <c r="CN26" t="inlineStr">
         <is>
           <t>26446</t>
         </is>
       </c>
-      <c r="CN26" t="inlineStr">
+      <c r="CO26" t="inlineStr">
         <is>
           <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
         </is>
       </c>
-      <c r="CO26" t="inlineStr">
+      <c r="CP26" t="inlineStr">
         <is>
           <t>佳格-食品工業-上市</t>
         </is>
       </c>
-      <c r="CP26" t="inlineStr">
+      <c r="CQ26" t="inlineStr">
         <is>
           <t>食品工業右下上市</t>
         </is>
       </c>
-      <c r="CQ26" t="inlineStr">
+      <c r="CR26" t="inlineStr">
         <is>
           <t>29.4</t>
         </is>
       </c>
-      <c r="CR26" t="inlineStr">
+      <c r="CS26" t="inlineStr">
         <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="CS26" t="inlineStr">
+      <c r="CT26" t="inlineStr">
         <is>
           <t>29.2</t>
         </is>
       </c>
-      <c r="CT26" t="inlineStr">
+      <c r="CU26" t="inlineStr">
         <is>
           <t>29.2</t>
         </is>
       </c>
-      <c r="CU26" t="inlineStr">
+      <c r="CV26" t="inlineStr">
         <is>
           <t>19.66</t>
         </is>
       </c>
-      <c r="CV26" t="inlineStr">
+      <c r="CW26" t="inlineStr">
         <is>
           <t>** 食品 - 營養食品</t>
         </is>
       </c>
-      <c r="CW26" t="inlineStr">
+      <c r="CX26" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX26" t="inlineStr">
+      <c r="CY26" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CY26" t="inlineStr">
+      <c r="CZ26" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -13618,250 +13748,255 @@
           <t>29.31</t>
         </is>
       </c>
-      <c r="AZ27" t="n">
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>29.355</t>
+        </is>
+      </c>
+      <c r="BA27" t="n">
         <v>29.58</v>
       </c>
-      <c r="BA27" t="n">
+      <c r="BB27" t="n">
         <v>30.22</v>
       </c>
-      <c r="BB27" t="inlineStr">
+      <c r="BC27" t="inlineStr">
         <is>
           <t>30.67</t>
         </is>
       </c>
-      <c r="BC27" t="inlineStr">
+      <c r="BD27" t="inlineStr">
         <is>
           <t>8.86</t>
         </is>
       </c>
-      <c r="BD27" t="n">
+      <c r="BE27" t="n">
         <v>-0.29</v>
       </c>
-      <c r="BE27" t="n">
+      <c r="BF27" t="n">
         <v>-0.31</v>
       </c>
-      <c r="BF27" t="inlineStr">
+      <c r="BG27" t="inlineStr">
         <is>
           <t>0.89</t>
         </is>
       </c>
-      <c r="BG27" t="inlineStr">
+      <c r="BH27" t="inlineStr">
         <is>
           <t>-135.33</t>
         </is>
       </c>
-      <c r="BH27" t="inlineStr">
+      <c r="BI27" t="inlineStr">
         <is>
           <t>2026/02/09</t>
         </is>
       </c>
-      <c r="BI27" t="inlineStr">
+      <c r="BJ27" t="inlineStr">
         <is>
           <t>35140491.56066536</t>
         </is>
       </c>
-      <c r="BJ27" t="inlineStr">
+      <c r="BK27" t="inlineStr">
         <is>
           <t>22088096.0</t>
         </is>
       </c>
-      <c r="BK27" t="n">
+      <c r="BL27" t="n">
         <v>22675815.4</v>
       </c>
-      <c r="BL27" t="inlineStr">
+      <c r="BM27" t="inlineStr">
         <is>
           <t>26693420.2</t>
         </is>
       </c>
-      <c r="BM27" t="n">
+      <c r="BN27" t="n">
         <v>16884946.42</v>
       </c>
-      <c r="BN27" t="inlineStr">
+      <c r="BO27" t="inlineStr">
         <is>
           <t>-4017604</t>
         </is>
       </c>
-      <c r="BO27" t="inlineStr">
+      <c r="BP27" t="inlineStr">
         <is>
           <t>1539078.135049219</t>
         </is>
       </c>
-      <c r="BP27" t="inlineStr">
+      <c r="BQ27" t="inlineStr">
         <is>
           <t>785214.264425572</t>
         </is>
       </c>
-      <c r="BQ27" t="inlineStr">
+      <c r="BR27" t="inlineStr">
         <is>
           <t>22088096.0</t>
         </is>
       </c>
-      <c r="BR27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BS27" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT27" t="inlineStr">
+        <is>
           <t>33.95</t>
         </is>
       </c>
-      <c r="BT27" t="inlineStr">
+      <c r="BU27" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BU27" t="inlineStr">
+      <c r="BV27" t="inlineStr">
         <is>
           <t>-13.11</t>
         </is>
       </c>
-      <c r="BV27" t="inlineStr">
+      <c r="BW27" t="inlineStr">
         <is>
           <t>佳格</t>
         </is>
       </c>
-      <c r="BW27" t="inlineStr">
+      <c r="BX27" t="inlineStr">
         <is>
           <t>佳格</t>
         </is>
       </c>
-      <c r="BX27" t="inlineStr">
+      <c r="BY27" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY27" t="inlineStr">
+      <c r="BZ27" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BZ27" t="inlineStr">
+      <c r="CA27" t="inlineStr">
         <is>
           <t>0.41</t>
         </is>
       </c>
-      <c r="CA27" t="inlineStr">
+      <c r="CB27" t="inlineStr">
         <is>
           <t>6.237608785148733</t>
         </is>
       </c>
-      <c r="CB27" t="inlineStr">
+      <c r="CC27" t="inlineStr">
         <is>
           <t>-17.09267911306208</t>
         </is>
       </c>
-      <c r="CC27" t="inlineStr">
+      <c r="CD27" t="inlineStr">
         <is>
           <t>-3.78772922691385</t>
         </is>
       </c>
-      <c r="CD27" t="inlineStr">
+      <c r="CE27" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CE27" t="inlineStr">
+      <c r="CF27" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CF27" t="inlineStr">
+      <c r="CG27" t="inlineStr">
         <is>
           <t>1.50</t>
         </is>
       </c>
-      <c r="CG27" t="inlineStr">
+      <c r="CH27" t="inlineStr">
         <is>
           <t>4.84</t>
         </is>
       </c>
-      <c r="CH27" t="inlineStr">
+      <c r="CI27" t="inlineStr">
         <is>
           <t>8.02</t>
         </is>
       </c>
-      <c r="CI27" t="inlineStr">
+      <c r="CJ27" t="inlineStr">
         <is>
           <t>19.79</t>
         </is>
       </c>
-      <c r="CJ27" t="inlineStr">
+      <c r="CK27" t="inlineStr">
         <is>
           <t>23.06%</t>
         </is>
       </c>
-      <c r="CK27" t="inlineStr">
+      <c r="CL27" t="inlineStr">
         <is>
           <t>4.46%</t>
         </is>
       </c>
-      <c r="CL27" t="inlineStr">
+      <c r="CM27" t="inlineStr">
         <is>
           <t>25.48</t>
         </is>
       </c>
-      <c r="CM27" t="inlineStr">
+      <c r="CN27" t="inlineStr">
         <is>
           <t>26446</t>
         </is>
       </c>
-      <c r="CN27" t="inlineStr">
+      <c r="CO27" t="inlineStr">
         <is>
           <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
         </is>
       </c>
-      <c r="CO27" t="inlineStr">
+      <c r="CP27" t="inlineStr">
         <is>
           <t>佳格-食品工業-上市</t>
         </is>
       </c>
-      <c r="CP27" t="inlineStr">
+      <c r="CQ27" t="inlineStr">
         <is>
           <t>食品工業右下上市</t>
         </is>
       </c>
-      <c r="CQ27" t="inlineStr">
+      <c r="CR27" t="inlineStr">
         <is>
           <t>29.6</t>
         </is>
       </c>
-      <c r="CR27" t="inlineStr">
+      <c r="CS27" t="inlineStr">
         <is>
           <t>29.65</t>
         </is>
       </c>
-      <c r="CS27" t="inlineStr">
+      <c r="CT27" t="inlineStr">
         <is>
           <t>29.3</t>
         </is>
       </c>
-      <c r="CT27" t="inlineStr">
+      <c r="CU27" t="inlineStr">
         <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="CU27" t="inlineStr">
+      <c r="CV27" t="inlineStr">
         <is>
           <t>19.66</t>
         </is>
       </c>
-      <c r="CV27" t="inlineStr">
+      <c r="CW27" t="inlineStr">
         <is>
           <t>** 食品 - 營養食品</t>
         </is>
       </c>
-      <c r="CW27" t="inlineStr">
+      <c r="CX27" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX27" t="inlineStr">
+      <c r="CY27" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CY27" t="inlineStr">
+      <c r="CZ27" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -14115,250 +14250,255 @@
           <t>29.24</t>
         </is>
       </c>
-      <c r="AZ28" t="n">
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>29.37</t>
+        </is>
+      </c>
+      <c r="BA28" t="n">
         <v>29.62</v>
       </c>
-      <c r="BA28" t="n">
+      <c r="BB28" t="n">
         <v>30.24</v>
       </c>
-      <c r="BB28" t="inlineStr">
+      <c r="BC28" t="inlineStr">
         <is>
           <t>30.68</t>
         </is>
       </c>
-      <c r="BC28" t="inlineStr">
+      <c r="BD28" t="inlineStr">
         <is>
           <t>2.12</t>
         </is>
       </c>
-      <c r="BD28" t="n">
+      <c r="BE28" t="n">
         <v>-0.31</v>
       </c>
-      <c r="BE28" t="n">
+      <c r="BF28" t="n">
         <v>-0.32</v>
       </c>
-      <c r="BF28" t="inlineStr">
+      <c r="BG28" t="inlineStr">
         <is>
           <t>0.89</t>
         </is>
       </c>
-      <c r="BG28" t="inlineStr">
+      <c r="BH28" t="inlineStr">
         <is>
           <t>-136.11</t>
         </is>
       </c>
-      <c r="BH28" t="inlineStr">
+      <c r="BI28" t="inlineStr">
         <is>
           <t>2026/02/09</t>
         </is>
       </c>
-      <c r="BI28" t="inlineStr">
+      <c r="BJ28" t="inlineStr">
         <is>
           <t>35140491.56066536</t>
         </is>
       </c>
-      <c r="BJ28" t="inlineStr">
+      <c r="BK28" t="inlineStr">
         <is>
           <t>36951577.0</t>
         </is>
       </c>
-      <c r="BK28" t="n">
+      <c r="BL28" t="n">
         <v>25211363.2</v>
       </c>
-      <c r="BL28" t="inlineStr">
+      <c r="BM28" t="inlineStr">
         <is>
           <t>26502871.8</t>
         </is>
       </c>
-      <c r="BM28" t="n">
+      <c r="BN28" t="n">
         <v>16852284.6</v>
       </c>
-      <c r="BN28" t="inlineStr">
+      <c r="BO28" t="inlineStr">
         <is>
           <t>-1291508</t>
         </is>
       </c>
-      <c r="BO28" t="inlineStr">
+      <c r="BP28" t="inlineStr">
         <is>
           <t>1676144.293344427</t>
         </is>
       </c>
-      <c r="BP28" t="inlineStr">
+      <c r="BQ28" t="inlineStr">
         <is>
           <t>1249830.669164084</t>
         </is>
       </c>
-      <c r="BQ28" t="inlineStr">
+      <c r="BR28" t="inlineStr">
         <is>
           <t>36951577.0</t>
         </is>
       </c>
-      <c r="BR28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BS28" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT28" t="inlineStr">
+        <is>
           <t>33.95</t>
         </is>
       </c>
-      <c r="BT28" t="inlineStr">
+      <c r="BU28" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BU28" t="inlineStr">
+      <c r="BV28" t="inlineStr">
         <is>
           <t>-13.11</t>
         </is>
       </c>
-      <c r="BV28" t="inlineStr">
+      <c r="BW28" t="inlineStr">
         <is>
           <t>佳格</t>
         </is>
       </c>
-      <c r="BW28" t="inlineStr">
+      <c r="BX28" t="inlineStr">
         <is>
           <t>佳格</t>
         </is>
       </c>
-      <c r="BX28" t="inlineStr">
+      <c r="BY28" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY28" t="inlineStr">
+      <c r="BZ28" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BZ28" t="inlineStr">
+      <c r="CA28" t="inlineStr">
         <is>
           <t>0.41</t>
         </is>
       </c>
-      <c r="CA28" t="inlineStr">
+      <c r="CB28" t="inlineStr">
         <is>
           <t>6.237608785148733</t>
         </is>
       </c>
-      <c r="CB28" t="inlineStr">
+      <c r="CC28" t="inlineStr">
         <is>
           <t>-17.09267911306208</t>
         </is>
       </c>
-      <c r="CC28" t="inlineStr">
+      <c r="CD28" t="inlineStr">
         <is>
           <t>-3.78772922691385</t>
         </is>
       </c>
-      <c r="CD28" t="inlineStr">
+      <c r="CE28" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CE28" t="inlineStr">
+      <c r="CF28" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CF28" t="inlineStr">
+      <c r="CG28" t="inlineStr">
         <is>
           <t>1.50</t>
         </is>
       </c>
-      <c r="CG28" t="inlineStr">
+      <c r="CH28" t="inlineStr">
         <is>
           <t>4.84</t>
         </is>
       </c>
-      <c r="CH28" t="inlineStr">
+      <c r="CI28" t="inlineStr">
         <is>
           <t>8.02</t>
         </is>
       </c>
-      <c r="CI28" t="inlineStr">
+      <c r="CJ28" t="inlineStr">
         <is>
           <t>19.79</t>
         </is>
       </c>
-      <c r="CJ28" t="inlineStr">
+      <c r="CK28" t="inlineStr">
         <is>
           <t>23.06%</t>
         </is>
       </c>
-      <c r="CK28" t="inlineStr">
+      <c r="CL28" t="inlineStr">
         <is>
           <t>4.46%</t>
         </is>
       </c>
-      <c r="CL28" t="inlineStr">
+      <c r="CM28" t="inlineStr">
         <is>
           <t>25.48</t>
         </is>
       </c>
-      <c r="CM28" t="inlineStr">
+      <c r="CN28" t="inlineStr">
         <is>
           <t>26446</t>
         </is>
       </c>
-      <c r="CN28" t="inlineStr">
+      <c r="CO28" t="inlineStr">
         <is>
           <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
         </is>
       </c>
-      <c r="CO28" t="inlineStr">
+      <c r="CP28" t="inlineStr">
         <is>
           <t>佳格-食品工業-上市</t>
         </is>
       </c>
-      <c r="CP28" t="inlineStr">
+      <c r="CQ28" t="inlineStr">
         <is>
           <t>食品工業右下上市</t>
         </is>
       </c>
-      <c r="CQ28" t="inlineStr">
+      <c r="CR28" t="inlineStr">
         <is>
           <t>29.3</t>
         </is>
       </c>
-      <c r="CR28" t="inlineStr">
+      <c r="CS28" t="inlineStr">
         <is>
           <t>29.75</t>
         </is>
       </c>
-      <c r="CS28" t="inlineStr">
+      <c r="CT28" t="inlineStr">
         <is>
           <t>29.3</t>
         </is>
       </c>
-      <c r="CT28" t="inlineStr">
+      <c r="CU28" t="inlineStr">
         <is>
           <t>29.5</t>
         </is>
       </c>
-      <c r="CU28" t="inlineStr">
+      <c r="CV28" t="inlineStr">
         <is>
           <t>19.66</t>
         </is>
       </c>
-      <c r="CV28" t="inlineStr">
+      <c r="CW28" t="inlineStr">
         <is>
           <t>** 食品 - 營養食品</t>
         </is>
       </c>
-      <c r="CW28" t="inlineStr">
+      <c r="CX28" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX28" t="inlineStr">
+      <c r="CY28" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CY28" t="inlineStr">
+      <c r="CZ28" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -14612,250 +14752,255 @@
           <t>29.2</t>
         </is>
       </c>
-      <c r="AZ29" t="n">
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>29.37</t>
+        </is>
+      </c>
+      <c r="BA29" t="n">
         <v>29.68</v>
       </c>
-      <c r="BA29" t="n">
+      <c r="BB29" t="n">
         <v>30.27</v>
       </c>
-      <c r="BB29" t="inlineStr">
+      <c r="BC29" t="inlineStr">
         <is>
           <t>30.69</t>
         </is>
       </c>
-      <c r="BC29" t="inlineStr">
+      <c r="BD29" t="inlineStr">
         <is>
           <t>-7.01</t>
         </is>
       </c>
-      <c r="BD29" t="n">
+      <c r="BE29" t="n">
         <v>-0.35</v>
       </c>
-      <c r="BE29" t="n">
+      <c r="BF29" t="n">
         <v>-0.32</v>
       </c>
-      <c r="BF29" t="inlineStr">
+      <c r="BG29" t="inlineStr">
         <is>
           <t>0.89</t>
         </is>
       </c>
-      <c r="BG29" t="inlineStr">
+      <c r="BH29" t="inlineStr">
         <is>
           <t>-136.30</t>
         </is>
       </c>
-      <c r="BH29" t="inlineStr">
+      <c r="BI29" t="inlineStr">
         <is>
           <t>2026/02/09</t>
         </is>
       </c>
-      <c r="BI29" t="inlineStr">
+      <c r="BJ29" t="inlineStr">
         <is>
           <t>35140491.56066536</t>
         </is>
       </c>
-      <c r="BJ29" t="inlineStr">
+      <c r="BK29" t="inlineStr">
         <is>
           <t>16274454.0</t>
         </is>
       </c>
-      <c r="BK29" t="n">
+      <c r="BL29" t="n">
         <v>25719627.8</v>
       </c>
-      <c r="BL29" t="inlineStr">
+      <c r="BM29" t="inlineStr">
         <is>
           <t>25467490.4</t>
         </is>
       </c>
-      <c r="BM29" t="n">
+      <c r="BN29" t="n">
         <v>16380710.06</v>
       </c>
-      <c r="BN29" t="inlineStr">
+      <c r="BO29" t="inlineStr">
         <is>
           <t>252137</t>
         </is>
       </c>
-      <c r="BO29" t="inlineStr">
+      <c r="BP29" t="inlineStr">
         <is>
           <t>1753655.861377217</t>
         </is>
       </c>
-      <c r="BP29" t="inlineStr">
+      <c r="BQ29" t="inlineStr">
         <is>
           <t>276415.7591775246</t>
         </is>
       </c>
-      <c r="BQ29" t="inlineStr">
+      <c r="BR29" t="inlineStr">
         <is>
           <t>16274454.0</t>
         </is>
       </c>
-      <c r="BR29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BS29" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BT29" t="inlineStr">
+        <is>
           <t>33.95</t>
         </is>
       </c>
-      <c r="BT29" t="inlineStr">
+      <c r="BU29" t="inlineStr">
         <is>
           <t>2025/10/15</t>
         </is>
       </c>
-      <c r="BU29" t="inlineStr">
+      <c r="BV29" t="inlineStr">
         <is>
           <t>-13.84</t>
         </is>
       </c>
-      <c r="BV29" t="inlineStr">
+      <c r="BW29" t="inlineStr">
         <is>
           <t>佳格</t>
         </is>
       </c>
-      <c r="BW29" t="inlineStr">
+      <c r="BX29" t="inlineStr">
         <is>
           <t>佳格</t>
         </is>
       </c>
-      <c r="BX29" t="inlineStr">
+      <c r="BY29" t="inlineStr">
         <is>
           <t>食品工業</t>
         </is>
       </c>
-      <c r="BY29" t="inlineStr">
+      <c r="BZ29" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BZ29" t="inlineStr">
+      <c r="CA29" t="inlineStr">
         <is>
           <t>0.41</t>
         </is>
       </c>
-      <c r="CA29" t="inlineStr">
+      <c r="CB29" t="inlineStr">
         <is>
           <t>6.237608785148733</t>
         </is>
       </c>
-      <c r="CB29" t="inlineStr">
+      <c r="CC29" t="inlineStr">
         <is>
           <t>-17.09267911306208</t>
         </is>
       </c>
-      <c r="CC29" t="inlineStr">
+      <c r="CD29" t="inlineStr">
         <is>
           <t>-3.78772922691385</t>
         </is>
       </c>
-      <c r="CD29" t="inlineStr">
+      <c r="CE29" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="CE29" t="inlineStr">
+      <c r="CF29" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CF29" t="inlineStr">
+      <c r="CG29" t="inlineStr">
         <is>
           <t>1.49</t>
         </is>
       </c>
-      <c r="CG29" t="inlineStr">
+      <c r="CH29" t="inlineStr">
         <is>
           <t>4.84</t>
         </is>
       </c>
-      <c r="CH29" t="inlineStr">
+      <c r="CI29" t="inlineStr">
         <is>
           <t>8.02</t>
         </is>
       </c>
-      <c r="CI29" t="inlineStr">
+      <c r="CJ29" t="inlineStr">
         <is>
           <t>19.79</t>
         </is>
       </c>
-      <c r="CJ29" t="inlineStr">
+      <c r="CK29" t="inlineStr">
         <is>
           <t>23.06%</t>
         </is>
       </c>
-      <c r="CK29" t="inlineStr">
+      <c r="CL29" t="inlineStr">
         <is>
           <t>4.46%</t>
         </is>
       </c>
-      <c r="CL29" t="inlineStr">
+      <c r="CM29" t="inlineStr">
         <is>
           <t>25.48</t>
         </is>
       </c>
-      <c r="CM29" t="inlineStr">
+      <c r="CN29" t="inlineStr">
         <is>
           <t>26446</t>
         </is>
       </c>
-      <c r="CN29" t="inlineStr">
+      <c r="CO29" t="inlineStr">
         <is>
           <t>廚房料理食品54.00%、營養食品36.00%、其他類10.00% (2024年)</t>
         </is>
       </c>
-      <c r="CO29" t="inlineStr">
+      <c r="CP29" t="inlineStr">
         <is>
           <t>佳格-食品工業-上市</t>
         </is>
       </c>
-      <c r="CP29" t="inlineStr">
+      <c r="CQ29" t="inlineStr">
         <is>
           <t>食品工業右下上市</t>
         </is>
       </c>
-      <c r="CQ29" t="inlineStr">
+      <c r="CR29" t="inlineStr">
         <is>
           <t>29.3</t>
         </is>
       </c>
-      <c r="CR29" t="inlineStr">
+      <c r="CS29" t="inlineStr">
         <is>
           <t>29.35</t>
         </is>
       </c>
-      <c r="CS29" t="inlineStr">
+      <c r="CT29" t="inlineStr">
         <is>
           <t>29.1</t>
         </is>
       </c>
-      <c r="CT29" t="inlineStr">
+      <c r="CU29" t="inlineStr">
         <is>
           <t>29.25</t>
         </is>
       </c>
-      <c r="CU29" t="inlineStr">
+      <c r="CV29" t="inlineStr">
         <is>
           <t>19.66</t>
         </is>
       </c>
-      <c r="CV29" t="inlineStr">
+      <c r="CW29" t="inlineStr">
         <is>
           <t>** 食品 - 營養食品</t>
         </is>
       </c>
-      <c r="CW29" t="inlineStr">
+      <c r="CX29" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="CX29" t="inlineStr">
+      <c r="CY29" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CY29" t="inlineStr">
+      <c r="CZ29" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
